--- a/ライフプラン_猪飼.xlsx
+++ b/ライフプラン_猪飼.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC_USER\Documents\LocalLifeplanRepo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16D80DBF-71B6-44B5-95AE-A14045D76F84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69ED5398-DEAC-40DB-A7A6-FDDD395D3F6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{934FA03D-99BD-49E0-BFEC-291BD79F4879}"/>
   </bookViews>
@@ -72,7 +72,7 @@
           <t>マンション片付け
 キッチン（食洗器＋ガス台＋レンジ＋網戸）取替
 トイレ修理
-内壁除去</t>
+リビング内壁除去　＋　書斎クローゼット除去</t>
         </r>
       </text>
     </comment>
@@ -737,7 +737,53 @@
         </r>
       </text>
     </comment>
+    <comment ref="G113" authorId="0" shapeId="0" xr:uid="{3867A11D-F368-47C4-B52D-35EE01EC474A}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="MS P ゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>kaz
+ 国民厚生年金　　+45
+ パナ年金　　　  +12
+ 全労済個人年金  + 2　
+ ﾌﾟﾙﾃﾞﾝｼｬﾙ保険金 + 9
+nao</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="F126" authorId="0" shapeId="0" xr:uid="{9D0EDA07-5D89-456F-A52C-3AAD29C57E72}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="MS P ゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>PC_USER:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="MS P ゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E131" authorId="0" shapeId="0" xr:uid="{D3A0D358-7411-4045-8E31-BB4827CBD402}">
       <text>
         <r>
           <rPr>
@@ -809,18 +855,8 @@
             <family val="3"/>
             <charset val="128"/>
           </rPr>
-          <t>PC_USER:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="MS P ゴシック"/>
-            <family val="3"/>
-            <charset val="128"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
+          <t>kazへ返済 -12 (ｶｲﾛ：6、CPAP：1、中山会：１。ﾋﾞｭｰ：1。医療費他)
+naoへ返済 -3（網代0.5、出雲＆瀬戸0.4、牛乳交通費食品等2）</t>
         </r>
       </text>
     </comment>
@@ -3709,6 +3745,109 @@
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" textRotation="255"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="42" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="23" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="24" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="46" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" textRotation="255"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" textRotation="255"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -3718,10 +3857,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" textRotation="255"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" textRotation="255"/>
@@ -3775,105 +3910,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" textRotation="255"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="42" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="23" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" textRotation="255"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="24" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="46" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -5571,7 +5607,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="31"/>
                 <c:pt idx="0">
-                  <c:v>#N/A</c:v>
+                  <c:v>1080</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>#N/A</c:v>
@@ -9023,7 +9059,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="31"/>
                 <c:pt idx="0">
-                  <c:v>#N/A</c:v>
+                  <c:v>733</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>#N/A</c:v>
@@ -12474,7 +12510,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="31"/>
                 <c:pt idx="0">
-                  <c:v>#N/A</c:v>
+                  <c:v>1813</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>#N/A</c:v>
@@ -16410,12 +16446,12 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="99" t="s">
+      <c r="B1" s="128" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="100"/>
-      <c r="D1" s="100"/>
-      <c r="E1" s="101"/>
+      <c r="C1" s="129"/>
+      <c r="D1" s="129"/>
+      <c r="E1" s="130"/>
       <c r="F1" s="2" t="s">
         <v>2</v>
       </c>
@@ -16516,13 +16552,13 @@
       <c r="AM1" s="4"/>
     </row>
     <row r="2" spans="1:39" ht="18.75" customHeight="1">
-      <c r="A2" s="102" t="s">
+      <c r="A2" s="99" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="105" t="s">
+      <c r="B2" s="133" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="112"/>
+      <c r="C2" s="140"/>
       <c r="D2" s="6" t="s">
         <v>5</v>
       </c>
@@ -16607,9 +16643,9 @@
       <c r="AM2" s="4"/>
     </row>
     <row r="3" spans="1:39" ht="19.5" thickBot="1">
-      <c r="A3" s="103"/>
-      <c r="B3" s="106"/>
-      <c r="C3" s="113"/>
+      <c r="A3" s="131"/>
+      <c r="B3" s="134"/>
+      <c r="C3" s="141"/>
       <c r="D3" s="9" t="s">
         <v>7</v>
       </c>
@@ -16710,11 +16746,11 @@
       <c r="AM3" s="4"/>
     </row>
     <row r="4" spans="1:39">
-      <c r="A4" s="103"/>
-      <c r="B4" s="105" t="s">
+      <c r="A4" s="131"/>
+      <c r="B4" s="133" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="114"/>
+      <c r="C4" s="142"/>
       <c r="D4" s="12" t="s">
         <v>10</v>
       </c>
@@ -16759,9 +16795,9 @@
       <c r="AM4" s="4"/>
     </row>
     <row r="5" spans="1:39">
-      <c r="A5" s="103"/>
-      <c r="B5" s="107"/>
-      <c r="C5" s="115"/>
+      <c r="A5" s="131"/>
+      <c r="B5" s="135"/>
+      <c r="C5" s="143"/>
       <c r="D5" s="15" t="s">
         <v>12</v>
       </c>
@@ -16806,9 +16842,9 @@
       <c r="AM5" s="4"/>
     </row>
     <row r="6" spans="1:39">
-      <c r="A6" s="103"/>
-      <c r="B6" s="107"/>
-      <c r="C6" s="115"/>
+      <c r="A6" s="131"/>
+      <c r="B6" s="135"/>
+      <c r="C6" s="143"/>
       <c r="D6" s="15"/>
       <c r="E6" s="16"/>
       <c r="F6" s="17"/>
@@ -16847,9 +16883,9 @@
       <c r="AM6" s="4"/>
     </row>
     <row r="7" spans="1:39">
-      <c r="A7" s="103"/>
-      <c r="B7" s="107"/>
-      <c r="C7" s="115"/>
+      <c r="A7" s="131"/>
+      <c r="B7" s="135"/>
+      <c r="C7" s="143"/>
       <c r="D7" s="15"/>
       <c r="E7" s="16"/>
       <c r="F7" s="17"/>
@@ -16888,9 +16924,9 @@
       <c r="AM7" s="4"/>
     </row>
     <row r="8" spans="1:39">
-      <c r="A8" s="103"/>
-      <c r="B8" s="108"/>
-      <c r="C8" s="116"/>
+      <c r="A8" s="131"/>
+      <c r="B8" s="136"/>
+      <c r="C8" s="144"/>
       <c r="D8" s="15"/>
       <c r="E8" s="16"/>
       <c r="F8" s="17"/>
@@ -16929,12 +16965,12 @@
       <c r="AM8" s="4"/>
     </row>
     <row r="9" spans="1:39" ht="19.5" thickBot="1">
-      <c r="A9" s="103"/>
-      <c r="B9" s="109" t="s">
+      <c r="A9" s="131"/>
+      <c r="B9" s="137" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="110"/>
-      <c r="D9" s="111"/>
+      <c r="C9" s="138"/>
+      <c r="D9" s="139"/>
       <c r="E9" s="18" t="s">
         <v>15</v>
       </c>
@@ -17070,11 +17106,11 @@
       <c r="AM9" s="4"/>
     </row>
     <row r="10" spans="1:39">
-      <c r="A10" s="103"/>
-      <c r="B10" s="105" t="s">
+      <c r="A10" s="131"/>
+      <c r="B10" s="133" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="114"/>
+      <c r="C10" s="142"/>
       <c r="D10" s="15" t="s">
         <v>17</v>
       </c>
@@ -17173,9 +17209,9 @@
       <c r="AM10" s="4"/>
     </row>
     <row r="11" spans="1:39">
-      <c r="A11" s="103"/>
-      <c r="B11" s="107"/>
-      <c r="C11" s="115"/>
+      <c r="A11" s="131"/>
+      <c r="B11" s="135"/>
+      <c r="C11" s="143"/>
       <c r="D11" s="15" t="s">
         <v>19</v>
       </c>
@@ -17225,9 +17261,9 @@
       <c r="AM11" s="4"/>
     </row>
     <row r="12" spans="1:39">
-      <c r="A12" s="103"/>
-      <c r="B12" s="107"/>
-      <c r="C12" s="115"/>
+      <c r="A12" s="131"/>
+      <c r="B12" s="135"/>
+      <c r="C12" s="143"/>
       <c r="D12" s="15" t="s">
         <v>21</v>
       </c>
@@ -17299,9 +17335,9 @@
       <c r="AM12" s="4"/>
     </row>
     <row r="13" spans="1:39">
-      <c r="A13" s="103"/>
-      <c r="B13" s="107"/>
-      <c r="C13" s="115"/>
+      <c r="A13" s="131"/>
+      <c r="B13" s="135"/>
+      <c r="C13" s="143"/>
       <c r="D13" s="15" t="s">
         <v>22</v>
       </c>
@@ -17350,9 +17386,9 @@
       <c r="AM13" s="4"/>
     </row>
     <row r="14" spans="1:39">
-      <c r="A14" s="103"/>
-      <c r="B14" s="108"/>
-      <c r="C14" s="116"/>
+      <c r="A14" s="131"/>
+      <c r="B14" s="136"/>
+      <c r="C14" s="144"/>
       <c r="D14" s="15"/>
       <c r="E14" s="16"/>
       <c r="F14" s="23"/>
@@ -17391,12 +17427,12 @@
       <c r="AM14" s="4"/>
     </row>
     <row r="15" spans="1:39" ht="19.5" thickBot="1">
-      <c r="A15" s="104"/>
-      <c r="B15" s="109" t="s">
+      <c r="A15" s="132"/>
+      <c r="B15" s="137" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="110"/>
-      <c r="D15" s="111"/>
+      <c r="C15" s="138"/>
+      <c r="D15" s="139"/>
       <c r="E15" s="18" t="s">
         <v>25</v>
       </c>
@@ -17532,16 +17568,16 @@
       <c r="AM15" s="4"/>
     </row>
     <row r="16" spans="1:39">
-      <c r="A16" s="102" t="s">
+      <c r="A16" s="99" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="136" t="s">
+      <c r="B16" s="126" t="s">
         <v>132</v>
       </c>
       <c r="C16" s="118" t="s">
         <v>108</v>
       </c>
-      <c r="D16" s="120" t="s">
+      <c r="D16" s="119" t="s">
         <v>112</v>
       </c>
       <c r="E16" s="16" t="s">
@@ -17623,10 +17659,10 @@
       <c r="AM16" s="4"/>
     </row>
     <row r="17" spans="1:39">
-      <c r="A17" s="138"/>
-      <c r="B17" s="134"/>
-      <c r="C17" s="119"/>
-      <c r="D17" s="119"/>
+      <c r="A17" s="100"/>
+      <c r="B17" s="124"/>
+      <c r="C17" s="107"/>
+      <c r="D17" s="107"/>
       <c r="E17" s="16" t="s">
         <v>30</v>
       </c>
@@ -17712,12 +17748,12 @@
       <c r="AM17" s="4"/>
     </row>
     <row r="18" spans="1:39">
-      <c r="A18" s="138"/>
-      <c r="B18" s="134"/>
-      <c r="C18" s="121" t="s">
+      <c r="A18" s="100"/>
+      <c r="B18" s="124"/>
+      <c r="C18" s="110" t="s">
         <v>109</v>
       </c>
-      <c r="D18" s="123" t="s">
+      <c r="D18" s="111" t="s">
         <v>114</v>
       </c>
       <c r="E18" s="13" t="s">
@@ -17799,10 +17835,10 @@
       <c r="AM18" s="27"/>
     </row>
     <row r="19" spans="1:39">
-      <c r="A19" s="138"/>
-      <c r="B19" s="134"/>
-      <c r="C19" s="122"/>
-      <c r="D19" s="122"/>
+      <c r="A19" s="100"/>
+      <c r="B19" s="124"/>
+      <c r="C19" s="112"/>
+      <c r="D19" s="112"/>
       <c r="E19" s="16" t="s">
         <v>28</v>
       </c>
@@ -17870,10 +17906,10 @@
       <c r="AM19" s="27"/>
     </row>
     <row r="20" spans="1:39">
-      <c r="A20" s="138"/>
-      <c r="B20" s="134"/>
-      <c r="C20" s="122"/>
-      <c r="D20" s="119"/>
+      <c r="A20" s="100"/>
+      <c r="B20" s="124"/>
+      <c r="C20" s="112"/>
+      <c r="D20" s="107"/>
       <c r="E20" s="16" t="s">
         <v>29</v>
       </c>
@@ -17923,9 +17959,9 @@
       <c r="AM20" s="27"/>
     </row>
     <row r="21" spans="1:39">
-      <c r="A21" s="138"/>
-      <c r="B21" s="134"/>
-      <c r="C21" s="119"/>
+      <c r="A21" s="100"/>
+      <c r="B21" s="124"/>
+      <c r="C21" s="107"/>
       <c r="D21" s="57" t="s">
         <v>115</v>
       </c>
@@ -17976,9 +18012,9 @@
       <c r="AM21" s="27"/>
     </row>
     <row r="22" spans="1:39">
-      <c r="A22" s="138"/>
-      <c r="B22" s="134"/>
-      <c r="C22" s="121" t="s">
+      <c r="A22" s="100"/>
+      <c r="B22" s="124"/>
+      <c r="C22" s="110" t="s">
         <v>110</v>
       </c>
       <c r="D22" s="57" t="s">
@@ -18023,9 +18059,9 @@
       <c r="AM22" s="27"/>
     </row>
     <row r="23" spans="1:39">
-      <c r="A23" s="138"/>
-      <c r="B23" s="134"/>
-      <c r="C23" s="119"/>
+      <c r="A23" s="100"/>
+      <c r="B23" s="124"/>
+      <c r="C23" s="107"/>
       <c r="D23" s="57" t="s">
         <v>117</v>
       </c>
@@ -18068,12 +18104,12 @@
       <c r="AM23" s="27"/>
     </row>
     <row r="24" spans="1:39">
-      <c r="A24" s="138"/>
-      <c r="B24" s="134"/>
-      <c r="C24" s="121" t="s">
+      <c r="A24" s="100"/>
+      <c r="B24" s="124"/>
+      <c r="C24" s="110" t="s">
         <v>111</v>
       </c>
-      <c r="D24" s="123" t="s">
+      <c r="D24" s="111" t="s">
         <v>118</v>
       </c>
       <c r="E24" s="16" t="s">
@@ -18155,10 +18191,10 @@
       <c r="AM24" s="27"/>
     </row>
     <row r="25" spans="1:39">
-      <c r="A25" s="138"/>
-      <c r="B25" s="134"/>
-      <c r="C25" s="122"/>
-      <c r="D25" s="122"/>
+      <c r="A25" s="100"/>
+      <c r="B25" s="124"/>
+      <c r="C25" s="112"/>
+      <c r="D25" s="112"/>
       <c r="E25" s="16" t="s">
         <v>33</v>
       </c>
@@ -18250,10 +18286,10 @@
       <c r="AM25" s="27"/>
     </row>
     <row r="26" spans="1:39">
-      <c r="A26" s="138"/>
-      <c r="B26" s="134"/>
-      <c r="C26" s="122"/>
-      <c r="D26" s="122"/>
+      <c r="A26" s="100"/>
+      <c r="B26" s="124"/>
+      <c r="C26" s="112"/>
+      <c r="D26" s="112"/>
       <c r="E26" s="16" t="s">
         <v>34</v>
       </c>
@@ -18295,10 +18331,10 @@
       <c r="AM26" s="27"/>
     </row>
     <row r="27" spans="1:39">
-      <c r="A27" s="138"/>
-      <c r="B27" s="134"/>
-      <c r="C27" s="122"/>
-      <c r="D27" s="122"/>
+      <c r="A27" s="100"/>
+      <c r="B27" s="124"/>
+      <c r="C27" s="112"/>
+      <c r="D27" s="112"/>
       <c r="E27" s="29" t="s">
         <v>35</v>
       </c>
@@ -18340,10 +18376,10 @@
       <c r="AM27" s="27"/>
     </row>
     <row r="28" spans="1:39">
-      <c r="A28" s="138"/>
-      <c r="B28" s="134"/>
-      <c r="C28" s="122"/>
-      <c r="D28" s="122"/>
+      <c r="A28" s="100"/>
+      <c r="B28" s="124"/>
+      <c r="C28" s="112"/>
+      <c r="D28" s="112"/>
       <c r="E28" s="16" t="s">
         <v>36</v>
       </c>
@@ -18403,10 +18439,10 @@
       <c r="AM28" s="27"/>
     </row>
     <row r="29" spans="1:39">
-      <c r="A29" s="138"/>
-      <c r="B29" s="134"/>
-      <c r="C29" s="122"/>
-      <c r="D29" s="119"/>
+      <c r="A29" s="100"/>
+      <c r="B29" s="124"/>
+      <c r="C29" s="112"/>
+      <c r="D29" s="107"/>
       <c r="E29" s="86" t="s">
         <v>120</v>
       </c>
@@ -18448,9 +18484,9 @@
       <c r="AM29" s="27"/>
     </row>
     <row r="30" spans="1:39">
-      <c r="A30" s="138"/>
-      <c r="B30" s="134"/>
-      <c r="C30" s="122"/>
+      <c r="A30" s="100"/>
+      <c r="B30" s="124"/>
+      <c r="C30" s="112"/>
       <c r="D30" s="57" t="s">
         <v>122</v>
       </c>
@@ -18493,9 +18529,9 @@
       <c r="AM30" s="27"/>
     </row>
     <row r="31" spans="1:39">
-      <c r="A31" s="138"/>
-      <c r="B31" s="135"/>
-      <c r="C31" s="119"/>
+      <c r="A31" s="100"/>
+      <c r="B31" s="125"/>
+      <c r="C31" s="107"/>
       <c r="D31" s="57" t="s">
         <v>123</v>
       </c>
@@ -18538,11 +18574,11 @@
       <c r="AM31" s="27"/>
     </row>
     <row r="32" spans="1:39">
-      <c r="A32" s="138"/>
-      <c r="B32" s="143" t="s">
+      <c r="A32" s="100"/>
+      <c r="B32" s="115" t="s">
         <v>131</v>
       </c>
-      <c r="C32" s="124"/>
+      <c r="C32" s="108"/>
       <c r="D32" s="17" t="s">
         <v>128</v>
       </c>
@@ -18641,9 +18677,9 @@
       <c r="AM32" s="27"/>
     </row>
     <row r="33" spans="1:39">
-      <c r="A33" s="138"/>
-      <c r="B33" s="144"/>
-      <c r="C33" s="126"/>
+      <c r="A33" s="100"/>
+      <c r="B33" s="116"/>
+      <c r="C33" s="105"/>
       <c r="D33" s="17" t="s">
         <v>129</v>
       </c>
@@ -18718,12 +18754,12 @@
       <c r="AM33" s="27"/>
     </row>
     <row r="34" spans="1:39">
-      <c r="A34" s="138"/>
-      <c r="B34" s="127" t="s">
+      <c r="A34" s="100"/>
+      <c r="B34" s="102" t="s">
         <v>9</v>
       </c>
-      <c r="C34" s="130"/>
-      <c r="D34" s="140"/>
+      <c r="C34" s="104"/>
+      <c r="D34" s="106"/>
       <c r="E34" s="34" t="str">
         <f t="shared" ref="E34:AK34" si="2">E4</f>
         <v>新潟実家の売却益　（妙子と折半）</v>
@@ -18860,10 +18896,10 @@
       <c r="AM34" s="27"/>
     </row>
     <row r="35" spans="1:39">
-      <c r="A35" s="138"/>
-      <c r="B35" s="129"/>
-      <c r="C35" s="126"/>
-      <c r="D35" s="119"/>
+      <c r="A35" s="100"/>
+      <c r="B35" s="103"/>
+      <c r="C35" s="105"/>
+      <c r="D35" s="107"/>
       <c r="E35" s="34" t="str">
         <f t="shared" ref="E35:AK35" si="3">E5</f>
         <v>横浜マンションの売却益</v>
@@ -19000,7 +19036,7 @@
       <c r="AM35" s="27"/>
     </row>
     <row r="36" spans="1:39" ht="19.5" thickBot="1">
-      <c r="A36" s="138"/>
+      <c r="A36" s="100"/>
       <c r="B36" s="35" t="s">
         <v>38</v>
       </c>
@@ -19139,8 +19175,8 @@
       <c r="AM36" s="27"/>
     </row>
     <row r="37" spans="1:39">
-      <c r="A37" s="138"/>
-      <c r="B37" s="133" t="s">
+      <c r="A37" s="100"/>
+      <c r="B37" s="123" t="s">
         <v>133</v>
       </c>
       <c r="C37" s="8" t="s">
@@ -19190,9 +19226,9 @@
       <c r="AM37" s="4"/>
     </row>
     <row r="38" spans="1:39">
-      <c r="A38" s="138"/>
-      <c r="B38" s="134"/>
-      <c r="C38" s="121" t="s">
+      <c r="A38" s="100"/>
+      <c r="B38" s="124"/>
+      <c r="C38" s="110" t="s">
         <v>109</v>
       </c>
       <c r="D38" s="57" t="s">
@@ -19237,9 +19273,9 @@
       <c r="AM38" s="4"/>
     </row>
     <row r="39" spans="1:39">
-      <c r="A39" s="138"/>
-      <c r="B39" s="134"/>
-      <c r="C39" s="119"/>
+      <c r="A39" s="100"/>
+      <c r="B39" s="124"/>
+      <c r="C39" s="107"/>
       <c r="D39" s="57" t="s">
         <v>115</v>
       </c>
@@ -19282,9 +19318,9 @@
       <c r="AM39" s="4"/>
     </row>
     <row r="40" spans="1:39">
-      <c r="A40" s="138"/>
-      <c r="B40" s="134"/>
-      <c r="C40" s="121" t="s">
+      <c r="A40" s="100"/>
+      <c r="B40" s="124"/>
+      <c r="C40" s="110" t="s">
         <v>110</v>
       </c>
       <c r="D40" s="57" t="s">
@@ -19385,9 +19421,9 @@
       <c r="AM40" s="27"/>
     </row>
     <row r="41" spans="1:39">
-      <c r="A41" s="138"/>
-      <c r="B41" s="134"/>
-      <c r="C41" s="119"/>
+      <c r="A41" s="100"/>
+      <c r="B41" s="124"/>
+      <c r="C41" s="107"/>
       <c r="D41" s="57" t="s">
         <v>117</v>
       </c>
@@ -19430,12 +19466,12 @@
       <c r="AM41" s="4"/>
     </row>
     <row r="42" spans="1:39">
-      <c r="A42" s="138"/>
-      <c r="B42" s="134"/>
-      <c r="C42" s="121" t="s">
+      <c r="A42" s="100"/>
+      <c r="B42" s="124"/>
+      <c r="C42" s="110" t="s">
         <v>111</v>
       </c>
-      <c r="D42" s="123" t="s">
+      <c r="D42" s="111" t="s">
         <v>118</v>
       </c>
       <c r="E42" s="16" t="s">
@@ -19481,10 +19517,10 @@
       <c r="AM42" s="27"/>
     </row>
     <row r="43" spans="1:39">
-      <c r="A43" s="138"/>
-      <c r="B43" s="134"/>
-      <c r="C43" s="122"/>
-      <c r="D43" s="122"/>
+      <c r="A43" s="100"/>
+      <c r="B43" s="124"/>
+      <c r="C43" s="112"/>
+      <c r="D43" s="112"/>
       <c r="E43" s="16" t="s">
         <v>49</v>
       </c>
@@ -19564,10 +19600,10 @@
       <c r="AM43" s="27"/>
     </row>
     <row r="44" spans="1:39">
-      <c r="A44" s="138"/>
-      <c r="B44" s="134"/>
-      <c r="C44" s="122"/>
-      <c r="D44" s="122"/>
+      <c r="A44" s="100"/>
+      <c r="B44" s="124"/>
+      <c r="C44" s="112"/>
+      <c r="D44" s="112"/>
       <c r="E44" s="16" t="s">
         <v>50</v>
       </c>
@@ -19639,10 +19675,10 @@
       <c r="AM44" s="27"/>
     </row>
     <row r="45" spans="1:39">
-      <c r="A45" s="138"/>
-      <c r="B45" s="134"/>
-      <c r="C45" s="122"/>
-      <c r="D45" s="119"/>
+      <c r="A45" s="100"/>
+      <c r="B45" s="124"/>
+      <c r="C45" s="112"/>
+      <c r="D45" s="107"/>
       <c r="E45" s="86" t="s">
         <v>124</v>
       </c>
@@ -19692,9 +19728,9 @@
       <c r="AM45" s="27"/>
     </row>
     <row r="46" spans="1:39">
-      <c r="A46" s="138"/>
-      <c r="B46" s="134"/>
-      <c r="C46" s="122"/>
+      <c r="A46" s="100"/>
+      <c r="B46" s="124"/>
+      <c r="C46" s="112"/>
       <c r="D46" s="57" t="s">
         <v>122</v>
       </c>
@@ -19787,9 +19823,9 @@
       <c r="AM46" s="27"/>
     </row>
     <row r="47" spans="1:39">
-      <c r="A47" s="138"/>
-      <c r="B47" s="135"/>
-      <c r="C47" s="119"/>
+      <c r="A47" s="100"/>
+      <c r="B47" s="125"/>
+      <c r="C47" s="107"/>
       <c r="D47" s="57" t="s">
         <v>123</v>
       </c>
@@ -19832,7 +19868,7 @@
       <c r="AM47" s="4"/>
     </row>
     <row r="48" spans="1:39">
-      <c r="A48" s="138"/>
+      <c r="A48" s="100"/>
       <c r="B48" s="66" t="s">
         <v>45</v>
       </c>
@@ -19917,7 +19953,7 @@
       <c r="AM48" s="27"/>
     </row>
     <row r="49" spans="1:39">
-      <c r="A49" s="138"/>
+      <c r="A49" s="100"/>
       <c r="B49" s="66" t="s">
         <v>52</v>
       </c>
@@ -20018,7 +20054,7 @@
       <c r="AM49" s="27"/>
     </row>
     <row r="50" spans="1:39">
-      <c r="A50" s="138"/>
+      <c r="A50" s="100"/>
       <c r="B50" s="66" t="s">
         <v>54</v>
       </c>
@@ -20119,11 +20155,11 @@
       <c r="AM50" s="27"/>
     </row>
     <row r="51" spans="1:39">
-      <c r="A51" s="138"/>
-      <c r="B51" s="132" t="s">
+      <c r="A51" s="100"/>
+      <c r="B51" s="122" t="s">
         <v>125</v>
       </c>
-      <c r="C51" s="124"/>
+      <c r="C51" s="108"/>
       <c r="D51" s="15" t="s">
         <v>43</v>
       </c>
@@ -20206,9 +20242,9 @@
       <c r="AM51" s="27"/>
     </row>
     <row r="52" spans="1:39">
-      <c r="A52" s="138"/>
-      <c r="B52" s="128"/>
-      <c r="C52" s="125"/>
+      <c r="A52" s="100"/>
+      <c r="B52" s="120"/>
+      <c r="C52" s="109"/>
       <c r="D52" s="15" t="s">
         <v>39</v>
       </c>
@@ -20253,9 +20289,9 @@
       <c r="AM52" s="27"/>
     </row>
     <row r="53" spans="1:39">
-      <c r="A53" s="138"/>
-      <c r="B53" s="129"/>
-      <c r="C53" s="126"/>
+      <c r="A53" s="100"/>
+      <c r="B53" s="103"/>
+      <c r="C53" s="105"/>
       <c r="D53" s="15" t="s">
         <v>41</v>
       </c>
@@ -20354,7 +20390,7 @@
       <c r="AM53" s="27"/>
     </row>
     <row r="54" spans="1:39">
-      <c r="A54" s="138"/>
+      <c r="A54" s="100"/>
       <c r="B54" s="84" t="s">
         <v>141</v>
       </c>
@@ -20457,11 +20493,11 @@
       <c r="AM54" s="27"/>
     </row>
     <row r="55" spans="1:39">
-      <c r="A55" s="138"/>
-      <c r="B55" s="141" t="s">
+      <c r="A55" s="100"/>
+      <c r="B55" s="113" t="s">
         <v>148</v>
       </c>
-      <c r="C55" s="142"/>
+      <c r="C55" s="114"/>
       <c r="D55" s="78" t="s">
         <v>127</v>
       </c>
@@ -20584,7 +20620,7 @@
       <c r="AM55" s="27"/>
     </row>
     <row r="56" spans="1:39">
-      <c r="A56" s="138"/>
+      <c r="A56" s="100"/>
       <c r="B56" s="67" t="s">
         <v>58</v>
       </c>
@@ -20713,7 +20749,7 @@
       <c r="AM56" s="27"/>
     </row>
     <row r="57" spans="1:39">
-      <c r="A57" s="138"/>
+      <c r="A57" s="100"/>
       <c r="B57" s="67" t="s">
         <v>60</v>
       </c>
@@ -20840,7 +20876,7 @@
       <c r="AM57" s="27"/>
     </row>
     <row r="58" spans="1:39" ht="19.5" thickBot="1">
-      <c r="A58" s="139"/>
+      <c r="A58" s="101"/>
       <c r="B58" s="61" t="s">
         <v>61</v>
       </c>
@@ -20969,7 +21005,7 @@
       <c r="AM58" s="27"/>
     </row>
     <row r="59" spans="1:39" ht="18.75" customHeight="1">
-      <c r="A59" s="102" t="s">
+      <c r="A59" s="99" t="s">
         <v>62</v>
       </c>
       <c r="B59" s="81" t="s">
@@ -21103,7 +21139,7 @@
       <c r="AM59" s="27"/>
     </row>
     <row r="60" spans="1:39" ht="19.5" thickBot="1">
-      <c r="A60" s="137"/>
+      <c r="A60" s="127"/>
       <c r="B60" s="61" t="s">
         <v>38</v>
       </c>
@@ -21233,7 +21269,7 @@
       <c r="AM60" s="27"/>
     </row>
     <row r="61" spans="1:39">
-      <c r="A61" s="137"/>
+      <c r="A61" s="127"/>
       <c r="B61" s="68" t="s">
         <v>138</v>
       </c>
@@ -21284,11 +21320,11 @@
       <c r="AM61" s="27"/>
     </row>
     <row r="62" spans="1:39">
-      <c r="A62" s="137"/>
-      <c r="B62" s="131" t="s">
+      <c r="A62" s="127"/>
+      <c r="B62" s="121" t="s">
         <v>125</v>
       </c>
-      <c r="C62" s="124"/>
+      <c r="C62" s="108"/>
       <c r="D62" s="72" t="s">
         <v>64</v>
       </c>
@@ -21387,9 +21423,9 @@
       <c r="AM62" s="27"/>
     </row>
     <row r="63" spans="1:39">
-      <c r="A63" s="137"/>
-      <c r="B63" s="128"/>
-      <c r="C63" s="125"/>
+      <c r="A63" s="127"/>
+      <c r="B63" s="120"/>
+      <c r="C63" s="109"/>
       <c r="D63" s="15" t="s">
         <v>66</v>
       </c>
@@ -21488,9 +21524,9 @@
       <c r="AM63" s="27"/>
     </row>
     <row r="64" spans="1:39">
-      <c r="A64" s="137"/>
-      <c r="B64" s="128"/>
-      <c r="C64" s="125"/>
+      <c r="A64" s="127"/>
+      <c r="B64" s="120"/>
+      <c r="C64" s="109"/>
       <c r="D64" s="15" t="s">
         <v>68</v>
       </c>
@@ -21589,9 +21625,9 @@
       <c r="AM64" s="27"/>
     </row>
     <row r="65" spans="1:39">
-      <c r="A65" s="137"/>
-      <c r="B65" s="128"/>
-      <c r="C65" s="125"/>
+      <c r="A65" s="127"/>
+      <c r="B65" s="120"/>
+      <c r="C65" s="109"/>
       <c r="D65" s="15" t="s">
         <v>70</v>
       </c>
@@ -21690,9 +21726,9 @@
       <c r="AM65" s="27"/>
     </row>
     <row r="66" spans="1:39">
-      <c r="A66" s="137"/>
-      <c r="B66" s="128"/>
-      <c r="C66" s="125"/>
+      <c r="A66" s="127"/>
+      <c r="B66" s="120"/>
+      <c r="C66" s="109"/>
       <c r="D66" s="15" t="s">
         <v>54</v>
       </c>
@@ -21791,9 +21827,9 @@
       <c r="AM66" s="27"/>
     </row>
     <row r="67" spans="1:39">
-      <c r="A67" s="137"/>
-      <c r="B67" s="128"/>
-      <c r="C67" s="125"/>
+      <c r="A67" s="127"/>
+      <c r="B67" s="120"/>
+      <c r="C67" s="109"/>
       <c r="D67" s="15" t="s">
         <v>73</v>
       </c>
@@ -21892,9 +21928,9 @@
       <c r="AM67" s="27"/>
     </row>
     <row r="68" spans="1:39">
-      <c r="A68" s="137"/>
-      <c r="B68" s="128"/>
-      <c r="C68" s="125"/>
+      <c r="A68" s="127"/>
+      <c r="B68" s="120"/>
+      <c r="C68" s="109"/>
       <c r="D68" s="15" t="s">
         <v>75</v>
       </c>
@@ -21993,9 +22029,9 @@
       <c r="AM68" s="27"/>
     </row>
     <row r="69" spans="1:39">
-      <c r="A69" s="137"/>
-      <c r="B69" s="128"/>
-      <c r="C69" s="125"/>
+      <c r="A69" s="127"/>
+      <c r="B69" s="120"/>
+      <c r="C69" s="109"/>
       <c r="D69" s="15" t="s">
         <v>77</v>
       </c>
@@ -22094,9 +22130,9 @@
       <c r="AM69" s="27"/>
     </row>
     <row r="70" spans="1:39">
-      <c r="A70" s="137"/>
-      <c r="B70" s="128"/>
-      <c r="C70" s="125"/>
+      <c r="A70" s="127"/>
+      <c r="B70" s="120"/>
+      <c r="C70" s="109"/>
       <c r="D70" s="15" t="s">
         <v>79</v>
       </c>
@@ -22195,10 +22231,10 @@
       <c r="AM70" s="27"/>
     </row>
     <row r="71" spans="1:39">
-      <c r="A71" s="137"/>
-      <c r="B71" s="128"/>
-      <c r="C71" s="125"/>
-      <c r="D71" s="121" t="s">
+      <c r="A71" s="127"/>
+      <c r="B71" s="120"/>
+      <c r="C71" s="109"/>
+      <c r="D71" s="110" t="s">
         <v>82</v>
       </c>
       <c r="E71" s="16" t="s">
@@ -22300,10 +22336,10 @@
       <c r="AM71" s="27"/>
     </row>
     <row r="72" spans="1:39">
-      <c r="A72" s="137"/>
-      <c r="B72" s="129"/>
-      <c r="C72" s="126"/>
-      <c r="D72" s="119"/>
+      <c r="A72" s="127"/>
+      <c r="B72" s="103"/>
+      <c r="C72" s="105"/>
+      <c r="D72" s="107"/>
       <c r="E72" s="16" t="s">
         <v>84</v>
       </c>
@@ -22403,11 +22439,11 @@
       <c r="AM72" s="27"/>
     </row>
     <row r="73" spans="1:39">
-      <c r="A73" s="137"/>
-      <c r="B73" s="127" t="s">
+      <c r="A73" s="127"/>
+      <c r="B73" s="102" t="s">
         <v>16</v>
       </c>
-      <c r="C73" s="130"/>
+      <c r="C73" s="104"/>
       <c r="D73" s="33" t="s">
         <v>134</v>
       </c>
@@ -22537,9 +22573,9 @@
       <c r="AM73" s="27"/>
     </row>
     <row r="74" spans="1:39">
-      <c r="A74" s="137"/>
-      <c r="B74" s="128"/>
-      <c r="C74" s="125"/>
+      <c r="A74" s="127"/>
+      <c r="B74" s="120"/>
+      <c r="C74" s="109"/>
       <c r="D74" s="33" t="s">
         <v>135</v>
       </c>
@@ -22669,9 +22705,9 @@
       <c r="AM74" s="27"/>
     </row>
     <row r="75" spans="1:39">
-      <c r="A75" s="137"/>
-      <c r="B75" s="128"/>
-      <c r="C75" s="125"/>
+      <c r="A75" s="127"/>
+      <c r="B75" s="120"/>
+      <c r="C75" s="109"/>
       <c r="D75" s="33" t="s">
         <v>136</v>
       </c>
@@ -22801,9 +22837,9 @@
       <c r="AM75" s="27"/>
     </row>
     <row r="76" spans="1:39">
-      <c r="A76" s="137"/>
-      <c r="B76" s="129"/>
-      <c r="C76" s="126"/>
+      <c r="A76" s="127"/>
+      <c r="B76" s="103"/>
+      <c r="C76" s="105"/>
       <c r="D76" s="33" t="s">
         <v>137</v>
       </c>
@@ -22933,7 +22969,7 @@
       <c r="AM76" s="27"/>
     </row>
     <row r="77" spans="1:39">
-      <c r="A77" s="137"/>
+      <c r="A77" s="127"/>
       <c r="B77" s="67" t="s">
         <v>58</v>
       </c>
@@ -23063,7 +23099,7 @@
       <c r="AM77" s="27"/>
     </row>
     <row r="78" spans="1:39">
-      <c r="A78" s="137"/>
+      <c r="A78" s="127"/>
       <c r="B78" s="67" t="s">
         <v>60</v>
       </c>
@@ -23322,7 +23358,7 @@
       <c r="AM79" s="27"/>
     </row>
     <row r="80" spans="1:39">
-      <c r="A80" s="102" t="s">
+      <c r="A80" s="99" t="s">
         <v>89</v>
       </c>
       <c r="B80" s="59" t="s">
@@ -24021,9 +24057,9 @@
       <c r="F93" s="55" t="s">
         <v>98</v>
       </c>
-      <c r="G93" s="56" t="e">
+      <c r="G93" s="56">
         <f t="shared" ref="G93:AK93" si="22">G113+G133</f>
-        <v>#N/A</v>
+        <v>1813</v>
       </c>
       <c r="H93" s="57" t="e">
         <f t="shared" si="22"/>
@@ -25778,8 +25814,8 @@
       <c r="F113" s="55" t="s">
         <v>98</v>
       </c>
-      <c r="G113" s="56" t="e">
-        <v>#N/A</v>
+      <c r="G113" s="56">
+        <v>1080</v>
       </c>
       <c r="H113" s="57" t="e">
         <v>#N/A</v>
@@ -27018,8 +27054,8 @@
         <v>151</v>
       </c>
     </row>
-    <row r="129" spans="6:37" ht="19.5" thickBot="1"/>
-    <row r="130" spans="6:37" ht="19.5" thickBot="1">
+    <row r="129" spans="5:37" ht="19.5" thickBot="1"/>
+    <row r="130" spans="5:37" ht="19.5" thickBot="1">
       <c r="F130" s="92" t="s">
         <v>107</v>
       </c>
@@ -27117,7 +27153,7 @@
         <v>2055</v>
       </c>
     </row>
-    <row r="131" spans="6:37">
+    <row r="131" spans="5:37">
       <c r="F131" s="88" t="s">
         <v>96</v>
       </c>
@@ -27216,7 +27252,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="132" spans="6:37">
+    <row r="132" spans="5:37">
       <c r="F132" s="55" t="s">
         <v>97</v>
       </c>
@@ -27314,12 +27350,12 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="133" spans="6:37">
+    <row r="133" spans="5:37">
       <c r="F133" s="55" t="s">
         <v>98</v>
       </c>
-      <c r="G133" s="56" t="e">
-        <v>#N/A</v>
+      <c r="G133" s="56">
+        <v>733</v>
       </c>
       <c r="H133" s="57" t="e">
         <v>#N/A</v>
@@ -27412,7 +27448,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="134" spans="6:37">
+    <row r="134" spans="5:37">
       <c r="F134" s="55" t="s">
         <v>99</v>
       </c>
@@ -27510,7 +27546,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="135" spans="6:37">
+    <row r="135" spans="5:37">
       <c r="F135" s="55" t="s">
         <v>100</v>
       </c>
@@ -27608,7 +27644,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="136" spans="6:37">
+    <row r="136" spans="5:37">
       <c r="F136" s="55" t="s">
         <v>101</v>
       </c>
@@ -27706,7 +27742,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="137" spans="6:37">
+    <row r="137" spans="5:37">
       <c r="F137" s="55" t="s">
         <v>102</v>
       </c>
@@ -27804,7 +27840,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="138" spans="6:37">
+    <row r="138" spans="5:37">
       <c r="F138" s="55" t="s">
         <v>103</v>
       </c>
@@ -27902,7 +27938,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="139" spans="6:37">
+    <row r="139" spans="5:37">
       <c r="F139" s="89" t="s">
         <v>104</v>
       </c>
@@ -28000,7 +28036,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="140" spans="6:37">
+    <row r="140" spans="5:37">
       <c r="F140" s="89" t="s">
         <v>93</v>
       </c>
@@ -28098,7 +28134,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="141" spans="6:37">
+    <row r="141" spans="5:37">
       <c r="F141" s="55" t="s">
         <v>94</v>
       </c>
@@ -28196,7 +28232,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="142" spans="6:37" ht="19.5" thickBot="1">
+    <row r="142" spans="5:37" ht="19.5" thickBot="1">
       <c r="F142" s="97" t="s">
         <v>95</v>
       </c>
@@ -28294,7 +28330,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="143" spans="6:37">
+    <row r="143" spans="5:37">
       <c r="F143" s="59" t="s">
         <v>105</v>
       </c>
@@ -28423,7 +28459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="6:37" ht="19.5" thickBot="1">
+    <row r="144" spans="5:37" ht="19.5" thickBot="1">
       <c r="F144" s="61" t="s">
         <v>106</v>
       </c>
@@ -28554,19 +28590,16 @@
     </row>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="A16:A58"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="C62:C72"/>
-    <mergeCell ref="D71:D72"/>
-    <mergeCell ref="D24:D29"/>
-    <mergeCell ref="D42:D45"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="C42:C47"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="A2:A15"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="B4:B8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B10:B14"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="C4:C8"/>
+    <mergeCell ref="C10:C14"/>
     <mergeCell ref="A80:A81"/>
     <mergeCell ref="C16:C17"/>
     <mergeCell ref="D16:D17"/>
@@ -28583,16 +28616,19 @@
     <mergeCell ref="B37:B47"/>
     <mergeCell ref="B16:B31"/>
     <mergeCell ref="A59:A79"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="A2:A15"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="B4:B8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B10:B14"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="C4:C8"/>
-    <mergeCell ref="C10:C14"/>
+    <mergeCell ref="A16:A58"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="C62:C72"/>
+    <mergeCell ref="D71:D72"/>
+    <mergeCell ref="D24:D29"/>
+    <mergeCell ref="D42:D45"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="C42:C47"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ライフプラン_猪飼.xlsx
+++ b/ライフプラン_猪飼.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC_USER\Documents\LocalLifeplanRepo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69ED5398-DEAC-40DB-A7A6-FDDD395D3F6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6505266-3ED1-4098-95CE-DB6112BD47D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{934FA03D-99BD-49E0-BFEC-291BD79F4879}"/>
   </bookViews>
@@ -679,7 +679,62 @@
         </r>
       </text>
     </comment>
+    <comment ref="G93" authorId="0" shapeId="0" xr:uid="{262036F5-01FA-4BC8-B8EB-1514CB55C6A6}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="MS P ゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>PC_USER:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="MS P ゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G94" authorId="0" shapeId="0" xr:uid="{69E2AA54-2427-4F59-AEE5-E8228FFFDD16}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="MS P ゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>PC_USER:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="MS P ゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="G107" authorId="0" shapeId="0" xr:uid="{38567A5A-08F1-44CE-8C1B-7B9A61C0360A}">
+      <text/>
+    </comment>
+    <comment ref="E108" authorId="0" shapeId="0" xr:uid="{0CFE7B6C-FEBF-4C82-A58B-E327835A20D7}">
       <text>
         <r>
           <rPr>
@@ -754,6 +809,70 @@
  全労済個人年金  + 2　
  ﾌﾟﾙﾃﾞﾝｼｬﾙ保険金 + 9
 nao</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G114" authorId="0" shapeId="0" xr:uid="{0F2950A9-8AE7-4919-82C2-D9C59D0C6A78}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="MS P ゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>kaz
+ 東北電力配当金  + 1
+ 全労済東１      + 4
+ ﾌﾟﾙﾃﾞﾝｼｬﾙ保険金 + 9
+nao</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G115" authorId="0" shapeId="0" xr:uid="{AA4D0E19-713A-481C-B4AD-6D9DEF9AEC0C}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="MS P ゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>kaz
+ 国民厚生年金　　+45
+ パナ年金　　　  +12　
+ ﾌﾟﾙﾃﾞﾝｼｬﾙ保険金 + 9
+nao</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J115" authorId="0" shapeId="0" xr:uid="{C621A1A5-ABEA-449D-808A-68EDB182D85A}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="MS P ゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>PC_USER:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="MS P ゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
         </r>
       </text>
     </comment>
@@ -857,6 +976,38 @@
           </rPr>
           <t>kazへ返済 -12 (ｶｲﾛ：6、CPAP：1、中山会：１。ﾋﾞｭｰ：1。医療費他)
 naoへ返済 -3（網代0.5、出雲＆瀬戸0.4、牛乳交通費食品等2）</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G134" authorId="0" shapeId="0" xr:uid="{536E0B11-8AD1-4BDA-A536-4C9DAB300E5A}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="MS P ゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>kazへ返済 -4 (新潟_網戸&amp;小嶋屋：1.1、医療費：1.4、ﾋﾞｭｰ：1。他)
+naoへ返済 -2.5（出雲；3，森永：0.3， 交通費返却：-0.7）</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G135" authorId="0" shapeId="0" xr:uid="{CAB7EF98-2301-4D34-AE07-4666B00D6496}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="MS P ゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>kazへ返済 -7 (墓参：1、飯山出雲&amp;鮎：1.2、実家修理：1.6，ﾋﾞｭｰ：1。衣笠浜寿司：1.2、他：1)
+naoへ返済 -2.5（飯山出雲；2，森永：0.2， 町内祭:0.3）</t>
         </r>
       </text>
     </comment>
@@ -3745,109 +3896,6 @@
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" textRotation="255"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="42" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="23" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="24" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="46" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" textRotation="255"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" textRotation="255"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -3857,6 +3905,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" textRotation="255"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" textRotation="255"/>
@@ -3910,6 +3962,105 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" textRotation="255"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="42" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="23" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" textRotation="255"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="24" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="46" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -5854,15 +6005,12 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="31"/>
                 <c:pt idx="0">
-                  <c:v>#N/A</c:v>
+                  <c:v>1076</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>#N/A</c:v>
-                </c:pt>
-                <c:pt idx="3">
                   <c:v>#N/A</c:v>
                 </c:pt>
                 <c:pt idx="4">
@@ -6101,7 +6249,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="31"/>
                 <c:pt idx="0">
-                  <c:v>#N/A</c:v>
+                  <c:v>1124</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>#N/A</c:v>
@@ -7341,6 +7489,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -7348,7 +7497,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -9306,7 +9454,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="31"/>
                 <c:pt idx="0">
-                  <c:v>#N/A</c:v>
+                  <c:v>691</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>#N/A</c:v>
@@ -9553,7 +9701,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="31"/>
                 <c:pt idx="0">
-                  <c:v>#N/A</c:v>
+                  <c:v>669</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>#N/A</c:v>
@@ -10796,6 +10944,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -10803,7 +10952,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -12757,7 +12905,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="31"/>
                 <c:pt idx="0">
-                  <c:v>#N/A</c:v>
+                  <c:v>1767</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>#N/A</c:v>
@@ -13004,7 +13152,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="31"/>
                 <c:pt idx="0">
-                  <c:v>#N/A</c:v>
+                  <c:v>1793</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>#N/A</c:v>
@@ -16446,12 +16594,12 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="128" t="s">
+      <c r="B1" s="99" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="129"/>
-      <c r="D1" s="129"/>
-      <c r="E1" s="130"/>
+      <c r="C1" s="100"/>
+      <c r="D1" s="100"/>
+      <c r="E1" s="101"/>
       <c r="F1" s="2" t="s">
         <v>2</v>
       </c>
@@ -16552,13 +16700,13 @@
       <c r="AM1" s="4"/>
     </row>
     <row r="2" spans="1:39" ht="18.75" customHeight="1">
-      <c r="A2" s="99" t="s">
+      <c r="A2" s="102" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="133" t="s">
+      <c r="B2" s="105" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="140"/>
+      <c r="C2" s="112"/>
       <c r="D2" s="6" t="s">
         <v>5</v>
       </c>
@@ -16643,9 +16791,9 @@
       <c r="AM2" s="4"/>
     </row>
     <row r="3" spans="1:39" ht="19.5" thickBot="1">
-      <c r="A3" s="131"/>
-      <c r="B3" s="134"/>
-      <c r="C3" s="141"/>
+      <c r="A3" s="103"/>
+      <c r="B3" s="106"/>
+      <c r="C3" s="113"/>
       <c r="D3" s="9" t="s">
         <v>7</v>
       </c>
@@ -16746,11 +16894,11 @@
       <c r="AM3" s="4"/>
     </row>
     <row r="4" spans="1:39">
-      <c r="A4" s="131"/>
-      <c r="B4" s="133" t="s">
+      <c r="A4" s="103"/>
+      <c r="B4" s="105" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="142"/>
+      <c r="C4" s="114"/>
       <c r="D4" s="12" t="s">
         <v>10</v>
       </c>
@@ -16795,9 +16943,9 @@
       <c r="AM4" s="4"/>
     </row>
     <row r="5" spans="1:39">
-      <c r="A5" s="131"/>
-      <c r="B5" s="135"/>
-      <c r="C5" s="143"/>
+      <c r="A5" s="103"/>
+      <c r="B5" s="107"/>
+      <c r="C5" s="115"/>
       <c r="D5" s="15" t="s">
         <v>12</v>
       </c>
@@ -16842,9 +16990,9 @@
       <c r="AM5" s="4"/>
     </row>
     <row r="6" spans="1:39">
-      <c r="A6" s="131"/>
-      <c r="B6" s="135"/>
-      <c r="C6" s="143"/>
+      <c r="A6" s="103"/>
+      <c r="B6" s="107"/>
+      <c r="C6" s="115"/>
       <c r="D6" s="15"/>
       <c r="E6" s="16"/>
       <c r="F6" s="17"/>
@@ -16883,9 +17031,9 @@
       <c r="AM6" s="4"/>
     </row>
     <row r="7" spans="1:39">
-      <c r="A7" s="131"/>
-      <c r="B7" s="135"/>
-      <c r="C7" s="143"/>
+      <c r="A7" s="103"/>
+      <c r="B7" s="107"/>
+      <c r="C7" s="115"/>
       <c r="D7" s="15"/>
       <c r="E7" s="16"/>
       <c r="F7" s="17"/>
@@ -16924,9 +17072,9 @@
       <c r="AM7" s="4"/>
     </row>
     <row r="8" spans="1:39">
-      <c r="A8" s="131"/>
-      <c r="B8" s="136"/>
-      <c r="C8" s="144"/>
+      <c r="A8" s="103"/>
+      <c r="B8" s="108"/>
+      <c r="C8" s="116"/>
       <c r="D8" s="15"/>
       <c r="E8" s="16"/>
       <c r="F8" s="17"/>
@@ -16965,12 +17113,12 @@
       <c r="AM8" s="4"/>
     </row>
     <row r="9" spans="1:39" ht="19.5" thickBot="1">
-      <c r="A9" s="131"/>
-      <c r="B9" s="137" t="s">
+      <c r="A9" s="103"/>
+      <c r="B9" s="109" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="138"/>
-      <c r="D9" s="139"/>
+      <c r="C9" s="110"/>
+      <c r="D9" s="111"/>
       <c r="E9" s="18" t="s">
         <v>15</v>
       </c>
@@ -17106,11 +17254,11 @@
       <c r="AM9" s="4"/>
     </row>
     <row r="10" spans="1:39">
-      <c r="A10" s="131"/>
-      <c r="B10" s="133" t="s">
+      <c r="A10" s="103"/>
+      <c r="B10" s="105" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="142"/>
+      <c r="C10" s="114"/>
       <c r="D10" s="15" t="s">
         <v>17</v>
       </c>
@@ -17209,9 +17357,9 @@
       <c r="AM10" s="4"/>
     </row>
     <row r="11" spans="1:39">
-      <c r="A11" s="131"/>
-      <c r="B11" s="135"/>
-      <c r="C11" s="143"/>
+      <c r="A11" s="103"/>
+      <c r="B11" s="107"/>
+      <c r="C11" s="115"/>
       <c r="D11" s="15" t="s">
         <v>19</v>
       </c>
@@ -17261,9 +17409,9 @@
       <c r="AM11" s="4"/>
     </row>
     <row r="12" spans="1:39">
-      <c r="A12" s="131"/>
-      <c r="B12" s="135"/>
-      <c r="C12" s="143"/>
+      <c r="A12" s="103"/>
+      <c r="B12" s="107"/>
+      <c r="C12" s="115"/>
       <c r="D12" s="15" t="s">
         <v>21</v>
       </c>
@@ -17335,9 +17483,9 @@
       <c r="AM12" s="4"/>
     </row>
     <row r="13" spans="1:39">
-      <c r="A13" s="131"/>
-      <c r="B13" s="135"/>
-      <c r="C13" s="143"/>
+      <c r="A13" s="103"/>
+      <c r="B13" s="107"/>
+      <c r="C13" s="115"/>
       <c r="D13" s="15" t="s">
         <v>22</v>
       </c>
@@ -17386,9 +17534,9 @@
       <c r="AM13" s="4"/>
     </row>
     <row r="14" spans="1:39">
-      <c r="A14" s="131"/>
-      <c r="B14" s="136"/>
-      <c r="C14" s="144"/>
+      <c r="A14" s="103"/>
+      <c r="B14" s="108"/>
+      <c r="C14" s="116"/>
       <c r="D14" s="15"/>
       <c r="E14" s="16"/>
       <c r="F14" s="23"/>
@@ -17427,12 +17575,12 @@
       <c r="AM14" s="4"/>
     </row>
     <row r="15" spans="1:39" ht="19.5" thickBot="1">
-      <c r="A15" s="132"/>
-      <c r="B15" s="137" t="s">
+      <c r="A15" s="104"/>
+      <c r="B15" s="109" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="138"/>
-      <c r="D15" s="139"/>
+      <c r="C15" s="110"/>
+      <c r="D15" s="111"/>
       <c r="E15" s="18" t="s">
         <v>25</v>
       </c>
@@ -17568,16 +17716,16 @@
       <c r="AM15" s="4"/>
     </row>
     <row r="16" spans="1:39">
-      <c r="A16" s="99" t="s">
+      <c r="A16" s="102" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="126" t="s">
+      <c r="B16" s="136" t="s">
         <v>132</v>
       </c>
       <c r="C16" s="118" t="s">
         <v>108</v>
       </c>
-      <c r="D16" s="119" t="s">
+      <c r="D16" s="120" t="s">
         <v>112</v>
       </c>
       <c r="E16" s="16" t="s">
@@ -17659,10 +17807,10 @@
       <c r="AM16" s="4"/>
     </row>
     <row r="17" spans="1:39">
-      <c r="A17" s="100"/>
-      <c r="B17" s="124"/>
-      <c r="C17" s="107"/>
-      <c r="D17" s="107"/>
+      <c r="A17" s="138"/>
+      <c r="B17" s="134"/>
+      <c r="C17" s="119"/>
+      <c r="D17" s="119"/>
       <c r="E17" s="16" t="s">
         <v>30</v>
       </c>
@@ -17748,12 +17896,12 @@
       <c r="AM17" s="4"/>
     </row>
     <row r="18" spans="1:39">
-      <c r="A18" s="100"/>
-      <c r="B18" s="124"/>
-      <c r="C18" s="110" t="s">
+      <c r="A18" s="138"/>
+      <c r="B18" s="134"/>
+      <c r="C18" s="121" t="s">
         <v>109</v>
       </c>
-      <c r="D18" s="111" t="s">
+      <c r="D18" s="123" t="s">
         <v>114</v>
       </c>
       <c r="E18" s="13" t="s">
@@ -17835,10 +17983,10 @@
       <c r="AM18" s="27"/>
     </row>
     <row r="19" spans="1:39">
-      <c r="A19" s="100"/>
-      <c r="B19" s="124"/>
-      <c r="C19" s="112"/>
-      <c r="D19" s="112"/>
+      <c r="A19" s="138"/>
+      <c r="B19" s="134"/>
+      <c r="C19" s="122"/>
+      <c r="D19" s="122"/>
       <c r="E19" s="16" t="s">
         <v>28</v>
       </c>
@@ -17906,10 +18054,10 @@
       <c r="AM19" s="27"/>
     </row>
     <row r="20" spans="1:39">
-      <c r="A20" s="100"/>
-      <c r="B20" s="124"/>
-      <c r="C20" s="112"/>
-      <c r="D20" s="107"/>
+      <c r="A20" s="138"/>
+      <c r="B20" s="134"/>
+      <c r="C20" s="122"/>
+      <c r="D20" s="119"/>
       <c r="E20" s="16" t="s">
         <v>29</v>
       </c>
@@ -17959,9 +18107,9 @@
       <c r="AM20" s="27"/>
     </row>
     <row r="21" spans="1:39">
-      <c r="A21" s="100"/>
-      <c r="B21" s="124"/>
-      <c r="C21" s="107"/>
+      <c r="A21" s="138"/>
+      <c r="B21" s="134"/>
+      <c r="C21" s="119"/>
       <c r="D21" s="57" t="s">
         <v>115</v>
       </c>
@@ -18012,9 +18160,9 @@
       <c r="AM21" s="27"/>
     </row>
     <row r="22" spans="1:39">
-      <c r="A22" s="100"/>
-      <c r="B22" s="124"/>
-      <c r="C22" s="110" t="s">
+      <c r="A22" s="138"/>
+      <c r="B22" s="134"/>
+      <c r="C22" s="121" t="s">
         <v>110</v>
       </c>
       <c r="D22" s="57" t="s">
@@ -18059,9 +18207,9 @@
       <c r="AM22" s="27"/>
     </row>
     <row r="23" spans="1:39">
-      <c r="A23" s="100"/>
-      <c r="B23" s="124"/>
-      <c r="C23" s="107"/>
+      <c r="A23" s="138"/>
+      <c r="B23" s="134"/>
+      <c r="C23" s="119"/>
       <c r="D23" s="57" t="s">
         <v>117</v>
       </c>
@@ -18104,12 +18252,12 @@
       <c r="AM23" s="27"/>
     </row>
     <row r="24" spans="1:39">
-      <c r="A24" s="100"/>
-      <c r="B24" s="124"/>
-      <c r="C24" s="110" t="s">
+      <c r="A24" s="138"/>
+      <c r="B24" s="134"/>
+      <c r="C24" s="121" t="s">
         <v>111</v>
       </c>
-      <c r="D24" s="111" t="s">
+      <c r="D24" s="123" t="s">
         <v>118</v>
       </c>
       <c r="E24" s="16" t="s">
@@ -18191,10 +18339,10 @@
       <c r="AM24" s="27"/>
     </row>
     <row r="25" spans="1:39">
-      <c r="A25" s="100"/>
-      <c r="B25" s="124"/>
-      <c r="C25" s="112"/>
-      <c r="D25" s="112"/>
+      <c r="A25" s="138"/>
+      <c r="B25" s="134"/>
+      <c r="C25" s="122"/>
+      <c r="D25" s="122"/>
       <c r="E25" s="16" t="s">
         <v>33</v>
       </c>
@@ -18286,10 +18434,10 @@
       <c r="AM25" s="27"/>
     </row>
     <row r="26" spans="1:39">
-      <c r="A26" s="100"/>
-      <c r="B26" s="124"/>
-      <c r="C26" s="112"/>
-      <c r="D26" s="112"/>
+      <c r="A26" s="138"/>
+      <c r="B26" s="134"/>
+      <c r="C26" s="122"/>
+      <c r="D26" s="122"/>
       <c r="E26" s="16" t="s">
         <v>34</v>
       </c>
@@ -18331,10 +18479,10 @@
       <c r="AM26" s="27"/>
     </row>
     <row r="27" spans="1:39">
-      <c r="A27" s="100"/>
-      <c r="B27" s="124"/>
-      <c r="C27" s="112"/>
-      <c r="D27" s="112"/>
+      <c r="A27" s="138"/>
+      <c r="B27" s="134"/>
+      <c r="C27" s="122"/>
+      <c r="D27" s="122"/>
       <c r="E27" s="29" t="s">
         <v>35</v>
       </c>
@@ -18376,10 +18524,10 @@
       <c r="AM27" s="27"/>
     </row>
     <row r="28" spans="1:39">
-      <c r="A28" s="100"/>
-      <c r="B28" s="124"/>
-      <c r="C28" s="112"/>
-      <c r="D28" s="112"/>
+      <c r="A28" s="138"/>
+      <c r="B28" s="134"/>
+      <c r="C28" s="122"/>
+      <c r="D28" s="122"/>
       <c r="E28" s="16" t="s">
         <v>36</v>
       </c>
@@ -18439,10 +18587,10 @@
       <c r="AM28" s="27"/>
     </row>
     <row r="29" spans="1:39">
-      <c r="A29" s="100"/>
-      <c r="B29" s="124"/>
-      <c r="C29" s="112"/>
-      <c r="D29" s="107"/>
+      <c r="A29" s="138"/>
+      <c r="B29" s="134"/>
+      <c r="C29" s="122"/>
+      <c r="D29" s="119"/>
       <c r="E29" s="86" t="s">
         <v>120</v>
       </c>
@@ -18484,9 +18632,9 @@
       <c r="AM29" s="27"/>
     </row>
     <row r="30" spans="1:39">
-      <c r="A30" s="100"/>
-      <c r="B30" s="124"/>
-      <c r="C30" s="112"/>
+      <c r="A30" s="138"/>
+      <c r="B30" s="134"/>
+      <c r="C30" s="122"/>
       <c r="D30" s="57" t="s">
         <v>122</v>
       </c>
@@ -18529,9 +18677,9 @@
       <c r="AM30" s="27"/>
     </row>
     <row r="31" spans="1:39">
-      <c r="A31" s="100"/>
-      <c r="B31" s="125"/>
-      <c r="C31" s="107"/>
+      <c r="A31" s="138"/>
+      <c r="B31" s="135"/>
+      <c r="C31" s="119"/>
       <c r="D31" s="57" t="s">
         <v>123</v>
       </c>
@@ -18574,11 +18722,11 @@
       <c r="AM31" s="27"/>
     </row>
     <row r="32" spans="1:39">
-      <c r="A32" s="100"/>
-      <c r="B32" s="115" t="s">
+      <c r="A32" s="138"/>
+      <c r="B32" s="143" t="s">
         <v>131</v>
       </c>
-      <c r="C32" s="108"/>
+      <c r="C32" s="124"/>
       <c r="D32" s="17" t="s">
         <v>128</v>
       </c>
@@ -18677,9 +18825,9 @@
       <c r="AM32" s="27"/>
     </row>
     <row r="33" spans="1:39">
-      <c r="A33" s="100"/>
-      <c r="B33" s="116"/>
-      <c r="C33" s="105"/>
+      <c r="A33" s="138"/>
+      <c r="B33" s="144"/>
+      <c r="C33" s="126"/>
       <c r="D33" s="17" t="s">
         <v>129</v>
       </c>
@@ -18754,12 +18902,12 @@
       <c r="AM33" s="27"/>
     </row>
     <row r="34" spans="1:39">
-      <c r="A34" s="100"/>
-      <c r="B34" s="102" t="s">
+      <c r="A34" s="138"/>
+      <c r="B34" s="127" t="s">
         <v>9</v>
       </c>
-      <c r="C34" s="104"/>
-      <c r="D34" s="106"/>
+      <c r="C34" s="130"/>
+      <c r="D34" s="140"/>
       <c r="E34" s="34" t="str">
         <f t="shared" ref="E34:AK34" si="2">E4</f>
         <v>新潟実家の売却益　（妙子と折半）</v>
@@ -18896,10 +19044,10 @@
       <c r="AM34" s="27"/>
     </row>
     <row r="35" spans="1:39">
-      <c r="A35" s="100"/>
-      <c r="B35" s="103"/>
-      <c r="C35" s="105"/>
-      <c r="D35" s="107"/>
+      <c r="A35" s="138"/>
+      <c r="B35" s="129"/>
+      <c r="C35" s="126"/>
+      <c r="D35" s="119"/>
       <c r="E35" s="34" t="str">
         <f t="shared" ref="E35:AK35" si="3">E5</f>
         <v>横浜マンションの売却益</v>
@@ -19036,7 +19184,7 @@
       <c r="AM35" s="27"/>
     </row>
     <row r="36" spans="1:39" ht="19.5" thickBot="1">
-      <c r="A36" s="100"/>
+      <c r="A36" s="138"/>
       <c r="B36" s="35" t="s">
         <v>38</v>
       </c>
@@ -19175,8 +19323,8 @@
       <c r="AM36" s="27"/>
     </row>
     <row r="37" spans="1:39">
-      <c r="A37" s="100"/>
-      <c r="B37" s="123" t="s">
+      <c r="A37" s="138"/>
+      <c r="B37" s="133" t="s">
         <v>133</v>
       </c>
       <c r="C37" s="8" t="s">
@@ -19226,9 +19374,9 @@
       <c r="AM37" s="4"/>
     </row>
     <row r="38" spans="1:39">
-      <c r="A38" s="100"/>
-      <c r="B38" s="124"/>
-      <c r="C38" s="110" t="s">
+      <c r="A38" s="138"/>
+      <c r="B38" s="134"/>
+      <c r="C38" s="121" t="s">
         <v>109</v>
       </c>
       <c r="D38" s="57" t="s">
@@ -19273,9 +19421,9 @@
       <c r="AM38" s="4"/>
     </row>
     <row r="39" spans="1:39">
-      <c r="A39" s="100"/>
-      <c r="B39" s="124"/>
-      <c r="C39" s="107"/>
+      <c r="A39" s="138"/>
+      <c r="B39" s="134"/>
+      <c r="C39" s="119"/>
       <c r="D39" s="57" t="s">
         <v>115</v>
       </c>
@@ -19318,9 +19466,9 @@
       <c r="AM39" s="4"/>
     </row>
     <row r="40" spans="1:39">
-      <c r="A40" s="100"/>
-      <c r="B40" s="124"/>
-      <c r="C40" s="110" t="s">
+      <c r="A40" s="138"/>
+      <c r="B40" s="134"/>
+      <c r="C40" s="121" t="s">
         <v>110</v>
       </c>
       <c r="D40" s="57" t="s">
@@ -19421,9 +19569,9 @@
       <c r="AM40" s="27"/>
     </row>
     <row r="41" spans="1:39">
-      <c r="A41" s="100"/>
-      <c r="B41" s="124"/>
-      <c r="C41" s="107"/>
+      <c r="A41" s="138"/>
+      <c r="B41" s="134"/>
+      <c r="C41" s="119"/>
       <c r="D41" s="57" t="s">
         <v>117</v>
       </c>
@@ -19466,12 +19614,12 @@
       <c r="AM41" s="4"/>
     </row>
     <row r="42" spans="1:39">
-      <c r="A42" s="100"/>
-      <c r="B42" s="124"/>
-      <c r="C42" s="110" t="s">
+      <c r="A42" s="138"/>
+      <c r="B42" s="134"/>
+      <c r="C42" s="121" t="s">
         <v>111</v>
       </c>
-      <c r="D42" s="111" t="s">
+      <c r="D42" s="123" t="s">
         <v>118</v>
       </c>
       <c r="E42" s="16" t="s">
@@ -19517,10 +19665,10 @@
       <c r="AM42" s="27"/>
     </row>
     <row r="43" spans="1:39">
-      <c r="A43" s="100"/>
-      <c r="B43" s="124"/>
-      <c r="C43" s="112"/>
-      <c r="D43" s="112"/>
+      <c r="A43" s="138"/>
+      <c r="B43" s="134"/>
+      <c r="C43" s="122"/>
+      <c r="D43" s="122"/>
       <c r="E43" s="16" t="s">
         <v>49</v>
       </c>
@@ -19600,10 +19748,10 @@
       <c r="AM43" s="27"/>
     </row>
     <row r="44" spans="1:39">
-      <c r="A44" s="100"/>
-      <c r="B44" s="124"/>
-      <c r="C44" s="112"/>
-      <c r="D44" s="112"/>
+      <c r="A44" s="138"/>
+      <c r="B44" s="134"/>
+      <c r="C44" s="122"/>
+      <c r="D44" s="122"/>
       <c r="E44" s="16" t="s">
         <v>50</v>
       </c>
@@ -19675,10 +19823,10 @@
       <c r="AM44" s="27"/>
     </row>
     <row r="45" spans="1:39">
-      <c r="A45" s="100"/>
-      <c r="B45" s="124"/>
-      <c r="C45" s="112"/>
-      <c r="D45" s="107"/>
+      <c r="A45" s="138"/>
+      <c r="B45" s="134"/>
+      <c r="C45" s="122"/>
+      <c r="D45" s="119"/>
       <c r="E45" s="86" t="s">
         <v>124</v>
       </c>
@@ -19728,9 +19876,9 @@
       <c r="AM45" s="27"/>
     </row>
     <row r="46" spans="1:39">
-      <c r="A46" s="100"/>
-      <c r="B46" s="124"/>
-      <c r="C46" s="112"/>
+      <c r="A46" s="138"/>
+      <c r="B46" s="134"/>
+      <c r="C46" s="122"/>
       <c r="D46" s="57" t="s">
         <v>122</v>
       </c>
@@ -19823,9 +19971,9 @@
       <c r="AM46" s="27"/>
     </row>
     <row r="47" spans="1:39">
-      <c r="A47" s="100"/>
-      <c r="B47" s="125"/>
-      <c r="C47" s="107"/>
+      <c r="A47" s="138"/>
+      <c r="B47" s="135"/>
+      <c r="C47" s="119"/>
       <c r="D47" s="57" t="s">
         <v>123</v>
       </c>
@@ -19868,7 +20016,7 @@
       <c r="AM47" s="4"/>
     </row>
     <row r="48" spans="1:39">
-      <c r="A48" s="100"/>
+      <c r="A48" s="138"/>
       <c r="B48" s="66" t="s">
         <v>45</v>
       </c>
@@ -19953,7 +20101,7 @@
       <c r="AM48" s="27"/>
     </row>
     <row r="49" spans="1:39">
-      <c r="A49" s="100"/>
+      <c r="A49" s="138"/>
       <c r="B49" s="66" t="s">
         <v>52</v>
       </c>
@@ -20054,7 +20202,7 @@
       <c r="AM49" s="27"/>
     </row>
     <row r="50" spans="1:39">
-      <c r="A50" s="100"/>
+      <c r="A50" s="138"/>
       <c r="B50" s="66" t="s">
         <v>54</v>
       </c>
@@ -20155,11 +20303,11 @@
       <c r="AM50" s="27"/>
     </row>
     <row r="51" spans="1:39">
-      <c r="A51" s="100"/>
-      <c r="B51" s="122" t="s">
+      <c r="A51" s="138"/>
+      <c r="B51" s="132" t="s">
         <v>125</v>
       </c>
-      <c r="C51" s="108"/>
+      <c r="C51" s="124"/>
       <c r="D51" s="15" t="s">
         <v>43</v>
       </c>
@@ -20242,9 +20390,9 @@
       <c r="AM51" s="27"/>
     </row>
     <row r="52" spans="1:39">
-      <c r="A52" s="100"/>
-      <c r="B52" s="120"/>
-      <c r="C52" s="109"/>
+      <c r="A52" s="138"/>
+      <c r="B52" s="128"/>
+      <c r="C52" s="125"/>
       <c r="D52" s="15" t="s">
         <v>39</v>
       </c>
@@ -20289,9 +20437,9 @@
       <c r="AM52" s="27"/>
     </row>
     <row r="53" spans="1:39">
-      <c r="A53" s="100"/>
-      <c r="B53" s="103"/>
-      <c r="C53" s="105"/>
+      <c r="A53" s="138"/>
+      <c r="B53" s="129"/>
+      <c r="C53" s="126"/>
       <c r="D53" s="15" t="s">
         <v>41</v>
       </c>
@@ -20390,7 +20538,7 @@
       <c r="AM53" s="27"/>
     </row>
     <row r="54" spans="1:39">
-      <c r="A54" s="100"/>
+      <c r="A54" s="138"/>
       <c r="B54" s="84" t="s">
         <v>141</v>
       </c>
@@ -20493,11 +20641,11 @@
       <c r="AM54" s="27"/>
     </row>
     <row r="55" spans="1:39">
-      <c r="A55" s="100"/>
-      <c r="B55" s="113" t="s">
+      <c r="A55" s="138"/>
+      <c r="B55" s="141" t="s">
         <v>148</v>
       </c>
-      <c r="C55" s="114"/>
+      <c r="C55" s="142"/>
       <c r="D55" s="78" t="s">
         <v>127</v>
       </c>
@@ -20620,7 +20768,7 @@
       <c r="AM55" s="27"/>
     </row>
     <row r="56" spans="1:39">
-      <c r="A56" s="100"/>
+      <c r="A56" s="138"/>
       <c r="B56" s="67" t="s">
         <v>58</v>
       </c>
@@ -20749,7 +20897,7 @@
       <c r="AM56" s="27"/>
     </row>
     <row r="57" spans="1:39">
-      <c r="A57" s="100"/>
+      <c r="A57" s="138"/>
       <c r="B57" s="67" t="s">
         <v>60</v>
       </c>
@@ -20876,7 +21024,7 @@
       <c r="AM57" s="27"/>
     </row>
     <row r="58" spans="1:39" ht="19.5" thickBot="1">
-      <c r="A58" s="101"/>
+      <c r="A58" s="139"/>
       <c r="B58" s="61" t="s">
         <v>61</v>
       </c>
@@ -21005,7 +21153,7 @@
       <c r="AM58" s="27"/>
     </row>
     <row r="59" spans="1:39" ht="18.75" customHeight="1">
-      <c r="A59" s="99" t="s">
+      <c r="A59" s="102" t="s">
         <v>62</v>
       </c>
       <c r="B59" s="81" t="s">
@@ -21139,7 +21287,7 @@
       <c r="AM59" s="27"/>
     </row>
     <row r="60" spans="1:39" ht="19.5" thickBot="1">
-      <c r="A60" s="127"/>
+      <c r="A60" s="137"/>
       <c r="B60" s="61" t="s">
         <v>38</v>
       </c>
@@ -21269,7 +21417,7 @@
       <c r="AM60" s="27"/>
     </row>
     <row r="61" spans="1:39">
-      <c r="A61" s="127"/>
+      <c r="A61" s="137"/>
       <c r="B61" s="68" t="s">
         <v>138</v>
       </c>
@@ -21320,11 +21468,11 @@
       <c r="AM61" s="27"/>
     </row>
     <row r="62" spans="1:39">
-      <c r="A62" s="127"/>
-      <c r="B62" s="121" t="s">
+      <c r="A62" s="137"/>
+      <c r="B62" s="131" t="s">
         <v>125</v>
       </c>
-      <c r="C62" s="108"/>
+      <c r="C62" s="124"/>
       <c r="D62" s="72" t="s">
         <v>64</v>
       </c>
@@ -21423,9 +21571,9 @@
       <c r="AM62" s="27"/>
     </row>
     <row r="63" spans="1:39">
-      <c r="A63" s="127"/>
-      <c r="B63" s="120"/>
-      <c r="C63" s="109"/>
+      <c r="A63" s="137"/>
+      <c r="B63" s="128"/>
+      <c r="C63" s="125"/>
       <c r="D63" s="15" t="s">
         <v>66</v>
       </c>
@@ -21524,9 +21672,9 @@
       <c r="AM63" s="27"/>
     </row>
     <row r="64" spans="1:39">
-      <c r="A64" s="127"/>
-      <c r="B64" s="120"/>
-      <c r="C64" s="109"/>
+      <c r="A64" s="137"/>
+      <c r="B64" s="128"/>
+      <c r="C64" s="125"/>
       <c r="D64" s="15" t="s">
         <v>68</v>
       </c>
@@ -21625,9 +21773,9 @@
       <c r="AM64" s="27"/>
     </row>
     <row r="65" spans="1:39">
-      <c r="A65" s="127"/>
-      <c r="B65" s="120"/>
-      <c r="C65" s="109"/>
+      <c r="A65" s="137"/>
+      <c r="B65" s="128"/>
+      <c r="C65" s="125"/>
       <c r="D65" s="15" t="s">
         <v>70</v>
       </c>
@@ -21726,9 +21874,9 @@
       <c r="AM65" s="27"/>
     </row>
     <row r="66" spans="1:39">
-      <c r="A66" s="127"/>
-      <c r="B66" s="120"/>
-      <c r="C66" s="109"/>
+      <c r="A66" s="137"/>
+      <c r="B66" s="128"/>
+      <c r="C66" s="125"/>
       <c r="D66" s="15" t="s">
         <v>54</v>
       </c>
@@ -21827,9 +21975,9 @@
       <c r="AM66" s="27"/>
     </row>
     <row r="67" spans="1:39">
-      <c r="A67" s="127"/>
-      <c r="B67" s="120"/>
-      <c r="C67" s="109"/>
+      <c r="A67" s="137"/>
+      <c r="B67" s="128"/>
+      <c r="C67" s="125"/>
       <c r="D67" s="15" t="s">
         <v>73</v>
       </c>
@@ -21928,9 +22076,9 @@
       <c r="AM67" s="27"/>
     </row>
     <row r="68" spans="1:39">
-      <c r="A68" s="127"/>
-      <c r="B68" s="120"/>
-      <c r="C68" s="109"/>
+      <c r="A68" s="137"/>
+      <c r="B68" s="128"/>
+      <c r="C68" s="125"/>
       <c r="D68" s="15" t="s">
         <v>75</v>
       </c>
@@ -22029,9 +22177,9 @@
       <c r="AM68" s="27"/>
     </row>
     <row r="69" spans="1:39">
-      <c r="A69" s="127"/>
-      <c r="B69" s="120"/>
-      <c r="C69" s="109"/>
+      <c r="A69" s="137"/>
+      <c r="B69" s="128"/>
+      <c r="C69" s="125"/>
       <c r="D69" s="15" t="s">
         <v>77</v>
       </c>
@@ -22130,9 +22278,9 @@
       <c r="AM69" s="27"/>
     </row>
     <row r="70" spans="1:39">
-      <c r="A70" s="127"/>
-      <c r="B70" s="120"/>
-      <c r="C70" s="109"/>
+      <c r="A70" s="137"/>
+      <c r="B70" s="128"/>
+      <c r="C70" s="125"/>
       <c r="D70" s="15" t="s">
         <v>79</v>
       </c>
@@ -22231,10 +22379,10 @@
       <c r="AM70" s="27"/>
     </row>
     <row r="71" spans="1:39">
-      <c r="A71" s="127"/>
-      <c r="B71" s="120"/>
-      <c r="C71" s="109"/>
-      <c r="D71" s="110" t="s">
+      <c r="A71" s="137"/>
+      <c r="B71" s="128"/>
+      <c r="C71" s="125"/>
+      <c r="D71" s="121" t="s">
         <v>82</v>
       </c>
       <c r="E71" s="16" t="s">
@@ -22336,10 +22484,10 @@
       <c r="AM71" s="27"/>
     </row>
     <row r="72" spans="1:39">
-      <c r="A72" s="127"/>
-      <c r="B72" s="103"/>
-      <c r="C72" s="105"/>
-      <c r="D72" s="107"/>
+      <c r="A72" s="137"/>
+      <c r="B72" s="129"/>
+      <c r="C72" s="126"/>
+      <c r="D72" s="119"/>
       <c r="E72" s="16" t="s">
         <v>84</v>
       </c>
@@ -22439,11 +22587,11 @@
       <c r="AM72" s="27"/>
     </row>
     <row r="73" spans="1:39">
-      <c r="A73" s="127"/>
-      <c r="B73" s="102" t="s">
+      <c r="A73" s="137"/>
+      <c r="B73" s="127" t="s">
         <v>16</v>
       </c>
-      <c r="C73" s="104"/>
+      <c r="C73" s="130"/>
       <c r="D73" s="33" t="s">
         <v>134</v>
       </c>
@@ -22573,9 +22721,9 @@
       <c r="AM73" s="27"/>
     </row>
     <row r="74" spans="1:39">
-      <c r="A74" s="127"/>
-      <c r="B74" s="120"/>
-      <c r="C74" s="109"/>
+      <c r="A74" s="137"/>
+      <c r="B74" s="128"/>
+      <c r="C74" s="125"/>
       <c r="D74" s="33" t="s">
         <v>135</v>
       </c>
@@ -22705,9 +22853,9 @@
       <c r="AM74" s="27"/>
     </row>
     <row r="75" spans="1:39">
-      <c r="A75" s="127"/>
-      <c r="B75" s="120"/>
-      <c r="C75" s="109"/>
+      <c r="A75" s="137"/>
+      <c r="B75" s="128"/>
+      <c r="C75" s="125"/>
       <c r="D75" s="33" t="s">
         <v>136</v>
       </c>
@@ -22837,9 +22985,9 @@
       <c r="AM75" s="27"/>
     </row>
     <row r="76" spans="1:39">
-      <c r="A76" s="127"/>
-      <c r="B76" s="103"/>
-      <c r="C76" s="105"/>
+      <c r="A76" s="137"/>
+      <c r="B76" s="129"/>
+      <c r="C76" s="126"/>
       <c r="D76" s="33" t="s">
         <v>137</v>
       </c>
@@ -22969,7 +23117,7 @@
       <c r="AM76" s="27"/>
     </row>
     <row r="77" spans="1:39">
-      <c r="A77" s="127"/>
+      <c r="A77" s="137"/>
       <c r="B77" s="67" t="s">
         <v>58</v>
       </c>
@@ -23099,7 +23247,7 @@
       <c r="AM77" s="27"/>
     </row>
     <row r="78" spans="1:39">
-      <c r="A78" s="127"/>
+      <c r="A78" s="137"/>
       <c r="B78" s="67" t="s">
         <v>60</v>
       </c>
@@ -23358,7 +23506,7 @@
       <c r="AM79" s="27"/>
     </row>
     <row r="80" spans="1:39">
-      <c r="A80" s="99" t="s">
+      <c r="A80" s="102" t="s">
         <v>89</v>
       </c>
       <c r="B80" s="59" t="s">
@@ -24186,9 +24334,9 @@
       <c r="F94" s="55" t="s">
         <v>99</v>
       </c>
-      <c r="G94" s="56" t="e">
+      <c r="G94" s="56">
         <f t="shared" ref="G94:AK94" si="23">G114+G134</f>
-        <v>#N/A</v>
+        <v>1767</v>
       </c>
       <c r="H94" s="57" t="e">
         <f t="shared" si="23"/>
@@ -24315,9 +24463,9 @@
       <c r="F95" s="55" t="s">
         <v>100</v>
       </c>
-      <c r="G95" s="56" t="e">
+      <c r="G95" s="56">
         <f t="shared" ref="G95:AK95" si="24">G115+G135</f>
-        <v>#N/A</v>
+        <v>1793</v>
       </c>
       <c r="H95" s="57" t="e">
         <f t="shared" si="24"/>
@@ -24569,7 +24717,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="97" spans="6:37">
+    <row r="97" spans="5:37">
       <c r="F97" s="55" t="s">
         <v>102</v>
       </c>
@@ -24698,7 +24846,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="98" spans="6:37">
+    <row r="98" spans="5:37">
       <c r="F98" s="55" t="s">
         <v>103</v>
       </c>
@@ -24827,7 +24975,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="99" spans="6:37">
+    <row r="99" spans="5:37">
       <c r="F99" s="89" t="s">
         <v>104</v>
       </c>
@@ -24956,7 +25104,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="100" spans="6:37">
+    <row r="100" spans="5:37">
       <c r="F100" s="89" t="s">
         <v>93</v>
       </c>
@@ -25085,7 +25233,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="101" spans="6:37">
+    <row r="101" spans="5:37">
       <c r="F101" s="55" t="s">
         <v>94</v>
       </c>
@@ -25214,7 +25362,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="102" spans="6:37" ht="19.5" thickBot="1">
+    <row r="102" spans="5:37" ht="19.5" thickBot="1">
       <c r="F102" s="95" t="s">
         <v>95</v>
       </c>
@@ -25343,7 +25491,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="103" spans="6:37">
+    <row r="103" spans="5:37">
       <c r="F103" s="67" t="s">
         <v>105</v>
       </c>
@@ -25472,19 +25620,46 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="6:37" ht="19.5" thickBot="1">
+    <row r="104" spans="5:37" ht="19.5" thickBot="1">
       <c r="F104" s="61" t="s">
         <v>106</v>
       </c>
-      <c r="G104" s="45"/>
-      <c r="H104" s="41"/>
-      <c r="I104" s="41"/>
-      <c r="J104" s="41"/>
-      <c r="K104" s="41"/>
-      <c r="L104" s="41"/>
-      <c r="M104" s="41"/>
-      <c r="N104" s="41"/>
-      <c r="O104" s="41"/>
+      <c r="G104" s="45" t="e">
+        <f>G103-G99</f>
+        <v>#N/A</v>
+      </c>
+      <c r="H104" s="41" t="e">
+        <f t="shared" ref="H104:O104" si="33">H103-H99</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I104" s="41" t="e">
+        <f t="shared" si="33"/>
+        <v>#N/A</v>
+      </c>
+      <c r="J104" s="41" t="e">
+        <f t="shared" si="33"/>
+        <v>#N/A</v>
+      </c>
+      <c r="K104" s="41" t="e">
+        <f t="shared" si="33"/>
+        <v>#N/A</v>
+      </c>
+      <c r="L104" s="41" t="e">
+        <f t="shared" si="33"/>
+        <v>#N/A</v>
+      </c>
+      <c r="M104" s="41" t="e">
+        <f t="shared" si="33"/>
+        <v>#N/A</v>
+      </c>
+      <c r="N104" s="41" t="e">
+        <f t="shared" si="33"/>
+        <v>#N/A</v>
+      </c>
+      <c r="O104" s="41" t="e">
+        <f t="shared" si="33"/>
+        <v>#N/A</v>
+      </c>
       <c r="P104" s="41"/>
       <c r="Q104" s="41"/>
       <c r="R104" s="41"/>
@@ -25508,14 +25683,14 @@
       <c r="AJ104" s="41"/>
       <c r="AK104" s="42"/>
     </row>
-    <row r="107" spans="6:37"/>
-    <row r="108" spans="6:37" ht="24">
+    <row r="107" spans="5:37"/>
+    <row r="108" spans="5:37" ht="24">
       <c r="F108" s="54" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="109" spans="6:37" ht="19.5" thickBot="1"/>
-    <row r="110" spans="6:37" ht="19.5" thickBot="1">
+    <row r="109" spans="5:37" ht="19.5" thickBot="1"/>
+    <row r="110" spans="5:37" ht="19.5" thickBot="1">
       <c r="F110" s="92" t="s">
         <v>107</v>
       </c>
@@ -25613,7 +25788,7 @@
         <v>2055</v>
       </c>
     </row>
-    <row r="111" spans="6:37">
+    <row r="111" spans="5:37">
       <c r="F111" s="88" t="s">
         <v>96</v>
       </c>
@@ -25712,7 +25887,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="112" spans="6:37">
+    <row r="112" spans="5:37">
       <c r="F112" s="55" t="s">
         <v>97</v>
       </c>
@@ -25912,8 +26087,8 @@
       <c r="F114" s="55" t="s">
         <v>99</v>
       </c>
-      <c r="G114" s="56" t="e">
-        <v>#N/A</v>
+      <c r="G114" s="56">
+        <v>1076</v>
       </c>
       <c r="H114" s="57" t="e">
         <v>#N/A</v>
@@ -25921,9 +26096,7 @@
       <c r="I114" s="57" t="e">
         <v>#N/A</v>
       </c>
-      <c r="J114" s="57" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="J114" s="57"/>
       <c r="K114" s="57" t="e">
         <v>#N/A</v>
       </c>
@@ -26010,8 +26183,8 @@
       <c r="F115" s="55" t="s">
         <v>100</v>
       </c>
-      <c r="G115" s="56" t="e">
-        <v>#N/A</v>
+      <c r="G115" s="56">
+        <v>1124</v>
       </c>
       <c r="H115" s="57" t="e">
         <v>#N/A</v>
@@ -26795,127 +26968,127 @@
         <v>105</v>
       </c>
       <c r="G123" s="46">
-        <f t="shared" ref="G123:AK123" si="33">G58</f>
+        <f t="shared" ref="G123:AK123" si="34">G58</f>
         <v>651</v>
       </c>
       <c r="H123" s="47">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>551</v>
       </c>
       <c r="I123" s="47">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>349</v>
       </c>
       <c r="J123" s="47">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>257</v>
       </c>
       <c r="K123" s="47">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>237</v>
       </c>
       <c r="L123" s="47">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>105</v>
       </c>
       <c r="M123" s="47">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>103</v>
       </c>
       <c r="N123" s="47">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>81</v>
       </c>
       <c r="O123" s="47">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>59</v>
       </c>
       <c r="P123" s="47">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>107</v>
       </c>
       <c r="Q123" s="47">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>-195</v>
       </c>
       <c r="R123" s="47">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>-197</v>
       </c>
       <c r="S123" s="47">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>-279</v>
       </c>
       <c r="T123" s="47">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>-341</v>
       </c>
       <c r="U123" s="47">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>-502</v>
       </c>
       <c r="V123" s="47">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>-653</v>
       </c>
       <c r="W123" s="47">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>-670</v>
       </c>
       <c r="X123" s="47">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>-707</v>
       </c>
       <c r="Y123" s="47">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>-724</v>
       </c>
       <c r="Z123" s="47">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>1559</v>
       </c>
       <c r="AA123" s="47">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>1395</v>
       </c>
       <c r="AB123" s="47">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>1231</v>
       </c>
       <c r="AC123" s="47">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>1047</v>
       </c>
       <c r="AD123" s="47">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>883</v>
       </c>
       <c r="AE123" s="47">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>719</v>
       </c>
       <c r="AF123" s="47">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>560</v>
       </c>
       <c r="AG123" s="47">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>401</v>
       </c>
       <c r="AH123" s="47">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>22</v>
       </c>
       <c r="AI123" s="47">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AJ123" s="47">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AK123" s="91">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
     </row>
@@ -26928,123 +27101,123 @@
         <v>#N/A</v>
       </c>
       <c r="H124" s="41" t="e">
-        <f t="shared" ref="H124:AK124" si="34">H123-H119</f>
+        <f t="shared" ref="H124:AK124" si="35">H123-H119</f>
         <v>#N/A</v>
       </c>
       <c r="I124" s="41" t="e">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>#N/A</v>
       </c>
       <c r="J124" s="41" t="e">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>#N/A</v>
       </c>
       <c r="K124" s="41" t="e">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>#N/A</v>
       </c>
       <c r="L124" s="41" t="e">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>#N/A</v>
       </c>
       <c r="M124" s="41" t="e">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>#N/A</v>
       </c>
       <c r="N124" s="41" t="e">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>#N/A</v>
       </c>
       <c r="O124" s="41" t="e">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>#N/A</v>
       </c>
       <c r="P124" s="41" t="e">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>#N/A</v>
       </c>
       <c r="Q124" s="41" t="e">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>#N/A</v>
       </c>
       <c r="R124" s="41" t="e">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>#N/A</v>
       </c>
       <c r="S124" s="41" t="e">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>#N/A</v>
       </c>
       <c r="T124" s="41" t="e">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>#N/A</v>
       </c>
       <c r="U124" s="41" t="e">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>#N/A</v>
       </c>
       <c r="V124" s="41" t="e">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>#N/A</v>
       </c>
       <c r="W124" s="41" t="e">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>#N/A</v>
       </c>
       <c r="X124" s="41" t="e">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>#N/A</v>
       </c>
       <c r="Y124" s="41" t="e">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>#N/A</v>
       </c>
       <c r="Z124" s="41" t="e">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>#N/A</v>
       </c>
       <c r="AA124" s="41" t="e">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>#N/A</v>
       </c>
       <c r="AB124" s="41" t="e">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>#N/A</v>
       </c>
       <c r="AC124" s="41" t="e">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>#N/A</v>
       </c>
       <c r="AD124" s="41" t="e">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>#N/A</v>
       </c>
       <c r="AE124" s="41" t="e">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>#N/A</v>
       </c>
       <c r="AF124" s="41" t="e">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>#N/A</v>
       </c>
       <c r="AG124" s="41" t="e">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>#N/A</v>
       </c>
       <c r="AH124" s="41" t="e">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>#N/A</v>
       </c>
       <c r="AI124" s="41" t="e">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>#N/A</v>
       </c>
       <c r="AJ124" s="41" t="e">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>#N/A</v>
       </c>
       <c r="AK124" s="42" t="e">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>#N/A</v>
       </c>
     </row>
@@ -27452,8 +27625,9 @@
       <c r="F134" s="55" t="s">
         <v>99</v>
       </c>
-      <c r="G134" s="56" t="e">
-        <v>#N/A</v>
+      <c r="G134" s="56">
+        <f>691</f>
+        <v>691</v>
       </c>
       <c r="H134" s="57" t="e">
         <v>#N/A</v>
@@ -27550,8 +27724,8 @@
       <c r="F135" s="55" t="s">
         <v>100</v>
       </c>
-      <c r="G135" s="56" t="e">
-        <v>#N/A</v>
+      <c r="G135" s="56">
+        <v>669</v>
       </c>
       <c r="H135" s="57" t="e">
         <v>#N/A</v>
@@ -28335,127 +28509,127 @@
         <v>105</v>
       </c>
       <c r="G143" s="46">
-        <f t="shared" ref="G143:AK143" si="35">G79</f>
+        <f t="shared" ref="G143:AK143" si="36">G79</f>
         <v>399</v>
       </c>
       <c r="H143" s="47">
-        <f t="shared" si="35"/>
+        <f>H79</f>
         <v>412</v>
       </c>
       <c r="I143" s="47">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>425</v>
       </c>
       <c r="J143" s="47">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>438</v>
       </c>
       <c r="K143" s="47">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>451</v>
       </c>
       <c r="L143" s="47">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>464</v>
       </c>
       <c r="M143" s="47">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>477</v>
       </c>
       <c r="N143" s="47">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>490</v>
       </c>
       <c r="O143" s="47">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>503</v>
       </c>
       <c r="P143" s="47">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>516</v>
       </c>
       <c r="Q143" s="47">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>529</v>
       </c>
       <c r="R143" s="47">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>542</v>
       </c>
       <c r="S143" s="47">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>555</v>
       </c>
       <c r="T143" s="47">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>568</v>
       </c>
       <c r="U143" s="47">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>581</v>
       </c>
       <c r="V143" s="47">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>594</v>
       </c>
       <c r="W143" s="47">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>607</v>
       </c>
       <c r="X143" s="47">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>620</v>
       </c>
       <c r="Y143" s="47">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>633</v>
       </c>
       <c r="Z143" s="47">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>646</v>
       </c>
       <c r="AA143" s="47">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>659</v>
       </c>
       <c r="AB143" s="47">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>672</v>
       </c>
       <c r="AC143" s="47">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>685</v>
       </c>
       <c r="AD143" s="47">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>698</v>
       </c>
       <c r="AE143" s="47">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>711</v>
       </c>
       <c r="AF143" s="47">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>724</v>
       </c>
       <c r="AG143" s="47">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>737</v>
       </c>
       <c r="AH143" s="47">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>750</v>
       </c>
       <c r="AI143" s="47">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="AJ143" s="47">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="AK143" s="91">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
     </row>
@@ -28468,138 +28642,141 @@
         <v>#N/A</v>
       </c>
       <c r="H144" s="41" t="e">
-        <f t="shared" ref="H144:AK144" si="36">H143-H139</f>
+        <f>H143-H139</f>
         <v>#N/A</v>
       </c>
       <c r="I144" s="41" t="e">
-        <f t="shared" si="36"/>
+        <f t="shared" ref="H144:AK144" si="37">I143-I139</f>
         <v>#N/A</v>
       </c>
       <c r="J144" s="41" t="e">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
       <c r="K144" s="41" t="e">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
       <c r="L144" s="41" t="e">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
       <c r="M144" s="41" t="e">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
       <c r="N144" s="41" t="e">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
       <c r="O144" s="41" t="e">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
       <c r="P144" s="41" t="e">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
       <c r="Q144" s="41" t="e">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
       <c r="R144" s="41" t="e">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
       <c r="S144" s="41" t="e">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
       <c r="T144" s="41" t="e">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
       <c r="U144" s="41" t="e">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
       <c r="V144" s="41" t="e">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
       <c r="W144" s="41" t="e">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
       <c r="X144" s="41" t="e">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
       <c r="Y144" s="41" t="e">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
       <c r="Z144" s="41" t="e">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
       <c r="AA144" s="41" t="e">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
       <c r="AB144" s="41" t="e">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
       <c r="AC144" s="41" t="e">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
       <c r="AD144" s="41" t="e">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
       <c r="AE144" s="41" t="e">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
       <c r="AF144" s="41" t="e">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
       <c r="AG144" s="41" t="e">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
       <c r="AH144" s="41" t="e">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
       <c r="AI144" s="41" t="e">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
       <c r="AJ144" s="41" t="e">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
       <c r="AK144" s="42" t="e">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="A2:A15"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="B4:B8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B10:B14"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="C4:C8"/>
-    <mergeCell ref="C10:C14"/>
+    <mergeCell ref="A16:A58"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="C62:C72"/>
+    <mergeCell ref="D71:D72"/>
+    <mergeCell ref="D24:D29"/>
+    <mergeCell ref="D42:D45"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="C42:C47"/>
     <mergeCell ref="A80:A81"/>
     <mergeCell ref="C16:C17"/>
     <mergeCell ref="D16:D17"/>
@@ -28616,19 +28793,16 @@
     <mergeCell ref="B37:B47"/>
     <mergeCell ref="B16:B31"/>
     <mergeCell ref="A59:A79"/>
-    <mergeCell ref="A16:A58"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="D34:D35"/>
-    <mergeCell ref="C62:C72"/>
-    <mergeCell ref="D71:D72"/>
-    <mergeCell ref="D24:D29"/>
-    <mergeCell ref="D42:D45"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="C42:C47"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="A2:A15"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="B4:B8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B10:B14"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="C4:C8"/>
+    <mergeCell ref="C10:C14"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ライフプラン_猪飼.xlsx
+++ b/ライフプラン_猪飼.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC_USER\Documents\LocalLifeplanRepo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6505266-3ED1-4098-95CE-DB6112BD47D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD020057-C120-4738-AC61-C472E1FB74AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{934FA03D-99BD-49E0-BFEC-291BD79F4879}"/>
   </bookViews>
@@ -134,7 +134,8 @@
           </rPr>
           <t>TV
 BDレコーダー
-スマホ</t>
+スマホ
+便座</t>
         </r>
       </text>
     </comment>
@@ -520,7 +521,7 @@
             <family val="3"/>
             <charset val="128"/>
           </rPr>
-          <t>本来メイン口座から支払うべき妻の健康保険料の24年度分が共通口座から引落しされてたので、25年度分を含めた全残金分をメイン口座から共通口座に前倒しで一括振込みする。</t>
+          <t>本来メイン口座から支払うべき妻の年金保険料の24年度分が共通口座から引落しされてたので、25年度分を含めた全残金分をメイン口座から共通口座に前倒しで一括振込みする。</t>
         </r>
       </text>
     </comment>
@@ -675,7 +676,7 @@
             <family val="3"/>
             <charset val="128"/>
           </rPr>
-          <t>国民健康保険料（妻）の残金を含む</t>
+          <t>国民年金保険料（妻）の残金を含む</t>
         </r>
       </text>
     </comment>
@@ -2528,31 +2529,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>*国民健康保険（妻）　24年度分（15万円）＋25年度分（9万円）</t>
-    <rPh sb="1" eb="3">
-      <t>コクミン</t>
-    </rPh>
-    <rPh sb="3" eb="7">
-      <t>ケンコウホケン</t>
-    </rPh>
-    <rPh sb="8" eb="9">
-      <t>ツマ</t>
-    </rPh>
-    <rPh sb="13" eb="16">
-      <t>ネンドブン</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>マンエン</t>
-    </rPh>
-    <rPh sb="25" eb="28">
-      <t>ネンドブン</t>
-    </rPh>
-    <rPh sb="30" eb="32">
-      <t>マンエン</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>（毎年４月定例前）</t>
     <rPh sb="1" eb="3">
       <t>マイトシ</t>
@@ -2620,6 +2596,34 @@
     </rPh>
     <rPh sb="29" eb="32">
       <t>カンソウキ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>*国民年金保険（妻）　24年度分（15万円）＋25年度分（9万円）</t>
+    <rPh sb="1" eb="3">
+      <t>コクミン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ネンキン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ホケン</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ツマ</t>
+    </rPh>
+    <rPh sb="13" eb="16">
+      <t>ネンドブン</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>マンエン</t>
+    </rPh>
+    <rPh sb="25" eb="28">
+      <t>ネンドブン</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>マンエン</t>
     </rPh>
     <phoneticPr fontId="3"/>
   </si>
@@ -4306,7 +4310,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="31"/>
                 <c:pt idx="0">
-                  <c:v>651</c:v>
+                  <c:v>661</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>551</c:v>
@@ -7759,88 +7763,88 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="31"/>
                 <c:pt idx="0">
-                  <c:v>399</c:v>
+                  <c:v>-23</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>412</c:v>
+                  <c:v>-10</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>425</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>438</c:v>
+                  <c:v>16</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>451</c:v>
+                  <c:v>29</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>464</c:v>
+                  <c:v>42</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>477</c:v>
+                  <c:v>55</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>490</c:v>
+                  <c:v>68</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>503</c:v>
+                  <c:v>81</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>516</c:v>
+                  <c:v>94</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>529</c:v>
+                  <c:v>107</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>542</c:v>
+                  <c:v>120</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>555</c:v>
+                  <c:v>133</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>568</c:v>
+                  <c:v>146</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>581</c:v>
+                  <c:v>159</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>594</c:v>
+                  <c:v>172</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>607</c:v>
+                  <c:v>185</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>620</c:v>
+                  <c:v>198</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>633</c:v>
+                  <c:v>211</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>646</c:v>
+                  <c:v>224</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>659</c:v>
+                  <c:v>237</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>672</c:v>
+                  <c:v>250</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>685</c:v>
+                  <c:v>263</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>698</c:v>
+                  <c:v>276</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>711</c:v>
+                  <c:v>289</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>724</c:v>
+                  <c:v>302</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>737</c:v>
+                  <c:v>315</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>750</c:v>
+                  <c:v>328</c:v>
                 </c:pt>
                 <c:pt idx="28">
                   <c:v>0</c:v>
@@ -11214,88 +11218,88 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="31"/>
                 <c:pt idx="0">
-                  <c:v>1050</c:v>
+                  <c:v>638</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>963</c:v>
+                  <c:v>541</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>774</c:v>
+                  <c:v>352</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>695</c:v>
+                  <c:v>273</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>688</c:v>
+                  <c:v>266</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>569</c:v>
+                  <c:v>147</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>580</c:v>
+                  <c:v>158</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>571</c:v>
+                  <c:v>149</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>562</c:v>
+                  <c:v>140</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>623</c:v>
+                  <c:v>201</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>334</c:v>
+                  <c:v>-88</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>345</c:v>
+                  <c:v>-77</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>276</c:v>
+                  <c:v>-146</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>227</c:v>
+                  <c:v>-195</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>79</c:v>
+                  <c:v>-343</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-59</c:v>
+                  <c:v>-481</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-63</c:v>
+                  <c:v>-485</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-87</c:v>
+                  <c:v>-509</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-91</c:v>
+                  <c:v>-513</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2205</c:v>
+                  <c:v>1783</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2054</c:v>
+                  <c:v>1632</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1903</c:v>
+                  <c:v>1481</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1732</c:v>
+                  <c:v>1310</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>1581</c:v>
+                  <c:v>1159</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>1430</c:v>
+                  <c:v>1008</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>1284</c:v>
+                  <c:v>862</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>1138</c:v>
+                  <c:v>716</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>772</c:v>
+                  <c:v>350</c:v>
                 </c:pt>
                 <c:pt idx="28">
                   <c:v>0</c:v>
@@ -17416,16 +17420,14 @@
         <v>21</v>
       </c>
       <c r="E12" s="16" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F12" s="23"/>
       <c r="G12" s="24">
-        <f>10</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H12" s="24">
-        <f>50+30+20</f>
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="I12" s="24">
         <f>50+50+10</f>
@@ -17590,11 +17592,11 @@
       </c>
       <c r="G15" s="20">
         <f>SUM(G10:G14)</f>
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="H15" s="20">
         <f t="shared" ref="H15:AK15" si="1">SUM(H10:H14)</f>
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="I15" s="20">
         <f t="shared" si="1"/>
@@ -19334,7 +19336,7 @@
         <v>112</v>
       </c>
       <c r="E37" s="86" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="F37" s="63"/>
       <c r="G37" s="86">
@@ -20643,7 +20645,7 @@
     <row r="55" spans="1:39">
       <c r="A55" s="138"/>
       <c r="B55" s="141" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C55" s="142"/>
       <c r="D55" s="78" t="s">
@@ -20657,11 +20659,11 @@
         <v>0</v>
       </c>
       <c r="G55" s="78">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="H55" s="78" cm="1">
         <f t="array" ref="H55:I55">H15:I15</f>
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="I55" s="78">
         <v>210</v>
@@ -20780,11 +20782,11 @@
       <c r="F56" s="35"/>
       <c r="G56" s="35">
         <f t="shared" ref="G56:AH56" si="5">SUM(G37:G55)</f>
-        <v>1394</v>
+        <v>1384</v>
       </c>
       <c r="H56" s="35">
         <f t="shared" si="5"/>
-        <v>1137</v>
+        <v>1147</v>
       </c>
       <c r="I56" s="35">
         <f t="shared" si="5"/>
@@ -20907,11 +20909,11 @@
       <c r="F57" s="35"/>
       <c r="G57" s="35">
         <f t="shared" ref="G57:AH57" si="6">G36-G56</f>
-        <v>-957</v>
+        <v>-947</v>
       </c>
       <c r="H57" s="35">
         <f t="shared" si="6"/>
-        <v>-100</v>
+        <v>-110</v>
       </c>
       <c r="I57" s="35">
         <f t="shared" si="6"/>
@@ -21036,7 +21038,7 @@
       </c>
       <c r="G58" s="44">
         <f>F58+G57</f>
-        <v>651</v>
+        <v>661</v>
       </c>
       <c r="H58" s="44">
         <f t="shared" ref="H58:AH58" si="7">G58+H57</f>
@@ -21170,11 +21172,11 @@
       </c>
       <c r="G59" s="86">
         <f>G54+G55+G37</f>
-        <v>834</v>
+        <v>824</v>
       </c>
       <c r="H59" s="82">
         <f t="shared" ref="H59:AH59" si="8">H54+H55</f>
-        <v>600</v>
+        <v>610</v>
       </c>
       <c r="I59" s="82">
         <f t="shared" si="8"/>
@@ -21295,16 +21297,15 @@
       <c r="D60" s="70"/>
       <c r="E60" s="71"/>
       <c r="F60" s="69">
-        <f t="shared" ref="F60:AH60" si="9">SUM(F59:F59)</f>
         <v>0</v>
       </c>
       <c r="G60" s="69">
-        <f t="shared" si="9"/>
-        <v>834</v>
+        <f t="shared" ref="F60:AH60" si="9">SUM(G59:G59)</f>
+        <v>824</v>
       </c>
       <c r="H60" s="69">
         <f t="shared" si="9"/>
-        <v>600</v>
+        <v>610</v>
       </c>
       <c r="I60" s="69">
         <f t="shared" si="9"/>
@@ -22868,11 +22869,11 @@
       </c>
       <c r="G75" s="38">
         <f t="shared" si="12"/>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H75" s="38">
         <f t="shared" si="12"/>
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="I75" s="38">
         <f t="shared" si="12"/>
@@ -23130,11 +23131,11 @@
       </c>
       <c r="G77" s="35">
         <f>SUM(G61:G76)</f>
-        <v>857</v>
+        <v>847</v>
       </c>
       <c r="H77" s="35">
         <f t="shared" ref="H77:AH77" si="14">SUM(H61:H76)</f>
-        <v>587</v>
+        <v>597</v>
       </c>
       <c r="I77" s="35">
         <f t="shared" si="14"/>
@@ -23255,11 +23256,10 @@
       <c r="D78" s="35"/>
       <c r="E78" s="40"/>
       <c r="F78" s="35">
-        <f t="shared" ref="F78:AH78" si="15">F60-F77</f>
         <v>0</v>
       </c>
       <c r="G78" s="35">
-        <f t="shared" si="15"/>
+        <f t="shared" ref="F78:AH78" si="15">G60-G77</f>
         <v>-23</v>
       </c>
       <c r="H78" s="35">
@@ -23384,120 +23384,121 @@
       <c r="C79" s="41"/>
       <c r="D79" s="41"/>
       <c r="E79" s="42"/>
-      <c r="F79" s="43">
-        <v>422</v>
+      <c r="F79" s="41">
+        <f>E79+F78</f>
+        <v>0</v>
       </c>
       <c r="G79" s="41">
         <f>F79+G78</f>
-        <v>399</v>
+        <v>-23</v>
       </c>
       <c r="H79" s="41">
         <f t="shared" ref="H79:AH79" si="16">G79+H78</f>
-        <v>412</v>
+        <v>-10</v>
       </c>
       <c r="I79" s="41">
         <f t="shared" si="16"/>
-        <v>425</v>
+        <v>3</v>
       </c>
       <c r="J79" s="41">
         <f t="shared" si="16"/>
-        <v>438</v>
+        <v>16</v>
       </c>
       <c r="K79" s="41">
         <f t="shared" si="16"/>
-        <v>451</v>
+        <v>29</v>
       </c>
       <c r="L79" s="41">
         <f t="shared" si="16"/>
-        <v>464</v>
+        <v>42</v>
       </c>
       <c r="M79" s="41">
         <f t="shared" si="16"/>
-        <v>477</v>
+        <v>55</v>
       </c>
       <c r="N79" s="41">
         <f t="shared" si="16"/>
-        <v>490</v>
+        <v>68</v>
       </c>
       <c r="O79" s="41">
         <f t="shared" si="16"/>
-        <v>503</v>
+        <v>81</v>
       </c>
       <c r="P79" s="41">
         <f t="shared" si="16"/>
-        <v>516</v>
+        <v>94</v>
       </c>
       <c r="Q79" s="41">
         <f t="shared" si="16"/>
-        <v>529</v>
+        <v>107</v>
       </c>
       <c r="R79" s="41">
         <f t="shared" si="16"/>
-        <v>542</v>
+        <v>120</v>
       </c>
       <c r="S79" s="41">
         <f t="shared" si="16"/>
-        <v>555</v>
+        <v>133</v>
       </c>
       <c r="T79" s="41">
         <f t="shared" si="16"/>
-        <v>568</v>
+        <v>146</v>
       </c>
       <c r="U79" s="41">
         <f t="shared" si="16"/>
-        <v>581</v>
+        <v>159</v>
       </c>
       <c r="V79" s="41">
         <f t="shared" si="16"/>
-        <v>594</v>
+        <v>172</v>
       </c>
       <c r="W79" s="41">
         <f t="shared" si="16"/>
-        <v>607</v>
+        <v>185</v>
       </c>
       <c r="X79" s="41">
         <f t="shared" si="16"/>
-        <v>620</v>
+        <v>198</v>
       </c>
       <c r="Y79" s="41">
         <f t="shared" si="16"/>
-        <v>633</v>
+        <v>211</v>
       </c>
       <c r="Z79" s="41">
         <f t="shared" si="16"/>
-        <v>646</v>
+        <v>224</v>
       </c>
       <c r="AA79" s="41">
         <f t="shared" si="16"/>
-        <v>659</v>
+        <v>237</v>
       </c>
       <c r="AB79" s="41">
         <f t="shared" si="16"/>
-        <v>672</v>
+        <v>250</v>
       </c>
       <c r="AC79" s="41">
         <f t="shared" si="16"/>
-        <v>685</v>
+        <v>263</v>
       </c>
       <c r="AD79" s="41">
         <f t="shared" si="16"/>
-        <v>698</v>
+        <v>276</v>
       </c>
       <c r="AE79" s="41">
         <f t="shared" si="16"/>
-        <v>711</v>
+        <v>289</v>
       </c>
       <c r="AF79" s="41">
         <f t="shared" si="16"/>
-        <v>724</v>
+        <v>302</v>
       </c>
       <c r="AG79" s="41">
         <f t="shared" si="16"/>
-        <v>737</v>
+        <v>315</v>
       </c>
       <c r="AH79" s="41">
         <f t="shared" si="16"/>
-        <v>750</v>
+        <v>328</v>
       </c>
       <c r="AI79" s="41"/>
       <c r="AJ79" s="41"/>
@@ -23521,11 +23522,11 @@
       </c>
       <c r="G80" s="47">
         <f t="shared" si="17"/>
-        <v>-980</v>
+        <v>-970</v>
       </c>
       <c r="H80" s="47">
         <f t="shared" si="17"/>
-        <v>-87</v>
+        <v>-97</v>
       </c>
       <c r="I80" s="47">
         <f t="shared" si="17"/>
@@ -23647,119 +23648,119 @@
       <c r="E81" s="49"/>
       <c r="F81" s="41">
         <f t="shared" ref="F81:AH81" si="18">F58+F79</f>
-        <v>2030</v>
+        <v>1608</v>
       </c>
       <c r="G81" s="41">
         <f t="shared" si="18"/>
-        <v>1050</v>
+        <v>638</v>
       </c>
       <c r="H81" s="41">
         <f t="shared" si="18"/>
-        <v>963</v>
+        <v>541</v>
       </c>
       <c r="I81" s="41">
         <f t="shared" si="18"/>
-        <v>774</v>
+        <v>352</v>
       </c>
       <c r="J81" s="41">
         <f t="shared" si="18"/>
-        <v>695</v>
+        <v>273</v>
       </c>
       <c r="K81" s="41">
         <f t="shared" si="18"/>
-        <v>688</v>
+        <v>266</v>
       </c>
       <c r="L81" s="41">
         <f t="shared" si="18"/>
-        <v>569</v>
+        <v>147</v>
       </c>
       <c r="M81" s="41">
         <f t="shared" si="18"/>
-        <v>580</v>
+        <v>158</v>
       </c>
       <c r="N81" s="41">
         <f t="shared" si="18"/>
-        <v>571</v>
+        <v>149</v>
       </c>
       <c r="O81" s="41">
         <f t="shared" si="18"/>
-        <v>562</v>
+        <v>140</v>
       </c>
       <c r="P81" s="41">
         <f t="shared" si="18"/>
-        <v>623</v>
+        <v>201</v>
       </c>
       <c r="Q81" s="41">
         <f t="shared" si="18"/>
-        <v>334</v>
+        <v>-88</v>
       </c>
       <c r="R81" s="41">
         <f t="shared" si="18"/>
-        <v>345</v>
+        <v>-77</v>
       </c>
       <c r="S81" s="41">
         <f t="shared" si="18"/>
-        <v>276</v>
+        <v>-146</v>
       </c>
       <c r="T81" s="41">
         <f t="shared" si="18"/>
-        <v>227</v>
+        <v>-195</v>
       </c>
       <c r="U81" s="41">
         <f t="shared" si="18"/>
-        <v>79</v>
+        <v>-343</v>
       </c>
       <c r="V81" s="41">
         <f t="shared" si="18"/>
-        <v>-59</v>
+        <v>-481</v>
       </c>
       <c r="W81" s="41">
         <f t="shared" si="18"/>
-        <v>-63</v>
+        <v>-485</v>
       </c>
       <c r="X81" s="41">
         <f t="shared" si="18"/>
-        <v>-87</v>
+        <v>-509</v>
       </c>
       <c r="Y81" s="41">
         <f t="shared" si="18"/>
-        <v>-91</v>
+        <v>-513</v>
       </c>
       <c r="Z81" s="41">
         <f t="shared" si="18"/>
-        <v>2205</v>
+        <v>1783</v>
       </c>
       <c r="AA81" s="41">
         <f t="shared" si="18"/>
-        <v>2054</v>
+        <v>1632</v>
       </c>
       <c r="AB81" s="41">
         <f t="shared" si="18"/>
-        <v>1903</v>
+        <v>1481</v>
       </c>
       <c r="AC81" s="41">
         <f t="shared" si="18"/>
-        <v>1732</v>
+        <v>1310</v>
       </c>
       <c r="AD81" s="41">
         <f t="shared" si="18"/>
-        <v>1581</v>
+        <v>1159</v>
       </c>
       <c r="AE81" s="41">
         <f t="shared" si="18"/>
-        <v>1430</v>
+        <v>1008</v>
       </c>
       <c r="AF81" s="41">
         <f t="shared" si="18"/>
-        <v>1284</v>
+        <v>862</v>
       </c>
       <c r="AG81" s="41">
         <f t="shared" si="18"/>
-        <v>1138</v>
+        <v>716</v>
       </c>
       <c r="AH81" s="41">
         <f t="shared" si="18"/>
-        <v>772</v>
+        <v>350</v>
       </c>
       <c r="AI81" s="41"/>
       <c r="AJ81" s="41"/>
@@ -23810,7 +23811,7 @@
     </row>
     <row r="88" spans="1:38" ht="24">
       <c r="F88" s="54" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="89" spans="1:38" ht="19.5" thickBot="1"/>
@@ -25497,115 +25498,115 @@
       </c>
       <c r="G103" s="96">
         <f t="shared" ref="G103:AK103" si="32">G81</f>
-        <v>1050</v>
+        <v>638</v>
       </c>
       <c r="H103" s="35">
         <f t="shared" si="32"/>
-        <v>963</v>
+        <v>541</v>
       </c>
       <c r="I103" s="35">
         <f t="shared" si="32"/>
-        <v>774</v>
+        <v>352</v>
       </c>
       <c r="J103" s="35">
         <f t="shared" si="32"/>
-        <v>695</v>
+        <v>273</v>
       </c>
       <c r="K103" s="35">
         <f t="shared" si="32"/>
-        <v>688</v>
+        <v>266</v>
       </c>
       <c r="L103" s="35">
         <f t="shared" si="32"/>
-        <v>569</v>
+        <v>147</v>
       </c>
       <c r="M103" s="35">
         <f t="shared" si="32"/>
-        <v>580</v>
+        <v>158</v>
       </c>
       <c r="N103" s="35">
         <f t="shared" si="32"/>
-        <v>571</v>
+        <v>149</v>
       </c>
       <c r="O103" s="35">
         <f t="shared" si="32"/>
-        <v>562</v>
+        <v>140</v>
       </c>
       <c r="P103" s="35">
         <f t="shared" si="32"/>
-        <v>623</v>
+        <v>201</v>
       </c>
       <c r="Q103" s="35">
         <f t="shared" si="32"/>
-        <v>334</v>
+        <v>-88</v>
       </c>
       <c r="R103" s="35">
         <f t="shared" si="32"/>
-        <v>345</v>
+        <v>-77</v>
       </c>
       <c r="S103" s="35">
         <f t="shared" si="32"/>
-        <v>276</v>
+        <v>-146</v>
       </c>
       <c r="T103" s="35">
         <f t="shared" si="32"/>
-        <v>227</v>
+        <v>-195</v>
       </c>
       <c r="U103" s="35">
         <f t="shared" si="32"/>
-        <v>79</v>
+        <v>-343</v>
       </c>
       <c r="V103" s="35">
         <f t="shared" si="32"/>
-        <v>-59</v>
+        <v>-481</v>
       </c>
       <c r="W103" s="35">
         <f t="shared" si="32"/>
-        <v>-63</v>
+        <v>-485</v>
       </c>
       <c r="X103" s="35">
         <f t="shared" si="32"/>
-        <v>-87</v>
+        <v>-509</v>
       </c>
       <c r="Y103" s="35">
         <f t="shared" si="32"/>
-        <v>-91</v>
+        <v>-513</v>
       </c>
       <c r="Z103" s="35">
         <f t="shared" si="32"/>
-        <v>2205</v>
+        <v>1783</v>
       </c>
       <c r="AA103" s="35">
         <f t="shared" si="32"/>
-        <v>2054</v>
+        <v>1632</v>
       </c>
       <c r="AB103" s="35">
         <f t="shared" si="32"/>
-        <v>1903</v>
+        <v>1481</v>
       </c>
       <c r="AC103" s="35">
         <f t="shared" si="32"/>
-        <v>1732</v>
+        <v>1310</v>
       </c>
       <c r="AD103" s="35">
         <f t="shared" si="32"/>
-        <v>1581</v>
+        <v>1159</v>
       </c>
       <c r="AE103" s="35">
         <f t="shared" si="32"/>
-        <v>1430</v>
+        <v>1008</v>
       </c>
       <c r="AF103" s="35">
         <f t="shared" si="32"/>
-        <v>1284</v>
+        <v>862</v>
       </c>
       <c r="AG103" s="35">
         <f t="shared" si="32"/>
-        <v>1138</v>
+        <v>716</v>
       </c>
       <c r="AH103" s="35">
         <f t="shared" si="32"/>
-        <v>772</v>
+        <v>350</v>
       </c>
       <c r="AI103" s="35">
         <f t="shared" si="32"/>
@@ -25686,7 +25687,7 @@
     <row r="107" spans="5:37"/>
     <row r="108" spans="5:37" ht="24">
       <c r="F108" s="54" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="109" spans="5:37" ht="19.5" thickBot="1"/>
@@ -26969,7 +26970,7 @@
       </c>
       <c r="G123" s="46">
         <f t="shared" ref="G123:AK123" si="34">G58</f>
-        <v>651</v>
+        <v>661</v>
       </c>
       <c r="H123" s="47">
         <f t="shared" si="34"/>
@@ -27224,7 +27225,7 @@
     <row r="126" spans="6:37"/>
     <row r="128" spans="6:37" ht="24">
       <c r="F128" s="54" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="129" spans="5:37" ht="19.5" thickBot="1"/>
@@ -28510,115 +28511,115 @@
       </c>
       <c r="G143" s="46">
         <f t="shared" ref="G143:AK143" si="36">G79</f>
-        <v>399</v>
+        <v>-23</v>
       </c>
       <c r="H143" s="47">
         <f>H79</f>
-        <v>412</v>
+        <v>-10</v>
       </c>
       <c r="I143" s="47">
         <f t="shared" si="36"/>
-        <v>425</v>
+        <v>3</v>
       </c>
       <c r="J143" s="47">
         <f t="shared" si="36"/>
-        <v>438</v>
+        <v>16</v>
       </c>
       <c r="K143" s="47">
         <f t="shared" si="36"/>
-        <v>451</v>
+        <v>29</v>
       </c>
       <c r="L143" s="47">
         <f t="shared" si="36"/>
-        <v>464</v>
+        <v>42</v>
       </c>
       <c r="M143" s="47">
         <f t="shared" si="36"/>
-        <v>477</v>
+        <v>55</v>
       </c>
       <c r="N143" s="47">
         <f t="shared" si="36"/>
-        <v>490</v>
+        <v>68</v>
       </c>
       <c r="O143" s="47">
         <f t="shared" si="36"/>
-        <v>503</v>
+        <v>81</v>
       </c>
       <c r="P143" s="47">
         <f t="shared" si="36"/>
-        <v>516</v>
+        <v>94</v>
       </c>
       <c r="Q143" s="47">
         <f t="shared" si="36"/>
-        <v>529</v>
+        <v>107</v>
       </c>
       <c r="R143" s="47">
         <f t="shared" si="36"/>
-        <v>542</v>
+        <v>120</v>
       </c>
       <c r="S143" s="47">
         <f t="shared" si="36"/>
-        <v>555</v>
+        <v>133</v>
       </c>
       <c r="T143" s="47">
         <f t="shared" si="36"/>
-        <v>568</v>
+        <v>146</v>
       </c>
       <c r="U143" s="47">
         <f t="shared" si="36"/>
-        <v>581</v>
+        <v>159</v>
       </c>
       <c r="V143" s="47">
         <f t="shared" si="36"/>
-        <v>594</v>
+        <v>172</v>
       </c>
       <c r="W143" s="47">
         <f t="shared" si="36"/>
-        <v>607</v>
+        <v>185</v>
       </c>
       <c r="X143" s="47">
         <f t="shared" si="36"/>
-        <v>620</v>
+        <v>198</v>
       </c>
       <c r="Y143" s="47">
         <f t="shared" si="36"/>
-        <v>633</v>
+        <v>211</v>
       </c>
       <c r="Z143" s="47">
         <f t="shared" si="36"/>
-        <v>646</v>
+        <v>224</v>
       </c>
       <c r="AA143" s="47">
         <f t="shared" si="36"/>
-        <v>659</v>
+        <v>237</v>
       </c>
       <c r="AB143" s="47">
         <f t="shared" si="36"/>
-        <v>672</v>
+        <v>250</v>
       </c>
       <c r="AC143" s="47">
         <f t="shared" si="36"/>
-        <v>685</v>
+        <v>263</v>
       </c>
       <c r="AD143" s="47">
         <f t="shared" si="36"/>
-        <v>698</v>
+        <v>276</v>
       </c>
       <c r="AE143" s="47">
         <f t="shared" si="36"/>
-        <v>711</v>
+        <v>289</v>
       </c>
       <c r="AF143" s="47">
         <f t="shared" si="36"/>
-        <v>724</v>
+        <v>302</v>
       </c>
       <c r="AG143" s="47">
         <f t="shared" si="36"/>
-        <v>737</v>
+        <v>315</v>
       </c>
       <c r="AH143" s="47">
         <f t="shared" si="36"/>
-        <v>750</v>
+        <v>328</v>
       </c>
       <c r="AI143" s="47">
         <f t="shared" si="36"/>

--- a/ライフプラン_猪飼.xlsx
+++ b/ライフプラン_猪飼.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC_USER\Documents\LocalLifeplanRepo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD020057-C120-4738-AC61-C472E1FB74AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C402420C-5A87-41EF-A48B-3351A5A0D2F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{934FA03D-99BD-49E0-BFEC-291BD79F4879}"/>
   </bookViews>
@@ -107,19 +107,7 @@
       </text>
     </comment>
     <comment ref="G12" authorId="1" shapeId="0" xr:uid="{A75EC272-0EA6-45F5-A5BD-BD752B3901E3}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="MS P ゴシック"/>
-            <family val="3"/>
-            <charset val="128"/>
-          </rPr>
-          <t>便座</t>
-        </r>
-      </text>
+      <text/>
     </comment>
     <comment ref="H12" authorId="1" shapeId="0" xr:uid="{B9A45C49-D949-4109-B5F8-D413C4BCB125}">
       <text>
@@ -877,6 +865,26 @@
         </r>
       </text>
     </comment>
+    <comment ref="G116" authorId="0" shapeId="0" xr:uid="{B56A3F48-96A8-4986-A566-5802F97A6C98}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="MS P ゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>kaz
+ 東北電力配当金  + 1
+ 全労済東１      + 4
+ ﾌﾟﾙﾃﾞﾝｼｬﾙ保険金 + 9
+ 普通預金利息　　+ 1
+nao</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="F126" authorId="0" shapeId="0" xr:uid="{9D0EDA07-5D89-456F-A52C-3AAD29C57E72}">
       <text>
         <r>
@@ -1009,6 +1017,22 @@
           </rPr>
           <t>kazへ返済 -7 (墓参：1、飯山出雲&amp;鮎：1.2、実家修理：1.6，ﾋﾞｭｰ：1。衣笠浜寿司：1.2、他：1)
 naoへ返済 -2.5（飯山出雲；2，森永：0.2， 町内祭:0.3）</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G136" authorId="0" shapeId="0" xr:uid="{BF817CDE-6E07-46B8-AC4D-02248735669C}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="MS P ゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>kazへ返済 -6.5 (南川商品券：1、医療費：2、ﾋﾞｭｰ：1、食代など：2.5)
+naoへ返済 -9（ﾀﾞﾝｽ：6.4，南川商品券：1、新潟SUICA費：1.6）</t>
         </r>
       </text>
     </comment>
@@ -6500,7 +6524,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="31"/>
                 <c:pt idx="0">
-                  <c:v>#N/A</c:v>
+                  <c:v>1118</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>#N/A</c:v>
@@ -9952,7 +9976,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="31"/>
                 <c:pt idx="0">
-                  <c:v>#N/A</c:v>
+                  <c:v>630</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>#N/A</c:v>
@@ -13403,7 +13427,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="31"/>
                 <c:pt idx="0">
-                  <c:v>#N/A</c:v>
+                  <c:v>1748</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>#N/A</c:v>
@@ -21300,7 +21324,7 @@
         <v>0</v>
       </c>
       <c r="G60" s="69">
-        <f t="shared" ref="F60:AH60" si="9">SUM(G59:G59)</f>
+        <f t="shared" ref="G60:AH60" si="9">SUM(G59:G59)</f>
         <v>824</v>
       </c>
       <c r="H60" s="69">
@@ -23259,7 +23283,7 @@
         <v>0</v>
       </c>
       <c r="G78" s="35">
-        <f t="shared" ref="F78:AH78" si="15">G60-G77</f>
+        <f t="shared" ref="G78:AH78" si="15">G60-G77</f>
         <v>-23</v>
       </c>
       <c r="H78" s="35">
@@ -24593,9 +24617,9 @@
       <c r="F96" s="55" t="s">
         <v>101</v>
       </c>
-      <c r="G96" s="56" t="e">
+      <c r="G96" s="56">
         <f t="shared" ref="G96:AK96" si="25">G116+G136</f>
-        <v>#N/A</v>
+        <v>1748</v>
       </c>
       <c r="H96" s="57" t="e">
         <f t="shared" si="25"/>
@@ -26282,8 +26306,8 @@
       <c r="F116" s="55" t="s">
         <v>101</v>
       </c>
-      <c r="G116" s="56" t="e">
-        <v>#N/A</v>
+      <c r="G116" s="56">
+        <v>1118</v>
       </c>
       <c r="H116" s="57" t="e">
         <v>#N/A</v>
@@ -27823,8 +27847,8 @@
       <c r="F136" s="55" t="s">
         <v>101</v>
       </c>
-      <c r="G136" s="56" t="e">
-        <v>#N/A</v>
+      <c r="G136" s="56">
+        <v>630</v>
       </c>
       <c r="H136" s="57" t="e">
         <v>#N/A</v>
@@ -28647,7 +28671,7 @@
         <v>#N/A</v>
       </c>
       <c r="I144" s="41" t="e">
-        <f t="shared" ref="H144:AK144" si="37">I143-I139</f>
+        <f t="shared" ref="I144:AK144" si="37">I143-I139</f>
         <v>#N/A</v>
       </c>
       <c r="J144" s="41" t="e">
@@ -28807,7 +28831,8 @@
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
--- a/ライフプラン_猪飼.xlsx
+++ b/ライフプラン_猪飼.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC_USER\Documents\LocalLifeplanRepo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C402420C-5A87-41EF-A48B-3351A5A0D2F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31FB8774-5E3A-47BD-9734-AAA0F419503E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{934FA03D-99BD-49E0-BFEC-291BD79F4879}"/>
   </bookViews>
@@ -720,9 +720,6 @@
         </r>
       </text>
     </comment>
-    <comment ref="G107" authorId="0" shapeId="0" xr:uid="{38567A5A-08F1-44CE-8C1B-7B9A61C0360A}">
-      <text/>
-    </comment>
     <comment ref="E108" authorId="0" shapeId="0" xr:uid="{0CFE7B6C-FEBF-4C82-A58B-E327835A20D7}">
       <text>
         <r>
@@ -885,7 +882,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F126" authorId="0" shapeId="0" xr:uid="{9D0EDA07-5D89-456F-A52C-3AAD29C57E72}">
+    <comment ref="G117" authorId="0" shapeId="0" xr:uid="{C5ACF506-080C-44E3-A0DC-FC576421F2C7}">
       <text>
         <r>
           <rPr>
@@ -896,18 +893,12 @@
             <family val="3"/>
             <charset val="128"/>
           </rPr>
-          <t>PC_USER:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="MS P ゴシック"/>
-            <family val="3"/>
-            <charset val="128"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
+          <t>kaz
+ 国民厚生年金　　+45
+ パナ年金　　　  +12
+ 全労済個人年金  + 4　
+ ﾌﾟﾙﾃﾞﾝｼｬﾙ保険金 + 9
+nao</t>
         </r>
       </text>
     </comment>
@@ -1033,6 +1024,22 @@
           </rPr>
           <t>kazへ返済 -6.5 (南川商品券：1、医療費：2、ﾋﾞｭｰ：1、食代など：2.5)
 naoへ返済 -9（ﾀﾞﾝｽ：6.4，南川商品券：1、新潟SUICA費：1.6）</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G137" authorId="0" shapeId="0" xr:uid="{D280A25F-E67D-4378-AAC4-DFA1C1795F46}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="MS P ゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>kazへ返済 -1.7 (医療費：1、ビューカード：0.3、瀬戸神社:0.2，他：0.2+商品券払)
+naoへ返済 -0.4（医療費：0.7、交通費：0.4、香典：0.5、森永：0.3、ｻﾝﾘｵ：-1、食品：-0.5）</t>
         </r>
       </text>
     </comment>
@@ -6771,7 +6778,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="31"/>
                 <c:pt idx="0">
-                  <c:v>#N/A</c:v>
+                  <c:v>1173</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>#N/A</c:v>
@@ -10223,7 +10230,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="31"/>
                 <c:pt idx="0">
-                  <c:v>#N/A</c:v>
+                  <c:v>615</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>#N/A</c:v>
@@ -13674,7 +13681,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="31"/>
                 <c:pt idx="0">
-                  <c:v>#N/A</c:v>
+                  <c:v>1788</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>#N/A</c:v>
@@ -24746,9 +24753,9 @@
       <c r="F97" s="55" t="s">
         <v>102</v>
       </c>
-      <c r="G97" s="56" t="e">
+      <c r="G97" s="56">
         <f t="shared" ref="G97:AK97" si="26">G117+G137</f>
-        <v>#N/A</v>
+        <v>1788</v>
       </c>
       <c r="H97" s="57" t="e">
         <f t="shared" si="26"/>
@@ -25708,7 +25715,6 @@
       <c r="AJ104" s="41"/>
       <c r="AK104" s="42"/>
     </row>
-    <row r="107" spans="5:37"/>
     <row r="108" spans="5:37" ht="24">
       <c r="F108" s="54" t="s">
         <v>149</v>
@@ -26404,8 +26410,8 @@
       <c r="F117" s="55" t="s">
         <v>102</v>
       </c>
-      <c r="G117" s="56" t="e">
-        <v>#N/A</v>
+      <c r="G117" s="56">
+        <v>1173</v>
       </c>
       <c r="H117" s="57" t="e">
         <v>#N/A</v>
@@ -27246,7 +27252,6 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="126" spans="6:37"/>
     <row r="128" spans="6:37" ht="24">
       <c r="F128" s="54" t="s">
         <v>150</v>
@@ -27945,8 +27950,8 @@
       <c r="F137" s="55" t="s">
         <v>102</v>
       </c>
-      <c r="G137" s="56" t="e">
-        <v>#N/A</v>
+      <c r="G137" s="56">
+        <v>615</v>
       </c>
       <c r="H137" s="57" t="e">
         <v>#N/A</v>

--- a/ライフプラン_猪飼.xlsx
+++ b/ライフプラン_猪飼.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC_USER\Documents\LocalLifeplanRepo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31FB8774-5E3A-47BD-9734-AAA0F419503E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7299378F-9257-4D03-8472-0FF0E528A6EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{934FA03D-99BD-49E0-BFEC-291BD79F4879}"/>
+    <workbookView xWindow="3660" yWindow="165" windowWidth="23250" windowHeight="15210" xr2:uid="{934FA03D-99BD-49E0-BFEC-291BD79F4879}"/>
   </bookViews>
   <sheets>
     <sheet name="マネーフロー" sheetId="1" r:id="rId1"/>
@@ -10230,7 +10230,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="31"/>
                 <c:pt idx="0">
-                  <c:v>615</c:v>
+                  <c:v>613</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>#N/A</c:v>
@@ -13681,7 +13681,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="31"/>
                 <c:pt idx="0">
-                  <c:v>1788</c:v>
+                  <c:v>1786</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>#N/A</c:v>
@@ -16105,23 +16105,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>595312</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>119062</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>228599</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>31</xdr:col>
-      <xdr:colOff>428624</xdr:colOff>
-      <xdr:row>66</xdr:row>
-      <xdr:rowOff>166687</xdr:rowOff>
+      <xdr:col>67</xdr:col>
+      <xdr:colOff>110066</xdr:colOff>
+      <xdr:row>129</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="図 4">
+        <xdr:cNvPr id="8" name="図 7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E25C464C-544B-8607-5624-1FE66E8AAC8D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C389235D-6822-0844-2C17-72ED2EB6B4BF}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -16144,8 +16144,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="595312" y="1071562"/>
-          <a:ext cx="21240750" cy="14811375"/>
+          <a:off x="2285999" y="876300"/>
+          <a:ext cx="43772667" cy="28651200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -24755,7 +24755,7 @@
       </c>
       <c r="G97" s="56">
         <f t="shared" ref="G97:AK97" si="26">G117+G137</f>
-        <v>1788</v>
+        <v>1786</v>
       </c>
       <c r="H97" s="57" t="e">
         <f t="shared" si="26"/>
@@ -27951,7 +27951,7 @@
         <v>102</v>
       </c>
       <c r="G137" s="56">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="H137" s="57" t="e">
         <v>#N/A</v>

--- a/ライフプラン_猪飼.xlsx
+++ b/ライフプラン_猪飼.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC_USER\Documents\LocalLifeplanRepo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37367209-6DE7-4C4E-8878-C791321453B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBBFC497-F893-41DE-B7CA-98CB68B610B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{934FA03D-99BD-49E0-BFEC-291BD79F4879}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{934FA03D-99BD-49E0-BFEC-291BD79F4879}"/>
   </bookViews>
   <sheets>
     <sheet name="マネーフロー" sheetId="1" r:id="rId1"/>
@@ -185,6 +185,7 @@
 WiFiﾙｰﾀｰ     ｜ 1        ｜ﾊﾞｯﾌｧﾛｰ WSR-3000AX4P  ｜4LDKﾏﾝｼｮﾝ向け，Wi-Fi6
 便座         ｜10        ｜ﾋﾞｭｰﾃｨ･ﾄﾜﾚ AWM600     ｜ｽﾃﾝﾚｽﾉｽﾞﾙ，ﾊﾈ抑制
 冷蔵庫       ｜15         ｜ｼｬｰﾌﾟSJ-PW37P-H       ｜ｽﾘﾑﾀｲﾌﾟ，2暮らし向けの374L，節電ﾓｰﾄﾞ
+電子レンジ　  | 5         | ｼﾛｶ SX-2001S1         | ｵﾌﾞﾝﾚﾝｼﾞ，20L，900W，湿度&amp;温度ｾﾝｻｰ
 洗濯機       ｜10         ｜AQUA AQW-VX10A-W      ｜洗濯容量8kg，縦型，自動槽洗浄機能
 乾燥機       ｜10         ｜TOSHIBA ED-60A4       ｜乾燥容量6kg，洗濯機の上に設置可
 ﾄﾞﾗﾑ式洗乾機 ｜32         ｜ｼｬｰﾌﾟ ES-12X1-WL      ｜洗濯12kg，乾燥6kg
@@ -196,7 +197,20 @@
       </text>
     </comment>
     <comment ref="G12" authorId="1" shapeId="0" xr:uid="{A75EC272-0EA6-45F5-A5BD-BD752B3901E3}">
-      <text/>
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="游ゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>電子ﾚﾝｼﾞ: 5</t>
+        </r>
+      </text>
     </comment>
     <comment ref="H12" authorId="1" shapeId="0" xr:uid="{B9A45C49-D949-4109-B5F8-D413C4BCB125}">
       <text>
@@ -2820,7 +2834,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2904,6 +2918,15 @@
       <name val="MS P ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="10">
@@ -4103,121 +4126,6 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" textRotation="255"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="42" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="45" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="23" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="36" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="24" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="35" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="46" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" textRotation="255"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" textRotation="255"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -4227,6 +4135,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" textRotation="255"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" textRotation="255"/>
@@ -4280,6 +4192,117 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" textRotation="255"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="42" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="23" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" textRotation="255"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="45" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="36" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="24" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="35" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="46" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4530,88 +4553,88 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="31"/>
                 <c:pt idx="0">
-                  <c:v>661</c:v>
+                  <c:v>656</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>600</c:v>
+                  <c:v>595</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>503</c:v>
+                  <c:v>498</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>416</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>421</c:v>
                 </c:pt>
-                <c:pt idx="4">
-                  <c:v>426</c:v>
-                </c:pt>
                 <c:pt idx="5">
-                  <c:v>294</c:v>
+                  <c:v>289</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>312</c:v>
+                  <c:v>307</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>310</c:v>
+                  <c:v>305</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>308</c:v>
+                  <c:v>303</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>626</c:v>
+                  <c:v>621</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>344</c:v>
+                  <c:v>339</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>362</c:v>
+                  <c:v>357</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>300</c:v>
+                  <c:v>295</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>258</c:v>
+                  <c:v>253</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>117</c:v>
+                  <c:v>112</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-14</c:v>
+                  <c:v>-19</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-31</c:v>
+                  <c:v>-36</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-68</c:v>
+                  <c:v>-73</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-85</c:v>
+                  <c:v>-90</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2198</c:v>
+                  <c:v>2193</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2034</c:v>
+                  <c:v>2029</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1870</c:v>
+                  <c:v>1865</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1686</c:v>
+                  <c:v>1681</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>1522</c:v>
+                  <c:v>1517</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>1358</c:v>
+                  <c:v>1353</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>1199</c:v>
+                  <c:v>1194</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>1040</c:v>
+                  <c:v>1035</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>661</c:v>
+                  <c:v>656</c:v>
                 </c:pt>
                 <c:pt idx="28">
                   <c:v>0</c:v>
@@ -11441,88 +11464,88 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="31"/>
                 <c:pt idx="0">
-                  <c:v>638</c:v>
+                  <c:v>633</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>590</c:v>
+                  <c:v>585</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>506</c:v>
+                  <c:v>501</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>437</c:v>
+                  <c:v>432</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>455</c:v>
+                  <c:v>450</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>336</c:v>
+                  <c:v>331</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>367</c:v>
+                  <c:v>362</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>378</c:v>
+                  <c:v>373</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>389</c:v>
+                  <c:v>384</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>720</c:v>
+                  <c:v>715</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>451</c:v>
+                  <c:v>446</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>482</c:v>
+                  <c:v>477</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>433</c:v>
+                  <c:v>428</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>404</c:v>
+                  <c:v>399</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>276</c:v>
+                  <c:v>271</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>158</c:v>
+                  <c:v>153</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>154</c:v>
+                  <c:v>149</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>130</c:v>
+                  <c:v>125</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>126</c:v>
+                  <c:v>121</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2422</c:v>
+                  <c:v>2417</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2271</c:v>
+                  <c:v>2266</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>2120</c:v>
+                  <c:v>2115</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1949</c:v>
+                  <c:v>1944</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>1798</c:v>
+                  <c:v>1793</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>1647</c:v>
+                  <c:v>1642</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>1501</c:v>
+                  <c:v>1496</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>1355</c:v>
+                  <c:v>1350</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>989</c:v>
+                  <c:v>984</c:v>
                 </c:pt>
                 <c:pt idx="28">
                   <c:v>0</c:v>
@@ -16997,12 +17020,12 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="134" t="s">
+      <c r="B1" s="102" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="135"/>
-      <c r="D1" s="135"/>
-      <c r="E1" s="136"/>
+      <c r="C1" s="103"/>
+      <c r="D1" s="103"/>
+      <c r="E1" s="104"/>
       <c r="F1" s="2" t="s">
         <v>2</v>
       </c>
@@ -17103,13 +17126,13 @@
       <c r="AM1" s="4"/>
     </row>
     <row r="2" spans="1:39" ht="18.75" customHeight="1">
-      <c r="A2" s="102" t="s">
+      <c r="A2" s="105" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="139" t="s">
+      <c r="B2" s="108" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="146"/>
+      <c r="C2" s="115"/>
       <c r="D2" s="6" t="s">
         <v>5</v>
       </c>
@@ -17194,9 +17217,9 @@
       <c r="AM2" s="4"/>
     </row>
     <row r="3" spans="1:39" ht="19.5" thickBot="1">
-      <c r="A3" s="137"/>
-      <c r="B3" s="140"/>
-      <c r="C3" s="147"/>
+      <c r="A3" s="106"/>
+      <c r="B3" s="109"/>
+      <c r="C3" s="116"/>
       <c r="D3" s="9" t="s">
         <v>7</v>
       </c>
@@ -17297,11 +17320,11 @@
       <c r="AM3" s="4"/>
     </row>
     <row r="4" spans="1:39">
-      <c r="A4" s="137"/>
-      <c r="B4" s="139" t="s">
+      <c r="A4" s="106"/>
+      <c r="B4" s="108" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="148"/>
+      <c r="C4" s="117"/>
       <c r="D4" s="12" t="s">
         <v>10</v>
       </c>
@@ -17346,9 +17369,9 @@
       <c r="AM4" s="4"/>
     </row>
     <row r="5" spans="1:39">
-      <c r="A5" s="137"/>
-      <c r="B5" s="141"/>
-      <c r="C5" s="149"/>
+      <c r="A5" s="106"/>
+      <c r="B5" s="110"/>
+      <c r="C5" s="118"/>
       <c r="D5" s="15" t="s">
         <v>12</v>
       </c>
@@ -17393,9 +17416,9 @@
       <c r="AM5" s="4"/>
     </row>
     <row r="6" spans="1:39">
-      <c r="A6" s="137"/>
-      <c r="B6" s="141"/>
-      <c r="C6" s="149"/>
+      <c r="A6" s="106"/>
+      <c r="B6" s="110"/>
+      <c r="C6" s="118"/>
       <c r="D6" s="15"/>
       <c r="E6" s="16"/>
       <c r="F6" s="17"/>
@@ -17434,9 +17457,9 @@
       <c r="AM6" s="4"/>
     </row>
     <row r="7" spans="1:39">
-      <c r="A7" s="137"/>
-      <c r="B7" s="141"/>
-      <c r="C7" s="149"/>
+      <c r="A7" s="106"/>
+      <c r="B7" s="110"/>
+      <c r="C7" s="118"/>
       <c r="D7" s="15"/>
       <c r="E7" s="16"/>
       <c r="F7" s="17"/>
@@ -17475,9 +17498,9 @@
       <c r="AM7" s="4"/>
     </row>
     <row r="8" spans="1:39">
-      <c r="A8" s="137"/>
-      <c r="B8" s="142"/>
-      <c r="C8" s="150"/>
+      <c r="A8" s="106"/>
+      <c r="B8" s="111"/>
+      <c r="C8" s="119"/>
       <c r="D8" s="15"/>
       <c r="E8" s="16"/>
       <c r="F8" s="17"/>
@@ -17516,12 +17539,12 @@
       <c r="AM8" s="4"/>
     </row>
     <row r="9" spans="1:39" ht="19.5" thickBot="1">
-      <c r="A9" s="137"/>
-      <c r="B9" s="143" t="s">
+      <c r="A9" s="106"/>
+      <c r="B9" s="112" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="144"/>
-      <c r="D9" s="145"/>
+      <c r="C9" s="113"/>
+      <c r="D9" s="114"/>
       <c r="E9" s="18" t="s">
         <v>15</v>
       </c>
@@ -17657,11 +17680,11 @@
       <c r="AM9" s="4"/>
     </row>
     <row r="10" spans="1:39">
-      <c r="A10" s="137"/>
-      <c r="B10" s="139" t="s">
+      <c r="A10" s="106"/>
+      <c r="B10" s="108" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="148"/>
+      <c r="C10" s="117"/>
       <c r="D10" s="15" t="s">
         <v>17</v>
       </c>
@@ -17760,9 +17783,9 @@
       <c r="AM10" s="4"/>
     </row>
     <row r="11" spans="1:39">
-      <c r="A11" s="137"/>
-      <c r="B11" s="141"/>
-      <c r="C11" s="149"/>
+      <c r="A11" s="106"/>
+      <c r="B11" s="110"/>
+      <c r="C11" s="118"/>
       <c r="D11" s="15" t="s">
         <v>19</v>
       </c>
@@ -17811,9 +17834,9 @@
       <c r="AM11" s="4"/>
     </row>
     <row r="12" spans="1:39">
-      <c r="A12" s="137"/>
-      <c r="B12" s="141"/>
-      <c r="C12" s="149"/>
+      <c r="A12" s="106"/>
+      <c r="B12" s="110"/>
+      <c r="C12" s="118"/>
       <c r="D12" s="15" t="s">
         <v>21</v>
       </c>
@@ -17822,7 +17845,7 @@
       </c>
       <c r="F12" s="23"/>
       <c r="G12" s="24">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H12" s="24">
         <v>61</v>
@@ -17884,9 +17907,9 @@
       <c r="AM12" s="4"/>
     </row>
     <row r="13" spans="1:39">
-      <c r="A13" s="137"/>
-      <c r="B13" s="141"/>
-      <c r="C13" s="149"/>
+      <c r="A13" s="106"/>
+      <c r="B13" s="110"/>
+      <c r="C13" s="118"/>
       <c r="D13" s="15" t="s">
         <v>22</v>
       </c>
@@ -17935,9 +17958,9 @@
       <c r="AM13" s="4"/>
     </row>
     <row r="14" spans="1:39">
-      <c r="A14" s="137"/>
-      <c r="B14" s="142"/>
-      <c r="C14" s="150"/>
+      <c r="A14" s="106"/>
+      <c r="B14" s="111"/>
+      <c r="C14" s="119"/>
       <c r="D14" s="15"/>
       <c r="E14" s="16"/>
       <c r="F14" s="23"/>
@@ -17976,12 +17999,12 @@
       <c r="AM14" s="4"/>
     </row>
     <row r="15" spans="1:39" ht="19.5" thickBot="1">
-      <c r="A15" s="138"/>
-      <c r="B15" s="143" t="s">
+      <c r="A15" s="107"/>
+      <c r="B15" s="112" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="144"/>
-      <c r="D15" s="145"/>
+      <c r="C15" s="113"/>
+      <c r="D15" s="114"/>
       <c r="E15" s="18" t="s">
         <v>25</v>
       </c>
@@ -17991,7 +18014,7 @@
       </c>
       <c r="G15" s="20">
         <f>SUM(G10:G14)</f>
-        <v>600</v>
+        <v>605</v>
       </c>
       <c r="H15" s="20">
         <f t="shared" ref="H15:AK15" si="1">SUM(H10:H14)</f>
@@ -18117,16 +18140,16 @@
       <c r="AM15" s="4"/>
     </row>
     <row r="16" spans="1:39">
-      <c r="A16" s="102" t="s">
+      <c r="A16" s="105" t="s">
         <v>152</v>
       </c>
-      <c r="B16" s="132" t="s">
+      <c r="B16" s="139" t="s">
         <v>131</v>
       </c>
-      <c r="C16" s="123" t="s">
+      <c r="C16" s="121" t="s">
         <v>107</v>
       </c>
-      <c r="D16" s="124" t="s">
+      <c r="D16" s="123" t="s">
         <v>111</v>
       </c>
       <c r="E16" s="16" t="s">
@@ -18208,10 +18231,10 @@
       <c r="AM16" s="4"/>
     </row>
     <row r="17" spans="1:39">
-      <c r="A17" s="103"/>
-      <c r="B17" s="130"/>
-      <c r="C17" s="115"/>
-      <c r="D17" s="115"/>
+      <c r="A17" s="141"/>
+      <c r="B17" s="137"/>
+      <c r="C17" s="122"/>
+      <c r="D17" s="122"/>
       <c r="E17" s="16" t="s">
         <v>29</v>
       </c>
@@ -18297,12 +18320,12 @@
       <c r="AM17" s="4"/>
     </row>
     <row r="18" spans="1:39">
-      <c r="A18" s="103"/>
-      <c r="B18" s="130"/>
-      <c r="C18" s="114" t="s">
+      <c r="A18" s="141"/>
+      <c r="B18" s="137"/>
+      <c r="C18" s="124" t="s">
         <v>108</v>
       </c>
-      <c r="D18" s="116" t="s">
+      <c r="D18" s="126" t="s">
         <v>113</v>
       </c>
       <c r="E18" s="13" t="s">
@@ -18384,10 +18407,10 @@
       <c r="AM18" s="27"/>
     </row>
     <row r="19" spans="1:39">
-      <c r="A19" s="103"/>
-      <c r="B19" s="130"/>
-      <c r="C19" s="117"/>
-      <c r="D19" s="117"/>
+      <c r="A19" s="141"/>
+      <c r="B19" s="137"/>
+      <c r="C19" s="125"/>
+      <c r="D19" s="125"/>
       <c r="E19" s="16" t="s">
         <v>27</v>
       </c>
@@ -18455,10 +18478,10 @@
       <c r="AM19" s="27"/>
     </row>
     <row r="20" spans="1:39">
-      <c r="A20" s="103"/>
-      <c r="B20" s="130"/>
-      <c r="C20" s="117"/>
-      <c r="D20" s="115"/>
+      <c r="A20" s="141"/>
+      <c r="B20" s="137"/>
+      <c r="C20" s="125"/>
+      <c r="D20" s="122"/>
       <c r="E20" s="16" t="s">
         <v>28</v>
       </c>
@@ -18508,9 +18531,9 @@
       <c r="AM20" s="27"/>
     </row>
     <row r="21" spans="1:39">
-      <c r="A21" s="103"/>
-      <c r="B21" s="130"/>
-      <c r="C21" s="115"/>
+      <c r="A21" s="141"/>
+      <c r="B21" s="137"/>
+      <c r="C21" s="122"/>
       <c r="D21" s="57" t="s">
         <v>114</v>
       </c>
@@ -18561,9 +18584,9 @@
       <c r="AM21" s="27"/>
     </row>
     <row r="22" spans="1:39">
-      <c r="A22" s="103"/>
-      <c r="B22" s="130"/>
-      <c r="C22" s="114" t="s">
+      <c r="A22" s="141"/>
+      <c r="B22" s="137"/>
+      <c r="C22" s="124" t="s">
         <v>109</v>
       </c>
       <c r="D22" s="57" t="s">
@@ -18608,9 +18631,9 @@
       <c r="AM22" s="27"/>
     </row>
     <row r="23" spans="1:39">
-      <c r="A23" s="103"/>
-      <c r="B23" s="130"/>
-      <c r="C23" s="115"/>
+      <c r="A23" s="141"/>
+      <c r="B23" s="137"/>
+      <c r="C23" s="122"/>
       <c r="D23" s="57" t="s">
         <v>116</v>
       </c>
@@ -18653,12 +18676,12 @@
       <c r="AM23" s="27"/>
     </row>
     <row r="24" spans="1:39">
-      <c r="A24" s="103"/>
-      <c r="B24" s="130"/>
-      <c r="C24" s="114" t="s">
+      <c r="A24" s="141"/>
+      <c r="B24" s="137"/>
+      <c r="C24" s="124" t="s">
         <v>110</v>
       </c>
-      <c r="D24" s="116" t="s">
+      <c r="D24" s="126" t="s">
         <v>117</v>
       </c>
       <c r="E24" s="16" t="s">
@@ -18740,10 +18763,10 @@
       <c r="AM24" s="27"/>
     </row>
     <row r="25" spans="1:39">
-      <c r="A25" s="103"/>
-      <c r="B25" s="130"/>
-      <c r="C25" s="117"/>
-      <c r="D25" s="117"/>
+      <c r="A25" s="141"/>
+      <c r="B25" s="137"/>
+      <c r="C25" s="125"/>
+      <c r="D25" s="125"/>
       <c r="E25" s="16" t="s">
         <v>32</v>
       </c>
@@ -18835,10 +18858,10 @@
       <c r="AM25" s="27"/>
     </row>
     <row r="26" spans="1:39">
-      <c r="A26" s="103"/>
-      <c r="B26" s="130"/>
-      <c r="C26" s="117"/>
-      <c r="D26" s="117"/>
+      <c r="A26" s="141"/>
+      <c r="B26" s="137"/>
+      <c r="C26" s="125"/>
+      <c r="D26" s="125"/>
       <c r="E26" s="16" t="s">
         <v>33</v>
       </c>
@@ -18880,10 +18903,10 @@
       <c r="AM26" s="27"/>
     </row>
     <row r="27" spans="1:39">
-      <c r="A27" s="103"/>
-      <c r="B27" s="130"/>
-      <c r="C27" s="117"/>
-      <c r="D27" s="117"/>
+      <c r="A27" s="141"/>
+      <c r="B27" s="137"/>
+      <c r="C27" s="125"/>
+      <c r="D27" s="125"/>
       <c r="E27" s="29" t="s">
         <v>34</v>
       </c>
@@ -18925,10 +18948,10 @@
       <c r="AM27" s="27"/>
     </row>
     <row r="28" spans="1:39">
-      <c r="A28" s="103"/>
-      <c r="B28" s="130"/>
-      <c r="C28" s="117"/>
-      <c r="D28" s="117"/>
+      <c r="A28" s="141"/>
+      <c r="B28" s="137"/>
+      <c r="C28" s="125"/>
+      <c r="D28" s="125"/>
       <c r="E28" s="16" t="s">
         <v>35</v>
       </c>
@@ -18988,10 +19011,10 @@
       <c r="AM28" s="27"/>
     </row>
     <row r="29" spans="1:39">
-      <c r="A29" s="103"/>
-      <c r="B29" s="130"/>
-      <c r="C29" s="117"/>
-      <c r="D29" s="115"/>
+      <c r="A29" s="141"/>
+      <c r="B29" s="137"/>
+      <c r="C29" s="125"/>
+      <c r="D29" s="122"/>
       <c r="E29" s="86" t="s">
         <v>119</v>
       </c>
@@ -19033,9 +19056,9 @@
       <c r="AM29" s="27"/>
     </row>
     <row r="30" spans="1:39">
-      <c r="A30" s="103"/>
-      <c r="B30" s="130"/>
-      <c r="C30" s="117"/>
+      <c r="A30" s="141"/>
+      <c r="B30" s="137"/>
+      <c r="C30" s="125"/>
       <c r="D30" s="57" t="s">
         <v>121</v>
       </c>
@@ -19078,9 +19101,9 @@
       <c r="AM30" s="27"/>
     </row>
     <row r="31" spans="1:39">
-      <c r="A31" s="103"/>
-      <c r="B31" s="131"/>
-      <c r="C31" s="115"/>
+      <c r="A31" s="141"/>
+      <c r="B31" s="138"/>
+      <c r="C31" s="122"/>
       <c r="D31" s="57" t="s">
         <v>122</v>
       </c>
@@ -19123,11 +19146,11 @@
       <c r="AM31" s="27"/>
     </row>
     <row r="32" spans="1:39">
-      <c r="A32" s="103"/>
-      <c r="B32" s="120" t="s">
+      <c r="A32" s="141"/>
+      <c r="B32" s="149" t="s">
         <v>130</v>
       </c>
-      <c r="C32" s="111"/>
+      <c r="C32" s="127"/>
       <c r="D32" s="17" t="s">
         <v>127</v>
       </c>
@@ -19226,9 +19249,9 @@
       <c r="AM32" s="27"/>
     </row>
     <row r="33" spans="1:39">
-      <c r="A33" s="103"/>
-      <c r="B33" s="121"/>
-      <c r="C33" s="113"/>
+      <c r="A33" s="141"/>
+      <c r="B33" s="150"/>
+      <c r="C33" s="129"/>
       <c r="D33" s="17" t="s">
         <v>128</v>
       </c>
@@ -19303,12 +19326,12 @@
       <c r="AM33" s="27"/>
     </row>
     <row r="34" spans="1:39">
-      <c r="A34" s="103"/>
-      <c r="B34" s="105" t="s">
+      <c r="A34" s="141"/>
+      <c r="B34" s="130" t="s">
         <v>9</v>
       </c>
-      <c r="C34" s="107"/>
-      <c r="D34" s="109"/>
+      <c r="C34" s="133"/>
+      <c r="D34" s="145"/>
       <c r="E34" s="34" t="str">
         <f t="shared" ref="E34:AK34" si="2">E4</f>
         <v>新潟実家の売却益　（妙子と折半）</v>
@@ -19445,10 +19468,10 @@
       <c r="AM34" s="27"/>
     </row>
     <row r="35" spans="1:39">
-      <c r="A35" s="103"/>
-      <c r="B35" s="106"/>
-      <c r="C35" s="108"/>
-      <c r="D35" s="110"/>
+      <c r="A35" s="141"/>
+      <c r="B35" s="143"/>
+      <c r="C35" s="144"/>
+      <c r="D35" s="146"/>
       <c r="E35" s="34" t="str">
         <f>E5</f>
         <v>横浜マンションの売却益</v>
@@ -19585,10 +19608,10 @@
       <c r="AM35" s="27"/>
     </row>
     <row r="36" spans="1:39">
-      <c r="A36" s="103"/>
-      <c r="B36" s="106"/>
-      <c r="C36" s="108"/>
-      <c r="D36" s="110"/>
+      <c r="A36" s="141"/>
+      <c r="B36" s="143"/>
+      <c r="C36" s="144"/>
+      <c r="D36" s="146"/>
       <c r="E36" s="99" t="s">
         <v>151</v>
       </c>
@@ -19631,7 +19654,7 @@
       <c r="AM36" s="27"/>
     </row>
     <row r="37" spans="1:39" ht="19.5" thickBot="1">
-      <c r="A37" s="103"/>
+      <c r="A37" s="141"/>
       <c r="B37" s="35" t="s">
         <v>37</v>
       </c>
@@ -19770,8 +19793,8 @@
       <c r="AM37" s="27"/>
     </row>
     <row r="38" spans="1:39" ht="18.75" customHeight="1">
-      <c r="A38" s="103"/>
-      <c r="B38" s="129" t="s">
+      <c r="A38" s="141"/>
+      <c r="B38" s="136" t="s">
         <v>132</v>
       </c>
       <c r="C38" s="8" t="s">
@@ -19821,9 +19844,9 @@
       <c r="AM38" s="4"/>
     </row>
     <row r="39" spans="1:39">
-      <c r="A39" s="103"/>
-      <c r="B39" s="130"/>
-      <c r="C39" s="114" t="s">
+      <c r="A39" s="141"/>
+      <c r="B39" s="137"/>
+      <c r="C39" s="124" t="s">
         <v>108</v>
       </c>
       <c r="D39" s="57" t="s">
@@ -19868,9 +19891,9 @@
       <c r="AM39" s="4"/>
     </row>
     <row r="40" spans="1:39">
-      <c r="A40" s="103"/>
-      <c r="B40" s="130"/>
-      <c r="C40" s="115"/>
+      <c r="A40" s="141"/>
+      <c r="B40" s="137"/>
+      <c r="C40" s="122"/>
       <c r="D40" s="57" t="s">
         <v>114</v>
       </c>
@@ -19913,9 +19936,9 @@
       <c r="AM40" s="4"/>
     </row>
     <row r="41" spans="1:39">
-      <c r="A41" s="103"/>
-      <c r="B41" s="130"/>
-      <c r="C41" s="114" t="s">
+      <c r="A41" s="141"/>
+      <c r="B41" s="137"/>
+      <c r="C41" s="124" t="s">
         <v>109</v>
       </c>
       <c r="D41" s="57" t="s">
@@ -20016,9 +20039,9 @@
       <c r="AM41" s="27"/>
     </row>
     <row r="42" spans="1:39">
-      <c r="A42" s="103"/>
-      <c r="B42" s="130"/>
-      <c r="C42" s="115"/>
+      <c r="A42" s="141"/>
+      <c r="B42" s="137"/>
+      <c r="C42" s="122"/>
       <c r="D42" s="57" t="s">
         <v>116</v>
       </c>
@@ -20061,12 +20084,12 @@
       <c r="AM42" s="4"/>
     </row>
     <row r="43" spans="1:39">
-      <c r="A43" s="103"/>
-      <c r="B43" s="130"/>
-      <c r="C43" s="114" t="s">
+      <c r="A43" s="141"/>
+      <c r="B43" s="137"/>
+      <c r="C43" s="124" t="s">
         <v>110</v>
       </c>
-      <c r="D43" s="116" t="s">
+      <c r="D43" s="126" t="s">
         <v>117</v>
       </c>
       <c r="E43" s="16" t="s">
@@ -20111,10 +20134,10 @@
       <c r="AM43" s="27"/>
     </row>
     <row r="44" spans="1:39">
-      <c r="A44" s="103"/>
-      <c r="B44" s="130"/>
-      <c r="C44" s="117"/>
-      <c r="D44" s="117"/>
+      <c r="A44" s="141"/>
+      <c r="B44" s="137"/>
+      <c r="C44" s="125"/>
+      <c r="D44" s="125"/>
       <c r="E44" s="16" t="s">
         <v>48</v>
       </c>
@@ -20194,10 +20217,10 @@
       <c r="AM44" s="27"/>
     </row>
     <row r="45" spans="1:39">
-      <c r="A45" s="103"/>
-      <c r="B45" s="130"/>
-      <c r="C45" s="117"/>
-      <c r="D45" s="117"/>
+      <c r="A45" s="141"/>
+      <c r="B45" s="137"/>
+      <c r="C45" s="125"/>
+      <c r="D45" s="125"/>
       <c r="E45" s="16" t="s">
         <v>49</v>
       </c>
@@ -20269,10 +20292,10 @@
       <c r="AM45" s="27"/>
     </row>
     <row r="46" spans="1:39">
-      <c r="A46" s="103"/>
-      <c r="B46" s="130"/>
-      <c r="C46" s="117"/>
-      <c r="D46" s="115"/>
+      <c r="A46" s="141"/>
+      <c r="B46" s="137"/>
+      <c r="C46" s="125"/>
+      <c r="D46" s="122"/>
       <c r="E46" s="86" t="s">
         <v>123</v>
       </c>
@@ -20322,9 +20345,9 @@
       <c r="AM46" s="27"/>
     </row>
     <row r="47" spans="1:39">
-      <c r="A47" s="103"/>
-      <c r="B47" s="130"/>
-      <c r="C47" s="117"/>
+      <c r="A47" s="141"/>
+      <c r="B47" s="137"/>
+      <c r="C47" s="125"/>
       <c r="D47" s="57" t="s">
         <v>121</v>
       </c>
@@ -20417,9 +20440,9 @@
       <c r="AM47" s="27"/>
     </row>
     <row r="48" spans="1:39">
-      <c r="A48" s="103"/>
-      <c r="B48" s="131"/>
-      <c r="C48" s="115"/>
+      <c r="A48" s="141"/>
+      <c r="B48" s="138"/>
+      <c r="C48" s="122"/>
       <c r="D48" s="57" t="s">
         <v>122</v>
       </c>
@@ -20462,7 +20485,7 @@
       <c r="AM48" s="4"/>
     </row>
     <row r="49" spans="1:39">
-      <c r="A49" s="103"/>
+      <c r="A49" s="141"/>
       <c r="B49" s="66" t="s">
         <v>44</v>
       </c>
@@ -20547,7 +20570,7 @@
       <c r="AM49" s="27"/>
     </row>
     <row r="50" spans="1:39">
-      <c r="A50" s="103"/>
+      <c r="A50" s="141"/>
       <c r="B50" s="66" t="s">
         <v>51</v>
       </c>
@@ -20648,7 +20671,7 @@
       <c r="AM50" s="27"/>
     </row>
     <row r="51" spans="1:39">
-      <c r="A51" s="103"/>
+      <c r="A51" s="141"/>
       <c r="B51" s="66" t="s">
         <v>53</v>
       </c>
@@ -20749,11 +20772,11 @@
       <c r="AM51" s="27"/>
     </row>
     <row r="52" spans="1:39">
-      <c r="A52" s="103"/>
-      <c r="B52" s="128" t="s">
+      <c r="A52" s="141"/>
+      <c r="B52" s="135" t="s">
         <v>124</v>
       </c>
-      <c r="C52" s="111"/>
+      <c r="C52" s="127"/>
       <c r="D52" s="15" t="s">
         <v>42</v>
       </c>
@@ -20836,9 +20859,9 @@
       <c r="AM52" s="27"/>
     </row>
     <row r="53" spans="1:39">
-      <c r="A53" s="103"/>
-      <c r="B53" s="125"/>
-      <c r="C53" s="112"/>
+      <c r="A53" s="141"/>
+      <c r="B53" s="131"/>
+      <c r="C53" s="128"/>
       <c r="D53" s="15" t="s">
         <v>38</v>
       </c>
@@ -20883,9 +20906,9 @@
       <c r="AM53" s="27"/>
     </row>
     <row r="54" spans="1:39">
-      <c r="A54" s="103"/>
-      <c r="B54" s="126"/>
-      <c r="C54" s="113"/>
+      <c r="A54" s="141"/>
+      <c r="B54" s="132"/>
+      <c r="C54" s="129"/>
       <c r="D54" s="15" t="s">
         <v>40</v>
       </c>
@@ -20984,7 +21007,7 @@
       <c r="AM54" s="27"/>
     </row>
     <row r="55" spans="1:39">
-      <c r="A55" s="103"/>
+      <c r="A55" s="141"/>
       <c r="B55" s="84" t="s">
         <v>140</v>
       </c>
@@ -21087,11 +21110,11 @@
       <c r="AM55" s="27"/>
     </row>
     <row r="56" spans="1:39">
-      <c r="A56" s="103"/>
-      <c r="B56" s="118" t="s">
+      <c r="A56" s="141"/>
+      <c r="B56" s="147" t="s">
         <v>146</v>
       </c>
-      <c r="C56" s="119"/>
+      <c r="C56" s="148"/>
       <c r="D56" s="78" t="s">
         <v>126</v>
       </c>
@@ -21103,7 +21126,7 @@
         <v>0</v>
       </c>
       <c r="G56" s="78">
-        <v>600</v>
+        <v>605</v>
       </c>
       <c r="H56" s="78" cm="1">
         <f t="array" ref="H56:I56">H15:I15</f>
@@ -21214,7 +21237,7 @@
       <c r="AM56" s="27"/>
     </row>
     <row r="57" spans="1:39">
-      <c r="A57" s="103"/>
+      <c r="A57" s="141"/>
       <c r="B57" s="67" t="s">
         <v>57</v>
       </c>
@@ -21226,7 +21249,7 @@
       <c r="F57" s="35"/>
       <c r="G57" s="35">
         <f t="shared" ref="G57:AH57" si="5">SUM(G38:G56)</f>
-        <v>1484</v>
+        <v>1489</v>
       </c>
       <c r="H57" s="35">
         <f t="shared" si="5"/>
@@ -21343,7 +21366,7 @@
       <c r="AM57" s="27"/>
     </row>
     <row r="58" spans="1:39">
-      <c r="A58" s="103"/>
+      <c r="A58" s="141"/>
       <c r="B58" s="67" t="s">
         <v>59</v>
       </c>
@@ -21353,7 +21376,7 @@
       <c r="F58" s="35"/>
       <c r="G58" s="35">
         <f t="shared" ref="G58:AH58" si="6">G37-G57</f>
-        <v>-947</v>
+        <v>-952</v>
       </c>
       <c r="H58" s="35">
         <f t="shared" si="6"/>
@@ -21470,7 +21493,7 @@
       <c r="AM58" s="27"/>
     </row>
     <row r="59" spans="1:39" ht="19.5" thickBot="1">
-      <c r="A59" s="104"/>
+      <c r="A59" s="142"/>
       <c r="B59" s="61" t="s">
         <v>60</v>
       </c>
@@ -21482,115 +21505,115 @@
       </c>
       <c r="G59" s="44">
         <f>F59+G58</f>
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="H59" s="44">
         <f t="shared" ref="H59:AH59" si="7">G59+H58</f>
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="I59" s="44">
         <f t="shared" si="7"/>
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="J59" s="44">
         <f t="shared" si="7"/>
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="K59" s="44">
         <f t="shared" si="7"/>
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="L59" s="44">
         <f t="shared" si="7"/>
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="M59" s="44">
         <f t="shared" si="7"/>
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="N59" s="44">
         <f t="shared" si="7"/>
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="O59" s="44">
         <f t="shared" si="7"/>
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="P59" s="44">
         <f t="shared" si="7"/>
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="Q59" s="44">
         <f t="shared" si="7"/>
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="R59" s="44">
         <f t="shared" si="7"/>
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="S59" s="44">
         <f t="shared" si="7"/>
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="T59" s="44">
         <f t="shared" si="7"/>
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="U59" s="44">
         <f t="shared" si="7"/>
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="V59" s="44">
         <f t="shared" si="7"/>
-        <v>-14</v>
+        <v>-19</v>
       </c>
       <c r="W59" s="44">
         <f t="shared" si="7"/>
-        <v>-31</v>
+        <v>-36</v>
       </c>
       <c r="X59" s="44">
         <f t="shared" si="7"/>
-        <v>-68</v>
+        <v>-73</v>
       </c>
       <c r="Y59" s="44">
         <f t="shared" si="7"/>
-        <v>-85</v>
+        <v>-90</v>
       </c>
       <c r="Z59" s="44">
         <f t="shared" si="7"/>
-        <v>2198</v>
+        <v>2193</v>
       </c>
       <c r="AA59" s="44">
         <f t="shared" si="7"/>
-        <v>2034</v>
+        <v>2029</v>
       </c>
       <c r="AB59" s="44">
         <f t="shared" si="7"/>
-        <v>1870</v>
+        <v>1865</v>
       </c>
       <c r="AC59" s="44">
         <f t="shared" si="7"/>
-        <v>1686</v>
+        <v>1681</v>
       </c>
       <c r="AD59" s="44">
         <f t="shared" si="7"/>
-        <v>1522</v>
+        <v>1517</v>
       </c>
       <c r="AE59" s="44">
         <f t="shared" si="7"/>
-        <v>1358</v>
+        <v>1353</v>
       </c>
       <c r="AF59" s="44">
         <f t="shared" si="7"/>
-        <v>1199</v>
+        <v>1194</v>
       </c>
       <c r="AG59" s="44">
         <f t="shared" si="7"/>
-        <v>1040</v>
+        <v>1035</v>
       </c>
       <c r="AH59" s="44">
         <f t="shared" si="7"/>
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="AI59" s="44"/>
       <c r="AJ59" s="44"/>
@@ -21599,7 +21622,7 @@
       <c r="AM59" s="27"/>
     </row>
     <row r="60" spans="1:39" ht="18.75" customHeight="1">
-      <c r="A60" s="102" t="s">
+      <c r="A60" s="105" t="s">
         <v>61</v>
       </c>
       <c r="B60" s="81" t="s">
@@ -21616,7 +21639,7 @@
       </c>
       <c r="G60" s="86">
         <f>G55+G56+G38</f>
-        <v>924</v>
+        <v>929</v>
       </c>
       <c r="H60" s="82">
         <f t="shared" ref="H60:AH60" si="8">H55+H56</f>
@@ -21733,7 +21756,7 @@
       <c r="AM60" s="27"/>
     </row>
     <row r="61" spans="1:39" ht="19.5" thickBot="1">
-      <c r="A61" s="133"/>
+      <c r="A61" s="140"/>
       <c r="B61" s="61" t="s">
         <v>37</v>
       </c>
@@ -21745,7 +21768,7 @@
       </c>
       <c r="G61" s="69">
         <f t="shared" ref="G61:AH61" si="9">SUM(G60:G60)</f>
-        <v>924</v>
+        <v>929</v>
       </c>
       <c r="H61" s="69">
         <f t="shared" si="9"/>
@@ -21862,7 +21885,7 @@
       <c r="AM61" s="27"/>
     </row>
     <row r="62" spans="1:39">
-      <c r="A62" s="133"/>
+      <c r="A62" s="140"/>
       <c r="B62" s="68" t="s">
         <v>137</v>
       </c>
@@ -21913,11 +21936,11 @@
       <c r="AM62" s="27"/>
     </row>
     <row r="63" spans="1:39">
-      <c r="A63" s="133"/>
-      <c r="B63" s="127" t="s">
+      <c r="A63" s="140"/>
+      <c r="B63" s="134" t="s">
         <v>124</v>
       </c>
-      <c r="C63" s="111"/>
+      <c r="C63" s="127"/>
       <c r="D63" s="72" t="s">
         <v>63</v>
       </c>
@@ -22016,9 +22039,9 @@
       <c r="AM63" s="27"/>
     </row>
     <row r="64" spans="1:39">
-      <c r="A64" s="133"/>
-      <c r="B64" s="125"/>
-      <c r="C64" s="112"/>
+      <c r="A64" s="140"/>
+      <c r="B64" s="131"/>
+      <c r="C64" s="128"/>
       <c r="D64" s="15" t="s">
         <v>65</v>
       </c>
@@ -22117,9 +22140,9 @@
       <c r="AM64" s="27"/>
     </row>
     <row r="65" spans="1:39">
-      <c r="A65" s="133"/>
-      <c r="B65" s="125"/>
-      <c r="C65" s="112"/>
+      <c r="A65" s="140"/>
+      <c r="B65" s="131"/>
+      <c r="C65" s="128"/>
       <c r="D65" s="15" t="s">
         <v>67</v>
       </c>
@@ -22218,9 +22241,9 @@
       <c r="AM65" s="27"/>
     </row>
     <row r="66" spans="1:39">
-      <c r="A66" s="133"/>
-      <c r="B66" s="125"/>
-      <c r="C66" s="112"/>
+      <c r="A66" s="140"/>
+      <c r="B66" s="131"/>
+      <c r="C66" s="128"/>
       <c r="D66" s="15" t="s">
         <v>69</v>
       </c>
@@ -22319,9 +22342,9 @@
       <c r="AM66" s="27"/>
     </row>
     <row r="67" spans="1:39">
-      <c r="A67" s="133"/>
-      <c r="B67" s="125"/>
-      <c r="C67" s="112"/>
+      <c r="A67" s="140"/>
+      <c r="B67" s="131"/>
+      <c r="C67" s="128"/>
       <c r="D67" s="15" t="s">
         <v>53</v>
       </c>
@@ -22420,9 +22443,9 @@
       <c r="AM67" s="27"/>
     </row>
     <row r="68" spans="1:39">
-      <c r="A68" s="133"/>
-      <c r="B68" s="125"/>
-      <c r="C68" s="112"/>
+      <c r="A68" s="140"/>
+      <c r="B68" s="131"/>
+      <c r="C68" s="128"/>
       <c r="D68" s="15" t="s">
         <v>72</v>
       </c>
@@ -22521,9 +22544,9 @@
       <c r="AM68" s="27"/>
     </row>
     <row r="69" spans="1:39">
-      <c r="A69" s="133"/>
-      <c r="B69" s="125"/>
-      <c r="C69" s="112"/>
+      <c r="A69" s="140"/>
+      <c r="B69" s="131"/>
+      <c r="C69" s="128"/>
       <c r="D69" s="15" t="s">
         <v>74</v>
       </c>
@@ -22622,9 +22645,9 @@
       <c r="AM69" s="27"/>
     </row>
     <row r="70" spans="1:39">
-      <c r="A70" s="133"/>
-      <c r="B70" s="125"/>
-      <c r="C70" s="112"/>
+      <c r="A70" s="140"/>
+      <c r="B70" s="131"/>
+      <c r="C70" s="128"/>
       <c r="D70" s="15" t="s">
         <v>76</v>
       </c>
@@ -22723,9 +22746,9 @@
       <c r="AM70" s="27"/>
     </row>
     <row r="71" spans="1:39">
-      <c r="A71" s="133"/>
-      <c r="B71" s="125"/>
-      <c r="C71" s="112"/>
+      <c r="A71" s="140"/>
+      <c r="B71" s="131"/>
+      <c r="C71" s="128"/>
       <c r="D71" s="15" t="s">
         <v>78</v>
       </c>
@@ -22824,10 +22847,10 @@
       <c r="AM71" s="27"/>
     </row>
     <row r="72" spans="1:39">
-      <c r="A72" s="133"/>
-      <c r="B72" s="125"/>
-      <c r="C72" s="112"/>
-      <c r="D72" s="114" t="s">
+      <c r="A72" s="140"/>
+      <c r="B72" s="131"/>
+      <c r="C72" s="128"/>
+      <c r="D72" s="124" t="s">
         <v>81</v>
       </c>
       <c r="E72" s="16" t="s">
@@ -22929,10 +22952,10 @@
       <c r="AM72" s="27"/>
     </row>
     <row r="73" spans="1:39">
-      <c r="A73" s="133"/>
-      <c r="B73" s="126"/>
-      <c r="C73" s="113"/>
-      <c r="D73" s="115"/>
+      <c r="A73" s="140"/>
+      <c r="B73" s="132"/>
+      <c r="C73" s="129"/>
+      <c r="D73" s="122"/>
       <c r="E73" s="16" t="s">
         <v>83</v>
       </c>
@@ -23032,11 +23055,11 @@
       <c r="AM73" s="27"/>
     </row>
     <row r="74" spans="1:39">
-      <c r="A74" s="133"/>
-      <c r="B74" s="105" t="s">
+      <c r="A74" s="140"/>
+      <c r="B74" s="130" t="s">
         <v>16</v>
       </c>
-      <c r="C74" s="107"/>
+      <c r="C74" s="133"/>
       <c r="D74" s="33" t="s">
         <v>133</v>
       </c>
@@ -23166,9 +23189,9 @@
       <c r="AM74" s="27"/>
     </row>
     <row r="75" spans="1:39">
-      <c r="A75" s="133"/>
-      <c r="B75" s="125"/>
-      <c r="C75" s="112"/>
+      <c r="A75" s="140"/>
+      <c r="B75" s="131"/>
+      <c r="C75" s="128"/>
       <c r="D75" s="33" t="s">
         <v>134</v>
       </c>
@@ -23298,9 +23321,9 @@
       <c r="AM75" s="27"/>
     </row>
     <row r="76" spans="1:39">
-      <c r="A76" s="133"/>
-      <c r="B76" s="125"/>
-      <c r="C76" s="112"/>
+      <c r="A76" s="140"/>
+      <c r="B76" s="131"/>
+      <c r="C76" s="128"/>
       <c r="D76" s="33" t="s">
         <v>135</v>
       </c>
@@ -23313,7 +23336,7 @@
       </c>
       <c r="G76" s="38">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H76" s="38">
         <f t="shared" si="12"/>
@@ -23430,9 +23453,9 @@
       <c r="AM76" s="27"/>
     </row>
     <row r="77" spans="1:39">
-      <c r="A77" s="133"/>
-      <c r="B77" s="126"/>
-      <c r="C77" s="113"/>
+      <c r="A77" s="140"/>
+      <c r="B77" s="132"/>
+      <c r="C77" s="129"/>
       <c r="D77" s="33" t="s">
         <v>136</v>
       </c>
@@ -23562,7 +23585,7 @@
       <c r="AM77" s="27"/>
     </row>
     <row r="78" spans="1:39">
-      <c r="A78" s="133"/>
+      <c r="A78" s="140"/>
       <c r="B78" s="67" t="s">
         <v>57</v>
       </c>
@@ -23575,7 +23598,7 @@
       </c>
       <c r="G78" s="35">
         <f>SUM(G62:G77)</f>
-        <v>947</v>
+        <v>952</v>
       </c>
       <c r="H78" s="35">
         <f t="shared" ref="H78:AH78" si="14">SUM(H62:H77)</f>
@@ -23692,7 +23715,7 @@
       <c r="AM78" s="27"/>
     </row>
     <row r="79" spans="1:39">
-      <c r="A79" s="133"/>
+      <c r="A79" s="140"/>
       <c r="B79" s="67" t="s">
         <v>59</v>
       </c>
@@ -23821,7 +23844,7 @@
       <c r="AM79" s="27"/>
     </row>
     <row r="80" spans="1:39" ht="19.5" thickBot="1">
-      <c r="A80" s="122"/>
+      <c r="A80" s="120"/>
       <c r="B80" s="61" t="s">
         <v>60</v>
       </c>
@@ -23950,7 +23973,7 @@
       <c r="AM80" s="27"/>
     </row>
     <row r="81" spans="1:39">
-      <c r="A81" s="102" t="s">
+      <c r="A81" s="105" t="s">
         <v>88</v>
       </c>
       <c r="B81" s="59" t="s">
@@ -23965,7 +23988,7 @@
       </c>
       <c r="G81" s="47">
         <f t="shared" si="17"/>
-        <v>-970</v>
+        <v>-975</v>
       </c>
       <c r="H81" s="47">
         <f t="shared" si="17"/>
@@ -24082,7 +24105,7 @@
       <c r="AM81" s="27"/>
     </row>
     <row r="82" spans="1:39" ht="19.5" thickBot="1">
-      <c r="A82" s="122"/>
+      <c r="A82" s="120"/>
       <c r="B82" s="61" t="s">
         <v>90</v>
       </c>
@@ -24095,115 +24118,115 @@
       </c>
       <c r="G82" s="41">
         <f t="shared" si="18"/>
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="H82" s="41">
         <f t="shared" si="18"/>
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="I82" s="41">
         <f t="shared" si="18"/>
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="J82" s="41">
         <f t="shared" si="18"/>
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="K82" s="41">
         <f t="shared" si="18"/>
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="L82" s="41">
         <f t="shared" si="18"/>
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="M82" s="41">
         <f t="shared" si="18"/>
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="N82" s="41">
         <f t="shared" si="18"/>
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="O82" s="41">
         <f t="shared" si="18"/>
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="P82" s="41">
         <f t="shared" si="18"/>
-        <v>720</v>
+        <v>715</v>
       </c>
       <c r="Q82" s="41">
         <f t="shared" si="18"/>
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="R82" s="41">
         <f t="shared" si="18"/>
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="S82" s="41">
         <f t="shared" si="18"/>
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="T82" s="41">
         <f t="shared" si="18"/>
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="U82" s="41">
         <f t="shared" si="18"/>
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="V82" s="41">
         <f t="shared" si="18"/>
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="W82" s="41">
         <f t="shared" si="18"/>
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="X82" s="41">
         <f t="shared" si="18"/>
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="Y82" s="41">
         <f t="shared" si="18"/>
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="Z82" s="41">
         <f t="shared" si="18"/>
-        <v>2422</v>
+        <v>2417</v>
       </c>
       <c r="AA82" s="41">
         <f t="shared" si="18"/>
-        <v>2271</v>
+        <v>2266</v>
       </c>
       <c r="AB82" s="41">
         <f t="shared" si="18"/>
-        <v>2120</v>
+        <v>2115</v>
       </c>
       <c r="AC82" s="41">
         <f t="shared" si="18"/>
-        <v>1949</v>
+        <v>1944</v>
       </c>
       <c r="AD82" s="41">
         <f t="shared" si="18"/>
-        <v>1798</v>
+        <v>1793</v>
       </c>
       <c r="AE82" s="41">
         <f t="shared" si="18"/>
-        <v>1647</v>
+        <v>1642</v>
       </c>
       <c r="AF82" s="41">
         <f t="shared" si="18"/>
-        <v>1501</v>
+        <v>1496</v>
       </c>
       <c r="AG82" s="41">
         <f t="shared" si="18"/>
-        <v>1355</v>
+        <v>1350</v>
       </c>
       <c r="AH82" s="41">
         <f t="shared" si="18"/>
-        <v>989</v>
+        <v>984</v>
       </c>
       <c r="AI82" s="41"/>
       <c r="AJ82" s="41"/>
@@ -25941,115 +25964,115 @@
       </c>
       <c r="G104" s="96">
         <f t="shared" ref="G104:AK104" si="32">G82</f>
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="H104" s="35">
         <f t="shared" si="32"/>
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="I104" s="35">
         <f t="shared" si="32"/>
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="J104" s="35">
         <f t="shared" si="32"/>
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="K104" s="35">
         <f t="shared" si="32"/>
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="L104" s="35">
         <f t="shared" si="32"/>
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="M104" s="35">
         <f t="shared" si="32"/>
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="N104" s="35">
         <f t="shared" si="32"/>
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="O104" s="35">
         <f t="shared" si="32"/>
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="P104" s="35">
         <f t="shared" si="32"/>
-        <v>720</v>
+        <v>715</v>
       </c>
       <c r="Q104" s="35">
         <f t="shared" si="32"/>
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="R104" s="35">
         <f t="shared" si="32"/>
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="S104" s="35">
         <f t="shared" si="32"/>
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="T104" s="35">
         <f t="shared" si="32"/>
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="U104" s="35">
         <f t="shared" si="32"/>
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="V104" s="35">
         <f t="shared" si="32"/>
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="W104" s="35">
         <f t="shared" si="32"/>
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="X104" s="35">
         <f t="shared" si="32"/>
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="Y104" s="35">
         <f t="shared" si="32"/>
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="Z104" s="35">
         <f t="shared" si="32"/>
-        <v>2422</v>
+        <v>2417</v>
       </c>
       <c r="AA104" s="35">
         <f t="shared" si="32"/>
-        <v>2271</v>
+        <v>2266</v>
       </c>
       <c r="AB104" s="35">
         <f t="shared" si="32"/>
-        <v>2120</v>
+        <v>2115</v>
       </c>
       <c r="AC104" s="35">
         <f t="shared" si="32"/>
-        <v>1949</v>
+        <v>1944</v>
       </c>
       <c r="AD104" s="35">
         <f t="shared" si="32"/>
-        <v>1798</v>
+        <v>1793</v>
       </c>
       <c r="AE104" s="35">
         <f t="shared" si="32"/>
-        <v>1647</v>
+        <v>1642</v>
       </c>
       <c r="AF104" s="35">
         <f t="shared" si="32"/>
-        <v>1501</v>
+        <v>1496</v>
       </c>
       <c r="AG104" s="35">
         <f t="shared" si="32"/>
-        <v>1355</v>
+        <v>1350</v>
       </c>
       <c r="AH104" s="35">
         <f t="shared" si="32"/>
-        <v>989</v>
+        <v>984</v>
       </c>
       <c r="AI104" s="35">
         <f t="shared" si="32"/>
@@ -27414,115 +27437,115 @@
       </c>
       <c r="G124" s="46">
         <f t="shared" ref="G124:AK124" si="34">G59</f>
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="H124" s="47">
         <f t="shared" si="34"/>
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="I124" s="47">
         <f t="shared" si="34"/>
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="J124" s="47">
         <f t="shared" si="34"/>
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="K124" s="47">
         <f t="shared" si="34"/>
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="L124" s="47">
         <f t="shared" si="34"/>
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="M124" s="47">
         <f t="shared" si="34"/>
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="N124" s="47">
         <f t="shared" si="34"/>
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="O124" s="47">
         <f t="shared" si="34"/>
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="P124" s="47">
         <f t="shared" si="34"/>
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="Q124" s="47">
         <f t="shared" si="34"/>
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="R124" s="47">
         <f t="shared" si="34"/>
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="S124" s="47">
         <f t="shared" si="34"/>
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="T124" s="47">
         <f t="shared" si="34"/>
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="U124" s="47">
         <f t="shared" si="34"/>
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="V124" s="47">
         <f t="shared" si="34"/>
-        <v>-14</v>
+        <v>-19</v>
       </c>
       <c r="W124" s="47">
         <f t="shared" si="34"/>
-        <v>-31</v>
+        <v>-36</v>
       </c>
       <c r="X124" s="47">
         <f t="shared" si="34"/>
-        <v>-68</v>
+        <v>-73</v>
       </c>
       <c r="Y124" s="47">
         <f t="shared" si="34"/>
-        <v>-85</v>
+        <v>-90</v>
       </c>
       <c r="Z124" s="47">
         <f t="shared" si="34"/>
-        <v>2198</v>
+        <v>2193</v>
       </c>
       <c r="AA124" s="47">
         <f t="shared" si="34"/>
-        <v>2034</v>
+        <v>2029</v>
       </c>
       <c r="AB124" s="47">
         <f t="shared" si="34"/>
-        <v>1870</v>
+        <v>1865</v>
       </c>
       <c r="AC124" s="47">
         <f t="shared" si="34"/>
-        <v>1686</v>
+        <v>1681</v>
       </c>
       <c r="AD124" s="47">
         <f t="shared" si="34"/>
-        <v>1522</v>
+        <v>1517</v>
       </c>
       <c r="AE124" s="47">
         <f t="shared" si="34"/>
-        <v>1358</v>
+        <v>1353</v>
       </c>
       <c r="AF124" s="47">
         <f t="shared" si="34"/>
-        <v>1199</v>
+        <v>1194</v>
       </c>
       <c r="AG124" s="47">
         <f t="shared" si="34"/>
-        <v>1040</v>
+        <v>1035</v>
       </c>
       <c r="AH124" s="47">
         <f t="shared" si="34"/>
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="AI124" s="47">
         <f t="shared" si="34"/>
@@ -29209,16 +29232,19 @@
     </row>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="A2:A15"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="B4:B8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B10:B14"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="C4:C8"/>
-    <mergeCell ref="C10:C14"/>
+    <mergeCell ref="A16:A59"/>
+    <mergeCell ref="B34:B36"/>
+    <mergeCell ref="C34:C36"/>
+    <mergeCell ref="D34:D36"/>
+    <mergeCell ref="C63:C73"/>
+    <mergeCell ref="D72:D73"/>
+    <mergeCell ref="D24:D29"/>
+    <mergeCell ref="D43:D46"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="C43:C48"/>
     <mergeCell ref="A81:A82"/>
     <mergeCell ref="C16:C17"/>
     <mergeCell ref="D16:D17"/>
@@ -29235,19 +29261,16 @@
     <mergeCell ref="B38:B48"/>
     <mergeCell ref="B16:B31"/>
     <mergeCell ref="A60:A80"/>
-    <mergeCell ref="A16:A59"/>
-    <mergeCell ref="B34:B36"/>
-    <mergeCell ref="C34:C36"/>
-    <mergeCell ref="D34:D36"/>
-    <mergeCell ref="C63:C73"/>
-    <mergeCell ref="D72:D73"/>
-    <mergeCell ref="D24:D29"/>
-    <mergeCell ref="D43:D46"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="C43:C48"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="A2:A15"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="B4:B8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B10:B14"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="C4:C8"/>
+    <mergeCell ref="C10:C14"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ライフプラン_猪飼.xlsx
+++ b/ライフプラン_猪飼.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC_USER\Documents\LocalLifeplanRepo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBBFC497-F893-41DE-B7CA-98CB68B610B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07B43407-D572-49C5-9B09-505CBE4DB057}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{934FA03D-99BD-49E0-BFEC-291BD79F4879}"/>
   </bookViews>
@@ -1057,6 +1057,28 @@
         </r>
       </text>
     </comment>
+    <comment ref="G120" authorId="0" shapeId="0" xr:uid="{66602433-5A36-4C7D-8CE5-79F078D29009}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="MS P ゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>kaz
+ 国民厚生年金　　+46
+ パナ年金　　　  +12
+ 確定拠出(明治)  + 2　
+ ﾌﾟﾙﾃﾞﾝｼｬﾙ保険金 + 9
+ 特許報奨金　　　 + 8
+ 東北電力 配当金  + 1
+nao</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="E132" authorId="0" shapeId="0" xr:uid="{D3A0D358-7411-4045-8E31-BB4827CBD402}">
       <text>
         <r>
@@ -1211,6 +1233,48 @@
           </rPr>
           <t>kazへ返済 -17.9 (医療費：1.6、金華山：6.8、雅章会_信州：7.7、ビューカード：0.6、瀬戸神社:0.2，消耗品：0.4、他：0.6)
 naoへ返済 -0.9（医療費：0.7、金華山弁財天：1、慶子土産代返却：-1，森永：0.3）</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G140" authorId="0" shapeId="0" xr:uid="{B4217193-1500-4C79-BD7E-B9E35A8116AF}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="MS P ゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>kazへ返済 -13.1 (医療費：6.7、ビューカード：1.2、瀬戸神社:0.2、電波会：1.5、西源寺:1.1，外食：0.9，他：2.1)
+naoへ返済 -1.3（医療費：1.3，森永：0.2，返却：-0.2）</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L151" authorId="0" shapeId="0" xr:uid="{184EDB87-28C2-496E-A1AE-488732220946}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="MS P ゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>PC_USER:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="MS P ゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
         </r>
       </text>
     </comment>
@@ -4126,6 +4190,121 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" textRotation="255"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="42" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="45" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="23" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="36" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="24" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="35" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="46" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" textRotation="255"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" textRotation="255"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -4135,10 +4314,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" textRotation="255"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" textRotation="255"/>
@@ -4192,117 +4367,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" textRotation="255"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="42" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="23" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" textRotation="255"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="45" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="36" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="24" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="35" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="46" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4559,82 +4623,82 @@
                   <c:v>595</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>498</c:v>
+                  <c:v>518</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>416</c:v>
+                  <c:v>456</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>421</c:v>
+                  <c:v>481</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>289</c:v>
+                  <c:v>369</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>307</c:v>
+                  <c:v>407</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>305</c:v>
+                  <c:v>425</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>303</c:v>
+                  <c:v>443</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>621</c:v>
+                  <c:v>781</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>339</c:v>
+                  <c:v>519</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>357</c:v>
+                  <c:v>557</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>295</c:v>
+                  <c:v>495</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>253</c:v>
+                  <c:v>453</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>112</c:v>
+                  <c:v>312</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-19</c:v>
+                  <c:v>181</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-36</c:v>
+                  <c:v>164</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-73</c:v>
+                  <c:v>127</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-90</c:v>
+                  <c:v>110</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2193</c:v>
+                  <c:v>2393</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2029</c:v>
+                  <c:v>2229</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1865</c:v>
+                  <c:v>2065</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1681</c:v>
+                  <c:v>1881</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>1517</c:v>
+                  <c:v>1717</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>1353</c:v>
+                  <c:v>1553</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>1194</c:v>
+                  <c:v>1394</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>1035</c:v>
+                  <c:v>1235</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>656</c:v>
+                  <c:v>856</c:v>
                 </c:pt>
                 <c:pt idx="28">
                   <c:v>0</c:v>
@@ -7490,7 +7554,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="31"/>
                 <c:pt idx="0">
-                  <c:v>#N/A</c:v>
+                  <c:v>1230</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>#N/A</c:v>
@@ -10942,7 +11006,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="31"/>
                 <c:pt idx="0">
-                  <c:v>#N/A</c:v>
+                  <c:v>536</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>#N/A</c:v>
@@ -11470,82 +11534,82 @@
                   <c:v>585</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>501</c:v>
+                  <c:v>521</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>432</c:v>
+                  <c:v>472</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>450</c:v>
+                  <c:v>510</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>331</c:v>
+                  <c:v>411</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>362</c:v>
+                  <c:v>462</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>373</c:v>
+                  <c:v>493</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>384</c:v>
+                  <c:v>524</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>715</c:v>
+                  <c:v>875</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>446</c:v>
+                  <c:v>626</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>477</c:v>
+                  <c:v>677</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>428</c:v>
+                  <c:v>628</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>399</c:v>
+                  <c:v>599</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>271</c:v>
+                  <c:v>471</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>153</c:v>
+                  <c:v>353</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>149</c:v>
+                  <c:v>349</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>125</c:v>
+                  <c:v>325</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>121</c:v>
+                  <c:v>321</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2417</c:v>
+                  <c:v>2617</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2266</c:v>
+                  <c:v>2466</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>2115</c:v>
+                  <c:v>2315</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1944</c:v>
+                  <c:v>2144</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>1793</c:v>
+                  <c:v>1993</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>1642</c:v>
+                  <c:v>1842</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>1496</c:v>
+                  <c:v>1696</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>1350</c:v>
+                  <c:v>1550</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>984</c:v>
+                  <c:v>1184</c:v>
                 </c:pt>
                 <c:pt idx="28">
                   <c:v>0</c:v>
@@ -14393,7 +14457,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="31"/>
                 <c:pt idx="0">
-                  <c:v>#N/A</c:v>
+                  <c:v>1766</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>#N/A</c:v>
@@ -17005,14 +17069,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{472A185D-039A-4781-AC6E-0DA5DC6C89E1}">
-  <dimension ref="A1:AM145"/>
+  <dimension ref="A1:AM151"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="11" style="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.625" style="5" customWidth="1"/>
     <col min="3" max="3" width="10.375" style="5" customWidth="1"/>
     <col min="4" max="4" width="11" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="69.625" style="5" customWidth="1"/>
+    <col min="5" max="5" width="71" style="5" customWidth="1"/>
     <col min="6" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
@@ -17020,12 +17084,12 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="102" t="s">
+      <c r="B1" s="134" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="103"/>
-      <c r="D1" s="103"/>
-      <c r="E1" s="104"/>
+      <c r="C1" s="135"/>
+      <c r="D1" s="135"/>
+      <c r="E1" s="136"/>
       <c r="F1" s="2" t="s">
         <v>2</v>
       </c>
@@ -17126,13 +17190,13 @@
       <c r="AM1" s="4"/>
     </row>
     <row r="2" spans="1:39" ht="18.75" customHeight="1">
-      <c r="A2" s="105" t="s">
+      <c r="A2" s="102" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="108" t="s">
+      <c r="B2" s="139" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="115"/>
+      <c r="C2" s="146"/>
       <c r="D2" s="6" t="s">
         <v>5</v>
       </c>
@@ -17217,9 +17281,9 @@
       <c r="AM2" s="4"/>
     </row>
     <row r="3" spans="1:39" ht="19.5" thickBot="1">
-      <c r="A3" s="106"/>
-      <c r="B3" s="109"/>
-      <c r="C3" s="116"/>
+      <c r="A3" s="137"/>
+      <c r="B3" s="140"/>
+      <c r="C3" s="147"/>
       <c r="D3" s="9" t="s">
         <v>7</v>
       </c>
@@ -17320,11 +17384,11 @@
       <c r="AM3" s="4"/>
     </row>
     <row r="4" spans="1:39">
-      <c r="A4" s="106"/>
-      <c r="B4" s="108" t="s">
+      <c r="A4" s="137"/>
+      <c r="B4" s="139" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="117"/>
+      <c r="C4" s="148"/>
       <c r="D4" s="12" t="s">
         <v>10</v>
       </c>
@@ -17369,9 +17433,9 @@
       <c r="AM4" s="4"/>
     </row>
     <row r="5" spans="1:39">
-      <c r="A5" s="106"/>
-      <c r="B5" s="110"/>
-      <c r="C5" s="118"/>
+      <c r="A5" s="137"/>
+      <c r="B5" s="141"/>
+      <c r="C5" s="149"/>
       <c r="D5" s="15" t="s">
         <v>12</v>
       </c>
@@ -17416,9 +17480,9 @@
       <c r="AM5" s="4"/>
     </row>
     <row r="6" spans="1:39">
-      <c r="A6" s="106"/>
-      <c r="B6" s="110"/>
-      <c r="C6" s="118"/>
+      <c r="A6" s="137"/>
+      <c r="B6" s="141"/>
+      <c r="C6" s="149"/>
       <c r="D6" s="15"/>
       <c r="E6" s="16"/>
       <c r="F6" s="17"/>
@@ -17457,9 +17521,9 @@
       <c r="AM6" s="4"/>
     </row>
     <row r="7" spans="1:39">
-      <c r="A7" s="106"/>
-      <c r="B7" s="110"/>
-      <c r="C7" s="118"/>
+      <c r="A7" s="137"/>
+      <c r="B7" s="141"/>
+      <c r="C7" s="149"/>
       <c r="D7" s="15"/>
       <c r="E7" s="16"/>
       <c r="F7" s="17"/>
@@ -17498,9 +17562,9 @@
       <c r="AM7" s="4"/>
     </row>
     <row r="8" spans="1:39">
-      <c r="A8" s="106"/>
-      <c r="B8" s="111"/>
-      <c r="C8" s="119"/>
+      <c r="A8" s="137"/>
+      <c r="B8" s="142"/>
+      <c r="C8" s="150"/>
       <c r="D8" s="15"/>
       <c r="E8" s="16"/>
       <c r="F8" s="17"/>
@@ -17539,12 +17603,12 @@
       <c r="AM8" s="4"/>
     </row>
     <row r="9" spans="1:39" ht="19.5" thickBot="1">
-      <c r="A9" s="106"/>
-      <c r="B9" s="112" t="s">
+      <c r="A9" s="137"/>
+      <c r="B9" s="143" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="113"/>
-      <c r="D9" s="114"/>
+      <c r="C9" s="144"/>
+      <c r="D9" s="145"/>
       <c r="E9" s="18" t="s">
         <v>15</v>
       </c>
@@ -17680,11 +17744,11 @@
       <c r="AM9" s="4"/>
     </row>
     <row r="10" spans="1:39">
-      <c r="A10" s="106"/>
-      <c r="B10" s="108" t="s">
+      <c r="A10" s="137"/>
+      <c r="B10" s="139" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="117"/>
+      <c r="C10" s="148"/>
       <c r="D10" s="15" t="s">
         <v>17</v>
       </c>
@@ -17783,9 +17847,9 @@
       <c r="AM10" s="4"/>
     </row>
     <row r="11" spans="1:39">
-      <c r="A11" s="106"/>
-      <c r="B11" s="110"/>
-      <c r="C11" s="118"/>
+      <c r="A11" s="137"/>
+      <c r="B11" s="141"/>
+      <c r="C11" s="149"/>
       <c r="D11" s="15" t="s">
         <v>19</v>
       </c>
@@ -17834,9 +17898,9 @@
       <c r="AM11" s="4"/>
     </row>
     <row r="12" spans="1:39">
-      <c r="A12" s="106"/>
-      <c r="B12" s="110"/>
-      <c r="C12" s="118"/>
+      <c r="A12" s="137"/>
+      <c r="B12" s="141"/>
+      <c r="C12" s="149"/>
       <c r="D12" s="15" t="s">
         <v>21</v>
       </c>
@@ -17907,9 +17971,9 @@
       <c r="AM12" s="4"/>
     </row>
     <row r="13" spans="1:39">
-      <c r="A13" s="106"/>
-      <c r="B13" s="110"/>
-      <c r="C13" s="118"/>
+      <c r="A13" s="137"/>
+      <c r="B13" s="141"/>
+      <c r="C13" s="149"/>
       <c r="D13" s="15" t="s">
         <v>22</v>
       </c>
@@ -17958,9 +18022,9 @@
       <c r="AM13" s="4"/>
     </row>
     <row r="14" spans="1:39">
-      <c r="A14" s="106"/>
-      <c r="B14" s="111"/>
-      <c r="C14" s="119"/>
+      <c r="A14" s="137"/>
+      <c r="B14" s="142"/>
+      <c r="C14" s="150"/>
       <c r="D14" s="15"/>
       <c r="E14" s="16"/>
       <c r="F14" s="23"/>
@@ -17999,12 +18063,12 @@
       <c r="AM14" s="4"/>
     </row>
     <row r="15" spans="1:39" ht="19.5" thickBot="1">
-      <c r="A15" s="107"/>
-      <c r="B15" s="112" t="s">
+      <c r="A15" s="138"/>
+      <c r="B15" s="143" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="113"/>
-      <c r="D15" s="114"/>
+      <c r="C15" s="144"/>
+      <c r="D15" s="145"/>
       <c r="E15" s="18" t="s">
         <v>25</v>
       </c>
@@ -18140,16 +18204,16 @@
       <c r="AM15" s="4"/>
     </row>
     <row r="16" spans="1:39">
-      <c r="A16" s="105" t="s">
+      <c r="A16" s="102" t="s">
         <v>152</v>
       </c>
-      <c r="B16" s="139" t="s">
+      <c r="B16" s="132" t="s">
         <v>131</v>
       </c>
-      <c r="C16" s="121" t="s">
+      <c r="C16" s="123" t="s">
         <v>107</v>
       </c>
-      <c r="D16" s="123" t="s">
+      <c r="D16" s="124" t="s">
         <v>111</v>
       </c>
       <c r="E16" s="16" t="s">
@@ -18231,10 +18295,10 @@
       <c r="AM16" s="4"/>
     </row>
     <row r="17" spans="1:39">
-      <c r="A17" s="141"/>
-      <c r="B17" s="137"/>
-      <c r="C17" s="122"/>
-      <c r="D17" s="122"/>
+      <c r="A17" s="103"/>
+      <c r="B17" s="130"/>
+      <c r="C17" s="115"/>
+      <c r="D17" s="115"/>
       <c r="E17" s="16" t="s">
         <v>29</v>
       </c>
@@ -18320,12 +18384,12 @@
       <c r="AM17" s="4"/>
     </row>
     <row r="18" spans="1:39">
-      <c r="A18" s="141"/>
-      <c r="B18" s="137"/>
-      <c r="C18" s="124" t="s">
+      <c r="A18" s="103"/>
+      <c r="B18" s="130"/>
+      <c r="C18" s="114" t="s">
         <v>108</v>
       </c>
-      <c r="D18" s="126" t="s">
+      <c r="D18" s="116" t="s">
         <v>113</v>
       </c>
       <c r="E18" s="13" t="s">
@@ -18407,10 +18471,10 @@
       <c r="AM18" s="27"/>
     </row>
     <row r="19" spans="1:39">
-      <c r="A19" s="141"/>
-      <c r="B19" s="137"/>
-      <c r="C19" s="125"/>
-      <c r="D19" s="125"/>
+      <c r="A19" s="103"/>
+      <c r="B19" s="130"/>
+      <c r="C19" s="117"/>
+      <c r="D19" s="117"/>
       <c r="E19" s="16" t="s">
         <v>27</v>
       </c>
@@ -18478,10 +18542,10 @@
       <c r="AM19" s="27"/>
     </row>
     <row r="20" spans="1:39">
-      <c r="A20" s="141"/>
-      <c r="B20" s="137"/>
-      <c r="C20" s="125"/>
-      <c r="D20" s="122"/>
+      <c r="A20" s="103"/>
+      <c r="B20" s="130"/>
+      <c r="C20" s="117"/>
+      <c r="D20" s="115"/>
       <c r="E20" s="16" t="s">
         <v>28</v>
       </c>
@@ -18531,9 +18595,9 @@
       <c r="AM20" s="27"/>
     </row>
     <row r="21" spans="1:39">
-      <c r="A21" s="141"/>
-      <c r="B21" s="137"/>
-      <c r="C21" s="122"/>
+      <c r="A21" s="103"/>
+      <c r="B21" s="130"/>
+      <c r="C21" s="115"/>
       <c r="D21" s="57" t="s">
         <v>114</v>
       </c>
@@ -18584,9 +18648,9 @@
       <c r="AM21" s="27"/>
     </row>
     <row r="22" spans="1:39">
-      <c r="A22" s="141"/>
-      <c r="B22" s="137"/>
-      <c r="C22" s="124" t="s">
+      <c r="A22" s="103"/>
+      <c r="B22" s="130"/>
+      <c r="C22" s="114" t="s">
         <v>109</v>
       </c>
       <c r="D22" s="57" t="s">
@@ -18631,9 +18695,9 @@
       <c r="AM22" s="27"/>
     </row>
     <row r="23" spans="1:39">
-      <c r="A23" s="141"/>
-      <c r="B23" s="137"/>
-      <c r="C23" s="122"/>
+      <c r="A23" s="103"/>
+      <c r="B23" s="130"/>
+      <c r="C23" s="115"/>
       <c r="D23" s="57" t="s">
         <v>116</v>
       </c>
@@ -18676,12 +18740,12 @@
       <c r="AM23" s="27"/>
     </row>
     <row r="24" spans="1:39">
-      <c r="A24" s="141"/>
-      <c r="B24" s="137"/>
-      <c r="C24" s="124" t="s">
+      <c r="A24" s="103"/>
+      <c r="B24" s="130"/>
+      <c r="C24" s="114" t="s">
         <v>110</v>
       </c>
-      <c r="D24" s="126" t="s">
+      <c r="D24" s="116" t="s">
         <v>117</v>
       </c>
       <c r="E24" s="16" t="s">
@@ -18763,10 +18827,10 @@
       <c r="AM24" s="27"/>
     </row>
     <row r="25" spans="1:39">
-      <c r="A25" s="141"/>
-      <c r="B25" s="137"/>
-      <c r="C25" s="125"/>
-      <c r="D25" s="125"/>
+      <c r="A25" s="103"/>
+      <c r="B25" s="130"/>
+      <c r="C25" s="117"/>
+      <c r="D25" s="117"/>
       <c r="E25" s="16" t="s">
         <v>32</v>
       </c>
@@ -18858,10 +18922,10 @@
       <c r="AM25" s="27"/>
     </row>
     <row r="26" spans="1:39">
-      <c r="A26" s="141"/>
-      <c r="B26" s="137"/>
-      <c r="C26" s="125"/>
-      <c r="D26" s="125"/>
+      <c r="A26" s="103"/>
+      <c r="B26" s="130"/>
+      <c r="C26" s="117"/>
+      <c r="D26" s="117"/>
       <c r="E26" s="16" t="s">
         <v>33</v>
       </c>
@@ -18903,10 +18967,10 @@
       <c r="AM26" s="27"/>
     </row>
     <row r="27" spans="1:39">
-      <c r="A27" s="141"/>
-      <c r="B27" s="137"/>
-      <c r="C27" s="125"/>
-      <c r="D27" s="125"/>
+      <c r="A27" s="103"/>
+      <c r="B27" s="130"/>
+      <c r="C27" s="117"/>
+      <c r="D27" s="117"/>
       <c r="E27" s="29" t="s">
         <v>34</v>
       </c>
@@ -18948,10 +19012,10 @@
       <c r="AM27" s="27"/>
     </row>
     <row r="28" spans="1:39">
-      <c r="A28" s="141"/>
-      <c r="B28" s="137"/>
-      <c r="C28" s="125"/>
-      <c r="D28" s="125"/>
+      <c r="A28" s="103"/>
+      <c r="B28" s="130"/>
+      <c r="C28" s="117"/>
+      <c r="D28" s="117"/>
       <c r="E28" s="16" t="s">
         <v>35</v>
       </c>
@@ -18959,34 +19023,34 @@
       <c r="G28" s="26"/>
       <c r="H28" s="26"/>
       <c r="I28" s="26">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="J28" s="26">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="K28" s="26">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="L28" s="26">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="M28" s="26">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="N28" s="26">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="O28" s="26">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="P28" s="26">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="Q28" s="26">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="R28" s="26">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="S28" s="26"/>
       <c r="T28" s="26"/>
@@ -19011,10 +19075,10 @@
       <c r="AM28" s="27"/>
     </row>
     <row r="29" spans="1:39">
-      <c r="A29" s="141"/>
-      <c r="B29" s="137"/>
-      <c r="C29" s="125"/>
-      <c r="D29" s="122"/>
+      <c r="A29" s="103"/>
+      <c r="B29" s="130"/>
+      <c r="C29" s="117"/>
+      <c r="D29" s="115"/>
       <c r="E29" s="86" t="s">
         <v>119</v>
       </c>
@@ -19056,9 +19120,9 @@
       <c r="AM29" s="27"/>
     </row>
     <row r="30" spans="1:39">
-      <c r="A30" s="141"/>
-      <c r="B30" s="137"/>
-      <c r="C30" s="125"/>
+      <c r="A30" s="103"/>
+      <c r="B30" s="130"/>
+      <c r="C30" s="117"/>
       <c r="D30" s="57" t="s">
         <v>121</v>
       </c>
@@ -19101,9 +19165,9 @@
       <c r="AM30" s="27"/>
     </row>
     <row r="31" spans="1:39">
-      <c r="A31" s="141"/>
-      <c r="B31" s="138"/>
-      <c r="C31" s="122"/>
+      <c r="A31" s="103"/>
+      <c r="B31" s="131"/>
+      <c r="C31" s="115"/>
       <c r="D31" s="57" t="s">
         <v>122</v>
       </c>
@@ -19146,11 +19210,11 @@
       <c r="AM31" s="27"/>
     </row>
     <row r="32" spans="1:39">
-      <c r="A32" s="141"/>
-      <c r="B32" s="149" t="s">
+      <c r="A32" s="103"/>
+      <c r="B32" s="120" t="s">
         <v>130</v>
       </c>
-      <c r="C32" s="127"/>
+      <c r="C32" s="111"/>
       <c r="D32" s="17" t="s">
         <v>127</v>
       </c>
@@ -19249,9 +19313,9 @@
       <c r="AM32" s="27"/>
     </row>
     <row r="33" spans="1:39">
-      <c r="A33" s="141"/>
-      <c r="B33" s="150"/>
-      <c r="C33" s="129"/>
+      <c r="A33" s="103"/>
+      <c r="B33" s="121"/>
+      <c r="C33" s="113"/>
       <c r="D33" s="17" t="s">
         <v>128</v>
       </c>
@@ -19326,12 +19390,12 @@
       <c r="AM33" s="27"/>
     </row>
     <row r="34" spans="1:39">
-      <c r="A34" s="141"/>
-      <c r="B34" s="130" t="s">
+      <c r="A34" s="103"/>
+      <c r="B34" s="105" t="s">
         <v>9</v>
       </c>
-      <c r="C34" s="133"/>
-      <c r="D34" s="145"/>
+      <c r="C34" s="107"/>
+      <c r="D34" s="109"/>
       <c r="E34" s="34" t="str">
         <f t="shared" ref="E34:AK34" si="2">E4</f>
         <v>新潟実家の売却益　（妙子と折半）</v>
@@ -19468,10 +19532,10 @@
       <c r="AM34" s="27"/>
     </row>
     <row r="35" spans="1:39">
-      <c r="A35" s="141"/>
-      <c r="B35" s="143"/>
-      <c r="C35" s="144"/>
-      <c r="D35" s="146"/>
+      <c r="A35" s="103"/>
+      <c r="B35" s="106"/>
+      <c r="C35" s="108"/>
+      <c r="D35" s="110"/>
       <c r="E35" s="34" t="str">
         <f>E5</f>
         <v>横浜マンションの売却益</v>
@@ -19608,10 +19672,10 @@
       <c r="AM35" s="27"/>
     </row>
     <row r="36" spans="1:39">
-      <c r="A36" s="141"/>
-      <c r="B36" s="143"/>
-      <c r="C36" s="144"/>
-      <c r="D36" s="146"/>
+      <c r="A36" s="103"/>
+      <c r="B36" s="106"/>
+      <c r="C36" s="108"/>
+      <c r="D36" s="110"/>
       <c r="E36" s="99" t="s">
         <v>151</v>
       </c>
@@ -19654,7 +19718,7 @@
       <c r="AM36" s="27"/>
     </row>
     <row r="37" spans="1:39" ht="19.5" thickBot="1">
-      <c r="A37" s="141"/>
+      <c r="A37" s="103"/>
       <c r="B37" s="35" t="s">
         <v>37</v>
       </c>
@@ -19675,43 +19739,43 @@
       </c>
       <c r="I37" s="35">
         <f t="shared" si="4"/>
-        <v>565</v>
+        <v>585</v>
       </c>
       <c r="J37" s="35">
         <f t="shared" si="4"/>
-        <v>565</v>
+        <v>585</v>
       </c>
       <c r="K37" s="35">
         <f t="shared" si="4"/>
-        <v>648</v>
+        <v>668</v>
       </c>
       <c r="L37" s="35">
         <f t="shared" si="4"/>
-        <v>643</v>
+        <v>663</v>
       </c>
       <c r="M37" s="35">
         <f t="shared" si="4"/>
-        <v>643</v>
+        <v>663</v>
       </c>
       <c r="N37" s="35">
         <f t="shared" si="4"/>
-        <v>643</v>
+        <v>663</v>
       </c>
       <c r="O37" s="35">
         <f t="shared" si="4"/>
-        <v>643</v>
+        <v>663</v>
       </c>
       <c r="P37" s="35">
         <f t="shared" si="4"/>
-        <v>1143</v>
+        <v>1163</v>
       </c>
       <c r="Q37" s="35">
         <f t="shared" si="4"/>
-        <v>643</v>
+        <v>663</v>
       </c>
       <c r="R37" s="35">
         <f t="shared" si="4"/>
-        <v>643</v>
+        <v>663</v>
       </c>
       <c r="S37" s="35">
         <f t="shared" si="4"/>
@@ -19793,8 +19857,8 @@
       <c r="AM37" s="27"/>
     </row>
     <row r="38" spans="1:39" ht="18.75" customHeight="1">
-      <c r="A38" s="141"/>
-      <c r="B38" s="136" t="s">
+      <c r="A38" s="103"/>
+      <c r="B38" s="129" t="s">
         <v>132</v>
       </c>
       <c r="C38" s="8" t="s">
@@ -19844,9 +19908,9 @@
       <c r="AM38" s="4"/>
     </row>
     <row r="39" spans="1:39">
-      <c r="A39" s="141"/>
-      <c r="B39" s="137"/>
-      <c r="C39" s="124" t="s">
+      <c r="A39" s="103"/>
+      <c r="B39" s="130"/>
+      <c r="C39" s="114" t="s">
         <v>108</v>
       </c>
       <c r="D39" s="57" t="s">
@@ -19891,9 +19955,9 @@
       <c r="AM39" s="4"/>
     </row>
     <row r="40" spans="1:39">
-      <c r="A40" s="141"/>
-      <c r="B40" s="137"/>
-      <c r="C40" s="122"/>
+      <c r="A40" s="103"/>
+      <c r="B40" s="130"/>
+      <c r="C40" s="115"/>
       <c r="D40" s="57" t="s">
         <v>114</v>
       </c>
@@ -19936,9 +20000,9 @@
       <c r="AM40" s="4"/>
     </row>
     <row r="41" spans="1:39">
-      <c r="A41" s="141"/>
-      <c r="B41" s="137"/>
-      <c r="C41" s="124" t="s">
+      <c r="A41" s="103"/>
+      <c r="B41" s="130"/>
+      <c r="C41" s="114" t="s">
         <v>109</v>
       </c>
       <c r="D41" s="57" t="s">
@@ -20039,9 +20103,9 @@
       <c r="AM41" s="27"/>
     </row>
     <row r="42" spans="1:39">
-      <c r="A42" s="141"/>
-      <c r="B42" s="137"/>
-      <c r="C42" s="122"/>
+      <c r="A42" s="103"/>
+      <c r="B42" s="130"/>
+      <c r="C42" s="115"/>
       <c r="D42" s="57" t="s">
         <v>116</v>
       </c>
@@ -20084,12 +20148,12 @@
       <c r="AM42" s="4"/>
     </row>
     <row r="43" spans="1:39">
-      <c r="A43" s="141"/>
-      <c r="B43" s="137"/>
-      <c r="C43" s="124" t="s">
+      <c r="A43" s="103"/>
+      <c r="B43" s="130"/>
+      <c r="C43" s="114" t="s">
         <v>110</v>
       </c>
-      <c r="D43" s="126" t="s">
+      <c r="D43" s="116" t="s">
         <v>117</v>
       </c>
       <c r="E43" s="16" t="s">
@@ -20134,10 +20198,10 @@
       <c r="AM43" s="27"/>
     </row>
     <row r="44" spans="1:39">
-      <c r="A44" s="141"/>
-      <c r="B44" s="137"/>
-      <c r="C44" s="125"/>
-      <c r="D44" s="125"/>
+      <c r="A44" s="103"/>
+      <c r="B44" s="130"/>
+      <c r="C44" s="117"/>
+      <c r="D44" s="117"/>
       <c r="E44" s="16" t="s">
         <v>48</v>
       </c>
@@ -20217,10 +20281,10 @@
       <c r="AM44" s="27"/>
     </row>
     <row r="45" spans="1:39">
-      <c r="A45" s="141"/>
-      <c r="B45" s="137"/>
-      <c r="C45" s="125"/>
-      <c r="D45" s="125"/>
+      <c r="A45" s="103"/>
+      <c r="B45" s="130"/>
+      <c r="C45" s="117"/>
+      <c r="D45" s="117"/>
       <c r="E45" s="16" t="s">
         <v>49</v>
       </c>
@@ -20292,10 +20356,10 @@
       <c r="AM45" s="27"/>
     </row>
     <row r="46" spans="1:39">
-      <c r="A46" s="141"/>
-      <c r="B46" s="137"/>
-      <c r="C46" s="125"/>
-      <c r="D46" s="122"/>
+      <c r="A46" s="103"/>
+      <c r="B46" s="130"/>
+      <c r="C46" s="117"/>
+      <c r="D46" s="115"/>
       <c r="E46" s="86" t="s">
         <v>123</v>
       </c>
@@ -20345,9 +20409,9 @@
       <c r="AM46" s="27"/>
     </row>
     <row r="47" spans="1:39">
-      <c r="A47" s="141"/>
-      <c r="B47" s="137"/>
-      <c r="C47" s="125"/>
+      <c r="A47" s="103"/>
+      <c r="B47" s="130"/>
+      <c r="C47" s="117"/>
       <c r="D47" s="57" t="s">
         <v>121</v>
       </c>
@@ -20440,9 +20504,9 @@
       <c r="AM47" s="27"/>
     </row>
     <row r="48" spans="1:39">
-      <c r="A48" s="141"/>
-      <c r="B48" s="138"/>
-      <c r="C48" s="122"/>
+      <c r="A48" s="103"/>
+      <c r="B48" s="131"/>
+      <c r="C48" s="115"/>
       <c r="D48" s="57" t="s">
         <v>122</v>
       </c>
@@ -20485,7 +20549,7 @@
       <c r="AM48" s="4"/>
     </row>
     <row r="49" spans="1:39">
-      <c r="A49" s="141"/>
+      <c r="A49" s="103"/>
       <c r="B49" s="66" t="s">
         <v>44</v>
       </c>
@@ -20570,7 +20634,7 @@
       <c r="AM49" s="27"/>
     </row>
     <row r="50" spans="1:39">
-      <c r="A50" s="141"/>
+      <c r="A50" s="103"/>
       <c r="B50" s="66" t="s">
         <v>51</v>
       </c>
@@ -20671,7 +20735,7 @@
       <c r="AM50" s="27"/>
     </row>
     <row r="51" spans="1:39">
-      <c r="A51" s="141"/>
+      <c r="A51" s="103"/>
       <c r="B51" s="66" t="s">
         <v>53</v>
       </c>
@@ -20772,11 +20836,11 @@
       <c r="AM51" s="27"/>
     </row>
     <row r="52" spans="1:39">
-      <c r="A52" s="141"/>
-      <c r="B52" s="135" t="s">
+      <c r="A52" s="103"/>
+      <c r="B52" s="128" t="s">
         <v>124</v>
       </c>
-      <c r="C52" s="127"/>
+      <c r="C52" s="111"/>
       <c r="D52" s="15" t="s">
         <v>42</v>
       </c>
@@ -20859,9 +20923,9 @@
       <c r="AM52" s="27"/>
     </row>
     <row r="53" spans="1:39">
-      <c r="A53" s="141"/>
-      <c r="B53" s="131"/>
-      <c r="C53" s="128"/>
+      <c r="A53" s="103"/>
+      <c r="B53" s="125"/>
+      <c r="C53" s="112"/>
       <c r="D53" s="15" t="s">
         <v>38</v>
       </c>
@@ -20906,9 +20970,9 @@
       <c r="AM53" s="27"/>
     </row>
     <row r="54" spans="1:39">
-      <c r="A54" s="141"/>
-      <c r="B54" s="132"/>
-      <c r="C54" s="129"/>
+      <c r="A54" s="103"/>
+      <c r="B54" s="126"/>
+      <c r="C54" s="113"/>
       <c r="D54" s="15" t="s">
         <v>40</v>
       </c>
@@ -21007,7 +21071,7 @@
       <c r="AM54" s="27"/>
     </row>
     <row r="55" spans="1:39">
-      <c r="A55" s="141"/>
+      <c r="A55" s="103"/>
       <c r="B55" s="84" t="s">
         <v>140</v>
       </c>
@@ -21110,11 +21174,11 @@
       <c r="AM55" s="27"/>
     </row>
     <row r="56" spans="1:39">
-      <c r="A56" s="141"/>
-      <c r="B56" s="147" t="s">
+      <c r="A56" s="103"/>
+      <c r="B56" s="118" t="s">
         <v>146</v>
       </c>
-      <c r="C56" s="148"/>
+      <c r="C56" s="119"/>
       <c r="D56" s="78" t="s">
         <v>126</v>
       </c>
@@ -21237,7 +21301,7 @@
       <c r="AM56" s="27"/>
     </row>
     <row r="57" spans="1:39">
-      <c r="A57" s="141"/>
+      <c r="A57" s="103"/>
       <c r="B57" s="67" t="s">
         <v>57</v>
       </c>
@@ -21366,7 +21430,7 @@
       <c r="AM57" s="27"/>
     </row>
     <row r="58" spans="1:39">
-      <c r="A58" s="141"/>
+      <c r="A58" s="103"/>
       <c r="B58" s="67" t="s">
         <v>59</v>
       </c>
@@ -21384,43 +21448,43 @@
       </c>
       <c r="I58" s="35">
         <f t="shared" si="6"/>
-        <v>-97</v>
+        <v>-77</v>
       </c>
       <c r="J58" s="35">
         <f t="shared" si="6"/>
-        <v>-82</v>
+        <v>-62</v>
       </c>
       <c r="K58" s="35">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="L58" s="35">
         <f t="shared" si="6"/>
-        <v>-132</v>
+        <v>-112</v>
       </c>
       <c r="M58" s="35">
         <f t="shared" si="6"/>
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="N58" s="35">
         <f t="shared" si="6"/>
-        <v>-2</v>
+        <v>18</v>
       </c>
       <c r="O58" s="35">
         <f t="shared" si="6"/>
-        <v>-2</v>
+        <v>18</v>
       </c>
       <c r="P58" s="35">
         <f t="shared" si="6"/>
-        <v>318</v>
+        <v>338</v>
       </c>
       <c r="Q58" s="35">
         <f t="shared" si="6"/>
-        <v>-282</v>
+        <v>-262</v>
       </c>
       <c r="R58" s="35">
         <f t="shared" si="6"/>
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="S58" s="35">
         <f t="shared" si="6"/>
@@ -21493,7 +21557,7 @@
       <c r="AM58" s="27"/>
     </row>
     <row r="59" spans="1:39" ht="19.5" thickBot="1">
-      <c r="A59" s="142"/>
+      <c r="A59" s="104"/>
       <c r="B59" s="61" t="s">
         <v>60</v>
       </c>
@@ -21513,107 +21577,107 @@
       </c>
       <c r="I59" s="44">
         <f t="shared" si="7"/>
-        <v>498</v>
+        <v>518</v>
       </c>
       <c r="J59" s="44">
         <f t="shared" si="7"/>
-        <v>416</v>
+        <v>456</v>
       </c>
       <c r="K59" s="44">
         <f t="shared" si="7"/>
-        <v>421</v>
+        <v>481</v>
       </c>
       <c r="L59" s="44">
         <f t="shared" si="7"/>
-        <v>289</v>
+        <v>369</v>
       </c>
       <c r="M59" s="44">
         <f t="shared" si="7"/>
-        <v>307</v>
+        <v>407</v>
       </c>
       <c r="N59" s="44">
         <f t="shared" si="7"/>
-        <v>305</v>
+        <v>425</v>
       </c>
       <c r="O59" s="44">
         <f t="shared" si="7"/>
-        <v>303</v>
+        <v>443</v>
       </c>
       <c r="P59" s="44">
         <f t="shared" si="7"/>
-        <v>621</v>
+        <v>781</v>
       </c>
       <c r="Q59" s="44">
         <f t="shared" si="7"/>
-        <v>339</v>
+        <v>519</v>
       </c>
       <c r="R59" s="44">
         <f t="shared" si="7"/>
-        <v>357</v>
+        <v>557</v>
       </c>
       <c r="S59" s="44">
         <f t="shared" si="7"/>
-        <v>295</v>
+        <v>495</v>
       </c>
       <c r="T59" s="44">
         <f t="shared" si="7"/>
-        <v>253</v>
+        <v>453</v>
       </c>
       <c r="U59" s="44">
         <f t="shared" si="7"/>
-        <v>112</v>
+        <v>312</v>
       </c>
       <c r="V59" s="44">
         <f t="shared" si="7"/>
-        <v>-19</v>
+        <v>181</v>
       </c>
       <c r="W59" s="44">
         <f t="shared" si="7"/>
-        <v>-36</v>
+        <v>164</v>
       </c>
       <c r="X59" s="44">
         <f t="shared" si="7"/>
-        <v>-73</v>
+        <v>127</v>
       </c>
       <c r="Y59" s="44">
         <f t="shared" si="7"/>
-        <v>-90</v>
+        <v>110</v>
       </c>
       <c r="Z59" s="44">
         <f t="shared" si="7"/>
-        <v>2193</v>
+        <v>2393</v>
       </c>
       <c r="AA59" s="44">
         <f t="shared" si="7"/>
-        <v>2029</v>
+        <v>2229</v>
       </c>
       <c r="AB59" s="44">
         <f t="shared" si="7"/>
-        <v>1865</v>
+        <v>2065</v>
       </c>
       <c r="AC59" s="44">
         <f t="shared" si="7"/>
-        <v>1681</v>
+        <v>1881</v>
       </c>
       <c r="AD59" s="44">
         <f t="shared" si="7"/>
-        <v>1517</v>
+        <v>1717</v>
       </c>
       <c r="AE59" s="44">
         <f t="shared" si="7"/>
-        <v>1353</v>
+        <v>1553</v>
       </c>
       <c r="AF59" s="44">
         <f t="shared" si="7"/>
-        <v>1194</v>
+        <v>1394</v>
       </c>
       <c r="AG59" s="44">
         <f t="shared" si="7"/>
-        <v>1035</v>
+        <v>1235</v>
       </c>
       <c r="AH59" s="44">
         <f t="shared" si="7"/>
-        <v>656</v>
+        <v>856</v>
       </c>
       <c r="AI59" s="44"/>
       <c r="AJ59" s="44"/>
@@ -21622,7 +21686,7 @@
       <c r="AM59" s="27"/>
     </row>
     <row r="60" spans="1:39" ht="18.75" customHeight="1">
-      <c r="A60" s="105" t="s">
+      <c r="A60" s="102" t="s">
         <v>61</v>
       </c>
       <c r="B60" s="81" t="s">
@@ -21756,7 +21820,7 @@
       <c r="AM60" s="27"/>
     </row>
     <row r="61" spans="1:39" ht="19.5" thickBot="1">
-      <c r="A61" s="140"/>
+      <c r="A61" s="133"/>
       <c r="B61" s="61" t="s">
         <v>37</v>
       </c>
@@ -21885,7 +21949,7 @@
       <c r="AM61" s="27"/>
     </row>
     <row r="62" spans="1:39">
-      <c r="A62" s="140"/>
+      <c r="A62" s="133"/>
       <c r="B62" s="68" t="s">
         <v>137</v>
       </c>
@@ -21936,11 +22000,11 @@
       <c r="AM62" s="27"/>
     </row>
     <row r="63" spans="1:39">
-      <c r="A63" s="140"/>
-      <c r="B63" s="134" t="s">
+      <c r="A63" s="133"/>
+      <c r="B63" s="127" t="s">
         <v>124</v>
       </c>
-      <c r="C63" s="127"/>
+      <c r="C63" s="111"/>
       <c r="D63" s="72" t="s">
         <v>63</v>
       </c>
@@ -22039,9 +22103,9 @@
       <c r="AM63" s="27"/>
     </row>
     <row r="64" spans="1:39">
-      <c r="A64" s="140"/>
-      <c r="B64" s="131"/>
-      <c r="C64" s="128"/>
+      <c r="A64" s="133"/>
+      <c r="B64" s="125"/>
+      <c r="C64" s="112"/>
       <c r="D64" s="15" t="s">
         <v>65</v>
       </c>
@@ -22140,9 +22204,9 @@
       <c r="AM64" s="27"/>
     </row>
     <row r="65" spans="1:39">
-      <c r="A65" s="140"/>
-      <c r="B65" s="131"/>
-      <c r="C65" s="128"/>
+      <c r="A65" s="133"/>
+      <c r="B65" s="125"/>
+      <c r="C65" s="112"/>
       <c r="D65" s="15" t="s">
         <v>67</v>
       </c>
@@ -22241,9 +22305,9 @@
       <c r="AM65" s="27"/>
     </row>
     <row r="66" spans="1:39">
-      <c r="A66" s="140"/>
-      <c r="B66" s="131"/>
-      <c r="C66" s="128"/>
+      <c r="A66" s="133"/>
+      <c r="B66" s="125"/>
+      <c r="C66" s="112"/>
       <c r="D66" s="15" t="s">
         <v>69</v>
       </c>
@@ -22342,9 +22406,9 @@
       <c r="AM66" s="27"/>
     </row>
     <row r="67" spans="1:39">
-      <c r="A67" s="140"/>
-      <c r="B67" s="131"/>
-      <c r="C67" s="128"/>
+      <c r="A67" s="133"/>
+      <c r="B67" s="125"/>
+      <c r="C67" s="112"/>
       <c r="D67" s="15" t="s">
         <v>53</v>
       </c>
@@ -22443,9 +22507,9 @@
       <c r="AM67" s="27"/>
     </row>
     <row r="68" spans="1:39">
-      <c r="A68" s="140"/>
-      <c r="B68" s="131"/>
-      <c r="C68" s="128"/>
+      <c r="A68" s="133"/>
+      <c r="B68" s="125"/>
+      <c r="C68" s="112"/>
       <c r="D68" s="15" t="s">
         <v>72</v>
       </c>
@@ -22544,9 +22608,9 @@
       <c r="AM68" s="27"/>
     </row>
     <row r="69" spans="1:39">
-      <c r="A69" s="140"/>
-      <c r="B69" s="131"/>
-      <c r="C69" s="128"/>
+      <c r="A69" s="133"/>
+      <c r="B69" s="125"/>
+      <c r="C69" s="112"/>
       <c r="D69" s="15" t="s">
         <v>74</v>
       </c>
@@ -22645,9 +22709,9 @@
       <c r="AM69" s="27"/>
     </row>
     <row r="70" spans="1:39">
-      <c r="A70" s="140"/>
-      <c r="B70" s="131"/>
-      <c r="C70" s="128"/>
+      <c r="A70" s="133"/>
+      <c r="B70" s="125"/>
+      <c r="C70" s="112"/>
       <c r="D70" s="15" t="s">
         <v>76</v>
       </c>
@@ -22746,9 +22810,9 @@
       <c r="AM70" s="27"/>
     </row>
     <row r="71" spans="1:39">
-      <c r="A71" s="140"/>
-      <c r="B71" s="131"/>
-      <c r="C71" s="128"/>
+      <c r="A71" s="133"/>
+      <c r="B71" s="125"/>
+      <c r="C71" s="112"/>
       <c r="D71" s="15" t="s">
         <v>78</v>
       </c>
@@ -22847,10 +22911,10 @@
       <c r="AM71" s="27"/>
     </row>
     <row r="72" spans="1:39">
-      <c r="A72" s="140"/>
-      <c r="B72" s="131"/>
-      <c r="C72" s="128"/>
-      <c r="D72" s="124" t="s">
+      <c r="A72" s="133"/>
+      <c r="B72" s="125"/>
+      <c r="C72" s="112"/>
+      <c r="D72" s="114" t="s">
         <v>81</v>
       </c>
       <c r="E72" s="16" t="s">
@@ -22952,10 +23016,10 @@
       <c r="AM72" s="27"/>
     </row>
     <row r="73" spans="1:39">
-      <c r="A73" s="140"/>
-      <c r="B73" s="132"/>
-      <c r="C73" s="129"/>
-      <c r="D73" s="122"/>
+      <c r="A73" s="133"/>
+      <c r="B73" s="126"/>
+      <c r="C73" s="113"/>
+      <c r="D73" s="115"/>
       <c r="E73" s="16" t="s">
         <v>83</v>
       </c>
@@ -23055,11 +23119,11 @@
       <c r="AM73" s="27"/>
     </row>
     <row r="74" spans="1:39">
-      <c r="A74" s="140"/>
-      <c r="B74" s="130" t="s">
+      <c r="A74" s="133"/>
+      <c r="B74" s="105" t="s">
         <v>16</v>
       </c>
-      <c r="C74" s="133"/>
+      <c r="C74" s="107"/>
       <c r="D74" s="33" t="s">
         <v>133</v>
       </c>
@@ -23189,9 +23253,9 @@
       <c r="AM74" s="27"/>
     </row>
     <row r="75" spans="1:39">
-      <c r="A75" s="140"/>
-      <c r="B75" s="131"/>
-      <c r="C75" s="128"/>
+      <c r="A75" s="133"/>
+      <c r="B75" s="125"/>
+      <c r="C75" s="112"/>
       <c r="D75" s="33" t="s">
         <v>134</v>
       </c>
@@ -23321,9 +23385,9 @@
       <c r="AM75" s="27"/>
     </row>
     <row r="76" spans="1:39">
-      <c r="A76" s="140"/>
-      <c r="B76" s="131"/>
-      <c r="C76" s="128"/>
+      <c r="A76" s="133"/>
+      <c r="B76" s="125"/>
+      <c r="C76" s="112"/>
       <c r="D76" s="33" t="s">
         <v>135</v>
       </c>
@@ -23453,9 +23517,9 @@
       <c r="AM76" s="27"/>
     </row>
     <row r="77" spans="1:39">
-      <c r="A77" s="140"/>
-      <c r="B77" s="132"/>
-      <c r="C77" s="129"/>
+      <c r="A77" s="133"/>
+      <c r="B77" s="126"/>
+      <c r="C77" s="113"/>
       <c r="D77" s="33" t="s">
         <v>136</v>
       </c>
@@ -23585,7 +23649,7 @@
       <c r="AM77" s="27"/>
     </row>
     <row r="78" spans="1:39">
-      <c r="A78" s="140"/>
+      <c r="A78" s="133"/>
       <c r="B78" s="67" t="s">
         <v>57</v>
       </c>
@@ -23715,7 +23779,7 @@
       <c r="AM78" s="27"/>
     </row>
     <row r="79" spans="1:39">
-      <c r="A79" s="140"/>
+      <c r="A79" s="133"/>
       <c r="B79" s="67" t="s">
         <v>59</v>
       </c>
@@ -23844,7 +23908,7 @@
       <c r="AM79" s="27"/>
     </row>
     <row r="80" spans="1:39" ht="19.5" thickBot="1">
-      <c r="A80" s="120"/>
+      <c r="A80" s="122"/>
       <c r="B80" s="61" t="s">
         <v>60</v>
       </c>
@@ -23973,7 +24037,7 @@
       <c r="AM80" s="27"/>
     </row>
     <row r="81" spans="1:39">
-      <c r="A81" s="105" t="s">
+      <c r="A81" s="102" t="s">
         <v>88</v>
       </c>
       <c r="B81" s="59" t="s">
@@ -23996,43 +24060,43 @@
       </c>
       <c r="I81" s="47">
         <f t="shared" si="17"/>
-        <v>-84</v>
+        <v>-64</v>
       </c>
       <c r="J81" s="47">
         <f t="shared" si="17"/>
-        <v>-69</v>
+        <v>-49</v>
       </c>
       <c r="K81" s="47">
         <f t="shared" si="17"/>
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="L81" s="47">
         <f t="shared" si="17"/>
-        <v>-119</v>
+        <v>-99</v>
       </c>
       <c r="M81" s="47">
         <f t="shared" si="17"/>
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="N81" s="47">
         <f t="shared" si="17"/>
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="O81" s="47">
         <f t="shared" si="17"/>
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="P81" s="47">
         <f t="shared" si="17"/>
-        <v>331</v>
+        <v>351</v>
       </c>
       <c r="Q81" s="47">
         <f t="shared" si="17"/>
-        <v>-269</v>
+        <v>-249</v>
       </c>
       <c r="R81" s="47">
         <f t="shared" si="17"/>
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="S81" s="47">
         <f t="shared" si="17"/>
@@ -24105,7 +24169,7 @@
       <c r="AM81" s="27"/>
     </row>
     <row r="82" spans="1:39" ht="19.5" thickBot="1">
-      <c r="A82" s="120"/>
+      <c r="A82" s="122"/>
       <c r="B82" s="61" t="s">
         <v>90</v>
       </c>
@@ -24126,107 +24190,107 @@
       </c>
       <c r="I82" s="41">
         <f t="shared" si="18"/>
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="J82" s="41">
         <f t="shared" si="18"/>
-        <v>432</v>
+        <v>472</v>
       </c>
       <c r="K82" s="41">
         <f t="shared" si="18"/>
-        <v>450</v>
+        <v>510</v>
       </c>
       <c r="L82" s="41">
         <f t="shared" si="18"/>
-        <v>331</v>
+        <v>411</v>
       </c>
       <c r="M82" s="41">
         <f t="shared" si="18"/>
-        <v>362</v>
+        <v>462</v>
       </c>
       <c r="N82" s="41">
         <f t="shared" si="18"/>
-        <v>373</v>
+        <v>493</v>
       </c>
       <c r="O82" s="41">
         <f t="shared" si="18"/>
-        <v>384</v>
+        <v>524</v>
       </c>
       <c r="P82" s="41">
         <f t="shared" si="18"/>
-        <v>715</v>
+        <v>875</v>
       </c>
       <c r="Q82" s="41">
         <f t="shared" si="18"/>
-        <v>446</v>
+        <v>626</v>
       </c>
       <c r="R82" s="41">
         <f t="shared" si="18"/>
-        <v>477</v>
+        <v>677</v>
       </c>
       <c r="S82" s="41">
         <f t="shared" si="18"/>
-        <v>428</v>
+        <v>628</v>
       </c>
       <c r="T82" s="41">
         <f t="shared" si="18"/>
-        <v>399</v>
+        <v>599</v>
       </c>
       <c r="U82" s="41">
         <f t="shared" si="18"/>
-        <v>271</v>
+        <v>471</v>
       </c>
       <c r="V82" s="41">
         <f t="shared" si="18"/>
-        <v>153</v>
+        <v>353</v>
       </c>
       <c r="W82" s="41">
         <f t="shared" si="18"/>
-        <v>149</v>
+        <v>349</v>
       </c>
       <c r="X82" s="41">
         <f t="shared" si="18"/>
-        <v>125</v>
+        <v>325</v>
       </c>
       <c r="Y82" s="41">
         <f t="shared" si="18"/>
-        <v>121</v>
+        <v>321</v>
       </c>
       <c r="Z82" s="41">
         <f t="shared" si="18"/>
-        <v>2417</v>
+        <v>2617</v>
       </c>
       <c r="AA82" s="41">
         <f t="shared" si="18"/>
-        <v>2266</v>
+        <v>2466</v>
       </c>
       <c r="AB82" s="41">
         <f t="shared" si="18"/>
-        <v>2115</v>
+        <v>2315</v>
       </c>
       <c r="AC82" s="41">
         <f t="shared" si="18"/>
-        <v>1944</v>
+        <v>2144</v>
       </c>
       <c r="AD82" s="41">
         <f t="shared" si="18"/>
-        <v>1793</v>
+        <v>1993</v>
       </c>
       <c r="AE82" s="41">
         <f t="shared" si="18"/>
-        <v>1642</v>
+        <v>1842</v>
       </c>
       <c r="AF82" s="41">
         <f t="shared" si="18"/>
-        <v>1496</v>
+        <v>1696</v>
       </c>
       <c r="AG82" s="41">
         <f t="shared" si="18"/>
-        <v>1350</v>
+        <v>1550</v>
       </c>
       <c r="AH82" s="41">
         <f t="shared" si="18"/>
-        <v>984</v>
+        <v>1184</v>
       </c>
       <c r="AI82" s="41"/>
       <c r="AJ82" s="41"/>
@@ -25446,9 +25510,9 @@
       <c r="F100" s="89" t="s">
         <v>103</v>
       </c>
-      <c r="G100" s="56" t="e">
+      <c r="G100" s="56">
         <f t="shared" ref="G100:AK100" si="28">G120+G140</f>
-        <v>#N/A</v>
+        <v>1766</v>
       </c>
       <c r="H100" s="57" t="e">
         <f t="shared" si="28"/>
@@ -25972,107 +26036,107 @@
       </c>
       <c r="I104" s="35">
         <f t="shared" si="32"/>
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="J104" s="35">
         <f t="shared" si="32"/>
-        <v>432</v>
+        <v>472</v>
       </c>
       <c r="K104" s="35">
         <f t="shared" si="32"/>
-        <v>450</v>
+        <v>510</v>
       </c>
       <c r="L104" s="35">
         <f t="shared" si="32"/>
-        <v>331</v>
+        <v>411</v>
       </c>
       <c r="M104" s="35">
         <f t="shared" si="32"/>
-        <v>362</v>
+        <v>462</v>
       </c>
       <c r="N104" s="35">
         <f t="shared" si="32"/>
-        <v>373</v>
+        <v>493</v>
       </c>
       <c r="O104" s="35">
         <f t="shared" si="32"/>
-        <v>384</v>
+        <v>524</v>
       </c>
       <c r="P104" s="35">
         <f t="shared" si="32"/>
-        <v>715</v>
+        <v>875</v>
       </c>
       <c r="Q104" s="35">
         <f t="shared" si="32"/>
-        <v>446</v>
+        <v>626</v>
       </c>
       <c r="R104" s="35">
         <f t="shared" si="32"/>
-        <v>477</v>
+        <v>677</v>
       </c>
       <c r="S104" s="35">
         <f t="shared" si="32"/>
-        <v>428</v>
+        <v>628</v>
       </c>
       <c r="T104" s="35">
         <f t="shared" si="32"/>
-        <v>399</v>
+        <v>599</v>
       </c>
       <c r="U104" s="35">
         <f t="shared" si="32"/>
-        <v>271</v>
+        <v>471</v>
       </c>
       <c r="V104" s="35">
         <f t="shared" si="32"/>
-        <v>153</v>
+        <v>353</v>
       </c>
       <c r="W104" s="35">
         <f t="shared" si="32"/>
-        <v>149</v>
+        <v>349</v>
       </c>
       <c r="X104" s="35">
         <f t="shared" si="32"/>
-        <v>125</v>
+        <v>325</v>
       </c>
       <c r="Y104" s="35">
         <f t="shared" si="32"/>
-        <v>121</v>
+        <v>321</v>
       </c>
       <c r="Z104" s="35">
         <f t="shared" si="32"/>
-        <v>2417</v>
+        <v>2617</v>
       </c>
       <c r="AA104" s="35">
         <f t="shared" si="32"/>
-        <v>2266</v>
+        <v>2466</v>
       </c>
       <c r="AB104" s="35">
         <f t="shared" si="32"/>
-        <v>2115</v>
+        <v>2315</v>
       </c>
       <c r="AC104" s="35">
         <f t="shared" si="32"/>
-        <v>1944</v>
+        <v>2144</v>
       </c>
       <c r="AD104" s="35">
         <f t="shared" si="32"/>
-        <v>1793</v>
+        <v>1993</v>
       </c>
       <c r="AE104" s="35">
         <f t="shared" si="32"/>
-        <v>1642</v>
+        <v>1842</v>
       </c>
       <c r="AF104" s="35">
         <f t="shared" si="32"/>
-        <v>1496</v>
+        <v>1696</v>
       </c>
       <c r="AG104" s="35">
         <f t="shared" si="32"/>
-        <v>1350</v>
+        <v>1550</v>
       </c>
       <c r="AH104" s="35">
         <f t="shared" si="32"/>
-        <v>984</v>
+        <v>1184</v>
       </c>
       <c r="AI104" s="35">
         <f t="shared" si="32"/>
@@ -26091,9 +26155,9 @@
       <c r="F105" s="61" t="s">
         <v>105</v>
       </c>
-      <c r="G105" s="45" t="e">
+      <c r="G105" s="45">
         <f>G104-G100</f>
-        <v>#N/A</v>
+        <v>-1133</v>
       </c>
       <c r="H105" s="41" t="e">
         <f t="shared" ref="H105:O105" si="33">H104-H100</f>
@@ -27043,8 +27107,8 @@
       <c r="F120" s="89" t="s">
         <v>103</v>
       </c>
-      <c r="G120" s="56" t="e">
-        <v>#N/A</v>
+      <c r="G120" s="56">
+        <v>1230</v>
       </c>
       <c r="H120" s="57" t="e">
         <v>#N/A</v>
@@ -27445,107 +27509,107 @@
       </c>
       <c r="I124" s="47">
         <f t="shared" si="34"/>
-        <v>498</v>
+        <v>518</v>
       </c>
       <c r="J124" s="47">
         <f t="shared" si="34"/>
-        <v>416</v>
+        <v>456</v>
       </c>
       <c r="K124" s="47">
         <f t="shared" si="34"/>
-        <v>421</v>
+        <v>481</v>
       </c>
       <c r="L124" s="47">
         <f t="shared" si="34"/>
-        <v>289</v>
+        <v>369</v>
       </c>
       <c r="M124" s="47">
         <f t="shared" si="34"/>
-        <v>307</v>
+        <v>407</v>
       </c>
       <c r="N124" s="47">
         <f t="shared" si="34"/>
-        <v>305</v>
+        <v>425</v>
       </c>
       <c r="O124" s="47">
         <f t="shared" si="34"/>
-        <v>303</v>
+        <v>443</v>
       </c>
       <c r="P124" s="47">
         <f t="shared" si="34"/>
-        <v>621</v>
+        <v>781</v>
       </c>
       <c r="Q124" s="47">
         <f t="shared" si="34"/>
-        <v>339</v>
+        <v>519</v>
       </c>
       <c r="R124" s="47">
         <f t="shared" si="34"/>
-        <v>357</v>
+        <v>557</v>
       </c>
       <c r="S124" s="47">
         <f t="shared" si="34"/>
-        <v>295</v>
+        <v>495</v>
       </c>
       <c r="T124" s="47">
         <f t="shared" si="34"/>
-        <v>253</v>
+        <v>453</v>
       </c>
       <c r="U124" s="47">
         <f t="shared" si="34"/>
-        <v>112</v>
+        <v>312</v>
       </c>
       <c r="V124" s="47">
         <f t="shared" si="34"/>
-        <v>-19</v>
+        <v>181</v>
       </c>
       <c r="W124" s="47">
         <f t="shared" si="34"/>
-        <v>-36</v>
+        <v>164</v>
       </c>
       <c r="X124" s="47">
         <f t="shared" si="34"/>
-        <v>-73</v>
+        <v>127</v>
       </c>
       <c r="Y124" s="47">
         <f t="shared" si="34"/>
-        <v>-90</v>
+        <v>110</v>
       </c>
       <c r="Z124" s="47">
         <f t="shared" si="34"/>
-        <v>2193</v>
+        <v>2393</v>
       </c>
       <c r="AA124" s="47">
         <f t="shared" si="34"/>
-        <v>2029</v>
+        <v>2229</v>
       </c>
       <c r="AB124" s="47">
         <f t="shared" si="34"/>
-        <v>1865</v>
+        <v>2065</v>
       </c>
       <c r="AC124" s="47">
         <f t="shared" si="34"/>
-        <v>1681</v>
+        <v>1881</v>
       </c>
       <c r="AD124" s="47">
         <f t="shared" si="34"/>
-        <v>1517</v>
+        <v>1717</v>
       </c>
       <c r="AE124" s="47">
         <f t="shared" si="34"/>
-        <v>1353</v>
+        <v>1553</v>
       </c>
       <c r="AF124" s="47">
         <f t="shared" si="34"/>
-        <v>1194</v>
+        <v>1394</v>
       </c>
       <c r="AG124" s="47">
         <f t="shared" si="34"/>
-        <v>1035</v>
+        <v>1235</v>
       </c>
       <c r="AH124" s="47">
         <f t="shared" si="34"/>
-        <v>656</v>
+        <v>856</v>
       </c>
       <c r="AI124" s="47">
         <f t="shared" si="34"/>
@@ -27564,9 +27628,9 @@
       <c r="F125" s="61" t="s">
         <v>105</v>
       </c>
-      <c r="G125" s="45" t="e">
+      <c r="G125" s="45">
         <f>G124-G120</f>
-        <v>#N/A</v>
+        <v>-574</v>
       </c>
       <c r="H125" s="41" t="e">
         <f t="shared" ref="H125:AK125" si="35">H124-H120</f>
@@ -28584,8 +28648,8 @@
       <c r="F140" s="89" t="s">
         <v>103</v>
       </c>
-      <c r="G140" s="56" t="e">
-        <v>#N/A</v>
+      <c r="G140" s="56">
+        <v>536</v>
       </c>
       <c r="H140" s="57" t="e">
         <v>#N/A</v>
@@ -29105,9 +29169,9 @@
       <c r="F145" s="61" t="s">
         <v>105</v>
       </c>
-      <c r="G145" s="45" t="e">
+      <c r="G145" s="45">
         <f>G144-G140</f>
-        <v>#N/A</v>
+        <v>-559</v>
       </c>
       <c r="H145" s="41" t="e">
         <f>H144-H140</f>
@@ -29230,21 +29294,19 @@
         <v>#N/A</v>
       </c>
     </row>
+    <row r="151" spans="6:37"/>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="A16:A59"/>
-    <mergeCell ref="B34:B36"/>
-    <mergeCell ref="C34:C36"/>
-    <mergeCell ref="D34:D36"/>
-    <mergeCell ref="C63:C73"/>
-    <mergeCell ref="D72:D73"/>
-    <mergeCell ref="D24:D29"/>
-    <mergeCell ref="D43:D46"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="C43:C48"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="A2:A15"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="B4:B8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B10:B14"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="C4:C8"/>
+    <mergeCell ref="C10:C14"/>
     <mergeCell ref="A81:A82"/>
     <mergeCell ref="C16:C17"/>
     <mergeCell ref="D16:D17"/>
@@ -29261,16 +29323,19 @@
     <mergeCell ref="B38:B48"/>
     <mergeCell ref="B16:B31"/>
     <mergeCell ref="A60:A80"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="A2:A15"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="B4:B8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B10:B14"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="C4:C8"/>
-    <mergeCell ref="C10:C14"/>
+    <mergeCell ref="A16:A59"/>
+    <mergeCell ref="B34:B36"/>
+    <mergeCell ref="C34:C36"/>
+    <mergeCell ref="D34:D36"/>
+    <mergeCell ref="C63:C73"/>
+    <mergeCell ref="D72:D73"/>
+    <mergeCell ref="D24:D29"/>
+    <mergeCell ref="D43:D46"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="C43:C48"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ライフプラン_猪飼.xlsx
+++ b/ライフプラン_猪飼.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC_USER\Documents\LocalLifeplanRepo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07B43407-D572-49C5-9B09-505CBE4DB057}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{807572A9-4335-4896-8AD2-E64117710520}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{934FA03D-99BD-49E0-BFEC-291BD79F4879}"/>
   </bookViews>
@@ -853,6 +853,58 @@
         </r>
       </text>
     </comment>
+    <comment ref="J107" authorId="0" shapeId="0" xr:uid="{291AE3EE-FC44-4EFC-ACD1-4DA497F99570}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="MS P ゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>PC_USER:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="MS P ゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E108" authorId="0" shapeId="0" xr:uid="{90AC550F-2A66-4918-ACDB-8E847B1B20BB}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="MS P ゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>PC_USER:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="MS P ゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="E109" authorId="0" shapeId="0" xr:uid="{0CFE7B6C-FEBF-4C82-A58B-E327835A20D7}">
       <text>
         <r>
@@ -1079,6 +1131,24 @@
         </r>
       </text>
     </comment>
+    <comment ref="G121" authorId="0" shapeId="0" xr:uid="{491E6ECB-CBBA-4F68-8CD9-2B9F44F3BFD0}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="MS P ゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>kaz
+ 全労済個人年金  + 4　
+ ﾌﾟﾙﾃﾞﾝｼｬﾙ保険金 + 9
+nao</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="E132" authorId="0" shapeId="0" xr:uid="{D3A0D358-7411-4045-8E31-BB4827CBD402}">
       <text>
         <r>
@@ -1249,6 +1319,22 @@
           </rPr>
           <t>kazへ返済 -13.1 (医療費：6.7、ビューカード：1.2、瀬戸神社:0.2、電波会：1.5、西源寺:1.1，外食：0.9，他：2.1)
 naoへ返済 -1.3（医療費：1.3，森永：0.2，返却：-0.2）</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G141" authorId="0" shapeId="0" xr:uid="{725F792E-684A-4D14-A239-5D6C6DB5579A}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="MS P ゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>kazへ返済 -8.6 (医療費：2.8、ビューカード：0.9、鶴岡・瀬戸神社:1.7、外食：0.9，他：2.3)
+naoへ返済 -10.4（医療費：1.3，森永：0.4，お年玉：3.0，神社関係:3.5，ﾀﾞﾝｽ：6.4，他：0.8，前借：-5.0)</t>
         </r>
       </text>
     </comment>
@@ -4858,7 +4944,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="31"/>
                 <c:pt idx="0">
-                  <c:v>#N/A</c:v>
+                  <c:v>1224</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>#N/A</c:v>
@@ -8314,7 +8400,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="31"/>
                 <c:pt idx="0">
-                  <c:v>#N/A</c:v>
+                  <c:v>495</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>#N/A</c:v>
@@ -11767,7 +11853,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="31"/>
                 <c:pt idx="0">
-                  <c:v>#N/A</c:v>
+                  <c:v>1719</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>#N/A</c:v>
@@ -25639,9 +25725,9 @@
       <c r="F101" s="89" t="s">
         <v>92</v>
       </c>
-      <c r="G101" s="56" t="e">
+      <c r="G101" s="56">
         <f t="shared" ref="G101:AK101" si="29">G121+G141</f>
-        <v>#N/A</v>
+        <v>1719</v>
       </c>
       <c r="H101" s="57" t="e">
         <f t="shared" si="29"/>
@@ -26214,6 +26300,8 @@
       <c r="AJ105" s="41"/>
       <c r="AK105" s="42"/>
     </row>
+    <row r="107" spans="5:37"/>
+    <row r="108" spans="5:37"/>
     <row r="109" spans="5:37" ht="24">
       <c r="F109" s="54" t="s">
         <v>148</v>
@@ -27205,8 +27293,8 @@
       <c r="F121" s="89" t="s">
         <v>92</v>
       </c>
-      <c r="G121" s="56" t="e">
-        <v>#N/A</v>
+      <c r="G121" s="56">
+        <v>1224</v>
       </c>
       <c r="H121" s="57" t="e">
         <v>#N/A</v>
@@ -28746,8 +28834,8 @@
       <c r="F141" s="89" t="s">
         <v>92</v>
       </c>
-      <c r="G141" s="56" t="e">
-        <v>#N/A</v>
+      <c r="G141" s="56">
+        <v>495</v>
       </c>
       <c r="H141" s="57" t="e">
         <v>#N/A</v>

--- a/ライフプラン_猪飼.xlsx
+++ b/ライフプラン_猪飼.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC_USER\Documents\LocalLifeplanRepo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF79DF96-90CE-423E-9A3D-9CBFCCC6FF3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{034D5BAF-58E3-4BD1-919E-E2D8047E5ADE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{934FA03D-99BD-49E0-BFEC-291BD79F4879}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{934FA03D-99BD-49E0-BFEC-291BD79F4879}"/>
   </bookViews>
   <sheets>
     <sheet name="マネーフロー" sheetId="1" r:id="rId1"/>
@@ -1102,6 +1102,25 @@
         </r>
       </text>
     </comment>
+    <comment ref="G123" authorId="0" shapeId="0" xr:uid="{455574BB-26F2-423E-96EC-B6ABB6E593A0}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="MS P ゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>kaz
+ 国民厚生年金　　+45
+ パナ年金　　　  +12
+ ﾌﾟﾙﾃﾞﾝｼｬﾙ保険金 + 9
+ 普通預金利息　　+ 1</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="E133" authorId="0" shapeId="0" xr:uid="{D3A0D358-7411-4045-8E31-BB4827CBD402}">
       <text>
         <r>
@@ -1288,6 +1307,22 @@
           </rPr>
           <t>kazへ返済 -8.6 (医療費：2.8、ビューカード：0.9、鶴岡・瀬戸神社:1.7、外食：0.9，他：2.3)
 naoへ返済 -10.4（医療費：1.3，森永：0.4，お年玉：3.0，神社関係:3.5，ﾀﾞﾝｽ：6.4，他：0.8，前借：-5.0)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G143" authorId="0" shapeId="0" xr:uid="{B87394A5-B240-4E29-96B2-F4985C38B7E1}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="MS P ゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>kazへ返済 -6.1 (医療費：1.2、ビューカード：0.6、瀬戸神社:0.2、松子叔母葬儀：6.5、野乃陽お年玉:4.0、外食：1.9，前借：-10.0，他：1.2)
+naoへ返済 -4.8（医療費：0.2，カイロ：1.3，森永：0.2，神社関係:1.5，ビューカード：1.0，食料品：0.5)</t>
         </r>
       </text>
     </comment>
@@ -4235,6 +4270,125 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" textRotation="255"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="42" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="45" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="23" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="36" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="24" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="35" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="46" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" textRotation="255"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" textRotation="255"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -4244,10 +4398,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" textRotation="255"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" textRotation="255"/>
@@ -4301,121 +4451,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" textRotation="255"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="42" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="23" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" textRotation="255"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="45" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="36" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="24" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="35" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="46" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -5148,7 +5183,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="31"/>
                 <c:pt idx="0">
-                  <c:v>#N/A</c:v>
+                  <c:v>1272</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>#N/A</c:v>
@@ -8604,7 +8639,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="31"/>
                 <c:pt idx="0">
-                  <c:v>#N/A</c:v>
+                  <c:v>459</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>#N/A</c:v>
@@ -12055,7 +12090,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="31"/>
                 <c:pt idx="0">
-                  <c:v>#N/A</c:v>
+                  <c:v>1731</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>#N/A</c:v>
@@ -17312,12 +17347,12 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="101" t="s">
+      <c r="B1" s="134" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="102"/>
-      <c r="D1" s="102"/>
-      <c r="E1" s="103"/>
+      <c r="C1" s="135"/>
+      <c r="D1" s="135"/>
+      <c r="E1" s="136"/>
       <c r="F1" s="2" t="s">
         <v>2</v>
       </c>
@@ -17418,13 +17453,13 @@
       <c r="AM1" s="4"/>
     </row>
     <row r="2" spans="1:39" ht="18.75" customHeight="1">
-      <c r="A2" s="104" t="s">
+      <c r="A2" s="101" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="107" t="s">
+      <c r="B2" s="139" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="114"/>
+      <c r="C2" s="146"/>
       <c r="D2" s="6" t="s">
         <v>5</v>
       </c>
@@ -17509,9 +17544,9 @@
       <c r="AM2" s="4"/>
     </row>
     <row r="3" spans="1:39" ht="19.5" thickBot="1">
-      <c r="A3" s="105"/>
-      <c r="B3" s="108"/>
-      <c r="C3" s="115"/>
+      <c r="A3" s="137"/>
+      <c r="B3" s="140"/>
+      <c r="C3" s="147"/>
       <c r="D3" s="9" t="s">
         <v>7</v>
       </c>
@@ -17612,11 +17647,11 @@
       <c r="AM3" s="4"/>
     </row>
     <row r="4" spans="1:39">
-      <c r="A4" s="105"/>
-      <c r="B4" s="107" t="s">
+      <c r="A4" s="137"/>
+      <c r="B4" s="139" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="116"/>
+      <c r="C4" s="148"/>
       <c r="D4" s="12" t="s">
         <v>10</v>
       </c>
@@ -17661,9 +17696,9 @@
       <c r="AM4" s="4"/>
     </row>
     <row r="5" spans="1:39">
-      <c r="A5" s="105"/>
-      <c r="B5" s="109"/>
-      <c r="C5" s="117"/>
+      <c r="A5" s="137"/>
+      <c r="B5" s="141"/>
+      <c r="C5" s="149"/>
       <c r="D5" s="15" t="s">
         <v>12</v>
       </c>
@@ -17708,9 +17743,9 @@
       <c r="AM5" s="4"/>
     </row>
     <row r="6" spans="1:39">
-      <c r="A6" s="105"/>
-      <c r="B6" s="109"/>
-      <c r="C6" s="117"/>
+      <c r="A6" s="137"/>
+      <c r="B6" s="141"/>
+      <c r="C6" s="149"/>
       <c r="D6" s="15"/>
       <c r="E6" s="16"/>
       <c r="F6" s="17"/>
@@ -17749,9 +17784,9 @@
       <c r="AM6" s="4"/>
     </row>
     <row r="7" spans="1:39">
-      <c r="A7" s="105"/>
-      <c r="B7" s="109"/>
-      <c r="C7" s="117"/>
+      <c r="A7" s="137"/>
+      <c r="B7" s="141"/>
+      <c r="C7" s="149"/>
       <c r="D7" s="15"/>
       <c r="E7" s="16"/>
       <c r="F7" s="17"/>
@@ -17790,9 +17825,9 @@
       <c r="AM7" s="4"/>
     </row>
     <row r="8" spans="1:39">
-      <c r="A8" s="105"/>
-      <c r="B8" s="110"/>
-      <c r="C8" s="118"/>
+      <c r="A8" s="137"/>
+      <c r="B8" s="142"/>
+      <c r="C8" s="150"/>
       <c r="D8" s="15"/>
       <c r="E8" s="16"/>
       <c r="F8" s="17"/>
@@ -17831,12 +17866,12 @@
       <c r="AM8" s="4"/>
     </row>
     <row r="9" spans="1:39" ht="19.5" thickBot="1">
-      <c r="A9" s="105"/>
-      <c r="B9" s="111" t="s">
+      <c r="A9" s="137"/>
+      <c r="B9" s="143" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="112"/>
-      <c r="D9" s="113"/>
+      <c r="C9" s="144"/>
+      <c r="D9" s="145"/>
       <c r="E9" s="18" t="s">
         <v>15</v>
       </c>
@@ -17972,11 +18007,11 @@
       <c r="AM9" s="4"/>
     </row>
     <row r="10" spans="1:39">
-      <c r="A10" s="105"/>
-      <c r="B10" s="107" t="s">
+      <c r="A10" s="137"/>
+      <c r="B10" s="139" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="116"/>
+      <c r="C10" s="148"/>
       <c r="D10" s="15" t="s">
         <v>17</v>
       </c>
@@ -18075,9 +18110,9 @@
       <c r="AM10" s="4"/>
     </row>
     <row r="11" spans="1:39">
-      <c r="A11" s="105"/>
-      <c r="B11" s="109"/>
-      <c r="C11" s="117"/>
+      <c r="A11" s="137"/>
+      <c r="B11" s="141"/>
+      <c r="C11" s="149"/>
       <c r="D11" s="15" t="s">
         <v>19</v>
       </c>
@@ -18126,9 +18161,9 @@
       <c r="AM11" s="4"/>
     </row>
     <row r="12" spans="1:39">
-      <c r="A12" s="105"/>
-      <c r="B12" s="109"/>
-      <c r="C12" s="117"/>
+      <c r="A12" s="137"/>
+      <c r="B12" s="141"/>
+      <c r="C12" s="149"/>
       <c r="D12" s="15" t="s">
         <v>21</v>
       </c>
@@ -18199,9 +18234,9 @@
       <c r="AM12" s="4"/>
     </row>
     <row r="13" spans="1:39">
-      <c r="A13" s="105"/>
-      <c r="B13" s="109"/>
-      <c r="C13" s="117"/>
+      <c r="A13" s="137"/>
+      <c r="B13" s="141"/>
+      <c r="C13" s="149"/>
       <c r="D13" s="15" t="s">
         <v>22</v>
       </c>
@@ -18250,9 +18285,9 @@
       <c r="AM13" s="4"/>
     </row>
     <row r="14" spans="1:39">
-      <c r="A14" s="105"/>
-      <c r="B14" s="110"/>
-      <c r="C14" s="118"/>
+      <c r="A14" s="137"/>
+      <c r="B14" s="142"/>
+      <c r="C14" s="150"/>
       <c r="D14" s="15"/>
       <c r="E14" s="16"/>
       <c r="F14" s="23"/>
@@ -18291,12 +18326,12 @@
       <c r="AM14" s="4"/>
     </row>
     <row r="15" spans="1:39" ht="19.5" thickBot="1">
-      <c r="A15" s="106"/>
-      <c r="B15" s="111" t="s">
+      <c r="A15" s="138"/>
+      <c r="B15" s="143" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="112"/>
-      <c r="D15" s="113"/>
+      <c r="C15" s="144"/>
+      <c r="D15" s="145"/>
       <c r="E15" s="18" t="s">
         <v>25</v>
       </c>
@@ -18432,16 +18467,16 @@
       <c r="AM15" s="4"/>
     </row>
     <row r="16" spans="1:39">
-      <c r="A16" s="104" t="s">
+      <c r="A16" s="101" t="s">
         <v>150</v>
       </c>
-      <c r="B16" s="137" t="s">
+      <c r="B16" s="132" t="s">
         <v>129</v>
       </c>
-      <c r="C16" s="120" t="s">
+      <c r="C16" s="123" t="s">
         <v>105</v>
       </c>
-      <c r="D16" s="122" t="s">
+      <c r="D16" s="125" t="s">
         <v>109</v>
       </c>
       <c r="E16" s="16" t="s">
@@ -18523,10 +18558,10 @@
       <c r="AM16" s="4"/>
     </row>
     <row r="17" spans="1:39">
-      <c r="A17" s="139"/>
-      <c r="B17" s="135"/>
-      <c r="C17" s="121"/>
-      <c r="D17" s="121"/>
+      <c r="A17" s="102"/>
+      <c r="B17" s="130"/>
+      <c r="C17" s="114"/>
+      <c r="D17" s="114"/>
       <c r="E17" s="16" t="s">
         <v>29</v>
       </c>
@@ -18612,12 +18647,12 @@
       <c r="AM17" s="4"/>
     </row>
     <row r="18" spans="1:39">
-      <c r="A18" s="139"/>
-      <c r="B18" s="135"/>
-      <c r="C18" s="123" t="s">
+      <c r="A18" s="102"/>
+      <c r="B18" s="130"/>
+      <c r="C18" s="113" t="s">
         <v>106</v>
       </c>
-      <c r="D18" s="125" t="s">
+      <c r="D18" s="115" t="s">
         <v>111</v>
       </c>
       <c r="E18" s="13" t="s">
@@ -18699,10 +18734,10 @@
       <c r="AM18" s="27"/>
     </row>
     <row r="19" spans="1:39">
-      <c r="A19" s="139"/>
-      <c r="B19" s="135"/>
-      <c r="C19" s="124"/>
-      <c r="D19" s="124"/>
+      <c r="A19" s="102"/>
+      <c r="B19" s="130"/>
+      <c r="C19" s="116"/>
+      <c r="D19" s="116"/>
       <c r="E19" s="16" t="s">
         <v>27</v>
       </c>
@@ -18770,10 +18805,10 @@
       <c r="AM19" s="27"/>
     </row>
     <row r="20" spans="1:39">
-      <c r="A20" s="139"/>
-      <c r="B20" s="135"/>
-      <c r="C20" s="124"/>
-      <c r="D20" s="121"/>
+      <c r="A20" s="102"/>
+      <c r="B20" s="130"/>
+      <c r="C20" s="116"/>
+      <c r="D20" s="114"/>
       <c r="E20" s="16" t="s">
         <v>28</v>
       </c>
@@ -18823,9 +18858,9 @@
       <c r="AM20" s="27"/>
     </row>
     <row r="21" spans="1:39">
-      <c r="A21" s="139"/>
-      <c r="B21" s="135"/>
-      <c r="C21" s="121"/>
+      <c r="A21" s="102"/>
+      <c r="B21" s="130"/>
+      <c r="C21" s="114"/>
       <c r="D21" s="57" t="s">
         <v>112</v>
       </c>
@@ -18876,9 +18911,9 @@
       <c r="AM21" s="27"/>
     </row>
     <row r="22" spans="1:39">
-      <c r="A22" s="139"/>
-      <c r="B22" s="135"/>
-      <c r="C22" s="123" t="s">
+      <c r="A22" s="102"/>
+      <c r="B22" s="130"/>
+      <c r="C22" s="113" t="s">
         <v>107</v>
       </c>
       <c r="D22" s="57" t="s">
@@ -18923,9 +18958,9 @@
       <c r="AM22" s="27"/>
     </row>
     <row r="23" spans="1:39">
-      <c r="A23" s="139"/>
-      <c r="B23" s="135"/>
-      <c r="C23" s="121"/>
+      <c r="A23" s="102"/>
+      <c r="B23" s="130"/>
+      <c r="C23" s="114"/>
       <c r="D23" s="57" t="s">
         <v>114</v>
       </c>
@@ -18968,12 +19003,12 @@
       <c r="AM23" s="27"/>
     </row>
     <row r="24" spans="1:39">
-      <c r="A24" s="139"/>
-      <c r="B24" s="135"/>
-      <c r="C24" s="123" t="s">
+      <c r="A24" s="102"/>
+      <c r="B24" s="130"/>
+      <c r="C24" s="113" t="s">
         <v>108</v>
       </c>
-      <c r="D24" s="125" t="s">
+      <c r="D24" s="115" t="s">
         <v>115</v>
       </c>
       <c r="E24" s="16" t="s">
@@ -19055,10 +19090,10 @@
       <c r="AM24" s="27"/>
     </row>
     <row r="25" spans="1:39">
-      <c r="A25" s="139"/>
-      <c r="B25" s="135"/>
-      <c r="C25" s="124"/>
-      <c r="D25" s="124"/>
+      <c r="A25" s="102"/>
+      <c r="B25" s="130"/>
+      <c r="C25" s="116"/>
+      <c r="D25" s="116"/>
       <c r="E25" s="16" t="s">
         <v>32</v>
       </c>
@@ -19150,10 +19185,10 @@
       <c r="AM25" s="27"/>
     </row>
     <row r="26" spans="1:39">
-      <c r="A26" s="139"/>
-      <c r="B26" s="135"/>
-      <c r="C26" s="124"/>
-      <c r="D26" s="124"/>
+      <c r="A26" s="102"/>
+      <c r="B26" s="130"/>
+      <c r="C26" s="116"/>
+      <c r="D26" s="116"/>
       <c r="E26" s="16" t="s">
         <v>33</v>
       </c>
@@ -19195,10 +19230,10 @@
       <c r="AM26" s="27"/>
     </row>
     <row r="27" spans="1:39">
-      <c r="A27" s="139"/>
-      <c r="B27" s="135"/>
-      <c r="C27" s="124"/>
-      <c r="D27" s="124"/>
+      <c r="A27" s="102"/>
+      <c r="B27" s="130"/>
+      <c r="C27" s="116"/>
+      <c r="D27" s="116"/>
       <c r="E27" s="29" t="s">
         <v>154</v>
       </c>
@@ -19240,10 +19275,10 @@
       <c r="AM27" s="27"/>
     </row>
     <row r="28" spans="1:39">
-      <c r="A28" s="139"/>
-      <c r="B28" s="135"/>
-      <c r="C28" s="124"/>
-      <c r="D28" s="124"/>
+      <c r="A28" s="102"/>
+      <c r="B28" s="130"/>
+      <c r="C28" s="116"/>
+      <c r="D28" s="116"/>
       <c r="E28" s="16" t="s">
         <v>34</v>
       </c>
@@ -19303,10 +19338,10 @@
       <c r="AM28" s="27"/>
     </row>
     <row r="29" spans="1:39">
-      <c r="A29" s="139"/>
-      <c r="B29" s="135"/>
-      <c r="C29" s="124"/>
-      <c r="D29" s="121"/>
+      <c r="A29" s="102"/>
+      <c r="B29" s="130"/>
+      <c r="C29" s="116"/>
+      <c r="D29" s="114"/>
       <c r="E29" s="85" t="s">
         <v>117</v>
       </c>
@@ -19348,9 +19383,9 @@
       <c r="AM29" s="27"/>
     </row>
     <row r="30" spans="1:39">
-      <c r="A30" s="139"/>
-      <c r="B30" s="135"/>
-      <c r="C30" s="124"/>
+      <c r="A30" s="102"/>
+      <c r="B30" s="130"/>
+      <c r="C30" s="116"/>
       <c r="D30" s="57" t="s">
         <v>119</v>
       </c>
@@ -19393,9 +19428,9 @@
       <c r="AM30" s="27"/>
     </row>
     <row r="31" spans="1:39">
-      <c r="A31" s="139"/>
-      <c r="B31" s="136"/>
-      <c r="C31" s="121"/>
+      <c r="A31" s="102"/>
+      <c r="B31" s="131"/>
+      <c r="C31" s="114"/>
       <c r="D31" s="57" t="s">
         <v>120</v>
       </c>
@@ -19438,11 +19473,11 @@
       <c r="AM31" s="27"/>
     </row>
     <row r="32" spans="1:39">
-      <c r="A32" s="139"/>
-      <c r="B32" s="147" t="s">
+      <c r="A32" s="102"/>
+      <c r="B32" s="119" t="s">
         <v>128</v>
       </c>
-      <c r="C32" s="126"/>
+      <c r="C32" s="110"/>
       <c r="D32" s="17" t="s">
         <v>125</v>
       </c>
@@ -19541,9 +19576,9 @@
       <c r="AM32" s="27"/>
     </row>
     <row r="33" spans="1:39">
-      <c r="A33" s="139"/>
-      <c r="B33" s="148"/>
-      <c r="C33" s="128"/>
+      <c r="A33" s="102"/>
+      <c r="B33" s="120"/>
+      <c r="C33" s="112"/>
       <c r="D33" s="17" t="s">
         <v>126</v>
       </c>
@@ -19618,12 +19653,12 @@
       <c r="AM33" s="27"/>
     </row>
     <row r="34" spans="1:39">
-      <c r="A34" s="139"/>
-      <c r="B34" s="129" t="s">
+      <c r="A34" s="102"/>
+      <c r="B34" s="104" t="s">
         <v>9</v>
       </c>
-      <c r="C34" s="132"/>
-      <c r="D34" s="143"/>
+      <c r="C34" s="106"/>
+      <c r="D34" s="108"/>
       <c r="E34" s="34" t="str">
         <f t="shared" ref="E34:AK34" si="2">E4</f>
         <v>新潟実家の売却益　（妙子と折半）</v>
@@ -19760,10 +19795,10 @@
       <c r="AM34" s="27"/>
     </row>
     <row r="35" spans="1:39">
-      <c r="A35" s="139"/>
-      <c r="B35" s="141"/>
-      <c r="C35" s="142"/>
-      <c r="D35" s="144"/>
+      <c r="A35" s="102"/>
+      <c r="B35" s="105"/>
+      <c r="C35" s="107"/>
+      <c r="D35" s="109"/>
       <c r="E35" s="34" t="str">
         <f>E5</f>
         <v>横浜マンションの売却益</v>
@@ -19900,10 +19935,10 @@
       <c r="AM35" s="27"/>
     </row>
     <row r="36" spans="1:39">
-      <c r="A36" s="139"/>
-      <c r="B36" s="141"/>
-      <c r="C36" s="142"/>
-      <c r="D36" s="144"/>
+      <c r="A36" s="102"/>
+      <c r="B36" s="105"/>
+      <c r="C36" s="107"/>
+      <c r="D36" s="109"/>
       <c r="E36" s="98" t="s">
         <v>149</v>
       </c>
@@ -19948,7 +19983,7 @@
       <c r="AM36" s="27"/>
     </row>
     <row r="37" spans="1:39" ht="19.5" thickBot="1">
-      <c r="A37" s="139"/>
+      <c r="A37" s="102"/>
       <c r="B37" s="35" t="s">
         <v>36</v>
       </c>
@@ -20087,8 +20122,8 @@
       <c r="AM37" s="27"/>
     </row>
     <row r="38" spans="1:39" ht="18.75" customHeight="1">
-      <c r="A38" s="139"/>
-      <c r="B38" s="134" t="s">
+      <c r="A38" s="102"/>
+      <c r="B38" s="129" t="s">
         <v>130</v>
       </c>
       <c r="C38" s="8" t="s">
@@ -20138,9 +20173,9 @@
       <c r="AM38" s="4"/>
     </row>
     <row r="39" spans="1:39">
-      <c r="A39" s="139"/>
-      <c r="B39" s="135"/>
-      <c r="C39" s="123" t="s">
+      <c r="A39" s="102"/>
+      <c r="B39" s="130"/>
+      <c r="C39" s="113" t="s">
         <v>106</v>
       </c>
       <c r="D39" s="57" t="s">
@@ -20185,9 +20220,9 @@
       <c r="AM39" s="4"/>
     </row>
     <row r="40" spans="1:39">
-      <c r="A40" s="139"/>
-      <c r="B40" s="135"/>
-      <c r="C40" s="121"/>
+      <c r="A40" s="102"/>
+      <c r="B40" s="130"/>
+      <c r="C40" s="114"/>
       <c r="D40" s="57" t="s">
         <v>112</v>
       </c>
@@ -20230,9 +20265,9 @@
       <c r="AM40" s="4"/>
     </row>
     <row r="41" spans="1:39">
-      <c r="A41" s="139"/>
-      <c r="B41" s="135"/>
-      <c r="C41" s="123" t="s">
+      <c r="A41" s="102"/>
+      <c r="B41" s="130"/>
+      <c r="C41" s="113" t="s">
         <v>107</v>
       </c>
       <c r="D41" s="57" t="s">
@@ -20333,9 +20368,9 @@
       <c r="AM41" s="27"/>
     </row>
     <row r="42" spans="1:39">
-      <c r="A42" s="139"/>
-      <c r="B42" s="135"/>
-      <c r="C42" s="121"/>
+      <c r="A42" s="102"/>
+      <c r="B42" s="130"/>
+      <c r="C42" s="114"/>
       <c r="D42" s="57" t="s">
         <v>114</v>
       </c>
@@ -20378,12 +20413,12 @@
       <c r="AM42" s="4"/>
     </row>
     <row r="43" spans="1:39">
-      <c r="A43" s="139"/>
-      <c r="B43" s="135"/>
-      <c r="C43" s="123" t="s">
+      <c r="A43" s="102"/>
+      <c r="B43" s="130"/>
+      <c r="C43" s="113" t="s">
         <v>108</v>
       </c>
-      <c r="D43" s="125" t="s">
+      <c r="D43" s="115" t="s">
         <v>115</v>
       </c>
       <c r="E43" s="16" t="s">
@@ -20428,10 +20463,10 @@
       <c r="AM43" s="27"/>
     </row>
     <row r="44" spans="1:39">
-      <c r="A44" s="139"/>
-      <c r="B44" s="135"/>
-      <c r="C44" s="124"/>
-      <c r="D44" s="124"/>
+      <c r="A44" s="102"/>
+      <c r="B44" s="130"/>
+      <c r="C44" s="116"/>
+      <c r="D44" s="116"/>
       <c r="E44" s="16" t="s">
         <v>47</v>
       </c>
@@ -20511,10 +20546,10 @@
       <c r="AM44" s="27"/>
     </row>
     <row r="45" spans="1:39">
-      <c r="A45" s="139"/>
-      <c r="B45" s="135"/>
-      <c r="C45" s="124"/>
-      <c r="D45" s="124"/>
+      <c r="A45" s="102"/>
+      <c r="B45" s="130"/>
+      <c r="C45" s="116"/>
+      <c r="D45" s="116"/>
       <c r="E45" s="16" t="s">
         <v>48</v>
       </c>
@@ -20586,10 +20621,10 @@
       <c r="AM45" s="27"/>
     </row>
     <row r="46" spans="1:39">
-      <c r="A46" s="139"/>
-      <c r="B46" s="135"/>
-      <c r="C46" s="124"/>
-      <c r="D46" s="121"/>
+      <c r="A46" s="102"/>
+      <c r="B46" s="130"/>
+      <c r="C46" s="116"/>
+      <c r="D46" s="114"/>
       <c r="E46" s="85" t="s">
         <v>121</v>
       </c>
@@ -20639,9 +20674,9 @@
       <c r="AM46" s="27"/>
     </row>
     <row r="47" spans="1:39">
-      <c r="A47" s="139"/>
-      <c r="B47" s="135"/>
-      <c r="C47" s="124"/>
+      <c r="A47" s="102"/>
+      <c r="B47" s="130"/>
+      <c r="C47" s="116"/>
       <c r="D47" s="57" t="s">
         <v>119</v>
       </c>
@@ -20734,9 +20769,9 @@
       <c r="AM47" s="27"/>
     </row>
     <row r="48" spans="1:39">
-      <c r="A48" s="139"/>
-      <c r="B48" s="136"/>
-      <c r="C48" s="121"/>
+      <c r="A48" s="102"/>
+      <c r="B48" s="131"/>
+      <c r="C48" s="114"/>
       <c r="D48" s="57" t="s">
         <v>120</v>
       </c>
@@ -20779,7 +20814,7 @@
       <c r="AM48" s="4"/>
     </row>
     <row r="49" spans="1:39">
-      <c r="A49" s="139"/>
+      <c r="A49" s="102"/>
       <c r="B49" s="66" t="s">
         <v>43</v>
       </c>
@@ -20864,7 +20899,7 @@
       <c r="AM49" s="27"/>
     </row>
     <row r="50" spans="1:39">
-      <c r="A50" s="139"/>
+      <c r="A50" s="102"/>
       <c r="B50" s="66" t="s">
         <v>50</v>
       </c>
@@ -20965,7 +21000,7 @@
       <c r="AM50" s="27"/>
     </row>
     <row r="51" spans="1:39">
-      <c r="A51" s="139"/>
+      <c r="A51" s="102"/>
       <c r="B51" s="66" t="s">
         <v>52</v>
       </c>
@@ -21066,11 +21101,11 @@
       <c r="AM51" s="27"/>
     </row>
     <row r="52" spans="1:39">
-      <c r="A52" s="139"/>
-      <c r="B52" s="133" t="s">
+      <c r="A52" s="102"/>
+      <c r="B52" s="128" t="s">
         <v>122</v>
       </c>
-      <c r="C52" s="126"/>
+      <c r="C52" s="110"/>
       <c r="D52" s="15" t="s">
         <v>41</v>
       </c>
@@ -21153,9 +21188,9 @@
       <c r="AM52" s="27"/>
     </row>
     <row r="53" spans="1:39">
-      <c r="A53" s="139"/>
-      <c r="B53" s="130"/>
-      <c r="C53" s="127"/>
+      <c r="A53" s="102"/>
+      <c r="B53" s="126"/>
+      <c r="C53" s="111"/>
       <c r="D53" s="15" t="s">
         <v>37</v>
       </c>
@@ -21200,9 +21235,9 @@
       <c r="AM53" s="27"/>
     </row>
     <row r="54" spans="1:39">
-      <c r="A54" s="139"/>
-      <c r="B54" s="131"/>
-      <c r="C54" s="128"/>
+      <c r="A54" s="102"/>
+      <c r="B54" s="127"/>
+      <c r="C54" s="112"/>
       <c r="D54" s="15" t="s">
         <v>39</v>
       </c>
@@ -21301,7 +21336,7 @@
       <c r="AM54" s="27"/>
     </row>
     <row r="55" spans="1:39">
-      <c r="A55" s="139"/>
+      <c r="A55" s="102"/>
       <c r="B55" s="83" t="s">
         <v>138</v>
       </c>
@@ -21404,11 +21439,11 @@
       <c r="AM55" s="27"/>
     </row>
     <row r="56" spans="1:39">
-      <c r="A56" s="139"/>
-      <c r="B56" s="145" t="s">
+      <c r="A56" s="102"/>
+      <c r="B56" s="117" t="s">
         <v>144</v>
       </c>
-      <c r="C56" s="146"/>
+      <c r="C56" s="118"/>
       <c r="D56" s="77" t="s">
         <v>124</v>
       </c>
@@ -21531,7 +21566,7 @@
       <c r="AM56" s="27"/>
     </row>
     <row r="57" spans="1:39">
-      <c r="A57" s="139"/>
+      <c r="A57" s="102"/>
       <c r="B57" s="67" t="s">
         <v>56</v>
       </c>
@@ -21660,7 +21695,7 @@
       <c r="AM57" s="27"/>
     </row>
     <row r="58" spans="1:39">
-      <c r="A58" s="139"/>
+      <c r="A58" s="102"/>
       <c r="B58" s="67" t="s">
         <v>58</v>
       </c>
@@ -21787,7 +21822,7 @@
       <c r="AM58" s="27"/>
     </row>
     <row r="59" spans="1:39" ht="19.5" thickBot="1">
-      <c r="A59" s="140"/>
+      <c r="A59" s="103"/>
       <c r="B59" s="61" t="s">
         <v>59</v>
       </c>
@@ -21916,7 +21951,7 @@
       <c r="AM59" s="27"/>
     </row>
     <row r="60" spans="1:39" ht="18.75" customHeight="1">
-      <c r="A60" s="104" t="s">
+      <c r="A60" s="101" t="s">
         <v>60</v>
       </c>
       <c r="B60" s="80" t="s">
@@ -22050,7 +22085,7 @@
       <c r="AM60" s="27"/>
     </row>
     <row r="61" spans="1:39" ht="19.5" thickBot="1">
-      <c r="A61" s="138"/>
+      <c r="A61" s="133"/>
       <c r="B61" s="61" t="s">
         <v>36</v>
       </c>
@@ -22179,14 +22214,14 @@
       <c r="AM61" s="27"/>
     </row>
     <row r="62" spans="1:39">
-      <c r="A62" s="138"/>
-      <c r="B62" s="149" t="s">
+      <c r="A62" s="133"/>
+      <c r="B62" s="121" t="s">
         <v>135</v>
       </c>
-      <c r="C62" s="120" t="s">
+      <c r="C62" s="123" t="s">
         <v>137</v>
       </c>
-      <c r="D62" s="120" t="s">
+      <c r="D62" s="123" t="s">
         <v>136</v>
       </c>
       <c r="E62" s="7" t="s">
@@ -22278,10 +22313,10 @@
       <c r="AM62" s="27"/>
     </row>
     <row r="63" spans="1:39">
-      <c r="A63" s="138"/>
-      <c r="B63" s="150"/>
-      <c r="C63" s="121"/>
-      <c r="D63" s="121"/>
+      <c r="A63" s="133"/>
+      <c r="B63" s="122"/>
+      <c r="C63" s="114"/>
+      <c r="D63" s="114"/>
       <c r="E63" s="13" t="s">
         <v>152</v>
       </c>
@@ -22323,11 +22358,11 @@
       <c r="AM63" s="27"/>
     </row>
     <row r="64" spans="1:39">
-      <c r="A64" s="138"/>
-      <c r="B64" s="133" t="s">
+      <c r="A64" s="133"/>
+      <c r="B64" s="128" t="s">
         <v>122</v>
       </c>
-      <c r="C64" s="126"/>
+      <c r="C64" s="110"/>
       <c r="D64" s="71" t="s">
         <v>62</v>
       </c>
@@ -22426,9 +22461,9 @@
       <c r="AM64" s="27"/>
     </row>
     <row r="65" spans="1:39">
-      <c r="A65" s="138"/>
-      <c r="B65" s="130"/>
-      <c r="C65" s="127"/>
+      <c r="A65" s="133"/>
+      <c r="B65" s="126"/>
+      <c r="C65" s="111"/>
       <c r="D65" s="15" t="s">
         <v>64</v>
       </c>
@@ -22527,9 +22562,9 @@
       <c r="AM65" s="27"/>
     </row>
     <row r="66" spans="1:39">
-      <c r="A66" s="138"/>
-      <c r="B66" s="130"/>
-      <c r="C66" s="127"/>
+      <c r="A66" s="133"/>
+      <c r="B66" s="126"/>
+      <c r="C66" s="111"/>
       <c r="D66" s="15" t="s">
         <v>66</v>
       </c>
@@ -22628,9 +22663,9 @@
       <c r="AM66" s="27"/>
     </row>
     <row r="67" spans="1:39">
-      <c r="A67" s="138"/>
-      <c r="B67" s="130"/>
-      <c r="C67" s="127"/>
+      <c r="A67" s="133"/>
+      <c r="B67" s="126"/>
+      <c r="C67" s="111"/>
       <c r="D67" s="15" t="s">
         <v>68</v>
       </c>
@@ -22729,9 +22764,9 @@
       <c r="AM67" s="27"/>
     </row>
     <row r="68" spans="1:39">
-      <c r="A68" s="138"/>
-      <c r="B68" s="130"/>
-      <c r="C68" s="127"/>
+      <c r="A68" s="133"/>
+      <c r="B68" s="126"/>
+      <c r="C68" s="111"/>
       <c r="D68" s="15" t="s">
         <v>52</v>
       </c>
@@ -22830,9 +22865,9 @@
       <c r="AM68" s="27"/>
     </row>
     <row r="69" spans="1:39">
-      <c r="A69" s="138"/>
-      <c r="B69" s="130"/>
-      <c r="C69" s="127"/>
+      <c r="A69" s="133"/>
+      <c r="B69" s="126"/>
+      <c r="C69" s="111"/>
       <c r="D69" s="15" t="s">
         <v>71</v>
       </c>
@@ -22931,9 +22966,9 @@
       <c r="AM69" s="27"/>
     </row>
     <row r="70" spans="1:39">
-      <c r="A70" s="138"/>
-      <c r="B70" s="130"/>
-      <c r="C70" s="127"/>
+      <c r="A70" s="133"/>
+      <c r="B70" s="126"/>
+      <c r="C70" s="111"/>
       <c r="D70" s="15" t="s">
         <v>73</v>
       </c>
@@ -23032,9 +23067,9 @@
       <c r="AM70" s="27"/>
     </row>
     <row r="71" spans="1:39">
-      <c r="A71" s="138"/>
-      <c r="B71" s="130"/>
-      <c r="C71" s="127"/>
+      <c r="A71" s="133"/>
+      <c r="B71" s="126"/>
+      <c r="C71" s="111"/>
       <c r="D71" s="15" t="s">
         <v>75</v>
       </c>
@@ -23133,9 +23168,9 @@
       <c r="AM71" s="27"/>
     </row>
     <row r="72" spans="1:39">
-      <c r="A72" s="138"/>
-      <c r="B72" s="130"/>
-      <c r="C72" s="127"/>
+      <c r="A72" s="133"/>
+      <c r="B72" s="126"/>
+      <c r="C72" s="111"/>
       <c r="D72" s="15" t="s">
         <v>77</v>
       </c>
@@ -23234,10 +23269,10 @@
       <c r="AM72" s="27"/>
     </row>
     <row r="73" spans="1:39">
-      <c r="A73" s="138"/>
-      <c r="B73" s="130"/>
-      <c r="C73" s="127"/>
-      <c r="D73" s="123" t="s">
+      <c r="A73" s="133"/>
+      <c r="B73" s="126"/>
+      <c r="C73" s="111"/>
+      <c r="D73" s="113" t="s">
         <v>79</v>
       </c>
       <c r="E73" s="16" t="s">
@@ -23339,10 +23374,10 @@
       <c r="AM73" s="27"/>
     </row>
     <row r="74" spans="1:39">
-      <c r="A74" s="138"/>
-      <c r="B74" s="131"/>
-      <c r="C74" s="128"/>
-      <c r="D74" s="121"/>
+      <c r="A74" s="133"/>
+      <c r="B74" s="127"/>
+      <c r="C74" s="112"/>
+      <c r="D74" s="114"/>
       <c r="E74" s="16" t="s">
         <v>81</v>
       </c>
@@ -23442,11 +23477,11 @@
       <c r="AM74" s="27"/>
     </row>
     <row r="75" spans="1:39">
-      <c r="A75" s="138"/>
-      <c r="B75" s="129" t="s">
+      <c r="A75" s="133"/>
+      <c r="B75" s="104" t="s">
         <v>16</v>
       </c>
-      <c r="C75" s="132"/>
+      <c r="C75" s="106"/>
       <c r="D75" s="33" t="s">
         <v>131</v>
       </c>
@@ -23454,119 +23489,119 @@
         <v>82</v>
       </c>
       <c r="F75" s="38">
-        <f>F10</f>
+        <f t="shared" ref="F75:AH75" si="10">F10</f>
         <v>0</v>
       </c>
       <c r="G75" s="38">
-        <f>G10</f>
+        <f t="shared" si="10"/>
         <v>100</v>
       </c>
       <c r="H75" s="38">
-        <f>H10</f>
+        <f t="shared" si="10"/>
         <v>200</v>
       </c>
       <c r="I75" s="38">
-        <f>I10</f>
+        <f t="shared" si="10"/>
         <v>80</v>
       </c>
       <c r="J75" s="38">
-        <f>J10</f>
+        <f t="shared" si="10"/>
         <v>80</v>
       </c>
       <c r="K75" s="38">
-        <f>K10</f>
+        <f t="shared" si="10"/>
         <v>80</v>
       </c>
       <c r="L75" s="38">
-        <f>L10</f>
+        <f t="shared" si="10"/>
         <v>200</v>
       </c>
       <c r="M75" s="38">
-        <f>M10</f>
+        <f t="shared" si="10"/>
         <v>80</v>
       </c>
       <c r="N75" s="38">
-        <f>N10</f>
+        <f t="shared" si="10"/>
         <v>80</v>
       </c>
       <c r="O75" s="38">
-        <f>O10</f>
+        <f t="shared" si="10"/>
         <v>80</v>
       </c>
       <c r="P75" s="38">
-        <f>P10</f>
+        <f t="shared" si="10"/>
         <v>80</v>
       </c>
       <c r="Q75" s="38">
-        <f>Q10</f>
+        <f t="shared" si="10"/>
         <v>80</v>
       </c>
       <c r="R75" s="38">
-        <f>R10</f>
+        <f t="shared" si="10"/>
         <v>80</v>
       </c>
       <c r="S75" s="38">
-        <f>S10</f>
+        <f t="shared" si="10"/>
         <v>80</v>
       </c>
       <c r="T75" s="38">
-        <f>T10</f>
+        <f t="shared" si="10"/>
         <v>80</v>
       </c>
       <c r="U75" s="38">
-        <f>U10</f>
+        <f t="shared" si="10"/>
         <v>80</v>
       </c>
       <c r="V75" s="38">
-        <f>V10</f>
+        <f t="shared" si="10"/>
         <v>80</v>
       </c>
       <c r="W75" s="38">
-        <f>W10</f>
+        <f t="shared" si="10"/>
         <v>50</v>
       </c>
       <c r="X75" s="38">
-        <f>X10</f>
+        <f t="shared" si="10"/>
         <v>50</v>
       </c>
       <c r="Y75" s="38">
-        <f>Y10</f>
+        <f t="shared" si="10"/>
         <v>50</v>
       </c>
       <c r="Z75" s="38">
-        <f>Z10</f>
+        <f t="shared" si="10"/>
         <v>50</v>
       </c>
       <c r="AA75" s="38">
-        <f>AA10</f>
+        <f t="shared" si="10"/>
         <v>30</v>
       </c>
       <c r="AB75" s="38">
-        <f>AB10</f>
+        <f t="shared" si="10"/>
         <v>30</v>
       </c>
       <c r="AC75" s="38">
-        <f>AC10</f>
+        <f t="shared" si="10"/>
         <v>30</v>
       </c>
       <c r="AD75" s="38">
-        <f>AD10</f>
+        <f t="shared" si="10"/>
         <v>30</v>
       </c>
       <c r="AE75" s="38">
-        <f>AE10</f>
+        <f t="shared" si="10"/>
         <v>30</v>
       </c>
       <c r="AF75" s="38">
-        <f>AF10</f>
+        <f t="shared" si="10"/>
         <v>30</v>
       </c>
       <c r="AG75" s="38">
-        <f>AG10</f>
+        <f t="shared" si="10"/>
         <v>30</v>
       </c>
       <c r="AH75" s="38">
-        <f>AH10</f>
+        <f t="shared" si="10"/>
         <v>30</v>
       </c>
       <c r="AI75" s="38"/>
@@ -23576,9 +23611,9 @@
       <c r="AM75" s="27"/>
     </row>
     <row r="76" spans="1:39">
-      <c r="A76" s="138"/>
-      <c r="B76" s="130"/>
-      <c r="C76" s="127"/>
+      <c r="A76" s="133"/>
+      <c r="B76" s="126"/>
+      <c r="C76" s="111"/>
       <c r="D76" s="33" t="s">
         <v>132</v>
       </c>
@@ -23586,119 +23621,119 @@
         <v>83</v>
       </c>
       <c r="F76" s="38">
-        <f>F11</f>
+        <f t="shared" ref="F76:AH76" si="11">F11</f>
         <v>0</v>
       </c>
       <c r="G76" s="38">
-        <f>G11</f>
+        <f t="shared" si="11"/>
         <v>500</v>
       </c>
       <c r="H76" s="38">
-        <f>H11</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="I76" s="38">
-        <f>I11</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="J76" s="38">
-        <f>J11</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="K76" s="38">
-        <f>K11</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="L76" s="38">
-        <f>L11</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="M76" s="38">
-        <f>M11</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="N76" s="38">
-        <f>N11</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="O76" s="38">
-        <f>O11</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P76" s="38">
-        <f>P11</f>
+        <f t="shared" si="11"/>
         <v>200</v>
       </c>
       <c r="Q76" s="38">
-        <f>Q11</f>
+        <f t="shared" si="11"/>
         <v>100</v>
       </c>
       <c r="R76" s="38">
-        <f>R11</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="S76" s="38">
-        <f>S11</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="T76" s="38">
-        <f>T11</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="U76" s="38">
-        <f>U11</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="V76" s="38">
-        <f>V11</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="W76" s="38">
-        <f>W11</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="X76" s="38">
-        <f>X11</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="Y76" s="38">
-        <f>Y11</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="Z76" s="38">
-        <f>Z11</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AA76" s="38">
-        <f>AA11</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AB76" s="38">
-        <f>AB11</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AC76" s="38">
-        <f>AC11</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AD76" s="38">
-        <f>AD11</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AE76" s="38">
-        <f>AE11</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AF76" s="38">
-        <f>AF11</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AG76" s="38">
-        <f>AG11</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AH76" s="38">
-        <f>AH11</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AI76" s="38"/>
@@ -23708,9 +23743,9 @@
       <c r="AM76" s="27"/>
     </row>
     <row r="77" spans="1:39">
-      <c r="A77" s="138"/>
-      <c r="B77" s="130"/>
-      <c r="C77" s="127"/>
+      <c r="A77" s="133"/>
+      <c r="B77" s="126"/>
+      <c r="C77" s="111"/>
       <c r="D77" s="33" t="s">
         <v>133</v>
       </c>
@@ -23718,119 +23753,119 @@
         <v>84</v>
       </c>
       <c r="F77" s="38">
-        <f>F12</f>
+        <f t="shared" ref="F77:AH77" si="12">F12</f>
         <v>0</v>
       </c>
       <c r="G77" s="38">
-        <f>G12</f>
+        <f t="shared" si="12"/>
         <v>5</v>
       </c>
       <c r="H77" s="38">
-        <f>H12</f>
+        <f t="shared" si="12"/>
         <v>61</v>
       </c>
       <c r="I77" s="38">
-        <f>I12</f>
+        <f t="shared" si="12"/>
         <v>25</v>
       </c>
       <c r="J77" s="38">
-        <f>J12</f>
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
       <c r="K77" s="38">
-        <f>K12</f>
+        <f t="shared" si="12"/>
         <v>15</v>
       </c>
       <c r="L77" s="38">
-        <f>L12</f>
+        <f t="shared" si="12"/>
         <v>30</v>
       </c>
       <c r="M77" s="38">
-        <f>M12</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="N77" s="38">
-        <f>N12</f>
+        <f t="shared" si="12"/>
         <v>20</v>
       </c>
       <c r="O77" s="38">
-        <f>O12</f>
+        <f t="shared" si="12"/>
         <v>20</v>
       </c>
       <c r="P77" s="38">
-        <f>P12</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q77" s="38">
-        <f>Q12</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="R77" s="38">
-        <f>R12</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="S77" s="38">
-        <f>S12</f>
+        <f t="shared" si="12"/>
         <v>20</v>
       </c>
       <c r="T77" s="38">
-        <f>T12</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="U77" s="38">
-        <f>U12</f>
+        <f t="shared" si="12"/>
         <v>30</v>
       </c>
       <c r="V77" s="38">
-        <f>V12</f>
+        <f t="shared" si="12"/>
         <v>20</v>
       </c>
       <c r="W77" s="38">
-        <f>W12</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="X77" s="38">
-        <f>X12</f>
+        <f t="shared" si="12"/>
         <v>20</v>
       </c>
       <c r="Y77" s="38">
-        <f>Y12</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Z77" s="38">
-        <f>Z12</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AA77" s="38">
-        <f>AA12</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AB77" s="38">
-        <f>AB12</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AC77" s="38">
-        <f>AC12</f>
+        <f t="shared" si="12"/>
         <v>20</v>
       </c>
       <c r="AD77" s="38">
-        <f>AD12</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AE77" s="38">
-        <f>AE12</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AF77" s="38">
-        <f>AF12</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AG77" s="38">
-        <f>AG12</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AH77" s="38">
-        <f>AH12</f>
+        <f t="shared" si="12"/>
         <v>20</v>
       </c>
       <c r="AI77" s="38"/>
@@ -23840,9 +23875,9 @@
       <c r="AM77" s="27"/>
     </row>
     <row r="78" spans="1:39">
-      <c r="A78" s="138"/>
-      <c r="B78" s="131"/>
-      <c r="C78" s="128"/>
+      <c r="A78" s="133"/>
+      <c r="B78" s="127"/>
+      <c r="C78" s="112"/>
       <c r="D78" s="33" t="s">
         <v>134</v>
       </c>
@@ -23850,119 +23885,119 @@
         <v>85</v>
       </c>
       <c r="F78" s="38">
-        <f>F13</f>
+        <f t="shared" ref="F78:AH78" si="13">F13</f>
         <v>0</v>
       </c>
       <c r="G78" s="38">
-        <f>G13</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="H78" s="38">
-        <f>H13</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="I78" s="38">
-        <f>I13</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="J78" s="38">
-        <f>J13</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="K78" s="38">
-        <f>K13</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="L78" s="38">
-        <f>L13</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="M78" s="38">
-        <f>M13</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="N78" s="38">
-        <f>N13</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="O78" s="38">
-        <f>O13</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="P78" s="38">
-        <f>P13</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="Q78" s="38">
-        <f>Q13</f>
+        <f t="shared" si="13"/>
         <v>200</v>
       </c>
       <c r="R78" s="38">
-        <f>R13</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="S78" s="38">
-        <f>S13</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="T78" s="38">
-        <f>T13</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="U78" s="38">
-        <f>U13</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="V78" s="38">
-        <f>V13</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="W78" s="38">
-        <f>W13</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="X78" s="38">
-        <f>X13</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="Y78" s="38">
-        <f>Y13</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="Z78" s="38">
-        <f>Z13</f>
+        <f t="shared" si="13"/>
         <v>200</v>
       </c>
       <c r="AA78" s="38">
-        <f>AA13</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AB78" s="38">
-        <f>AB13</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AC78" s="38">
-        <f>AC13</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AD78" s="38">
-        <f>AD13</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AE78" s="38">
-        <f>AE13</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AF78" s="38">
-        <f>AF13</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AG78" s="38">
-        <f>AG13</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AH78" s="38">
-        <f>AH13</f>
+        <f t="shared" si="13"/>
         <v>200</v>
       </c>
       <c r="AI78" s="38"/>
@@ -23972,7 +24007,7 @@
       <c r="AM78" s="27"/>
     </row>
     <row r="79" spans="1:39">
-      <c r="A79" s="138"/>
+      <c r="A79" s="133"/>
       <c r="B79" s="67" t="s">
         <v>56</v>
       </c>
@@ -23988,111 +24023,111 @@
         <v>942</v>
       </c>
       <c r="H79" s="35">
-        <f t="shared" ref="H79:AH79" si="10">SUM(H62:H78)</f>
+        <f t="shared" ref="H79:AH79" si="14">SUM(H62:H78)</f>
         <v>554</v>
       </c>
       <c r="I79" s="35">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>398</v>
       </c>
       <c r="J79" s="35">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>383</v>
       </c>
       <c r="K79" s="35">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>388</v>
       </c>
       <c r="L79" s="35">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>523</v>
       </c>
       <c r="M79" s="35">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>373</v>
       </c>
       <c r="N79" s="35">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>393</v>
       </c>
       <c r="O79" s="35">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>393</v>
       </c>
       <c r="P79" s="35">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>573</v>
       </c>
       <c r="Q79" s="35">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>673</v>
       </c>
       <c r="R79" s="35">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>373</v>
       </c>
       <c r="S79" s="35">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>393</v>
       </c>
       <c r="T79" s="35">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>373</v>
       </c>
       <c r="U79" s="35">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>403</v>
       </c>
       <c r="V79" s="35">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>393</v>
       </c>
       <c r="W79" s="35">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>343</v>
       </c>
       <c r="X79" s="35">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>363</v>
       </c>
       <c r="Y79" s="35">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>343</v>
       </c>
       <c r="Z79" s="35">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>543</v>
       </c>
       <c r="AA79" s="35">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>323</v>
       </c>
       <c r="AB79" s="35">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>323</v>
       </c>
       <c r="AC79" s="35">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>343</v>
       </c>
       <c r="AD79" s="35">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>323</v>
       </c>
       <c r="AE79" s="35">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>323</v>
       </c>
       <c r="AF79" s="35">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>317</v>
       </c>
       <c r="AG79" s="35">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>317</v>
       </c>
       <c r="AH79" s="35">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>537</v>
       </c>
       <c r="AI79" s="35"/>
@@ -24102,7 +24137,7 @@
       <c r="AM79" s="27"/>
     </row>
     <row r="80" spans="1:39">
-      <c r="A80" s="138"/>
+      <c r="A80" s="133"/>
       <c r="B80" s="67" t="s">
         <v>58</v>
       </c>
@@ -24113,115 +24148,115 @@
         <v>0</v>
       </c>
       <c r="G80" s="35">
-        <f>G61-G79</f>
+        <f t="shared" ref="G80:AH80" si="15">G61-G79</f>
         <v>-13</v>
       </c>
       <c r="H80" s="35">
-        <f>H61-H79</f>
+        <f t="shared" si="15"/>
         <v>7</v>
       </c>
       <c r="I80" s="35">
-        <f>I61-I79</f>
+        <f t="shared" si="15"/>
         <v>7</v>
       </c>
       <c r="J80" s="35">
-        <f>J61-J79</f>
+        <f t="shared" si="15"/>
         <v>7</v>
       </c>
       <c r="K80" s="35">
-        <f>K61-K79</f>
+        <f t="shared" si="15"/>
         <v>7</v>
       </c>
       <c r="L80" s="35">
-        <f>L61-L79</f>
+        <f t="shared" si="15"/>
         <v>7</v>
       </c>
       <c r="M80" s="35">
-        <f>M61-M79</f>
+        <f t="shared" si="15"/>
         <v>7</v>
       </c>
       <c r="N80" s="35">
-        <f>N61-N79</f>
+        <f t="shared" si="15"/>
         <v>7</v>
       </c>
       <c r="O80" s="35">
-        <f>O61-O79</f>
+        <f t="shared" si="15"/>
         <v>7</v>
       </c>
       <c r="P80" s="35">
-        <f>P61-P79</f>
+        <f t="shared" si="15"/>
         <v>7</v>
       </c>
       <c r="Q80" s="35">
-        <f>Q61-Q79</f>
+        <f t="shared" si="15"/>
         <v>7</v>
       </c>
       <c r="R80" s="35">
-        <f>R61-R79</f>
+        <f t="shared" si="15"/>
         <v>7</v>
       </c>
       <c r="S80" s="35">
-        <f>S61-S79</f>
+        <f t="shared" si="15"/>
         <v>7</v>
       </c>
       <c r="T80" s="35">
-        <f>T61-T79</f>
+        <f t="shared" si="15"/>
         <v>7</v>
       </c>
       <c r="U80" s="35">
-        <f>U61-U79</f>
+        <f t="shared" si="15"/>
         <v>7</v>
       </c>
       <c r="V80" s="35">
-        <f>V61-V79</f>
+        <f t="shared" si="15"/>
         <v>7</v>
       </c>
       <c r="W80" s="35">
-        <f>W61-W79</f>
+        <f t="shared" si="15"/>
         <v>7</v>
       </c>
       <c r="X80" s="35">
-        <f>X61-X79</f>
+        <f t="shared" si="15"/>
         <v>7</v>
       </c>
       <c r="Y80" s="35">
-        <f>Y61-Y79</f>
+        <f t="shared" si="15"/>
         <v>7</v>
       </c>
       <c r="Z80" s="35">
-        <f>Z61-Z79</f>
+        <f t="shared" si="15"/>
         <v>7</v>
       </c>
       <c r="AA80" s="35">
-        <f>AA61-AA79</f>
+        <f t="shared" si="15"/>
         <v>7</v>
       </c>
       <c r="AB80" s="35">
-        <f>AB61-AB79</f>
+        <f t="shared" si="15"/>
         <v>7</v>
       </c>
       <c r="AC80" s="35">
-        <f>AC61-AC79</f>
+        <f t="shared" si="15"/>
         <v>7</v>
       </c>
       <c r="AD80" s="35">
-        <f>AD61-AD79</f>
+        <f t="shared" si="15"/>
         <v>7</v>
       </c>
       <c r="AE80" s="35">
-        <f>AE61-AE79</f>
+        <f t="shared" si="15"/>
         <v>7</v>
       </c>
       <c r="AF80" s="35">
-        <f>AF61-AF79</f>
+        <f t="shared" si="15"/>
         <v>13</v>
       </c>
       <c r="AG80" s="35">
-        <f>AG61-AG79</f>
+        <f t="shared" si="15"/>
         <v>13</v>
       </c>
       <c r="AH80" s="35">
-        <f>AH61-AH79</f>
+        <f t="shared" si="15"/>
         <v>13</v>
       </c>
       <c r="AI80" s="35"/>
@@ -24231,7 +24266,7 @@
       <c r="AM80" s="27"/>
     </row>
     <row r="81" spans="1:39" ht="19.5" thickBot="1">
-      <c r="A81" s="119"/>
+      <c r="A81" s="124"/>
       <c r="B81" s="61" t="s">
         <v>59</v>
       </c>
@@ -24246,111 +24281,111 @@
         <v>-13</v>
       </c>
       <c r="H81" s="41">
-        <f t="shared" ref="H81:AH81" si="11">G81+H80</f>
+        <f t="shared" ref="H81:AH81" si="16">G81+H80</f>
         <v>-6</v>
       </c>
       <c r="I81" s="41">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>1</v>
       </c>
       <c r="J81" s="41">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>8</v>
       </c>
       <c r="K81" s="41">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>15</v>
       </c>
       <c r="L81" s="41">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>22</v>
       </c>
       <c r="M81" s="41">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>29</v>
       </c>
       <c r="N81" s="41">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>36</v>
       </c>
       <c r="O81" s="41">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>43</v>
       </c>
       <c r="P81" s="41">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>50</v>
       </c>
       <c r="Q81" s="41">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>57</v>
       </c>
       <c r="R81" s="41">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>64</v>
       </c>
       <c r="S81" s="41">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>71</v>
       </c>
       <c r="T81" s="41">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>78</v>
       </c>
       <c r="U81" s="41">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>85</v>
       </c>
       <c r="V81" s="41">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>92</v>
       </c>
       <c r="W81" s="41">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>99</v>
       </c>
       <c r="X81" s="41">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>106</v>
       </c>
       <c r="Y81" s="41">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>113</v>
       </c>
       <c r="Z81" s="41">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>120</v>
       </c>
       <c r="AA81" s="41">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>127</v>
       </c>
       <c r="AB81" s="41">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>134</v>
       </c>
       <c r="AC81" s="41">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>141</v>
       </c>
       <c r="AD81" s="41">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>148</v>
       </c>
       <c r="AE81" s="41">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>155</v>
       </c>
       <c r="AF81" s="41">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>168</v>
       </c>
       <c r="AG81" s="41">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>181</v>
       </c>
       <c r="AH81" s="41">
-        <f t="shared" si="11"/>
+        <f t="shared" si="16"/>
         <v>194</v>
       </c>
       <c r="AI81" s="41"/>
@@ -24360,7 +24395,7 @@
       <c r="AM81" s="27"/>
     </row>
     <row r="82" spans="1:39">
-      <c r="A82" s="104" t="s">
+      <c r="A82" s="101" t="s">
         <v>86</v>
       </c>
       <c r="B82" s="59" t="s">
@@ -24370,119 +24405,119 @@
       <c r="D82" s="47"/>
       <c r="E82" s="48"/>
       <c r="F82" s="47">
-        <f>F58+F80</f>
+        <f t="shared" ref="F82:AH82" si="17">F58+F80</f>
         <v>0</v>
       </c>
       <c r="G82" s="47">
-        <f>G58+G80</f>
+        <f t="shared" si="17"/>
         <v>-965</v>
       </c>
       <c r="H82" s="47">
-        <f>H58+H80</f>
+        <f t="shared" si="17"/>
         <v>-154</v>
       </c>
       <c r="I82" s="47">
-        <f>I58+I80</f>
+        <f t="shared" si="17"/>
         <v>-150</v>
       </c>
       <c r="J82" s="47">
-        <f>J58+J80</f>
+        <f t="shared" si="17"/>
         <v>-135</v>
       </c>
       <c r="K82" s="47">
-        <f>K58+K80</f>
+        <f t="shared" si="17"/>
         <v>-48</v>
       </c>
       <c r="L82" s="47">
-        <f>L58+L80</f>
+        <f t="shared" si="17"/>
         <v>15</v>
       </c>
       <c r="M82" s="47">
-        <f>M58+M80</f>
+        <f t="shared" si="17"/>
         <v>-35</v>
       </c>
       <c r="N82" s="47">
-        <f>N58+N80</f>
+        <f t="shared" si="17"/>
         <v>35</v>
       </c>
       <c r="O82" s="47">
-        <f>O58+O80</f>
+        <f t="shared" si="17"/>
         <v>35</v>
       </c>
       <c r="P82" s="47">
-        <f>P58+P80</f>
+        <f t="shared" si="17"/>
         <v>355</v>
       </c>
       <c r="Q82" s="47">
-        <f>Q58+Q80</f>
+        <f t="shared" si="17"/>
         <v>-245</v>
       </c>
       <c r="R82" s="47">
-        <f>R58+R80</f>
+        <f t="shared" si="17"/>
         <v>55</v>
       </c>
       <c r="S82" s="47">
-        <f>S58+S80</f>
+        <f t="shared" si="17"/>
         <v>35</v>
       </c>
       <c r="T82" s="47">
-        <f>T58+T80</f>
+        <f t="shared" si="17"/>
         <v>55</v>
       </c>
       <c r="U82" s="47">
-        <f>U58+U80</f>
+        <f t="shared" si="17"/>
         <v>-44</v>
       </c>
       <c r="V82" s="47">
-        <f>V58+V80</f>
+        <f t="shared" si="17"/>
         <v>-34</v>
       </c>
       <c r="W82" s="47">
-        <f>W58+W80</f>
+        <f t="shared" si="17"/>
         <v>80</v>
       </c>
       <c r="X82" s="47">
-        <f>X58+X80</f>
+        <f t="shared" si="17"/>
         <v>-30</v>
       </c>
       <c r="Y82" s="47">
-        <f>Y58+Y80</f>
+        <f t="shared" si="17"/>
         <v>-10</v>
       </c>
       <c r="Z82" s="47">
-        <f>Z58+Z80</f>
+        <f t="shared" si="17"/>
         <v>2290</v>
       </c>
       <c r="AA82" s="47">
-        <f>AA58+AA80</f>
+        <f t="shared" si="17"/>
         <v>-157</v>
       </c>
       <c r="AB82" s="47">
-        <f>AB58+AB80</f>
+        <f t="shared" si="17"/>
         <v>-157</v>
       </c>
       <c r="AC82" s="47">
-        <f>AC58+AC80</f>
+        <f t="shared" si="17"/>
         <v>-177</v>
       </c>
       <c r="AD82" s="47">
-        <f>AD58+AD80</f>
+        <f t="shared" si="17"/>
         <v>-157</v>
       </c>
       <c r="AE82" s="47">
-        <f>AE58+AE80</f>
+        <f t="shared" si="17"/>
         <v>-157</v>
       </c>
       <c r="AF82" s="47">
-        <f>AF58+AF80</f>
+        <f t="shared" si="17"/>
         <v>-146</v>
       </c>
       <c r="AG82" s="47">
-        <f>AG58+AG80</f>
+        <f t="shared" si="17"/>
         <v>-146</v>
       </c>
       <c r="AH82" s="47">
-        <f>AH58+AH80</f>
+        <f t="shared" si="17"/>
         <v>-366</v>
       </c>
       <c r="AI82" s="47"/>
@@ -24492,7 +24527,7 @@
       <c r="AM82" s="27"/>
     </row>
     <row r="83" spans="1:39" ht="19.5" thickBot="1">
-      <c r="A83" s="119"/>
+      <c r="A83" s="124"/>
       <c r="B83" s="61" t="s">
         <v>88</v>
       </c>
@@ -24500,119 +24535,119 @@
       <c r="D83" s="41"/>
       <c r="E83" s="49"/>
       <c r="F83" s="41">
-        <f>F59+F81</f>
+        <f t="shared" ref="F83:AH83" si="18">F59+F81</f>
         <v>1608</v>
       </c>
       <c r="G83" s="41">
-        <f>G59+G81</f>
+        <f t="shared" si="18"/>
         <v>643</v>
       </c>
       <c r="H83" s="41">
-        <f>H59+H81</f>
+        <f t="shared" si="18"/>
         <v>489</v>
       </c>
       <c r="I83" s="41">
-        <f>I59+I81</f>
+        <f t="shared" si="18"/>
         <v>339</v>
       </c>
       <c r="J83" s="41">
-        <f>J59+J81</f>
+        <f t="shared" si="18"/>
         <v>204</v>
       </c>
       <c r="K83" s="41">
-        <f>K59+K81</f>
+        <f t="shared" si="18"/>
         <v>156</v>
       </c>
       <c r="L83" s="41">
-        <f>L59+L81</f>
+        <f t="shared" si="18"/>
         <v>171</v>
       </c>
       <c r="M83" s="41">
-        <f>M59+M81</f>
+        <f t="shared" si="18"/>
         <v>136</v>
       </c>
       <c r="N83" s="41">
-        <f>N59+N81</f>
+        <f t="shared" si="18"/>
         <v>171</v>
       </c>
       <c r="O83" s="41">
-        <f>O59+O81</f>
+        <f t="shared" si="18"/>
         <v>206</v>
       </c>
       <c r="P83" s="41">
-        <f>P59+P81</f>
+        <f t="shared" si="18"/>
         <v>561</v>
       </c>
       <c r="Q83" s="41">
-        <f>Q59+Q81</f>
+        <f t="shared" si="18"/>
         <v>316</v>
       </c>
       <c r="R83" s="41">
-        <f>R59+R81</f>
+        <f t="shared" si="18"/>
         <v>371</v>
       </c>
       <c r="S83" s="41">
-        <f>S59+S81</f>
+        <f t="shared" si="18"/>
         <v>406</v>
       </c>
       <c r="T83" s="41">
-        <f>T59+T81</f>
+        <f t="shared" si="18"/>
         <v>461</v>
       </c>
       <c r="U83" s="41">
-        <f>U59+U81</f>
+        <f t="shared" si="18"/>
         <v>417</v>
       </c>
       <c r="V83" s="41">
-        <f>V59+V81</f>
+        <f t="shared" si="18"/>
         <v>383</v>
       </c>
       <c r="W83" s="41">
-        <f>W59+W81</f>
+        <f t="shared" si="18"/>
         <v>463</v>
       </c>
       <c r="X83" s="41">
-        <f>X59+X81</f>
+        <f t="shared" si="18"/>
         <v>433</v>
       </c>
       <c r="Y83" s="41">
-        <f>Y59+Y81</f>
+        <f t="shared" si="18"/>
         <v>423</v>
       </c>
       <c r="Z83" s="41">
-        <f>Z59+Z81</f>
+        <f t="shared" si="18"/>
         <v>2713</v>
       </c>
       <c r="AA83" s="41">
-        <f>AA59+AA81</f>
+        <f t="shared" si="18"/>
         <v>2556</v>
       </c>
       <c r="AB83" s="41">
-        <f>AB59+AB81</f>
+        <f t="shared" si="18"/>
         <v>2399</v>
       </c>
       <c r="AC83" s="41">
-        <f>AC59+AC81</f>
+        <f t="shared" si="18"/>
         <v>2222</v>
       </c>
       <c r="AD83" s="41">
-        <f>AD59+AD81</f>
+        <f t="shared" si="18"/>
         <v>2065</v>
       </c>
       <c r="AE83" s="41">
-        <f>AE59+AE81</f>
+        <f t="shared" si="18"/>
         <v>1908</v>
       </c>
       <c r="AF83" s="41">
-        <f>AF59+AF81</f>
+        <f t="shared" si="18"/>
         <v>1762</v>
       </c>
       <c r="AG83" s="41">
-        <f>AG59+AG81</f>
+        <f t="shared" si="18"/>
         <v>1616</v>
       </c>
       <c r="AH83" s="41">
-        <f>AH59+AH81</f>
+        <f t="shared" si="18"/>
         <v>1250</v>
       </c>
       <c r="AI83" s="41"/>
@@ -24673,127 +24708,127 @@
         <v>89</v>
       </c>
       <c r="G92" s="92">
-        <f>G1</f>
+        <f t="shared" ref="G92:AK92" si="19">G1</f>
         <v>2025</v>
       </c>
       <c r="H92" s="92">
-        <f>H1</f>
+        <f t="shared" si="19"/>
         <v>2026</v>
       </c>
       <c r="I92" s="92">
-        <f>I1</f>
+        <f t="shared" si="19"/>
         <v>2027</v>
       </c>
       <c r="J92" s="92">
-        <f>J1</f>
+        <f t="shared" si="19"/>
         <v>2028</v>
       </c>
       <c r="K92" s="92">
-        <f>K1</f>
+        <f t="shared" si="19"/>
         <v>2029</v>
       </c>
       <c r="L92" s="92">
-        <f>L1</f>
+        <f t="shared" si="19"/>
         <v>2030</v>
       </c>
       <c r="M92" s="92">
-        <f>M1</f>
+        <f t="shared" si="19"/>
         <v>2031</v>
       </c>
       <c r="N92" s="92">
-        <f>N1</f>
+        <f t="shared" si="19"/>
         <v>2032</v>
       </c>
       <c r="O92" s="92">
-        <f>O1</f>
+        <f t="shared" si="19"/>
         <v>2033</v>
       </c>
       <c r="P92" s="92">
-        <f>P1</f>
+        <f t="shared" si="19"/>
         <v>2034</v>
       </c>
       <c r="Q92" s="92">
-        <f>Q1</f>
+        <f t="shared" si="19"/>
         <v>2035</v>
       </c>
       <c r="R92" s="92">
-        <f>R1</f>
+        <f t="shared" si="19"/>
         <v>2036</v>
       </c>
       <c r="S92" s="92">
-        <f>S1</f>
+        <f t="shared" si="19"/>
         <v>2037</v>
       </c>
       <c r="T92" s="92">
-        <f>T1</f>
+        <f t="shared" si="19"/>
         <v>2038</v>
       </c>
       <c r="U92" s="92">
-        <f>U1</f>
+        <f t="shared" si="19"/>
         <v>2039</v>
       </c>
       <c r="V92" s="92">
-        <f>V1</f>
+        <f t="shared" si="19"/>
         <v>2040</v>
       </c>
       <c r="W92" s="92">
-        <f>W1</f>
+        <f t="shared" si="19"/>
         <v>2041</v>
       </c>
       <c r="X92" s="92">
-        <f>X1</f>
+        <f t="shared" si="19"/>
         <v>2042</v>
       </c>
       <c r="Y92" s="92">
-        <f>Y1</f>
+        <f t="shared" si="19"/>
         <v>2043</v>
       </c>
       <c r="Z92" s="92">
-        <f>Z1</f>
+        <f t="shared" si="19"/>
         <v>2044</v>
       </c>
       <c r="AA92" s="92">
-        <f>AA1</f>
+        <f t="shared" si="19"/>
         <v>2045</v>
       </c>
       <c r="AB92" s="92">
-        <f>AB1</f>
+        <f t="shared" si="19"/>
         <v>2046</v>
       </c>
       <c r="AC92" s="92">
-        <f>AC1</f>
+        <f t="shared" si="19"/>
         <v>2047</v>
       </c>
       <c r="AD92" s="92">
-        <f>AD1</f>
+        <f t="shared" si="19"/>
         <v>2048</v>
       </c>
       <c r="AE92" s="92">
-        <f>AE1</f>
+        <f t="shared" si="19"/>
         <v>2049</v>
       </c>
       <c r="AF92" s="92">
-        <f>AF1</f>
+        <f t="shared" si="19"/>
         <v>2050</v>
       </c>
       <c r="AG92" s="92">
-        <f>AG1</f>
+        <f t="shared" si="19"/>
         <v>2051</v>
       </c>
       <c r="AH92" s="92">
-        <f>AH1</f>
+        <f t="shared" si="19"/>
         <v>2052</v>
       </c>
       <c r="AI92" s="92">
-        <f>AI1</f>
+        <f t="shared" si="19"/>
         <v>2053</v>
       </c>
       <c r="AJ92" s="92">
-        <f>AJ1</f>
+        <f t="shared" si="19"/>
         <v>2054</v>
       </c>
       <c r="AK92" s="93">
-        <f>AK1</f>
+        <f t="shared" si="19"/>
         <v>2055</v>
       </c>
     </row>
@@ -24802,127 +24837,127 @@
         <v>93</v>
       </c>
       <c r="G93" s="56">
-        <f t="shared" ref="G93:AK93" si="12">G113+G133</f>
+        <f t="shared" ref="G93:AK93" si="20">G113+G133</f>
         <v>2113</v>
       </c>
       <c r="H93" s="57" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>#N/A</v>
       </c>
       <c r="I93" s="57" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>#N/A</v>
       </c>
       <c r="J93" s="57" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>#N/A</v>
       </c>
       <c r="K93" s="57" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>#N/A</v>
       </c>
       <c r="L93" s="57" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>#N/A</v>
       </c>
       <c r="M93" s="57" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>#N/A</v>
       </c>
       <c r="N93" s="57" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>#N/A</v>
       </c>
       <c r="O93" s="57" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>#N/A</v>
       </c>
       <c r="P93" s="57" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>#N/A</v>
       </c>
       <c r="Q93" s="57" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>#N/A</v>
       </c>
       <c r="R93" s="57" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>#N/A</v>
       </c>
       <c r="S93" s="57" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>#N/A</v>
       </c>
       <c r="T93" s="57" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>#N/A</v>
       </c>
       <c r="U93" s="57" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>#N/A</v>
       </c>
       <c r="V93" s="57" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>#N/A</v>
       </c>
       <c r="W93" s="57" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>#N/A</v>
       </c>
       <c r="X93" s="57" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>#N/A</v>
       </c>
       <c r="Y93" s="57" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>#N/A</v>
       </c>
       <c r="Z93" s="57" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>#N/A</v>
       </c>
       <c r="AA93" s="57" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>#N/A</v>
       </c>
       <c r="AB93" s="57" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>#N/A</v>
       </c>
       <c r="AC93" s="57" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>#N/A</v>
       </c>
       <c r="AD93" s="57" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>#N/A</v>
       </c>
       <c r="AE93" s="57" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>#N/A</v>
       </c>
       <c r="AF93" s="57" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>#N/A</v>
       </c>
       <c r="AG93" s="57" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>#N/A</v>
       </c>
       <c r="AH93" s="57" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>#N/A</v>
       </c>
       <c r="AI93" s="57" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>#N/A</v>
       </c>
       <c r="AJ93" s="57" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>#N/A</v>
       </c>
       <c r="AK93" s="58" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>#N/A</v>
       </c>
     </row>
@@ -24931,127 +24966,127 @@
         <v>94</v>
       </c>
       <c r="G94" s="56">
-        <f t="shared" ref="G94:AK94" si="13">G114+G134</f>
+        <f t="shared" ref="G94:AK94" si="21">G114+G134</f>
         <v>1789</v>
       </c>
       <c r="H94" s="57" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="21"/>
         <v>#N/A</v>
       </c>
       <c r="I94" s="57" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="21"/>
         <v>#N/A</v>
       </c>
       <c r="J94" s="57" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="21"/>
         <v>#N/A</v>
       </c>
       <c r="K94" s="57" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="21"/>
         <v>#N/A</v>
       </c>
       <c r="L94" s="57" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="21"/>
         <v>#N/A</v>
       </c>
       <c r="M94" s="57" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="21"/>
         <v>#N/A</v>
       </c>
       <c r="N94" s="57" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="21"/>
         <v>#N/A</v>
       </c>
       <c r="O94" s="57" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="21"/>
         <v>#N/A</v>
       </c>
       <c r="P94" s="57" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="21"/>
         <v>#N/A</v>
       </c>
       <c r="Q94" s="57" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="21"/>
         <v>#N/A</v>
       </c>
       <c r="R94" s="57" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="21"/>
         <v>#N/A</v>
       </c>
       <c r="S94" s="57" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="21"/>
         <v>#N/A</v>
       </c>
       <c r="T94" s="57" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="21"/>
         <v>#N/A</v>
       </c>
       <c r="U94" s="57" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="21"/>
         <v>#N/A</v>
       </c>
       <c r="V94" s="57" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="21"/>
         <v>#N/A</v>
       </c>
       <c r="W94" s="57" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="21"/>
         <v>#N/A</v>
       </c>
       <c r="X94" s="57" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="21"/>
         <v>#N/A</v>
       </c>
       <c r="Y94" s="57" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="21"/>
         <v>#N/A</v>
       </c>
       <c r="Z94" s="57" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="21"/>
         <v>#N/A</v>
       </c>
       <c r="AA94" s="57" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="21"/>
         <v>#N/A</v>
       </c>
       <c r="AB94" s="57" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="21"/>
         <v>#N/A</v>
       </c>
       <c r="AC94" s="57" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="21"/>
         <v>#N/A</v>
       </c>
       <c r="AD94" s="57" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="21"/>
         <v>#N/A</v>
       </c>
       <c r="AE94" s="57" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="21"/>
         <v>#N/A</v>
       </c>
       <c r="AF94" s="57" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="21"/>
         <v>#N/A</v>
       </c>
       <c r="AG94" s="57" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="21"/>
         <v>#N/A</v>
       </c>
       <c r="AH94" s="57" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="21"/>
         <v>#N/A</v>
       </c>
       <c r="AI94" s="57" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="21"/>
         <v>#N/A</v>
       </c>
       <c r="AJ94" s="57" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="21"/>
         <v>#N/A</v>
       </c>
       <c r="AK94" s="58" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="21"/>
         <v>#N/A</v>
       </c>
     </row>
@@ -25060,127 +25095,127 @@
         <v>95</v>
       </c>
       <c r="G95" s="56">
-        <f t="shared" ref="G95:AK95" si="14">G115+G135</f>
+        <f t="shared" ref="G95:AK95" si="22">G115+G135</f>
         <v>1813</v>
       </c>
       <c r="H95" s="57" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="22"/>
         <v>#N/A</v>
       </c>
       <c r="I95" s="57" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="22"/>
         <v>#N/A</v>
       </c>
       <c r="J95" s="57" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="22"/>
         <v>#N/A</v>
       </c>
       <c r="K95" s="57" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="22"/>
         <v>#N/A</v>
       </c>
       <c r="L95" s="57" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="22"/>
         <v>#N/A</v>
       </c>
       <c r="M95" s="57" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="22"/>
         <v>#N/A</v>
       </c>
       <c r="N95" s="57" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="22"/>
         <v>#N/A</v>
       </c>
       <c r="O95" s="57" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="22"/>
         <v>#N/A</v>
       </c>
       <c r="P95" s="57" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="22"/>
         <v>#N/A</v>
       </c>
       <c r="Q95" s="57" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="22"/>
         <v>#N/A</v>
       </c>
       <c r="R95" s="57" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="22"/>
         <v>#N/A</v>
       </c>
       <c r="S95" s="57" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="22"/>
         <v>#N/A</v>
       </c>
       <c r="T95" s="57" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="22"/>
         <v>#N/A</v>
       </c>
       <c r="U95" s="57" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="22"/>
         <v>#N/A</v>
       </c>
       <c r="V95" s="57" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="22"/>
         <v>#N/A</v>
       </c>
       <c r="W95" s="57" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="22"/>
         <v>#N/A</v>
       </c>
       <c r="X95" s="57" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="22"/>
         <v>#N/A</v>
       </c>
       <c r="Y95" s="57" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="22"/>
         <v>#N/A</v>
       </c>
       <c r="Z95" s="57" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="22"/>
         <v>#N/A</v>
       </c>
       <c r="AA95" s="57" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="22"/>
         <v>#N/A</v>
       </c>
       <c r="AB95" s="57" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="22"/>
         <v>#N/A</v>
       </c>
       <c r="AC95" s="57" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="22"/>
         <v>#N/A</v>
       </c>
       <c r="AD95" s="57" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="22"/>
         <v>#N/A</v>
       </c>
       <c r="AE95" s="57" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="22"/>
         <v>#N/A</v>
       </c>
       <c r="AF95" s="57" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="22"/>
         <v>#N/A</v>
       </c>
       <c r="AG95" s="57" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="22"/>
         <v>#N/A</v>
       </c>
       <c r="AH95" s="57" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="22"/>
         <v>#N/A</v>
       </c>
       <c r="AI95" s="57" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="22"/>
         <v>#N/A</v>
       </c>
       <c r="AJ95" s="57" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="22"/>
         <v>#N/A</v>
       </c>
       <c r="AK95" s="58" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="22"/>
         <v>#N/A</v>
       </c>
     </row>
@@ -25189,127 +25224,127 @@
         <v>96</v>
       </c>
       <c r="G96" s="56">
-        <f t="shared" ref="G96:AK96" si="15">G116+G136</f>
+        <f t="shared" ref="G96:AK96" si="23">G116+G136</f>
         <v>1767</v>
       </c>
       <c r="H96" s="57" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="23"/>
         <v>#N/A</v>
       </c>
       <c r="I96" s="57" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="23"/>
         <v>#N/A</v>
       </c>
       <c r="J96" s="57" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="23"/>
         <v>#N/A</v>
       </c>
       <c r="K96" s="57" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="23"/>
         <v>#N/A</v>
       </c>
       <c r="L96" s="57" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="23"/>
         <v>#N/A</v>
       </c>
       <c r="M96" s="57" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="23"/>
         <v>#N/A</v>
       </c>
       <c r="N96" s="57" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="23"/>
         <v>#N/A</v>
       </c>
       <c r="O96" s="57" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="23"/>
         <v>#N/A</v>
       </c>
       <c r="P96" s="57" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="23"/>
         <v>#N/A</v>
       </c>
       <c r="Q96" s="57" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="23"/>
         <v>#N/A</v>
       </c>
       <c r="R96" s="57" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="23"/>
         <v>#N/A</v>
       </c>
       <c r="S96" s="57" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="23"/>
         <v>#N/A</v>
       </c>
       <c r="T96" s="57" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="23"/>
         <v>#N/A</v>
       </c>
       <c r="U96" s="57" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="23"/>
         <v>#N/A</v>
       </c>
       <c r="V96" s="57" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="23"/>
         <v>#N/A</v>
       </c>
       <c r="W96" s="57" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="23"/>
         <v>#N/A</v>
       </c>
       <c r="X96" s="57" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="23"/>
         <v>#N/A</v>
       </c>
       <c r="Y96" s="57" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="23"/>
         <v>#N/A</v>
       </c>
       <c r="Z96" s="57" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="23"/>
         <v>#N/A</v>
       </c>
       <c r="AA96" s="57" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="23"/>
         <v>#N/A</v>
       </c>
       <c r="AB96" s="57" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="23"/>
         <v>#N/A</v>
       </c>
       <c r="AC96" s="57" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="23"/>
         <v>#N/A</v>
       </c>
       <c r="AD96" s="57" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="23"/>
         <v>#N/A</v>
       </c>
       <c r="AE96" s="57" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="23"/>
         <v>#N/A</v>
       </c>
       <c r="AF96" s="57" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="23"/>
         <v>#N/A</v>
       </c>
       <c r="AG96" s="57" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="23"/>
         <v>#N/A</v>
       </c>
       <c r="AH96" s="57" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="23"/>
         <v>#N/A</v>
       </c>
       <c r="AI96" s="57" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="23"/>
         <v>#N/A</v>
       </c>
       <c r="AJ96" s="57" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="23"/>
         <v>#N/A</v>
       </c>
       <c r="AK96" s="58" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="23"/>
         <v>#N/A</v>
       </c>
     </row>
@@ -25318,127 +25353,127 @@
         <v>97</v>
       </c>
       <c r="G97" s="56">
-        <f t="shared" ref="G97:AK97" si="16">G117+G137</f>
+        <f t="shared" ref="G97:AK97" si="24">G117+G137</f>
         <v>1793</v>
       </c>
       <c r="H97" s="57" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="24"/>
         <v>#N/A</v>
       </c>
       <c r="I97" s="57" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="24"/>
         <v>#N/A</v>
       </c>
       <c r="J97" s="57" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="24"/>
         <v>#N/A</v>
       </c>
       <c r="K97" s="57" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="24"/>
         <v>#N/A</v>
       </c>
       <c r="L97" s="57" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="24"/>
         <v>#N/A</v>
       </c>
       <c r="M97" s="57" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="24"/>
         <v>#N/A</v>
       </c>
       <c r="N97" s="57" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="24"/>
         <v>#N/A</v>
       </c>
       <c r="O97" s="57" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="24"/>
         <v>#N/A</v>
       </c>
       <c r="P97" s="57" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="24"/>
         <v>#N/A</v>
       </c>
       <c r="Q97" s="57" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="24"/>
         <v>#N/A</v>
       </c>
       <c r="R97" s="57" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="24"/>
         <v>#N/A</v>
       </c>
       <c r="S97" s="57" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="24"/>
         <v>#N/A</v>
       </c>
       <c r="T97" s="57" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="24"/>
         <v>#N/A</v>
       </c>
       <c r="U97" s="57" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="24"/>
         <v>#N/A</v>
       </c>
       <c r="V97" s="57" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="24"/>
         <v>#N/A</v>
       </c>
       <c r="W97" s="57" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="24"/>
         <v>#N/A</v>
       </c>
       <c r="X97" s="57" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="24"/>
         <v>#N/A</v>
       </c>
       <c r="Y97" s="57" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="24"/>
         <v>#N/A</v>
       </c>
       <c r="Z97" s="57" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="24"/>
         <v>#N/A</v>
       </c>
       <c r="AA97" s="57" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="24"/>
         <v>#N/A</v>
       </c>
       <c r="AB97" s="57" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="24"/>
         <v>#N/A</v>
       </c>
       <c r="AC97" s="57" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="24"/>
         <v>#N/A</v>
       </c>
       <c r="AD97" s="57" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="24"/>
         <v>#N/A</v>
       </c>
       <c r="AE97" s="57" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="24"/>
         <v>#N/A</v>
       </c>
       <c r="AF97" s="57" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="24"/>
         <v>#N/A</v>
       </c>
       <c r="AG97" s="57" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="24"/>
         <v>#N/A</v>
       </c>
       <c r="AH97" s="57" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="24"/>
         <v>#N/A</v>
       </c>
       <c r="AI97" s="57" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="24"/>
         <v>#N/A</v>
       </c>
       <c r="AJ97" s="57" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="24"/>
         <v>#N/A</v>
       </c>
       <c r="AK97" s="58" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="24"/>
         <v>#N/A</v>
       </c>
     </row>
@@ -25447,127 +25482,127 @@
         <v>98</v>
       </c>
       <c r="G98" s="56">
-        <f t="shared" ref="G98:AK98" si="17">G118+G138</f>
+        <f t="shared" ref="G98:AK98" si="25">G118+G138</f>
         <v>1748</v>
       </c>
       <c r="H98" s="57" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="25"/>
         <v>#N/A</v>
       </c>
       <c r="I98" s="57" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="25"/>
         <v>#N/A</v>
       </c>
       <c r="J98" s="57" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="25"/>
         <v>#N/A</v>
       </c>
       <c r="K98" s="57" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="25"/>
         <v>#N/A</v>
       </c>
       <c r="L98" s="57" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="25"/>
         <v>#N/A</v>
       </c>
       <c r="M98" s="57" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="25"/>
         <v>#N/A</v>
       </c>
       <c r="N98" s="57" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="25"/>
         <v>#N/A</v>
       </c>
       <c r="O98" s="57" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="25"/>
         <v>#N/A</v>
       </c>
       <c r="P98" s="57" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="25"/>
         <v>#N/A</v>
       </c>
       <c r="Q98" s="57" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="25"/>
         <v>#N/A</v>
       </c>
       <c r="R98" s="57" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="25"/>
         <v>#N/A</v>
       </c>
       <c r="S98" s="57" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="25"/>
         <v>#N/A</v>
       </c>
       <c r="T98" s="57" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="25"/>
         <v>#N/A</v>
       </c>
       <c r="U98" s="57" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="25"/>
         <v>#N/A</v>
       </c>
       <c r="V98" s="57" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="25"/>
         <v>#N/A</v>
       </c>
       <c r="W98" s="57" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="25"/>
         <v>#N/A</v>
       </c>
       <c r="X98" s="57" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="25"/>
         <v>#N/A</v>
       </c>
       <c r="Y98" s="57" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="25"/>
         <v>#N/A</v>
       </c>
       <c r="Z98" s="57" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="25"/>
         <v>#N/A</v>
       </c>
       <c r="AA98" s="57" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="25"/>
         <v>#N/A</v>
       </c>
       <c r="AB98" s="57" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="25"/>
         <v>#N/A</v>
       </c>
       <c r="AC98" s="57" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="25"/>
         <v>#N/A</v>
       </c>
       <c r="AD98" s="57" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="25"/>
         <v>#N/A</v>
       </c>
       <c r="AE98" s="57" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="25"/>
         <v>#N/A</v>
       </c>
       <c r="AF98" s="57" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="25"/>
         <v>#N/A</v>
       </c>
       <c r="AG98" s="57" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="25"/>
         <v>#N/A</v>
       </c>
       <c r="AH98" s="57" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="25"/>
         <v>#N/A</v>
       </c>
       <c r="AI98" s="57" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="25"/>
         <v>#N/A</v>
       </c>
       <c r="AJ98" s="57" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="25"/>
         <v>#N/A</v>
       </c>
       <c r="AK98" s="58" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="25"/>
         <v>#N/A</v>
       </c>
     </row>
@@ -25576,127 +25611,127 @@
         <v>99</v>
       </c>
       <c r="G99" s="56">
-        <f t="shared" ref="G99:AK99" si="18">G119+G139</f>
+        <f t="shared" ref="G99:AK99" si="26">G119+G139</f>
         <v>1786</v>
       </c>
       <c r="H99" s="57" t="e">
-        <f t="shared" si="18"/>
+        <f t="shared" si="26"/>
         <v>#N/A</v>
       </c>
       <c r="I99" s="57" t="e">
-        <f t="shared" si="18"/>
+        <f t="shared" si="26"/>
         <v>#N/A</v>
       </c>
       <c r="J99" s="57" t="e">
-        <f t="shared" si="18"/>
+        <f t="shared" si="26"/>
         <v>#N/A</v>
       </c>
       <c r="K99" s="57" t="e">
-        <f t="shared" si="18"/>
+        <f t="shared" si="26"/>
         <v>#N/A</v>
       </c>
       <c r="L99" s="57" t="e">
-        <f t="shared" si="18"/>
+        <f t="shared" si="26"/>
         <v>#N/A</v>
       </c>
       <c r="M99" s="57" t="e">
-        <f t="shared" si="18"/>
+        <f t="shared" si="26"/>
         <v>#N/A</v>
       </c>
       <c r="N99" s="57" t="e">
-        <f t="shared" si="18"/>
+        <f t="shared" si="26"/>
         <v>#N/A</v>
       </c>
       <c r="O99" s="57" t="e">
-        <f t="shared" si="18"/>
+        <f t="shared" si="26"/>
         <v>#N/A</v>
       </c>
       <c r="P99" s="57" t="e">
-        <f t="shared" si="18"/>
+        <f t="shared" si="26"/>
         <v>#N/A</v>
       </c>
       <c r="Q99" s="57" t="e">
-        <f t="shared" si="18"/>
+        <f t="shared" si="26"/>
         <v>#N/A</v>
       </c>
       <c r="R99" s="57" t="e">
-        <f t="shared" si="18"/>
+        <f t="shared" si="26"/>
         <v>#N/A</v>
       </c>
       <c r="S99" s="57" t="e">
-        <f t="shared" si="18"/>
+        <f t="shared" si="26"/>
         <v>#N/A</v>
       </c>
       <c r="T99" s="57" t="e">
-        <f t="shared" si="18"/>
+        <f t="shared" si="26"/>
         <v>#N/A</v>
       </c>
       <c r="U99" s="57" t="e">
-        <f t="shared" si="18"/>
+        <f t="shared" si="26"/>
         <v>#N/A</v>
       </c>
       <c r="V99" s="57" t="e">
-        <f t="shared" si="18"/>
+        <f t="shared" si="26"/>
         <v>#N/A</v>
       </c>
       <c r="W99" s="57" t="e">
-        <f t="shared" si="18"/>
+        <f t="shared" si="26"/>
         <v>#N/A</v>
       </c>
       <c r="X99" s="57" t="e">
-        <f t="shared" si="18"/>
+        <f t="shared" si="26"/>
         <v>#N/A</v>
       </c>
       <c r="Y99" s="57" t="e">
-        <f t="shared" si="18"/>
+        <f t="shared" si="26"/>
         <v>#N/A</v>
       </c>
       <c r="Z99" s="57" t="e">
-        <f t="shared" si="18"/>
+        <f t="shared" si="26"/>
         <v>#N/A</v>
       </c>
       <c r="AA99" s="57" t="e">
-        <f t="shared" si="18"/>
+        <f t="shared" si="26"/>
         <v>#N/A</v>
       </c>
       <c r="AB99" s="57" t="e">
-        <f t="shared" si="18"/>
+        <f t="shared" si="26"/>
         <v>#N/A</v>
       </c>
       <c r="AC99" s="57" t="e">
-        <f t="shared" si="18"/>
+        <f t="shared" si="26"/>
         <v>#N/A</v>
       </c>
       <c r="AD99" s="57" t="e">
-        <f t="shared" si="18"/>
+        <f t="shared" si="26"/>
         <v>#N/A</v>
       </c>
       <c r="AE99" s="57" t="e">
-        <f t="shared" si="18"/>
+        <f t="shared" si="26"/>
         <v>#N/A</v>
       </c>
       <c r="AF99" s="57" t="e">
-        <f t="shared" si="18"/>
+        <f t="shared" si="26"/>
         <v>#N/A</v>
       </c>
       <c r="AG99" s="57" t="e">
-        <f t="shared" si="18"/>
+        <f t="shared" si="26"/>
         <v>#N/A</v>
       </c>
       <c r="AH99" s="57" t="e">
-        <f t="shared" si="18"/>
+        <f t="shared" si="26"/>
         <v>#N/A</v>
       </c>
       <c r="AI99" s="57" t="e">
-        <f t="shared" si="18"/>
+        <f t="shared" si="26"/>
         <v>#N/A</v>
       </c>
       <c r="AJ99" s="57" t="e">
-        <f t="shared" si="18"/>
+        <f t="shared" si="26"/>
         <v>#N/A</v>
       </c>
       <c r="AK99" s="58" t="e">
-        <f t="shared" si="18"/>
+        <f t="shared" si="26"/>
         <v>#N/A</v>
       </c>
     </row>
@@ -25705,127 +25740,127 @@
         <v>100</v>
       </c>
       <c r="G100" s="56">
-        <f t="shared" ref="G100:AK100" si="19">G120+G140</f>
+        <f t="shared" ref="G100:AK100" si="27">G120+G140</f>
         <v>1748</v>
       </c>
       <c r="H100" s="57" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="27"/>
         <v>#N/A</v>
       </c>
       <c r="I100" s="57" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="27"/>
         <v>#N/A</v>
       </c>
       <c r="J100" s="57" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="27"/>
         <v>#N/A</v>
       </c>
       <c r="K100" s="57" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="27"/>
         <v>#N/A</v>
       </c>
       <c r="L100" s="57" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="27"/>
         <v>#N/A</v>
       </c>
       <c r="M100" s="57" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="27"/>
         <v>#N/A</v>
       </c>
       <c r="N100" s="57" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="27"/>
         <v>#N/A</v>
       </c>
       <c r="O100" s="57" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="27"/>
         <v>#N/A</v>
       </c>
       <c r="P100" s="57" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="27"/>
         <v>#N/A</v>
       </c>
       <c r="Q100" s="57" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="27"/>
         <v>#N/A</v>
       </c>
       <c r="R100" s="57" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="27"/>
         <v>#N/A</v>
       </c>
       <c r="S100" s="57" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="27"/>
         <v>#N/A</v>
       </c>
       <c r="T100" s="57" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="27"/>
         <v>#N/A</v>
       </c>
       <c r="U100" s="57" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="27"/>
         <v>#N/A</v>
       </c>
       <c r="V100" s="57" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="27"/>
         <v>#N/A</v>
       </c>
       <c r="W100" s="57" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="27"/>
         <v>#N/A</v>
       </c>
       <c r="X100" s="57" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="27"/>
         <v>#N/A</v>
       </c>
       <c r="Y100" s="57" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="27"/>
         <v>#N/A</v>
       </c>
       <c r="Z100" s="57" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="27"/>
         <v>#N/A</v>
       </c>
       <c r="AA100" s="57" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="27"/>
         <v>#N/A</v>
       </c>
       <c r="AB100" s="57" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="27"/>
         <v>#N/A</v>
       </c>
       <c r="AC100" s="57" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="27"/>
         <v>#N/A</v>
       </c>
       <c r="AD100" s="57" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="27"/>
         <v>#N/A</v>
       </c>
       <c r="AE100" s="57" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="27"/>
         <v>#N/A</v>
       </c>
       <c r="AF100" s="57" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="27"/>
         <v>#N/A</v>
       </c>
       <c r="AG100" s="57" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="27"/>
         <v>#N/A</v>
       </c>
       <c r="AH100" s="57" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="27"/>
         <v>#N/A</v>
       </c>
       <c r="AI100" s="57" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="27"/>
         <v>#N/A</v>
       </c>
       <c r="AJ100" s="57" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="27"/>
         <v>#N/A</v>
       </c>
       <c r="AK100" s="58" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="27"/>
         <v>#N/A</v>
       </c>
     </row>
@@ -25834,127 +25869,127 @@
         <v>101</v>
       </c>
       <c r="G101" s="56">
-        <f t="shared" ref="G101:AK101" si="20">G121+G141</f>
+        <f t="shared" ref="G101:AK101" si="28">G121+G141</f>
         <v>1766</v>
       </c>
       <c r="H101" s="57" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="28"/>
         <v>#N/A</v>
       </c>
       <c r="I101" s="57" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="28"/>
         <v>#N/A</v>
       </c>
       <c r="J101" s="57" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="28"/>
         <v>#N/A</v>
       </c>
       <c r="K101" s="57" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="28"/>
         <v>#N/A</v>
       </c>
       <c r="L101" s="57" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="28"/>
         <v>#N/A</v>
       </c>
       <c r="M101" s="57" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="28"/>
         <v>#N/A</v>
       </c>
       <c r="N101" s="57" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="28"/>
         <v>#N/A</v>
       </c>
       <c r="O101" s="57" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="28"/>
         <v>#N/A</v>
       </c>
       <c r="P101" s="57" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="28"/>
         <v>#N/A</v>
       </c>
       <c r="Q101" s="57" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="28"/>
         <v>#N/A</v>
       </c>
       <c r="R101" s="57" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="28"/>
         <v>#N/A</v>
       </c>
       <c r="S101" s="57" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="28"/>
         <v>#N/A</v>
       </c>
       <c r="T101" s="57" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="28"/>
         <v>#N/A</v>
       </c>
       <c r="U101" s="57" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="28"/>
         <v>#N/A</v>
       </c>
       <c r="V101" s="57" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="28"/>
         <v>#N/A</v>
       </c>
       <c r="W101" s="57" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="28"/>
         <v>#N/A</v>
       </c>
       <c r="X101" s="57" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="28"/>
         <v>#N/A</v>
       </c>
       <c r="Y101" s="57" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="28"/>
         <v>#N/A</v>
       </c>
       <c r="Z101" s="57" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="28"/>
         <v>#N/A</v>
       </c>
       <c r="AA101" s="57" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="28"/>
         <v>#N/A</v>
       </c>
       <c r="AB101" s="57" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="28"/>
         <v>#N/A</v>
       </c>
       <c r="AC101" s="57" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="28"/>
         <v>#N/A</v>
       </c>
       <c r="AD101" s="57" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="28"/>
         <v>#N/A</v>
       </c>
       <c r="AE101" s="57" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="28"/>
         <v>#N/A</v>
       </c>
       <c r="AF101" s="57" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="28"/>
         <v>#N/A</v>
       </c>
       <c r="AG101" s="57" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="28"/>
         <v>#N/A</v>
       </c>
       <c r="AH101" s="57" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="28"/>
         <v>#N/A</v>
       </c>
       <c r="AI101" s="57" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="28"/>
         <v>#N/A</v>
       </c>
       <c r="AJ101" s="57" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="28"/>
         <v>#N/A</v>
       </c>
       <c r="AK101" s="58" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="28"/>
         <v>#N/A</v>
       </c>
     </row>
@@ -25963,127 +25998,127 @@
         <v>90</v>
       </c>
       <c r="G102" s="56">
-        <f t="shared" ref="G102:AK102" si="21">G122+G142</f>
+        <f t="shared" ref="G102:AK102" si="29">G122+G142</f>
         <v>1719</v>
       </c>
       <c r="H102" s="57" t="e">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>#N/A</v>
       </c>
       <c r="I102" s="57" t="e">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>#N/A</v>
       </c>
       <c r="J102" s="57" t="e">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>#N/A</v>
       </c>
       <c r="K102" s="57" t="e">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>#N/A</v>
       </c>
       <c r="L102" s="57" t="e">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>#N/A</v>
       </c>
       <c r="M102" s="57" t="e">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>#N/A</v>
       </c>
       <c r="N102" s="57" t="e">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>#N/A</v>
       </c>
       <c r="O102" s="57" t="e">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>#N/A</v>
       </c>
       <c r="P102" s="57" t="e">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>#N/A</v>
       </c>
       <c r="Q102" s="57" t="e">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>#N/A</v>
       </c>
       <c r="R102" s="57" t="e">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>#N/A</v>
       </c>
       <c r="S102" s="57" t="e">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>#N/A</v>
       </c>
       <c r="T102" s="57" t="e">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>#N/A</v>
       </c>
       <c r="U102" s="57" t="e">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>#N/A</v>
       </c>
       <c r="V102" s="57" t="e">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>#N/A</v>
       </c>
       <c r="W102" s="57" t="e">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>#N/A</v>
       </c>
       <c r="X102" s="57" t="e">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>#N/A</v>
       </c>
       <c r="Y102" s="57" t="e">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>#N/A</v>
       </c>
       <c r="Z102" s="57" t="e">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>#N/A</v>
       </c>
       <c r="AA102" s="57" t="e">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>#N/A</v>
       </c>
       <c r="AB102" s="57" t="e">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>#N/A</v>
       </c>
       <c r="AC102" s="57" t="e">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>#N/A</v>
       </c>
       <c r="AD102" s="57" t="e">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>#N/A</v>
       </c>
       <c r="AE102" s="57" t="e">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>#N/A</v>
       </c>
       <c r="AF102" s="57" t="e">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>#N/A</v>
       </c>
       <c r="AG102" s="57" t="e">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>#N/A</v>
       </c>
       <c r="AH102" s="57" t="e">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>#N/A</v>
       </c>
       <c r="AI102" s="57" t="e">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>#N/A</v>
       </c>
       <c r="AJ102" s="57" t="e">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>#N/A</v>
       </c>
       <c r="AK102" s="58" t="e">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>#N/A</v>
       </c>
     </row>
@@ -26091,128 +26126,128 @@
       <c r="F103" s="55" t="s">
         <v>91</v>
       </c>
-      <c r="G103" s="56" t="e">
-        <f t="shared" ref="G103:AK103" si="22">G123+G143</f>
-        <v>#N/A</v>
+      <c r="G103" s="56">
+        <f t="shared" ref="G103:AK103" si="30">G123+G143</f>
+        <v>1731</v>
       </c>
       <c r="H103" s="57" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="30"/>
         <v>#N/A</v>
       </c>
       <c r="I103" s="57" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="30"/>
         <v>#N/A</v>
       </c>
       <c r="J103" s="57" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="30"/>
         <v>#N/A</v>
       </c>
       <c r="K103" s="57" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="30"/>
         <v>#N/A</v>
       </c>
       <c r="L103" s="57" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="30"/>
         <v>#N/A</v>
       </c>
       <c r="M103" s="57" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="30"/>
         <v>#N/A</v>
       </c>
       <c r="N103" s="57" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="30"/>
         <v>#N/A</v>
       </c>
       <c r="O103" s="57" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="30"/>
         <v>#N/A</v>
       </c>
       <c r="P103" s="57" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="30"/>
         <v>#N/A</v>
       </c>
       <c r="Q103" s="57" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="30"/>
         <v>#N/A</v>
       </c>
       <c r="R103" s="57" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="30"/>
         <v>#N/A</v>
       </c>
       <c r="S103" s="57" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="30"/>
         <v>#N/A</v>
       </c>
       <c r="T103" s="57" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="30"/>
         <v>#N/A</v>
       </c>
       <c r="U103" s="57" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="30"/>
         <v>#N/A</v>
       </c>
       <c r="V103" s="57" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="30"/>
         <v>#N/A</v>
       </c>
       <c r="W103" s="57" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="30"/>
         <v>#N/A</v>
       </c>
       <c r="X103" s="57" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="30"/>
         <v>#N/A</v>
       </c>
       <c r="Y103" s="57" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="30"/>
         <v>#N/A</v>
       </c>
       <c r="Z103" s="57" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="30"/>
         <v>#N/A</v>
       </c>
       <c r="AA103" s="57" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="30"/>
         <v>#N/A</v>
       </c>
       <c r="AB103" s="57" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="30"/>
         <v>#N/A</v>
       </c>
       <c r="AC103" s="57" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="30"/>
         <v>#N/A</v>
       </c>
       <c r="AD103" s="57" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="30"/>
         <v>#N/A</v>
       </c>
       <c r="AE103" s="57" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="30"/>
         <v>#N/A</v>
       </c>
       <c r="AF103" s="57" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="30"/>
         <v>#N/A</v>
       </c>
       <c r="AG103" s="57" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="30"/>
         <v>#N/A</v>
       </c>
       <c r="AH103" s="57" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="30"/>
         <v>#N/A</v>
       </c>
       <c r="AI103" s="57" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="30"/>
         <v>#N/A</v>
       </c>
       <c r="AJ103" s="57" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="30"/>
         <v>#N/A</v>
       </c>
       <c r="AK103" s="58" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="30"/>
         <v>#N/A</v>
       </c>
     </row>
@@ -26221,127 +26256,127 @@
         <v>92</v>
       </c>
       <c r="G104" s="51" t="e">
-        <f t="shared" ref="G104:AK104" si="23">G124+G144</f>
+        <f t="shared" ref="G104:AK104" si="31">G124+G144</f>
         <v>#N/A</v>
       </c>
       <c r="H104" s="57" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="31"/>
         <v>#N/A</v>
       </c>
       <c r="I104" s="57" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="31"/>
         <v>#N/A</v>
       </c>
       <c r="J104" s="57" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="31"/>
         <v>#N/A</v>
       </c>
       <c r="K104" s="57" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="31"/>
         <v>#N/A</v>
       </c>
       <c r="L104" s="57" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="31"/>
         <v>#N/A</v>
       </c>
       <c r="M104" s="57" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="31"/>
         <v>#N/A</v>
       </c>
       <c r="N104" s="57" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="31"/>
         <v>#N/A</v>
       </c>
       <c r="O104" s="57" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="31"/>
         <v>#N/A</v>
       </c>
       <c r="P104" s="57" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="31"/>
         <v>#N/A</v>
       </c>
       <c r="Q104" s="57" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="31"/>
         <v>#N/A</v>
       </c>
       <c r="R104" s="57" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="31"/>
         <v>#N/A</v>
       </c>
       <c r="S104" s="57" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="31"/>
         <v>#N/A</v>
       </c>
       <c r="T104" s="57" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="31"/>
         <v>#N/A</v>
       </c>
       <c r="U104" s="57" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="31"/>
         <v>#N/A</v>
       </c>
       <c r="V104" s="57" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="31"/>
         <v>#N/A</v>
       </c>
       <c r="W104" s="57" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="31"/>
         <v>#N/A</v>
       </c>
       <c r="X104" s="57" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="31"/>
         <v>#N/A</v>
       </c>
       <c r="Y104" s="57" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="31"/>
         <v>#N/A</v>
       </c>
       <c r="Z104" s="57" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="31"/>
         <v>#N/A</v>
       </c>
       <c r="AA104" s="57" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="31"/>
         <v>#N/A</v>
       </c>
       <c r="AB104" s="57" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="31"/>
         <v>#N/A</v>
       </c>
       <c r="AC104" s="57" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="31"/>
         <v>#N/A</v>
       </c>
       <c r="AD104" s="57" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="31"/>
         <v>#N/A</v>
       </c>
       <c r="AE104" s="57" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="31"/>
         <v>#N/A</v>
       </c>
       <c r="AF104" s="57" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="31"/>
         <v>#N/A</v>
       </c>
       <c r="AG104" s="57" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="31"/>
         <v>#N/A</v>
       </c>
       <c r="AH104" s="57" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="31"/>
         <v>#N/A</v>
       </c>
       <c r="AI104" s="57" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="31"/>
         <v>#N/A</v>
       </c>
       <c r="AJ104" s="57" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="31"/>
         <v>#N/A</v>
       </c>
       <c r="AK104" s="58" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="31"/>
         <v>#N/A</v>
       </c>
     </row>
@@ -26350,127 +26385,127 @@
         <v>102</v>
       </c>
       <c r="G105" s="95">
-        <f t="shared" ref="G105:AK105" si="24">G83</f>
+        <f t="shared" ref="G105:AK105" si="32">G83</f>
         <v>643</v>
       </c>
       <c r="H105" s="35">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>489</v>
       </c>
       <c r="I105" s="35">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>339</v>
       </c>
       <c r="J105" s="35">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>204</v>
       </c>
       <c r="K105" s="35">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>156</v>
       </c>
       <c r="L105" s="35">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>171</v>
       </c>
       <c r="M105" s="35">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>136</v>
       </c>
       <c r="N105" s="35">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>171</v>
       </c>
       <c r="O105" s="35">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>206</v>
       </c>
       <c r="P105" s="35">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>561</v>
       </c>
       <c r="Q105" s="35">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>316</v>
       </c>
       <c r="R105" s="35">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>371</v>
       </c>
       <c r="S105" s="35">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>406</v>
       </c>
       <c r="T105" s="35">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>461</v>
       </c>
       <c r="U105" s="35">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>417</v>
       </c>
       <c r="V105" s="35">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>383</v>
       </c>
       <c r="W105" s="35">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>463</v>
       </c>
       <c r="X105" s="35">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>433</v>
       </c>
       <c r="Y105" s="35">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>423</v>
       </c>
       <c r="Z105" s="35">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>2713</v>
       </c>
       <c r="AA105" s="35">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>2556</v>
       </c>
       <c r="AB105" s="35">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>2399</v>
       </c>
       <c r="AC105" s="35">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>2222</v>
       </c>
       <c r="AD105" s="35">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>2065</v>
       </c>
       <c r="AE105" s="35">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>1908</v>
       </c>
       <c r="AF105" s="35">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>1762</v>
       </c>
       <c r="AG105" s="35">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>1616</v>
       </c>
       <c r="AH105" s="35">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>1250</v>
       </c>
       <c r="AI105" s="35">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="AJ105" s="35">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="AK105" s="37">
-        <f t="shared" si="24"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
     </row>
@@ -26483,35 +26518,35 @@
         <v>-1123</v>
       </c>
       <c r="H106" s="41" t="e">
-        <f t="shared" ref="H106:O106" si="25">H105-H101</f>
+        <f t="shared" ref="H106:O106" si="33">H105-H101</f>
         <v>#N/A</v>
       </c>
       <c r="I106" s="41" t="e">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v>#N/A</v>
       </c>
       <c r="J106" s="41" t="e">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v>#N/A</v>
       </c>
       <c r="K106" s="41" t="e">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v>#N/A</v>
       </c>
       <c r="L106" s="41" t="e">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v>#N/A</v>
       </c>
       <c r="M106" s="41" t="e">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v>#N/A</v>
       </c>
       <c r="N106" s="41" t="e">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v>#N/A</v>
       </c>
       <c r="O106" s="41" t="e">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v>#N/A</v>
       </c>
       <c r="P106" s="41"/>
@@ -27626,8 +27661,8 @@
       <c r="F123" s="55" t="s">
         <v>91</v>
       </c>
-      <c r="G123" s="56" t="e">
-        <v>#N/A</v>
+      <c r="G123" s="56">
+        <v>1272</v>
       </c>
       <c r="H123" s="57" t="e">
         <v>#N/A</v>
@@ -27823,127 +27858,127 @@
         <v>102</v>
       </c>
       <c r="G125" s="46">
-        <f>G59</f>
+        <f t="shared" ref="G125:AK125" si="34">G59</f>
         <v>656</v>
       </c>
       <c r="H125" s="47">
-        <f>H59</f>
+        <f t="shared" si="34"/>
         <v>495</v>
       </c>
       <c r="I125" s="47">
-        <f>I59</f>
+        <f t="shared" si="34"/>
         <v>338</v>
       </c>
       <c r="J125" s="47">
-        <f>J59</f>
+        <f t="shared" si="34"/>
         <v>196</v>
       </c>
       <c r="K125" s="47">
-        <f>K59</f>
+        <f t="shared" si="34"/>
         <v>141</v>
       </c>
       <c r="L125" s="47">
-        <f>L59</f>
+        <f t="shared" si="34"/>
         <v>149</v>
       </c>
       <c r="M125" s="47">
-        <f>M59</f>
+        <f t="shared" si="34"/>
         <v>107</v>
       </c>
       <c r="N125" s="47">
-        <f>N59</f>
+        <f t="shared" si="34"/>
         <v>135</v>
       </c>
       <c r="O125" s="47">
-        <f>O59</f>
+        <f t="shared" si="34"/>
         <v>163</v>
       </c>
       <c r="P125" s="47">
-        <f>P59</f>
+        <f t="shared" si="34"/>
         <v>511</v>
       </c>
       <c r="Q125" s="47">
-        <f>Q59</f>
+        <f t="shared" si="34"/>
         <v>259</v>
       </c>
       <c r="R125" s="47">
-        <f>R59</f>
+        <f t="shared" si="34"/>
         <v>307</v>
       </c>
       <c r="S125" s="47">
-        <f>S59</f>
+        <f t="shared" si="34"/>
         <v>335</v>
       </c>
       <c r="T125" s="47">
-        <f>T59</f>
+        <f t="shared" si="34"/>
         <v>383</v>
       </c>
       <c r="U125" s="47">
-        <f>U59</f>
+        <f t="shared" si="34"/>
         <v>332</v>
       </c>
       <c r="V125" s="47">
-        <f>V59</f>
+        <f t="shared" si="34"/>
         <v>291</v>
       </c>
       <c r="W125" s="47">
-        <f>W59</f>
+        <f t="shared" si="34"/>
         <v>364</v>
       </c>
       <c r="X125" s="47">
-        <f>X59</f>
+        <f t="shared" si="34"/>
         <v>327</v>
       </c>
       <c r="Y125" s="47">
-        <f>Y59</f>
+        <f t="shared" si="34"/>
         <v>310</v>
       </c>
       <c r="Z125" s="47">
-        <f>Z59</f>
+        <f t="shared" si="34"/>
         <v>2593</v>
       </c>
       <c r="AA125" s="47">
-        <f>AA59</f>
+        <f t="shared" si="34"/>
         <v>2429</v>
       </c>
       <c r="AB125" s="47">
-        <f>AB59</f>
+        <f t="shared" si="34"/>
         <v>2265</v>
       </c>
       <c r="AC125" s="47">
-        <f>AC59</f>
+        <f t="shared" si="34"/>
         <v>2081</v>
       </c>
       <c r="AD125" s="47">
-        <f>AD59</f>
+        <f t="shared" si="34"/>
         <v>1917</v>
       </c>
       <c r="AE125" s="47">
-        <f>AE59</f>
+        <f t="shared" si="34"/>
         <v>1753</v>
       </c>
       <c r="AF125" s="47">
-        <f>AF59</f>
+        <f t="shared" si="34"/>
         <v>1594</v>
       </c>
       <c r="AG125" s="47">
-        <f>AG59</f>
+        <f t="shared" si="34"/>
         <v>1435</v>
       </c>
       <c r="AH125" s="47">
-        <f>AH59</f>
+        <f t="shared" si="34"/>
         <v>1056</v>
       </c>
       <c r="AI125" s="47">
-        <f>AI59</f>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AJ125" s="47">
-        <f>AJ59</f>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AK125" s="90">
-        <f>AK59</f>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
     </row>
@@ -27956,123 +27991,123 @@
         <v>-574</v>
       </c>
       <c r="H126" s="41" t="e">
-        <f t="shared" ref="H126:AK126" si="26">H125-H121</f>
+        <f t="shared" ref="H126:AK126" si="35">H125-H121</f>
         <v>#N/A</v>
       </c>
       <c r="I126" s="41" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>#N/A</v>
       </c>
       <c r="J126" s="41" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>#N/A</v>
       </c>
       <c r="K126" s="41" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>#N/A</v>
       </c>
       <c r="L126" s="41" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>#N/A</v>
       </c>
       <c r="M126" s="41" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>#N/A</v>
       </c>
       <c r="N126" s="41" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>#N/A</v>
       </c>
       <c r="O126" s="41" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>#N/A</v>
       </c>
       <c r="P126" s="41" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>#N/A</v>
       </c>
       <c r="Q126" s="41" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>#N/A</v>
       </c>
       <c r="R126" s="41" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>#N/A</v>
       </c>
       <c r="S126" s="41" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>#N/A</v>
       </c>
       <c r="T126" s="41" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>#N/A</v>
       </c>
       <c r="U126" s="41" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>#N/A</v>
       </c>
       <c r="V126" s="41" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>#N/A</v>
       </c>
       <c r="W126" s="41" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>#N/A</v>
       </c>
       <c r="X126" s="41" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>#N/A</v>
       </c>
       <c r="Y126" s="41" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>#N/A</v>
       </c>
       <c r="Z126" s="41" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>#N/A</v>
       </c>
       <c r="AA126" s="41" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>#N/A</v>
       </c>
       <c r="AB126" s="41" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>#N/A</v>
       </c>
       <c r="AC126" s="41" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>#N/A</v>
       </c>
       <c r="AD126" s="41" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>#N/A</v>
       </c>
       <c r="AE126" s="41" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>#N/A</v>
       </c>
       <c r="AF126" s="41" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>#N/A</v>
       </c>
       <c r="AG126" s="41" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>#N/A</v>
       </c>
       <c r="AH126" s="41" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>#N/A</v>
       </c>
       <c r="AI126" s="41" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>#N/A</v>
       </c>
       <c r="AJ126" s="41" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>#N/A</v>
       </c>
       <c r="AK126" s="42" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="35"/>
         <v>#N/A</v>
       </c>
     </row>
@@ -29167,8 +29202,8 @@
       <c r="F143" s="55" t="s">
         <v>91</v>
       </c>
-      <c r="G143" s="56" t="e">
-        <v>#N/A</v>
+      <c r="G143" s="56">
+        <v>459</v>
       </c>
       <c r="H143" s="57" t="e">
         <v>#N/A</v>
@@ -29364,7 +29399,7 @@
         <v>102</v>
       </c>
       <c r="G145" s="46">
-        <f t="shared" ref="G145:AK145" si="27">G81</f>
+        <f t="shared" ref="G145:AK145" si="36">G81</f>
         <v>-13</v>
       </c>
       <c r="H145" s="47">
@@ -29372,119 +29407,119 @@
         <v>-6</v>
       </c>
       <c r="I145" s="47">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>1</v>
       </c>
       <c r="J145" s="47">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>8</v>
       </c>
       <c r="K145" s="47">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>15</v>
       </c>
       <c r="L145" s="47">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>22</v>
       </c>
       <c r="M145" s="47">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>29</v>
       </c>
       <c r="N145" s="47">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>36</v>
       </c>
       <c r="O145" s="47">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>43</v>
       </c>
       <c r="P145" s="47">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>50</v>
       </c>
       <c r="Q145" s="47">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>57</v>
       </c>
       <c r="R145" s="47">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>64</v>
       </c>
       <c r="S145" s="47">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>71</v>
       </c>
       <c r="T145" s="47">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>78</v>
       </c>
       <c r="U145" s="47">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>85</v>
       </c>
       <c r="V145" s="47">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>92</v>
       </c>
       <c r="W145" s="47">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>99</v>
       </c>
       <c r="X145" s="47">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>106</v>
       </c>
       <c r="Y145" s="47">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>113</v>
       </c>
       <c r="Z145" s="47">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>120</v>
       </c>
       <c r="AA145" s="47">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>127</v>
       </c>
       <c r="AB145" s="47">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>134</v>
       </c>
       <c r="AC145" s="47">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>141</v>
       </c>
       <c r="AD145" s="47">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>148</v>
       </c>
       <c r="AE145" s="47">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>155</v>
       </c>
       <c r="AF145" s="47">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>168</v>
       </c>
       <c r="AG145" s="47">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>181</v>
       </c>
       <c r="AH145" s="47">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>194</v>
       </c>
       <c r="AI145" s="47">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="AJ145" s="47">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
       <c r="AK145" s="90">
-        <f t="shared" si="27"/>
+        <f t="shared" si="36"/>
         <v>0</v>
       </c>
     </row>
@@ -29501,125 +29536,151 @@
         <v>#N/A</v>
       </c>
       <c r="I146" s="41" t="e">
-        <f t="shared" ref="I146:AK146" si="28">I145-I141</f>
+        <f t="shared" ref="I146:AK146" si="37">I145-I141</f>
         <v>#N/A</v>
       </c>
       <c r="J146" s="41" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
       <c r="K146" s="41" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
       <c r="L146" s="41" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
       <c r="M146" s="41" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
       <c r="N146" s="41" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
       <c r="O146" s="41" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
       <c r="P146" s="41" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
       <c r="Q146" s="41" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
       <c r="R146" s="41" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
       <c r="S146" s="41" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
       <c r="T146" s="41" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
       <c r="U146" s="41" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
       <c r="V146" s="41" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
       <c r="W146" s="41" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
       <c r="X146" s="41" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
       <c r="Y146" s="41" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
       <c r="Z146" s="41" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
       <c r="AA146" s="41" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
       <c r="AB146" s="41" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
       <c r="AC146" s="41" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
       <c r="AD146" s="41" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
       <c r="AE146" s="41" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
       <c r="AF146" s="41" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
       <c r="AG146" s="41" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
       <c r="AH146" s="41" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
       <c r="AI146" s="41" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
       <c r="AJ146" s="41" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
       <c r="AK146" s="42" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="37"/>
         <v>#N/A</v>
       </c>
     </row>
     <row r="152" spans="6:37"/>
   </sheetData>
   <mergeCells count="42">
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="A2:A15"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="B4:B8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B10:B14"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="C4:C8"/>
+    <mergeCell ref="C10:C14"/>
+    <mergeCell ref="A82:A83"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="C18:C21"/>
+    <mergeCell ref="D18:D20"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="C24:C31"/>
+    <mergeCell ref="C52:C54"/>
+    <mergeCell ref="B75:B78"/>
+    <mergeCell ref="C75:C78"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="B64:B74"/>
+    <mergeCell ref="B52:B54"/>
+    <mergeCell ref="B38:B48"/>
+    <mergeCell ref="B16:B31"/>
+    <mergeCell ref="A60:A81"/>
     <mergeCell ref="A16:A59"/>
     <mergeCell ref="B34:B36"/>
     <mergeCell ref="C34:C36"/>
@@ -29636,32 +29697,6 @@
     <mergeCell ref="B62:B63"/>
     <mergeCell ref="C62:C63"/>
     <mergeCell ref="D62:D63"/>
-    <mergeCell ref="A82:A83"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="C18:C21"/>
-    <mergeCell ref="D18:D20"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="C24:C31"/>
-    <mergeCell ref="C52:C54"/>
-    <mergeCell ref="B75:B78"/>
-    <mergeCell ref="C75:C78"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="B64:B74"/>
-    <mergeCell ref="B52:B54"/>
-    <mergeCell ref="B38:B48"/>
-    <mergeCell ref="B16:B31"/>
-    <mergeCell ref="A60:A81"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="A2:A15"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="B4:B8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B10:B14"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="C4:C8"/>
-    <mergeCell ref="C10:C14"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ライフプラン_猪飼.xlsx
+++ b/ライフプラン_猪飼.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC_USER\Documents\LocalLifeplanRepo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{034D5BAF-58E3-4BD1-919E-E2D8047E5ADE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68EE31E3-AF7A-4C45-9F50-3E90B0B5FF80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{934FA03D-99BD-49E0-BFEC-291BD79F4879}"/>
+    <workbookView xWindow="-24120" yWindow="-960" windowWidth="24240" windowHeight="17520" activeTab="1" xr2:uid="{934FA03D-99BD-49E0-BFEC-291BD79F4879}"/>
   </bookViews>
   <sheets>
     <sheet name="マネーフロー" sheetId="1" r:id="rId1"/>
@@ -1121,6 +1121,24 @@
         </r>
       </text>
     </comment>
+    <comment ref="G124" authorId="0" shapeId="0" xr:uid="{273076BF-09B4-4D67-8F0D-D07123F3C7D3}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="MS P ゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t xml:space="preserve">kaz
+ 確定拠出(明治安田） + 2
+ ﾌﾟﾙﾃﾞﾝｼｬﾙ保険金　  + 9
+</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="E133" authorId="0" shapeId="0" xr:uid="{D3A0D358-7411-4045-8E31-BB4827CBD402}">
       <text>
         <r>
@@ -1326,7 +1344,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L152" authorId="0" shapeId="0" xr:uid="{184EDB87-28C2-496E-A1AE-488732220946}">
+    <comment ref="G144" authorId="0" shapeId="0" xr:uid="{79EC90F9-6615-487F-BCD5-43026010BC0C}">
       <text>
         <r>
           <rPr>
@@ -1337,18 +1355,8 @@
             <family val="3"/>
             <charset val="128"/>
           </rPr>
-          <t>PC_USER:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="MS P ゴシック"/>
-            <family val="3"/>
-            <charset val="128"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
+          <t>kazへ返済 -5.1 (医療費：4.6、ビューカード：0.9、瀬戸神社:0.2、外食：0.2，前借【Naoの靴代】：-2.5，他：2.1)
+naoへ返済 -0.2（カイロ：0.7，森永：1.0，前借【服飾代】：-1.5)</t>
         </r>
       </text>
     </comment>
@@ -5424,7 +5432,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="31"/>
                 <c:pt idx="0">
-                  <c:v>#N/A</c:v>
+                  <c:v>1264</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>#N/A</c:v>
@@ -8880,7 +8888,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="31"/>
                 <c:pt idx="0">
-                  <c:v>#N/A</c:v>
+                  <c:v>438</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>#N/A</c:v>
@@ -12331,7 +12339,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="31"/>
                 <c:pt idx="0">
-                  <c:v>#N/A</c:v>
+                  <c:v>1702</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>#N/A</c:v>
@@ -17332,7 +17340,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{472A185D-039A-4781-AC6E-0DA5DC6C89E1}">
-  <dimension ref="A1:AM152"/>
+  <dimension ref="A1:AM146"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="11" style="5" bestFit="1" customWidth="1"/>
@@ -26255,9 +26263,9 @@
       <c r="F104" s="94" t="s">
         <v>92</v>
       </c>
-      <c r="G104" s="51" t="e">
+      <c r="G104" s="51">
         <f t="shared" ref="G104:AK104" si="31">G124+G144</f>
-        <v>#N/A</v>
+        <v>1702</v>
       </c>
       <c r="H104" s="57" t="e">
         <f t="shared" si="31"/>
@@ -27759,8 +27767,8 @@
       <c r="F124" s="97" t="s">
         <v>92</v>
       </c>
-      <c r="G124" s="51" t="e">
-        <v>#N/A</v>
+      <c r="G124" s="51">
+        <v>1264</v>
       </c>
       <c r="H124" s="89" t="e">
         <v>#N/A</v>
@@ -29300,8 +29308,8 @@
       <c r="F144" s="96" t="s">
         <v>92</v>
       </c>
-      <c r="G144" s="51" t="e">
-        <v>#N/A</v>
+      <c r="G144" s="51">
+        <v>438</v>
       </c>
       <c r="H144" s="89" t="e">
         <v>#N/A</v>
@@ -29652,7 +29660,6 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="152" spans="6:37"/>
   </sheetData>
   <mergeCells count="42">
     <mergeCell ref="B1:E1"/>

--- a/ライフプラン_猪飼.xlsx
+++ b/ライフプラン_猪飼.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC_USER\Documents\LocalLifeplanRepo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68EE31E3-AF7A-4C45-9F50-3E90B0B5FF80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D78FD0F-695B-4BE8-AC0E-FAC951B15219}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-24120" yWindow="-960" windowWidth="24240" windowHeight="17520" activeTab="1" xr2:uid="{934FA03D-99BD-49E0-BFEC-291BD79F4879}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{934FA03D-99BD-49E0-BFEC-291BD79F4879}"/>
   </bookViews>
   <sheets>
     <sheet name="マネーフロー" sheetId="1" r:id="rId1"/>
     <sheet name="ライフプラン" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -901,6 +902,27 @@
         </r>
       </text>
     </comment>
+    <comment ref="H113" authorId="0" shapeId="0" xr:uid="{B537E54B-069E-4CDE-B3C9-13F66680B0DF}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="MS P ゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>kaz
+ 国民厚生年金　　　　+45
+ パナ年金　　　  　　+12
+ ﾌﾟﾙﾃﾞﾝｼｬﾙ保険金 　 + 9
+ 全労済　　　　 　　 + 4
+ 配当金(住友重機) 　 + 1
+ パナ健康保険料　   -33</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="G114" authorId="0" shapeId="0" xr:uid="{10DA67DA-68D6-4278-954A-276F536F8BA2}">
       <text>
         <r>
@@ -1180,6 +1202,22 @@
 Nao国民健康保険料残金　24
 kazへ返済 -5 (検診､抜歯他)
 naoへ返済 -2（出雲,歯科,黄金柑）</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H133" authorId="0" shapeId="0" xr:uid="{58B7ECF0-45C0-49AB-A615-046CB3F22129}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="MS P ゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>kazへ返済 -4.7 (医療費：1.3、ビューカード：0.6、瀬戸神社:0.2、外食：0.2，他：2.4)
+naoへ返済 -6.0（カイロ：0.7，医療費：0.6，ダンス：6.4，ランドリー：0.3，前借【服飾代】：-1.8）</t>
         </r>
       </text>
     </comment>
@@ -4818,10 +4856,8 @@
             <c:v>メイン口座＿1月実績</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -5059,10 +5095,8 @@
             <c:v>メイン口座＿2月実績</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -5300,10 +5334,8 @@
             <c:v>メイン口座＿3月実績</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent4"/>
-              </a:solidFill>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -5541,10 +5573,8 @@
             <c:v>メイン口座＿4月実績</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent5"/>
-              </a:solidFill>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -5676,7 +5706,7 @@
                   <c:v>1301</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>#N/A</c:v>
+                  <c:v>1289</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>#N/A</c:v>
@@ -5782,10 +5812,8 @@
             <c:v>メイン口座＿5月実績</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent6"/>
-              </a:solidFill>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -6023,12 +6051,8 @@
             <c:v>メイン口座＿6月実績</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -6270,12 +6294,8 @@
             <c:v>メイン口座＿7月実績</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -6517,12 +6537,8 @@
             <c:v>メイン口座＿8月実績</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent3">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -6764,12 +6780,8 @@
             <c:v>メイン口座＿9月実績</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent4">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -7011,12 +7023,8 @@
             <c:v>メイン口座＿10月実績</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent5">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -7258,12 +7266,8 @@
             <c:v>メイン口座＿11月実績</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent6">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -7505,13 +7509,8 @@
             <c:v>メイン口座＿12月実績</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="80000"/>
-                  <a:lumOff val="20000"/>
-                </a:schemeClr>
-              </a:solidFill>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -8274,10 +8273,8 @@
             <c:v>共通口座＿1月実績</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -8515,10 +8512,8 @@
             <c:v>共通口座＿2月実績</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -8756,10 +8751,8 @@
             <c:v>共通口座＿3月実績</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent4"/>
-              </a:solidFill>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -8997,10 +8990,8 @@
             <c:v>共通口座＿4月実績</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent5"/>
-              </a:solidFill>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -9132,7 +9123,7 @@
                   <c:v>812</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>#N/A</c:v>
+                  <c:v>402</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>#N/A</c:v>
@@ -9238,10 +9229,8 @@
             <c:v>共通口座＿5月実績</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent6"/>
-              </a:solidFill>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -9722,12 +9711,8 @@
             <c:v>共通口座＿7月実績</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -9969,12 +9954,8 @@
             <c:v>共通口座＿8月実績</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent3">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -10216,12 +10197,8 @@
             <c:v>共通口座＿9月実績</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent4">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -10463,12 +10440,8 @@
             <c:v>共通口座＿10月実績</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent5">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -10710,12 +10683,8 @@
             <c:v>共通口座＿11月実績</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent6">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -10957,13 +10926,8 @@
             <c:v>共通口座＿12月実績</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="80000"/>
-                  <a:lumOff val="20000"/>
-                </a:schemeClr>
-              </a:solidFill>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -12207,10 +12171,8 @@
             <c:v>総合＿3月実績</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent4"/>
-              </a:solidFill>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -12448,10 +12410,8 @@
             <c:v>総合＿4月実績</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent5"/>
-              </a:solidFill>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -12583,7 +12543,7 @@
                   <c:v>2113</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>#N/A</c:v>
+                  <c:v>1691</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>#N/A</c:v>
@@ -12689,10 +12649,8 @@
             <c:v>総合＿5月実績</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent6"/>
-              </a:solidFill>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -13173,12 +13131,8 @@
             <c:v>総合＿7月実績</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -13420,12 +13374,8 @@
             <c:v>総合＿8月実績</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent3">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -13667,12 +13617,8 @@
             <c:v>総合＿9月実績</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent4">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -13914,12 +13860,8 @@
             <c:v>総合＿10月実績</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent5">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -14161,12 +14103,8 @@
             <c:v>総合＿11月実績</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent6">
-                  <a:lumMod val="60000"/>
-                </a:schemeClr>
-              </a:solidFill>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -14408,13 +14346,8 @@
             <c:v>総合＿12月実績</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="80000"/>
-                  <a:lumOff val="20000"/>
-                </a:schemeClr>
-              </a:solidFill>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -24848,9 +24781,9 @@
         <f t="shared" ref="G93:AK93" si="20">G113+G133</f>
         <v>2113</v>
       </c>
-      <c r="H93" s="57" t="e">
+      <c r="H93" s="57">
         <f t="shared" si="20"/>
-        <v>#N/A</v>
+        <v>1691</v>
       </c>
       <c r="I93" s="57" t="e">
         <f t="shared" si="20"/>
@@ -26692,8 +26625,8 @@
         <f>1701-400</f>
         <v>1301</v>
       </c>
-      <c r="H113" s="57" t="e">
-        <v>#N/A</v>
+      <c r="H113" s="57">
+        <v>1289</v>
       </c>
       <c r="I113" s="57" t="e">
         <v>#N/A</v>
@@ -28231,8 +28164,8 @@
         <f>388+24+400</f>
         <v>812</v>
       </c>
-      <c r="H133" s="57" t="e">
-        <v>#N/A</v>
+      <c r="H133" s="57">
+        <v>402</v>
       </c>
       <c r="I133" s="57" t="e">
         <v>#N/A</v>

--- a/ライフプラン_猪飼.xlsx
+++ b/ライフプラン_猪飼.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC_USER\Documents\LocalLifeplanRepo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D78FD0F-695B-4BE8-AC0E-FAC951B15219}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{783CA1FD-CB8E-4283-A107-621649B536BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{934FA03D-99BD-49E0-BFEC-291BD79F4879}"/>
   </bookViews>
@@ -17,7 +17,6 @@
     <sheet name="ライフプラン" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -885,6 +884,32 @@
         </r>
       </text>
     </comment>
+    <comment ref="M110" authorId="0" shapeId="0" xr:uid="{810AE1A6-2695-4C15-9097-542FE06A2684}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="MS P ゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>PC_USER:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="MS P ゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="G113" authorId="0" shapeId="0" xr:uid="{23DA8E04-2475-49BD-AD45-69212BFA74D0}">
       <text>
         <r>
@@ -938,6 +963,23 @@
         </r>
       </text>
     </comment>
+    <comment ref="H114" authorId="0" shapeId="0" xr:uid="{1CFCF761-9A2A-4B5E-81EC-CB145BD3135B}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="MS P ゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t xml:space="preserve"> ﾌﾟﾙﾃﾞﾝｼｬﾙ保険金　     + 9
+ 税金控除（確定申告）　 + 7
+ ﾌﾟﾙﾃﾞﾝｼｬﾙ保険料(妻)  -283</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="G115" authorId="0" shapeId="0" xr:uid="{3867A11D-F368-47C4-B52D-35EE01EC474A}">
       <text>
         <r>
@@ -955,6 +997,26 @@
  全労済個人年金  + 2　
  ﾌﾟﾙﾃﾞﾝｼｬﾙ保険金 + 9
 nao</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H115" authorId="0" shapeId="0" xr:uid="{4DE89C56-794F-4B2E-9A1A-7727A0C66196}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="MS P ゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t xml:space="preserve">kaz
+ 国民厚生年金　　　　+45
+ パナ年金　　　  　　+12
+ ﾌﾟﾙﾃﾞﾝｼｬﾙ保険金 　 + 9
+ 明治安田生命　 　　 + 2
+ </t>
         </r>
       </text>
     </comment>
@@ -1238,6 +1300,22 @@
         </r>
       </text>
     </comment>
+    <comment ref="H134" authorId="0" shapeId="0" xr:uid="{560CC60B-FA3B-4A93-BBA3-F9EC9FE3C6B5}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="MS P ゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>kazへ返済 -10.2 (医療費：1.4、飲過罰金：-1.0，カイロ回数券：6.0，ビューカード：0.9，瀬戸神社:0.2、外食：0.2，他：2.4)
+naoへ返済 -0.0（森永（２か月）：0.7，カイロ：1.3，医療費：0.0，ダンス：0.0，【前借分】一碧湖：2.0）</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="G135" authorId="0" shapeId="0" xr:uid="{E02FD6DB-795A-4C84-B59F-D8CDDEA9F738}">
       <text>
         <r>
@@ -1251,6 +1329,22 @@
           </rPr>
           <t>kazへ返済 -12 (ｶｲﾛ：6、CPAP：1、中山会：１。ﾋﾞｭｰ：1。医療費他)
 naoへ返済 -3（網代0.5、出雲＆瀬戸0.4、牛乳交通費食品等2）</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H135" authorId="0" shapeId="0" xr:uid="{CA864FBF-7EB7-4F64-A184-1DA8DC398624}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="MS P ゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>kazへ返済 -6.2 (医療費：2.2、ビューカード：0.9，横須賀タクシー:0.2、奈良旅行：1.5，外食：0.3，【前刈分】揚物器：-0.2，他：1.3)
+naoへ返済 -0.8（森永：0.3，カイロ：0.7，医療費：0.0，ダンス：0.0，【前借分】慶子立替：0.2）</t>
         </r>
       </text>
     </comment>
@@ -4316,125 +4410,6 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" textRotation="255"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="42" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="45" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="23" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="36" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="24" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="35" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="46" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" textRotation="255"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" textRotation="255"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -4444,6 +4419,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" textRotation="255"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" textRotation="255"/>
@@ -4497,6 +4476,121 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" textRotation="255"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="42" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="23" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" textRotation="255"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="45" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="36" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="24" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="35" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="46" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -5945,7 +6039,7 @@
                   <c:v>1026</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>#N/A</c:v>
+                  <c:v>1033</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>#N/A</c:v>
@@ -6188,7 +6282,7 @@
                   <c:v>1080</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>#N/A</c:v>
+                  <c:v>1058</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>#N/A</c:v>
@@ -9362,7 +9456,7 @@
                   <c:v>763</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>#N/A</c:v>
+                  <c:v>368</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>#N/A</c:v>
@@ -9605,7 +9699,7 @@
                   <c:v>733</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>#N/A</c:v>
+                  <c:v>345</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>#N/A</c:v>
@@ -12782,7 +12876,7 @@
                   <c:v>1789</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>#N/A</c:v>
+                  <c:v>1401</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>#N/A</c:v>
@@ -13025,7 +13119,7 @@
                   <c:v>1813</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>#N/A</c:v>
+                  <c:v>1403</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>#N/A</c:v>
@@ -17288,12 +17382,12 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="134" t="s">
+      <c r="B1" s="101" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="135"/>
-      <c r="D1" s="135"/>
-      <c r="E1" s="136"/>
+      <c r="C1" s="102"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="103"/>
       <c r="F1" s="2" t="s">
         <v>2</v>
       </c>
@@ -17394,13 +17488,13 @@
       <c r="AM1" s="4"/>
     </row>
     <row r="2" spans="1:39" ht="18.75" customHeight="1">
-      <c r="A2" s="101" t="s">
+      <c r="A2" s="104" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="139" t="s">
+      <c r="B2" s="107" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="146"/>
+      <c r="C2" s="114"/>
       <c r="D2" s="6" t="s">
         <v>5</v>
       </c>
@@ -17485,9 +17579,9 @@
       <c r="AM2" s="4"/>
     </row>
     <row r="3" spans="1:39" ht="19.5" thickBot="1">
-      <c r="A3" s="137"/>
-      <c r="B3" s="140"/>
-      <c r="C3" s="147"/>
+      <c r="A3" s="105"/>
+      <c r="B3" s="108"/>
+      <c r="C3" s="115"/>
       <c r="D3" s="9" t="s">
         <v>7</v>
       </c>
@@ -17588,11 +17682,11 @@
       <c r="AM3" s="4"/>
     </row>
     <row r="4" spans="1:39">
-      <c r="A4" s="137"/>
-      <c r="B4" s="139" t="s">
+      <c r="A4" s="105"/>
+      <c r="B4" s="107" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="148"/>
+      <c r="C4" s="116"/>
       <c r="D4" s="12" t="s">
         <v>10</v>
       </c>
@@ -17637,9 +17731,9 @@
       <c r="AM4" s="4"/>
     </row>
     <row r="5" spans="1:39">
-      <c r="A5" s="137"/>
-      <c r="B5" s="141"/>
-      <c r="C5" s="149"/>
+      <c r="A5" s="105"/>
+      <c r="B5" s="109"/>
+      <c r="C5" s="117"/>
       <c r="D5" s="15" t="s">
         <v>12</v>
       </c>
@@ -17684,9 +17778,9 @@
       <c r="AM5" s="4"/>
     </row>
     <row r="6" spans="1:39">
-      <c r="A6" s="137"/>
-      <c r="B6" s="141"/>
-      <c r="C6" s="149"/>
+      <c r="A6" s="105"/>
+      <c r="B6" s="109"/>
+      <c r="C6" s="117"/>
       <c r="D6" s="15"/>
       <c r="E6" s="16"/>
       <c r="F6" s="17"/>
@@ -17725,9 +17819,9 @@
       <c r="AM6" s="4"/>
     </row>
     <row r="7" spans="1:39">
-      <c r="A7" s="137"/>
-      <c r="B7" s="141"/>
-      <c r="C7" s="149"/>
+      <c r="A7" s="105"/>
+      <c r="B7" s="109"/>
+      <c r="C7" s="117"/>
       <c r="D7" s="15"/>
       <c r="E7" s="16"/>
       <c r="F7" s="17"/>
@@ -17766,9 +17860,9 @@
       <c r="AM7" s="4"/>
     </row>
     <row r="8" spans="1:39">
-      <c r="A8" s="137"/>
-      <c r="B8" s="142"/>
-      <c r="C8" s="150"/>
+      <c r="A8" s="105"/>
+      <c r="B8" s="110"/>
+      <c r="C8" s="118"/>
       <c r="D8" s="15"/>
       <c r="E8" s="16"/>
       <c r="F8" s="17"/>
@@ -17807,12 +17901,12 @@
       <c r="AM8" s="4"/>
     </row>
     <row r="9" spans="1:39" ht="19.5" thickBot="1">
-      <c r="A9" s="137"/>
-      <c r="B9" s="143" t="s">
+      <c r="A9" s="105"/>
+      <c r="B9" s="111" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="144"/>
-      <c r="D9" s="145"/>
+      <c r="C9" s="112"/>
+      <c r="D9" s="113"/>
       <c r="E9" s="18" t="s">
         <v>15</v>
       </c>
@@ -17948,11 +18042,11 @@
       <c r="AM9" s="4"/>
     </row>
     <row r="10" spans="1:39">
-      <c r="A10" s="137"/>
-      <c r="B10" s="139" t="s">
+      <c r="A10" s="105"/>
+      <c r="B10" s="107" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="148"/>
+      <c r="C10" s="116"/>
       <c r="D10" s="15" t="s">
         <v>17</v>
       </c>
@@ -18051,9 +18145,9 @@
       <c r="AM10" s="4"/>
     </row>
     <row r="11" spans="1:39">
-      <c r="A11" s="137"/>
-      <c r="B11" s="141"/>
-      <c r="C11" s="149"/>
+      <c r="A11" s="105"/>
+      <c r="B11" s="109"/>
+      <c r="C11" s="117"/>
       <c r="D11" s="15" t="s">
         <v>19</v>
       </c>
@@ -18102,9 +18196,9 @@
       <c r="AM11" s="4"/>
     </row>
     <row r="12" spans="1:39">
-      <c r="A12" s="137"/>
-      <c r="B12" s="141"/>
-      <c r="C12" s="149"/>
+      <c r="A12" s="105"/>
+      <c r="B12" s="109"/>
+      <c r="C12" s="117"/>
       <c r="D12" s="15" t="s">
         <v>21</v>
       </c>
@@ -18175,9 +18269,9 @@
       <c r="AM12" s="4"/>
     </row>
     <row r="13" spans="1:39">
-      <c r="A13" s="137"/>
-      <c r="B13" s="141"/>
-      <c r="C13" s="149"/>
+      <c r="A13" s="105"/>
+      <c r="B13" s="109"/>
+      <c r="C13" s="117"/>
       <c r="D13" s="15" t="s">
         <v>22</v>
       </c>
@@ -18226,9 +18320,9 @@
       <c r="AM13" s="4"/>
     </row>
     <row r="14" spans="1:39">
-      <c r="A14" s="137"/>
-      <c r="B14" s="142"/>
-      <c r="C14" s="150"/>
+      <c r="A14" s="105"/>
+      <c r="B14" s="110"/>
+      <c r="C14" s="118"/>
       <c r="D14" s="15"/>
       <c r="E14" s="16"/>
       <c r="F14" s="23"/>
@@ -18267,12 +18361,12 @@
       <c r="AM14" s="4"/>
     </row>
     <row r="15" spans="1:39" ht="19.5" thickBot="1">
-      <c r="A15" s="138"/>
-      <c r="B15" s="143" t="s">
+      <c r="A15" s="106"/>
+      <c r="B15" s="111" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="144"/>
-      <c r="D15" s="145"/>
+      <c r="C15" s="112"/>
+      <c r="D15" s="113"/>
       <c r="E15" s="18" t="s">
         <v>25</v>
       </c>
@@ -18408,16 +18502,16 @@
       <c r="AM15" s="4"/>
     </row>
     <row r="16" spans="1:39">
-      <c r="A16" s="101" t="s">
+      <c r="A16" s="104" t="s">
         <v>150</v>
       </c>
-      <c r="B16" s="132" t="s">
+      <c r="B16" s="137" t="s">
         <v>129</v>
       </c>
-      <c r="C16" s="123" t="s">
+      <c r="C16" s="120" t="s">
         <v>105</v>
       </c>
-      <c r="D16" s="125" t="s">
+      <c r="D16" s="122" t="s">
         <v>109</v>
       </c>
       <c r="E16" s="16" t="s">
@@ -18499,10 +18593,10 @@
       <c r="AM16" s="4"/>
     </row>
     <row r="17" spans="1:39">
-      <c r="A17" s="102"/>
-      <c r="B17" s="130"/>
-      <c r="C17" s="114"/>
-      <c r="D17" s="114"/>
+      <c r="A17" s="139"/>
+      <c r="B17" s="135"/>
+      <c r="C17" s="121"/>
+      <c r="D17" s="121"/>
       <c r="E17" s="16" t="s">
         <v>29</v>
       </c>
@@ -18588,12 +18682,12 @@
       <c r="AM17" s="4"/>
     </row>
     <row r="18" spans="1:39">
-      <c r="A18" s="102"/>
-      <c r="B18" s="130"/>
-      <c r="C18" s="113" t="s">
+      <c r="A18" s="139"/>
+      <c r="B18" s="135"/>
+      <c r="C18" s="123" t="s">
         <v>106</v>
       </c>
-      <c r="D18" s="115" t="s">
+      <c r="D18" s="125" t="s">
         <v>111</v>
       </c>
       <c r="E18" s="13" t="s">
@@ -18675,10 +18769,10 @@
       <c r="AM18" s="27"/>
     </row>
     <row r="19" spans="1:39">
-      <c r="A19" s="102"/>
-      <c r="B19" s="130"/>
-      <c r="C19" s="116"/>
-      <c r="D19" s="116"/>
+      <c r="A19" s="139"/>
+      <c r="B19" s="135"/>
+      <c r="C19" s="124"/>
+      <c r="D19" s="124"/>
       <c r="E19" s="16" t="s">
         <v>27</v>
       </c>
@@ -18746,10 +18840,10 @@
       <c r="AM19" s="27"/>
     </row>
     <row r="20" spans="1:39">
-      <c r="A20" s="102"/>
-      <c r="B20" s="130"/>
-      <c r="C20" s="116"/>
-      <c r="D20" s="114"/>
+      <c r="A20" s="139"/>
+      <c r="B20" s="135"/>
+      <c r="C20" s="124"/>
+      <c r="D20" s="121"/>
       <c r="E20" s="16" t="s">
         <v>28</v>
       </c>
@@ -18799,9 +18893,9 @@
       <c r="AM20" s="27"/>
     </row>
     <row r="21" spans="1:39">
-      <c r="A21" s="102"/>
-      <c r="B21" s="130"/>
-      <c r="C21" s="114"/>
+      <c r="A21" s="139"/>
+      <c r="B21" s="135"/>
+      <c r="C21" s="121"/>
       <c r="D21" s="57" t="s">
         <v>112</v>
       </c>
@@ -18852,9 +18946,9 @@
       <c r="AM21" s="27"/>
     </row>
     <row r="22" spans="1:39">
-      <c r="A22" s="102"/>
-      <c r="B22" s="130"/>
-      <c r="C22" s="113" t="s">
+      <c r="A22" s="139"/>
+      <c r="B22" s="135"/>
+      <c r="C22" s="123" t="s">
         <v>107</v>
       </c>
       <c r="D22" s="57" t="s">
@@ -18899,9 +18993,9 @@
       <c r="AM22" s="27"/>
     </row>
     <row r="23" spans="1:39">
-      <c r="A23" s="102"/>
-      <c r="B23" s="130"/>
-      <c r="C23" s="114"/>
+      <c r="A23" s="139"/>
+      <c r="B23" s="135"/>
+      <c r="C23" s="121"/>
       <c r="D23" s="57" t="s">
         <v>114</v>
       </c>
@@ -18944,12 +19038,12 @@
       <c r="AM23" s="27"/>
     </row>
     <row r="24" spans="1:39">
-      <c r="A24" s="102"/>
-      <c r="B24" s="130"/>
-      <c r="C24" s="113" t="s">
+      <c r="A24" s="139"/>
+      <c r="B24" s="135"/>
+      <c r="C24" s="123" t="s">
         <v>108</v>
       </c>
-      <c r="D24" s="115" t="s">
+      <c r="D24" s="125" t="s">
         <v>115</v>
       </c>
       <c r="E24" s="16" t="s">
@@ -19031,10 +19125,10 @@
       <c r="AM24" s="27"/>
     </row>
     <row r="25" spans="1:39">
-      <c r="A25" s="102"/>
-      <c r="B25" s="130"/>
-      <c r="C25" s="116"/>
-      <c r="D25" s="116"/>
+      <c r="A25" s="139"/>
+      <c r="B25" s="135"/>
+      <c r="C25" s="124"/>
+      <c r="D25" s="124"/>
       <c r="E25" s="16" t="s">
         <v>32</v>
       </c>
@@ -19126,10 +19220,10 @@
       <c r="AM25" s="27"/>
     </row>
     <row r="26" spans="1:39">
-      <c r="A26" s="102"/>
-      <c r="B26" s="130"/>
-      <c r="C26" s="116"/>
-      <c r="D26" s="116"/>
+      <c r="A26" s="139"/>
+      <c r="B26" s="135"/>
+      <c r="C26" s="124"/>
+      <c r="D26" s="124"/>
       <c r="E26" s="16" t="s">
         <v>33</v>
       </c>
@@ -19171,10 +19265,10 @@
       <c r="AM26" s="27"/>
     </row>
     <row r="27" spans="1:39">
-      <c r="A27" s="102"/>
-      <c r="B27" s="130"/>
-      <c r="C27" s="116"/>
-      <c r="D27" s="116"/>
+      <c r="A27" s="139"/>
+      <c r="B27" s="135"/>
+      <c r="C27" s="124"/>
+      <c r="D27" s="124"/>
       <c r="E27" s="29" t="s">
         <v>154</v>
       </c>
@@ -19216,10 +19310,10 @@
       <c r="AM27" s="27"/>
     </row>
     <row r="28" spans="1:39">
-      <c r="A28" s="102"/>
-      <c r="B28" s="130"/>
-      <c r="C28" s="116"/>
-      <c r="D28" s="116"/>
+      <c r="A28" s="139"/>
+      <c r="B28" s="135"/>
+      <c r="C28" s="124"/>
+      <c r="D28" s="124"/>
       <c r="E28" s="16" t="s">
         <v>34</v>
       </c>
@@ -19279,10 +19373,10 @@
       <c r="AM28" s="27"/>
     </row>
     <row r="29" spans="1:39">
-      <c r="A29" s="102"/>
-      <c r="B29" s="130"/>
-      <c r="C29" s="116"/>
-      <c r="D29" s="114"/>
+      <c r="A29" s="139"/>
+      <c r="B29" s="135"/>
+      <c r="C29" s="124"/>
+      <c r="D29" s="121"/>
       <c r="E29" s="85" t="s">
         <v>117</v>
       </c>
@@ -19324,9 +19418,9 @@
       <c r="AM29" s="27"/>
     </row>
     <row r="30" spans="1:39">
-      <c r="A30" s="102"/>
-      <c r="B30" s="130"/>
-      <c r="C30" s="116"/>
+      <c r="A30" s="139"/>
+      <c r="B30" s="135"/>
+      <c r="C30" s="124"/>
       <c r="D30" s="57" t="s">
         <v>119</v>
       </c>
@@ -19369,9 +19463,9 @@
       <c r="AM30" s="27"/>
     </row>
     <row r="31" spans="1:39">
-      <c r="A31" s="102"/>
-      <c r="B31" s="131"/>
-      <c r="C31" s="114"/>
+      <c r="A31" s="139"/>
+      <c r="B31" s="136"/>
+      <c r="C31" s="121"/>
       <c r="D31" s="57" t="s">
         <v>120</v>
       </c>
@@ -19414,11 +19508,11 @@
       <c r="AM31" s="27"/>
     </row>
     <row r="32" spans="1:39">
-      <c r="A32" s="102"/>
-      <c r="B32" s="119" t="s">
+      <c r="A32" s="139"/>
+      <c r="B32" s="147" t="s">
         <v>128</v>
       </c>
-      <c r="C32" s="110"/>
+      <c r="C32" s="126"/>
       <c r="D32" s="17" t="s">
         <v>125</v>
       </c>
@@ -19517,9 +19611,9 @@
       <c r="AM32" s="27"/>
     </row>
     <row r="33" spans="1:39">
-      <c r="A33" s="102"/>
-      <c r="B33" s="120"/>
-      <c r="C33" s="112"/>
+      <c r="A33" s="139"/>
+      <c r="B33" s="148"/>
+      <c r="C33" s="128"/>
       <c r="D33" s="17" t="s">
         <v>126</v>
       </c>
@@ -19594,12 +19688,12 @@
       <c r="AM33" s="27"/>
     </row>
     <row r="34" spans="1:39">
-      <c r="A34" s="102"/>
-      <c r="B34" s="104" t="s">
+      <c r="A34" s="139"/>
+      <c r="B34" s="129" t="s">
         <v>9</v>
       </c>
-      <c r="C34" s="106"/>
-      <c r="D34" s="108"/>
+      <c r="C34" s="132"/>
+      <c r="D34" s="143"/>
       <c r="E34" s="34" t="str">
         <f t="shared" ref="E34:AK34" si="2">E4</f>
         <v>新潟実家の売却益　（妙子と折半）</v>
@@ -19736,10 +19830,10 @@
       <c r="AM34" s="27"/>
     </row>
     <row r="35" spans="1:39">
-      <c r="A35" s="102"/>
-      <c r="B35" s="105"/>
-      <c r="C35" s="107"/>
-      <c r="D35" s="109"/>
+      <c r="A35" s="139"/>
+      <c r="B35" s="141"/>
+      <c r="C35" s="142"/>
+      <c r="D35" s="144"/>
       <c r="E35" s="34" t="str">
         <f>E5</f>
         <v>横浜マンションの売却益</v>
@@ -19876,10 +19970,10 @@
       <c r="AM35" s="27"/>
     </row>
     <row r="36" spans="1:39">
-      <c r="A36" s="102"/>
-      <c r="B36" s="105"/>
-      <c r="C36" s="107"/>
-      <c r="D36" s="109"/>
+      <c r="A36" s="139"/>
+      <c r="B36" s="141"/>
+      <c r="C36" s="142"/>
+      <c r="D36" s="144"/>
       <c r="E36" s="98" t="s">
         <v>149</v>
       </c>
@@ -19924,7 +20018,7 @@
       <c r="AM36" s="27"/>
     </row>
     <row r="37" spans="1:39" ht="19.5" thickBot="1">
-      <c r="A37" s="102"/>
+      <c r="A37" s="139"/>
       <c r="B37" s="35" t="s">
         <v>36</v>
       </c>
@@ -20063,8 +20157,8 @@
       <c r="AM37" s="27"/>
     </row>
     <row r="38" spans="1:39" ht="18.75" customHeight="1">
-      <c r="A38" s="102"/>
-      <c r="B38" s="129" t="s">
+      <c r="A38" s="139"/>
+      <c r="B38" s="134" t="s">
         <v>130</v>
       </c>
       <c r="C38" s="8" t="s">
@@ -20114,9 +20208,9 @@
       <c r="AM38" s="4"/>
     </row>
     <row r="39" spans="1:39">
-      <c r="A39" s="102"/>
-      <c r="B39" s="130"/>
-      <c r="C39" s="113" t="s">
+      <c r="A39" s="139"/>
+      <c r="B39" s="135"/>
+      <c r="C39" s="123" t="s">
         <v>106</v>
       </c>
       <c r="D39" s="57" t="s">
@@ -20161,9 +20255,9 @@
       <c r="AM39" s="4"/>
     </row>
     <row r="40" spans="1:39">
-      <c r="A40" s="102"/>
-      <c r="B40" s="130"/>
-      <c r="C40" s="114"/>
+      <c r="A40" s="139"/>
+      <c r="B40" s="135"/>
+      <c r="C40" s="121"/>
       <c r="D40" s="57" t="s">
         <v>112</v>
       </c>
@@ -20206,9 +20300,9 @@
       <c r="AM40" s="4"/>
     </row>
     <row r="41" spans="1:39">
-      <c r="A41" s="102"/>
-      <c r="B41" s="130"/>
-      <c r="C41" s="113" t="s">
+      <c r="A41" s="139"/>
+      <c r="B41" s="135"/>
+      <c r="C41" s="123" t="s">
         <v>107</v>
       </c>
       <c r="D41" s="57" t="s">
@@ -20309,9 +20403,9 @@
       <c r="AM41" s="27"/>
     </row>
     <row r="42" spans="1:39">
-      <c r="A42" s="102"/>
-      <c r="B42" s="130"/>
-      <c r="C42" s="114"/>
+      <c r="A42" s="139"/>
+      <c r="B42" s="135"/>
+      <c r="C42" s="121"/>
       <c r="D42" s="57" t="s">
         <v>114</v>
       </c>
@@ -20354,12 +20448,12 @@
       <c r="AM42" s="4"/>
     </row>
     <row r="43" spans="1:39">
-      <c r="A43" s="102"/>
-      <c r="B43" s="130"/>
-      <c r="C43" s="113" t="s">
+      <c r="A43" s="139"/>
+      <c r="B43" s="135"/>
+      <c r="C43" s="123" t="s">
         <v>108</v>
       </c>
-      <c r="D43" s="115" t="s">
+      <c r="D43" s="125" t="s">
         <v>115</v>
       </c>
       <c r="E43" s="16" t="s">
@@ -20404,10 +20498,10 @@
       <c r="AM43" s="27"/>
     </row>
     <row r="44" spans="1:39">
-      <c r="A44" s="102"/>
-      <c r="B44" s="130"/>
-      <c r="C44" s="116"/>
-      <c r="D44" s="116"/>
+      <c r="A44" s="139"/>
+      <c r="B44" s="135"/>
+      <c r="C44" s="124"/>
+      <c r="D44" s="124"/>
       <c r="E44" s="16" t="s">
         <v>47</v>
       </c>
@@ -20487,10 +20581,10 @@
       <c r="AM44" s="27"/>
     </row>
     <row r="45" spans="1:39">
-      <c r="A45" s="102"/>
-      <c r="B45" s="130"/>
-      <c r="C45" s="116"/>
-      <c r="D45" s="116"/>
+      <c r="A45" s="139"/>
+      <c r="B45" s="135"/>
+      <c r="C45" s="124"/>
+      <c r="D45" s="124"/>
       <c r="E45" s="16" t="s">
         <v>48</v>
       </c>
@@ -20562,10 +20656,10 @@
       <c r="AM45" s="27"/>
     </row>
     <row r="46" spans="1:39">
-      <c r="A46" s="102"/>
-      <c r="B46" s="130"/>
-      <c r="C46" s="116"/>
-      <c r="D46" s="114"/>
+      <c r="A46" s="139"/>
+      <c r="B46" s="135"/>
+      <c r="C46" s="124"/>
+      <c r="D46" s="121"/>
       <c r="E46" s="85" t="s">
         <v>121</v>
       </c>
@@ -20615,9 +20709,9 @@
       <c r="AM46" s="27"/>
     </row>
     <row r="47" spans="1:39">
-      <c r="A47" s="102"/>
-      <c r="B47" s="130"/>
-      <c r="C47" s="116"/>
+      <c r="A47" s="139"/>
+      <c r="B47" s="135"/>
+      <c r="C47" s="124"/>
       <c r="D47" s="57" t="s">
         <v>119</v>
       </c>
@@ -20710,9 +20804,9 @@
       <c r="AM47" s="27"/>
     </row>
     <row r="48" spans="1:39">
-      <c r="A48" s="102"/>
-      <c r="B48" s="131"/>
-      <c r="C48" s="114"/>
+      <c r="A48" s="139"/>
+      <c r="B48" s="136"/>
+      <c r="C48" s="121"/>
       <c r="D48" s="57" t="s">
         <v>120</v>
       </c>
@@ -20755,7 +20849,7 @@
       <c r="AM48" s="4"/>
     </row>
     <row r="49" spans="1:39">
-      <c r="A49" s="102"/>
+      <c r="A49" s="139"/>
       <c r="B49" s="66" t="s">
         <v>43</v>
       </c>
@@ -20840,7 +20934,7 @@
       <c r="AM49" s="27"/>
     </row>
     <row r="50" spans="1:39">
-      <c r="A50" s="102"/>
+      <c r="A50" s="139"/>
       <c r="B50" s="66" t="s">
         <v>50</v>
       </c>
@@ -20941,7 +21035,7 @@
       <c r="AM50" s="27"/>
     </row>
     <row r="51" spans="1:39">
-      <c r="A51" s="102"/>
+      <c r="A51" s="139"/>
       <c r="B51" s="66" t="s">
         <v>52</v>
       </c>
@@ -21042,11 +21136,11 @@
       <c r="AM51" s="27"/>
     </row>
     <row r="52" spans="1:39">
-      <c r="A52" s="102"/>
-      <c r="B52" s="128" t="s">
+      <c r="A52" s="139"/>
+      <c r="B52" s="133" t="s">
         <v>122</v>
       </c>
-      <c r="C52" s="110"/>
+      <c r="C52" s="126"/>
       <c r="D52" s="15" t="s">
         <v>41</v>
       </c>
@@ -21129,9 +21223,9 @@
       <c r="AM52" s="27"/>
     </row>
     <row r="53" spans="1:39">
-      <c r="A53" s="102"/>
-      <c r="B53" s="126"/>
-      <c r="C53" s="111"/>
+      <c r="A53" s="139"/>
+      <c r="B53" s="130"/>
+      <c r="C53" s="127"/>
       <c r="D53" s="15" t="s">
         <v>37</v>
       </c>
@@ -21176,9 +21270,9 @@
       <c r="AM53" s="27"/>
     </row>
     <row r="54" spans="1:39">
-      <c r="A54" s="102"/>
-      <c r="B54" s="127"/>
-      <c r="C54" s="112"/>
+      <c r="A54" s="139"/>
+      <c r="B54" s="131"/>
+      <c r="C54" s="128"/>
       <c r="D54" s="15" t="s">
         <v>39</v>
       </c>
@@ -21277,7 +21371,7 @@
       <c r="AM54" s="27"/>
     </row>
     <row r="55" spans="1:39">
-      <c r="A55" s="102"/>
+      <c r="A55" s="139"/>
       <c r="B55" s="83" t="s">
         <v>138</v>
       </c>
@@ -21380,11 +21474,11 @@
       <c r="AM55" s="27"/>
     </row>
     <row r="56" spans="1:39">
-      <c r="A56" s="102"/>
-      <c r="B56" s="117" t="s">
+      <c r="A56" s="139"/>
+      <c r="B56" s="145" t="s">
         <v>144</v>
       </c>
-      <c r="C56" s="118"/>
+      <c r="C56" s="146"/>
       <c r="D56" s="77" t="s">
         <v>124</v>
       </c>
@@ -21507,7 +21601,7 @@
       <c r="AM56" s="27"/>
     </row>
     <row r="57" spans="1:39">
-      <c r="A57" s="102"/>
+      <c r="A57" s="139"/>
       <c r="B57" s="67" t="s">
         <v>56</v>
       </c>
@@ -21636,7 +21730,7 @@
       <c r="AM57" s="27"/>
     </row>
     <row r="58" spans="1:39">
-      <c r="A58" s="102"/>
+      <c r="A58" s="139"/>
       <c r="B58" s="67" t="s">
         <v>58</v>
       </c>
@@ -21763,7 +21857,7 @@
       <c r="AM58" s="27"/>
     </row>
     <row r="59" spans="1:39" ht="19.5" thickBot="1">
-      <c r="A59" s="103"/>
+      <c r="A59" s="140"/>
       <c r="B59" s="61" t="s">
         <v>59</v>
       </c>
@@ -21892,7 +21986,7 @@
       <c r="AM59" s="27"/>
     </row>
     <row r="60" spans="1:39" ht="18.75" customHeight="1">
-      <c r="A60" s="101" t="s">
+      <c r="A60" s="104" t="s">
         <v>60</v>
       </c>
       <c r="B60" s="80" t="s">
@@ -22026,7 +22120,7 @@
       <c r="AM60" s="27"/>
     </row>
     <row r="61" spans="1:39" ht="19.5" thickBot="1">
-      <c r="A61" s="133"/>
+      <c r="A61" s="138"/>
       <c r="B61" s="61" t="s">
         <v>36</v>
       </c>
@@ -22155,14 +22249,14 @@
       <c r="AM61" s="27"/>
     </row>
     <row r="62" spans="1:39">
-      <c r="A62" s="133"/>
-      <c r="B62" s="121" t="s">
+      <c r="A62" s="138"/>
+      <c r="B62" s="149" t="s">
         <v>135</v>
       </c>
-      <c r="C62" s="123" t="s">
+      <c r="C62" s="120" t="s">
         <v>137</v>
       </c>
-      <c r="D62" s="123" t="s">
+      <c r="D62" s="120" t="s">
         <v>136</v>
       </c>
       <c r="E62" s="7" t="s">
@@ -22254,10 +22348,10 @@
       <c r="AM62" s="27"/>
     </row>
     <row r="63" spans="1:39">
-      <c r="A63" s="133"/>
-      <c r="B63" s="122"/>
-      <c r="C63" s="114"/>
-      <c r="D63" s="114"/>
+      <c r="A63" s="138"/>
+      <c r="B63" s="150"/>
+      <c r="C63" s="121"/>
+      <c r="D63" s="121"/>
       <c r="E63" s="13" t="s">
         <v>152</v>
       </c>
@@ -22299,11 +22393,11 @@
       <c r="AM63" s="27"/>
     </row>
     <row r="64" spans="1:39">
-      <c r="A64" s="133"/>
-      <c r="B64" s="128" t="s">
+      <c r="A64" s="138"/>
+      <c r="B64" s="133" t="s">
         <v>122</v>
       </c>
-      <c r="C64" s="110"/>
+      <c r="C64" s="126"/>
       <c r="D64" s="71" t="s">
         <v>62</v>
       </c>
@@ -22402,9 +22496,9 @@
       <c r="AM64" s="27"/>
     </row>
     <row r="65" spans="1:39">
-      <c r="A65" s="133"/>
-      <c r="B65" s="126"/>
-      <c r="C65" s="111"/>
+      <c r="A65" s="138"/>
+      <c r="B65" s="130"/>
+      <c r="C65" s="127"/>
       <c r="D65" s="15" t="s">
         <v>64</v>
       </c>
@@ -22503,9 +22597,9 @@
       <c r="AM65" s="27"/>
     </row>
     <row r="66" spans="1:39">
-      <c r="A66" s="133"/>
-      <c r="B66" s="126"/>
-      <c r="C66" s="111"/>
+      <c r="A66" s="138"/>
+      <c r="B66" s="130"/>
+      <c r="C66" s="127"/>
       <c r="D66" s="15" t="s">
         <v>66</v>
       </c>
@@ -22604,9 +22698,9 @@
       <c r="AM66" s="27"/>
     </row>
     <row r="67" spans="1:39">
-      <c r="A67" s="133"/>
-      <c r="B67" s="126"/>
-      <c r="C67" s="111"/>
+      <c r="A67" s="138"/>
+      <c r="B67" s="130"/>
+      <c r="C67" s="127"/>
       <c r="D67" s="15" t="s">
         <v>68</v>
       </c>
@@ -22705,9 +22799,9 @@
       <c r="AM67" s="27"/>
     </row>
     <row r="68" spans="1:39">
-      <c r="A68" s="133"/>
-      <c r="B68" s="126"/>
-      <c r="C68" s="111"/>
+      <c r="A68" s="138"/>
+      <c r="B68" s="130"/>
+      <c r="C68" s="127"/>
       <c r="D68" s="15" t="s">
         <v>52</v>
       </c>
@@ -22806,9 +22900,9 @@
       <c r="AM68" s="27"/>
     </row>
     <row r="69" spans="1:39">
-      <c r="A69" s="133"/>
-      <c r="B69" s="126"/>
-      <c r="C69" s="111"/>
+      <c r="A69" s="138"/>
+      <c r="B69" s="130"/>
+      <c r="C69" s="127"/>
       <c r="D69" s="15" t="s">
         <v>71</v>
       </c>
@@ -22907,9 +23001,9 @@
       <c r="AM69" s="27"/>
     </row>
     <row r="70" spans="1:39">
-      <c r="A70" s="133"/>
-      <c r="B70" s="126"/>
-      <c r="C70" s="111"/>
+      <c r="A70" s="138"/>
+      <c r="B70" s="130"/>
+      <c r="C70" s="127"/>
       <c r="D70" s="15" t="s">
         <v>73</v>
       </c>
@@ -23008,9 +23102,9 @@
       <c r="AM70" s="27"/>
     </row>
     <row r="71" spans="1:39">
-      <c r="A71" s="133"/>
-      <c r="B71" s="126"/>
-      <c r="C71" s="111"/>
+      <c r="A71" s="138"/>
+      <c r="B71" s="130"/>
+      <c r="C71" s="127"/>
       <c r="D71" s="15" t="s">
         <v>75</v>
       </c>
@@ -23109,9 +23203,9 @@
       <c r="AM71" s="27"/>
     </row>
     <row r="72" spans="1:39">
-      <c r="A72" s="133"/>
-      <c r="B72" s="126"/>
-      <c r="C72" s="111"/>
+      <c r="A72" s="138"/>
+      <c r="B72" s="130"/>
+      <c r="C72" s="127"/>
       <c r="D72" s="15" t="s">
         <v>77</v>
       </c>
@@ -23210,10 +23304,10 @@
       <c r="AM72" s="27"/>
     </row>
     <row r="73" spans="1:39">
-      <c r="A73" s="133"/>
-      <c r="B73" s="126"/>
-      <c r="C73" s="111"/>
-      <c r="D73" s="113" t="s">
+      <c r="A73" s="138"/>
+      <c r="B73" s="130"/>
+      <c r="C73" s="127"/>
+      <c r="D73" s="123" t="s">
         <v>79</v>
       </c>
       <c r="E73" s="16" t="s">
@@ -23315,10 +23409,10 @@
       <c r="AM73" s="27"/>
     </row>
     <row r="74" spans="1:39">
-      <c r="A74" s="133"/>
-      <c r="B74" s="127"/>
-      <c r="C74" s="112"/>
-      <c r="D74" s="114"/>
+      <c r="A74" s="138"/>
+      <c r="B74" s="131"/>
+      <c r="C74" s="128"/>
+      <c r="D74" s="121"/>
       <c r="E74" s="16" t="s">
         <v>81</v>
       </c>
@@ -23418,11 +23512,11 @@
       <c r="AM74" s="27"/>
     </row>
     <row r="75" spans="1:39">
-      <c r="A75" s="133"/>
-      <c r="B75" s="104" t="s">
+      <c r="A75" s="138"/>
+      <c r="B75" s="129" t="s">
         <v>16</v>
       </c>
-      <c r="C75" s="106"/>
+      <c r="C75" s="132"/>
       <c r="D75" s="33" t="s">
         <v>131</v>
       </c>
@@ -23552,9 +23646,9 @@
       <c r="AM75" s="27"/>
     </row>
     <row r="76" spans="1:39">
-      <c r="A76" s="133"/>
-      <c r="B76" s="126"/>
-      <c r="C76" s="111"/>
+      <c r="A76" s="138"/>
+      <c r="B76" s="130"/>
+      <c r="C76" s="127"/>
       <c r="D76" s="33" t="s">
         <v>132</v>
       </c>
@@ -23684,9 +23778,9 @@
       <c r="AM76" s="27"/>
     </row>
     <row r="77" spans="1:39">
-      <c r="A77" s="133"/>
-      <c r="B77" s="126"/>
-      <c r="C77" s="111"/>
+      <c r="A77" s="138"/>
+      <c r="B77" s="130"/>
+      <c r="C77" s="127"/>
       <c r="D77" s="33" t="s">
         <v>133</v>
       </c>
@@ -23816,9 +23910,9 @@
       <c r="AM77" s="27"/>
     </row>
     <row r="78" spans="1:39">
-      <c r="A78" s="133"/>
-      <c r="B78" s="127"/>
-      <c r="C78" s="112"/>
+      <c r="A78" s="138"/>
+      <c r="B78" s="131"/>
+      <c r="C78" s="128"/>
       <c r="D78" s="33" t="s">
         <v>134</v>
       </c>
@@ -23948,7 +24042,7 @@
       <c r="AM78" s="27"/>
     </row>
     <row r="79" spans="1:39">
-      <c r="A79" s="133"/>
+      <c r="A79" s="138"/>
       <c r="B79" s="67" t="s">
         <v>56</v>
       </c>
@@ -24078,7 +24172,7 @@
       <c r="AM79" s="27"/>
     </row>
     <row r="80" spans="1:39">
-      <c r="A80" s="133"/>
+      <c r="A80" s="138"/>
       <c r="B80" s="67" t="s">
         <v>58</v>
       </c>
@@ -24207,7 +24301,7 @@
       <c r="AM80" s="27"/>
     </row>
     <row r="81" spans="1:39" ht="19.5" thickBot="1">
-      <c r="A81" s="124"/>
+      <c r="A81" s="119"/>
       <c r="B81" s="61" t="s">
         <v>59</v>
       </c>
@@ -24336,7 +24430,7 @@
       <c r="AM81" s="27"/>
     </row>
     <row r="82" spans="1:39">
-      <c r="A82" s="101" t="s">
+      <c r="A82" s="104" t="s">
         <v>86</v>
       </c>
       <c r="B82" s="59" t="s">
@@ -24468,7 +24562,7 @@
       <c r="AM82" s="27"/>
     </row>
     <row r="83" spans="1:39" ht="19.5" thickBot="1">
-      <c r="A83" s="124"/>
+      <c r="A83" s="119"/>
       <c r="B83" s="61" t="s">
         <v>88</v>
       </c>
@@ -24910,9 +25004,9 @@
         <f t="shared" ref="G94:AK94" si="21">G114+G134</f>
         <v>1789</v>
       </c>
-      <c r="H94" s="57" t="e">
+      <c r="H94" s="57">
         <f t="shared" si="21"/>
-        <v>#N/A</v>
+        <v>1401</v>
       </c>
       <c r="I94" s="57" t="e">
         <f t="shared" si="21"/>
@@ -25039,9 +25133,9 @@
         <f t="shared" ref="G95:AK95" si="22">G115+G135</f>
         <v>1813</v>
       </c>
-      <c r="H95" s="57" t="e">
+      <c r="H95" s="57">
         <f t="shared" si="22"/>
-        <v>#N/A</v>
+        <v>1403</v>
       </c>
       <c r="I95" s="57" t="e">
         <f t="shared" si="22"/>
@@ -26455,63 +26549,129 @@
         <v>103</v>
       </c>
       <c r="G106" s="45">
-        <f>G105-G101</f>
-        <v>-1123</v>
-      </c>
-      <c r="H106" s="41" t="e">
-        <f t="shared" ref="H106:O106" si="33">H105-H101</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I106" s="41" t="e">
+        <f>G104-G105</f>
+        <v>1059</v>
+      </c>
+      <c r="H106" s="45" t="e">
+        <f t="shared" ref="H106:O106" si="33">H104-H105</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I106" s="45" t="e">
         <f t="shared" si="33"/>
         <v>#N/A</v>
       </c>
-      <c r="J106" s="41" t="e">
+      <c r="J106" s="45" t="e">
         <f t="shared" si="33"/>
         <v>#N/A</v>
       </c>
-      <c r="K106" s="41" t="e">
+      <c r="K106" s="45" t="e">
         <f t="shared" si="33"/>
         <v>#N/A</v>
       </c>
-      <c r="L106" s="41" t="e">
+      <c r="L106" s="45" t="e">
         <f t="shared" si="33"/>
         <v>#N/A</v>
       </c>
-      <c r="M106" s="41" t="e">
+      <c r="M106" s="45" t="e">
         <f t="shared" si="33"/>
         <v>#N/A</v>
       </c>
-      <c r="N106" s="41" t="e">
+      <c r="N106" s="45" t="e">
         <f t="shared" si="33"/>
         <v>#N/A</v>
       </c>
-      <c r="O106" s="41" t="e">
+      <c r="O106" s="45" t="e">
         <f t="shared" si="33"/>
         <v>#N/A</v>
       </c>
-      <c r="P106" s="41"/>
-      <c r="Q106" s="41"/>
-      <c r="R106" s="41"/>
-      <c r="S106" s="41"/>
-      <c r="T106" s="41"/>
-      <c r="U106" s="41"/>
-      <c r="V106" s="41"/>
-      <c r="W106" s="41"/>
-      <c r="X106" s="41"/>
-      <c r="Y106" s="41"/>
-      <c r="Z106" s="41"/>
-      <c r="AA106" s="41"/>
-      <c r="AB106" s="41"/>
-      <c r="AC106" s="41"/>
-      <c r="AD106" s="41"/>
-      <c r="AE106" s="41"/>
-      <c r="AF106" s="41"/>
-      <c r="AG106" s="41"/>
-      <c r="AH106" s="41"/>
-      <c r="AI106" s="41"/>
-      <c r="AJ106" s="41"/>
-      <c r="AK106" s="42"/>
+      <c r="P106" s="45" t="e">
+        <f t="shared" ref="P106" si="34">P104-P105</f>
+        <v>#N/A</v>
+      </c>
+      <c r="Q106" s="45" t="e">
+        <f t="shared" ref="Q106" si="35">Q104-Q105</f>
+        <v>#N/A</v>
+      </c>
+      <c r="R106" s="45" t="e">
+        <f t="shared" ref="R106" si="36">R104-R105</f>
+        <v>#N/A</v>
+      </c>
+      <c r="S106" s="45" t="e">
+        <f t="shared" ref="S106" si="37">S104-S105</f>
+        <v>#N/A</v>
+      </c>
+      <c r="T106" s="45" t="e">
+        <f t="shared" ref="T106" si="38">T104-T105</f>
+        <v>#N/A</v>
+      </c>
+      <c r="U106" s="45" t="e">
+        <f t="shared" ref="U106" si="39">U104-U105</f>
+        <v>#N/A</v>
+      </c>
+      <c r="V106" s="45" t="e">
+        <f t="shared" ref="V106" si="40">V104-V105</f>
+        <v>#N/A</v>
+      </c>
+      <c r="W106" s="45" t="e">
+        <f t="shared" ref="W106" si="41">W104-W105</f>
+        <v>#N/A</v>
+      </c>
+      <c r="X106" s="45" t="e">
+        <f t="shared" ref="X106" si="42">X104-X105</f>
+        <v>#N/A</v>
+      </c>
+      <c r="Y106" s="45" t="e">
+        <f t="shared" ref="Y106" si="43">Y104-Y105</f>
+        <v>#N/A</v>
+      </c>
+      <c r="Z106" s="45" t="e">
+        <f t="shared" ref="Z106" si="44">Z104-Z105</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AA106" s="45" t="e">
+        <f t="shared" ref="AA106" si="45">AA104-AA105</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AB106" s="45" t="e">
+        <f t="shared" ref="AB106" si="46">AB104-AB105</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AC106" s="45" t="e">
+        <f t="shared" ref="AC106" si="47">AC104-AC105</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AD106" s="45" t="e">
+        <f t="shared" ref="AD106" si="48">AD104-AD105</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AE106" s="45" t="e">
+        <f t="shared" ref="AE106" si="49">AE104-AE105</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AF106" s="45" t="e">
+        <f t="shared" ref="AF106" si="50">AF104-AF105</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AG106" s="45" t="e">
+        <f t="shared" ref="AG106" si="51">AG104-AG105</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AH106" s="45" t="e">
+        <f t="shared" ref="AH106" si="52">AH104-AH105</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AI106" s="45" t="e">
+        <f t="shared" ref="AI106" si="53">AI104-AI105</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AJ106" s="45" t="e">
+        <f t="shared" ref="AJ106" si="54">AJ104-AJ105</f>
+        <v>#N/A</v>
+      </c>
+      <c r="AK106" s="45" t="e">
+        <f t="shared" ref="AK106" si="55">AK104-AK105</f>
+        <v>#N/A</v>
+      </c>
     </row>
     <row r="110" spans="6:37" ht="24">
       <c r="F110" s="54" t="s">
@@ -26723,8 +26883,8 @@
       <c r="G114" s="56">
         <v>1026</v>
       </c>
-      <c r="H114" s="57" t="e">
-        <v>#N/A</v>
+      <c r="H114" s="57">
+        <v>1033</v>
       </c>
       <c r="I114" s="57" t="e">
         <v>#N/A</v>
@@ -26821,8 +26981,8 @@
       <c r="G115" s="56">
         <v>1080</v>
       </c>
-      <c r="H115" s="57" t="e">
-        <v>#N/A</v>
+      <c r="H115" s="57">
+        <v>1058</v>
       </c>
       <c r="I115" s="57" t="e">
         <v>#N/A</v>
@@ -27799,127 +27959,127 @@
         <v>102</v>
       </c>
       <c r="G125" s="46">
-        <f t="shared" ref="G125:AK125" si="34">G59</f>
+        <f t="shared" ref="G125:AK125" si="56">G59</f>
         <v>656</v>
       </c>
       <c r="H125" s="47">
-        <f t="shared" si="34"/>
+        <f t="shared" si="56"/>
         <v>495</v>
       </c>
       <c r="I125" s="47">
-        <f t="shared" si="34"/>
+        <f t="shared" si="56"/>
         <v>338</v>
       </c>
       <c r="J125" s="47">
-        <f t="shared" si="34"/>
+        <f t="shared" si="56"/>
         <v>196</v>
       </c>
       <c r="K125" s="47">
-        <f t="shared" si="34"/>
+        <f t="shared" si="56"/>
         <v>141</v>
       </c>
       <c r="L125" s="47">
-        <f t="shared" si="34"/>
+        <f t="shared" si="56"/>
         <v>149</v>
       </c>
       <c r="M125" s="47">
-        <f t="shared" si="34"/>
+        <f t="shared" si="56"/>
         <v>107</v>
       </c>
       <c r="N125" s="47">
-        <f t="shared" si="34"/>
+        <f t="shared" si="56"/>
         <v>135</v>
       </c>
       <c r="O125" s="47">
-        <f t="shared" si="34"/>
+        <f t="shared" si="56"/>
         <v>163</v>
       </c>
       <c r="P125" s="47">
-        <f t="shared" si="34"/>
+        <f t="shared" si="56"/>
         <v>511</v>
       </c>
       <c r="Q125" s="47">
-        <f t="shared" si="34"/>
+        <f t="shared" si="56"/>
         <v>259</v>
       </c>
       <c r="R125" s="47">
-        <f t="shared" si="34"/>
+        <f t="shared" si="56"/>
         <v>307</v>
       </c>
       <c r="S125" s="47">
-        <f t="shared" si="34"/>
+        <f t="shared" si="56"/>
         <v>335</v>
       </c>
       <c r="T125" s="47">
-        <f t="shared" si="34"/>
+        <f t="shared" si="56"/>
         <v>383</v>
       </c>
       <c r="U125" s="47">
-        <f t="shared" si="34"/>
+        <f t="shared" si="56"/>
         <v>332</v>
       </c>
       <c r="V125" s="47">
-        <f t="shared" si="34"/>
+        <f t="shared" si="56"/>
         <v>291</v>
       </c>
       <c r="W125" s="47">
-        <f t="shared" si="34"/>
+        <f t="shared" si="56"/>
         <v>364</v>
       </c>
       <c r="X125" s="47">
-        <f t="shared" si="34"/>
+        <f t="shared" si="56"/>
         <v>327</v>
       </c>
       <c r="Y125" s="47">
-        <f t="shared" si="34"/>
+        <f t="shared" si="56"/>
         <v>310</v>
       </c>
       <c r="Z125" s="47">
-        <f t="shared" si="34"/>
+        <f t="shared" si="56"/>
         <v>2593</v>
       </c>
       <c r="AA125" s="47">
-        <f t="shared" si="34"/>
+        <f t="shared" si="56"/>
         <v>2429</v>
       </c>
       <c r="AB125" s="47">
-        <f t="shared" si="34"/>
+        <f t="shared" si="56"/>
         <v>2265</v>
       </c>
       <c r="AC125" s="47">
-        <f t="shared" si="34"/>
+        <f t="shared" si="56"/>
         <v>2081</v>
       </c>
       <c r="AD125" s="47">
-        <f t="shared" si="34"/>
+        <f t="shared" si="56"/>
         <v>1917</v>
       </c>
       <c r="AE125" s="47">
-        <f t="shared" si="34"/>
+        <f t="shared" si="56"/>
         <v>1753</v>
       </c>
       <c r="AF125" s="47">
-        <f t="shared" si="34"/>
+        <f t="shared" si="56"/>
         <v>1594</v>
       </c>
       <c r="AG125" s="47">
-        <f t="shared" si="34"/>
+        <f t="shared" si="56"/>
         <v>1435</v>
       </c>
       <c r="AH125" s="47">
-        <f t="shared" si="34"/>
+        <f t="shared" si="56"/>
         <v>1056</v>
       </c>
       <c r="AI125" s="47">
-        <f t="shared" si="34"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="AJ125" s="47">
-        <f t="shared" si="34"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="AK125" s="90">
-        <f t="shared" si="34"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
     </row>
@@ -27928,127 +28088,127 @@
         <v>103</v>
       </c>
       <c r="G126" s="45">
-        <f>G125-G121</f>
-        <v>-574</v>
-      </c>
-      <c r="H126" s="41" t="e">
-        <f t="shared" ref="H126:AK126" si="35">H125-H121</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I126" s="41" t="e">
-        <f t="shared" si="35"/>
-        <v>#N/A</v>
-      </c>
-      <c r="J126" s="41" t="e">
-        <f t="shared" si="35"/>
-        <v>#N/A</v>
-      </c>
-      <c r="K126" s="41" t="e">
-        <f t="shared" si="35"/>
-        <v>#N/A</v>
-      </c>
-      <c r="L126" s="41" t="e">
-        <f t="shared" si="35"/>
-        <v>#N/A</v>
-      </c>
-      <c r="M126" s="41" t="e">
-        <f t="shared" si="35"/>
-        <v>#N/A</v>
-      </c>
-      <c r="N126" s="41" t="e">
-        <f t="shared" si="35"/>
-        <v>#N/A</v>
-      </c>
-      <c r="O126" s="41" t="e">
-        <f t="shared" si="35"/>
-        <v>#N/A</v>
-      </c>
-      <c r="P126" s="41" t="e">
-        <f t="shared" si="35"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Q126" s="41" t="e">
-        <f t="shared" si="35"/>
-        <v>#N/A</v>
-      </c>
-      <c r="R126" s="41" t="e">
-        <f t="shared" si="35"/>
-        <v>#N/A</v>
-      </c>
-      <c r="S126" s="41" t="e">
-        <f t="shared" si="35"/>
-        <v>#N/A</v>
-      </c>
-      <c r="T126" s="41" t="e">
-        <f t="shared" si="35"/>
-        <v>#N/A</v>
-      </c>
-      <c r="U126" s="41" t="e">
-        <f t="shared" si="35"/>
-        <v>#N/A</v>
-      </c>
-      <c r="V126" s="41" t="e">
-        <f t="shared" si="35"/>
-        <v>#N/A</v>
-      </c>
-      <c r="W126" s="41" t="e">
-        <f t="shared" si="35"/>
-        <v>#N/A</v>
-      </c>
-      <c r="X126" s="41" t="e">
-        <f t="shared" si="35"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Y126" s="41" t="e">
-        <f t="shared" si="35"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Z126" s="41" t="e">
-        <f t="shared" si="35"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AA126" s="41" t="e">
-        <f t="shared" si="35"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AB126" s="41" t="e">
-        <f t="shared" si="35"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AC126" s="41" t="e">
-        <f t="shared" si="35"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AD126" s="41" t="e">
-        <f t="shared" si="35"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AE126" s="41" t="e">
-        <f t="shared" si="35"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AF126" s="41" t="e">
-        <f t="shared" si="35"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AG126" s="41" t="e">
-        <f t="shared" si="35"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AH126" s="41" t="e">
-        <f t="shared" si="35"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AI126" s="41" t="e">
-        <f t="shared" si="35"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AJ126" s="41" t="e">
-        <f t="shared" si="35"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AK126" s="42" t="e">
-        <f t="shared" si="35"/>
+        <f>G124-G125</f>
+        <v>608</v>
+      </c>
+      <c r="H126" s="45" t="e">
+        <f t="shared" ref="H126:AK126" si="57">H124-H125</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I126" s="45" t="e">
+        <f t="shared" si="57"/>
+        <v>#N/A</v>
+      </c>
+      <c r="J126" s="45" t="e">
+        <f t="shared" si="57"/>
+        <v>#N/A</v>
+      </c>
+      <c r="K126" s="45" t="e">
+        <f t="shared" si="57"/>
+        <v>#N/A</v>
+      </c>
+      <c r="L126" s="45" t="e">
+        <f t="shared" si="57"/>
+        <v>#N/A</v>
+      </c>
+      <c r="M126" s="45" t="e">
+        <f t="shared" si="57"/>
+        <v>#N/A</v>
+      </c>
+      <c r="N126" s="45" t="e">
+        <f t="shared" si="57"/>
+        <v>#N/A</v>
+      </c>
+      <c r="O126" s="45" t="e">
+        <f t="shared" si="57"/>
+        <v>#N/A</v>
+      </c>
+      <c r="P126" s="45" t="e">
+        <f t="shared" si="57"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q126" s="45" t="e">
+        <f t="shared" si="57"/>
+        <v>#N/A</v>
+      </c>
+      <c r="R126" s="45" t="e">
+        <f t="shared" si="57"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S126" s="45" t="e">
+        <f t="shared" si="57"/>
+        <v>#N/A</v>
+      </c>
+      <c r="T126" s="45" t="e">
+        <f t="shared" si="57"/>
+        <v>#N/A</v>
+      </c>
+      <c r="U126" s="45" t="e">
+        <f t="shared" si="57"/>
+        <v>#N/A</v>
+      </c>
+      <c r="V126" s="45" t="e">
+        <f t="shared" si="57"/>
+        <v>#N/A</v>
+      </c>
+      <c r="W126" s="45" t="e">
+        <f t="shared" si="57"/>
+        <v>#N/A</v>
+      </c>
+      <c r="X126" s="45" t="e">
+        <f t="shared" si="57"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y126" s="45" t="e">
+        <f t="shared" si="57"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Z126" s="45" t="e">
+        <f t="shared" si="57"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AA126" s="45" t="e">
+        <f t="shared" si="57"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AB126" s="45" t="e">
+        <f t="shared" si="57"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AC126" s="45" t="e">
+        <f t="shared" si="57"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AD126" s="45" t="e">
+        <f t="shared" si="57"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AE126" s="45" t="e">
+        <f t="shared" si="57"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AF126" s="45" t="e">
+        <f t="shared" si="57"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG126" s="45" t="e">
+        <f t="shared" si="57"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AH126" s="45" t="e">
+        <f t="shared" si="57"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AI126" s="45" t="e">
+        <f t="shared" si="57"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AJ126" s="45" t="e">
+        <f t="shared" si="57"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AK126" s="45" t="e">
+        <f t="shared" si="57"/>
         <v>#N/A</v>
       </c>
     </row>
@@ -28262,8 +28422,8 @@
       <c r="G134" s="56">
         <v>763</v>
       </c>
-      <c r="H134" s="57" t="e">
-        <v>#N/A</v>
+      <c r="H134" s="57">
+        <v>368</v>
       </c>
       <c r="I134" s="57" t="e">
         <v>#N/A</v>
@@ -28360,8 +28520,8 @@
       <c r="G135" s="56">
         <v>733</v>
       </c>
-      <c r="H135" s="57" t="e">
-        <v>#N/A</v>
+      <c r="H135" s="57">
+        <v>345</v>
       </c>
       <c r="I135" s="57" t="e">
         <v>#N/A</v>
@@ -29340,7 +29500,7 @@
         <v>102</v>
       </c>
       <c r="G145" s="46">
-        <f t="shared" ref="G145:AK145" si="36">G81</f>
+        <f t="shared" ref="G145:AK145" si="58">G81</f>
         <v>-13</v>
       </c>
       <c r="H145" s="47">
@@ -29348,119 +29508,119 @@
         <v>-6</v>
       </c>
       <c r="I145" s="47">
-        <f t="shared" si="36"/>
+        <f t="shared" si="58"/>
         <v>1</v>
       </c>
       <c r="J145" s="47">
-        <f t="shared" si="36"/>
+        <f t="shared" si="58"/>
         <v>8</v>
       </c>
       <c r="K145" s="47">
-        <f t="shared" si="36"/>
+        <f t="shared" si="58"/>
         <v>15</v>
       </c>
       <c r="L145" s="47">
-        <f t="shared" si="36"/>
+        <f t="shared" si="58"/>
         <v>22</v>
       </c>
       <c r="M145" s="47">
-        <f t="shared" si="36"/>
+        <f t="shared" si="58"/>
         <v>29</v>
       </c>
       <c r="N145" s="47">
-        <f t="shared" si="36"/>
+        <f t="shared" si="58"/>
         <v>36</v>
       </c>
       <c r="O145" s="47">
-        <f t="shared" si="36"/>
+        <f t="shared" si="58"/>
         <v>43</v>
       </c>
       <c r="P145" s="47">
-        <f t="shared" si="36"/>
+        <f t="shared" si="58"/>
         <v>50</v>
       </c>
       <c r="Q145" s="47">
-        <f t="shared" si="36"/>
+        <f t="shared" si="58"/>
         <v>57</v>
       </c>
       <c r="R145" s="47">
-        <f t="shared" si="36"/>
+        <f t="shared" si="58"/>
         <v>64</v>
       </c>
       <c r="S145" s="47">
-        <f t="shared" si="36"/>
+        <f t="shared" si="58"/>
         <v>71</v>
       </c>
       <c r="T145" s="47">
-        <f t="shared" si="36"/>
+        <f t="shared" si="58"/>
         <v>78</v>
       </c>
       <c r="U145" s="47">
-        <f t="shared" si="36"/>
+        <f t="shared" si="58"/>
         <v>85</v>
       </c>
       <c r="V145" s="47">
-        <f t="shared" si="36"/>
+        <f t="shared" si="58"/>
         <v>92</v>
       </c>
       <c r="W145" s="47">
-        <f t="shared" si="36"/>
+        <f t="shared" si="58"/>
         <v>99</v>
       </c>
       <c r="X145" s="47">
-        <f t="shared" si="36"/>
+        <f t="shared" si="58"/>
         <v>106</v>
       </c>
       <c r="Y145" s="47">
-        <f t="shared" si="36"/>
+        <f t="shared" si="58"/>
         <v>113</v>
       </c>
       <c r="Z145" s="47">
-        <f t="shared" si="36"/>
+        <f t="shared" si="58"/>
         <v>120</v>
       </c>
       <c r="AA145" s="47">
-        <f t="shared" si="36"/>
+        <f t="shared" si="58"/>
         <v>127</v>
       </c>
       <c r="AB145" s="47">
-        <f t="shared" si="36"/>
+        <f t="shared" si="58"/>
         <v>134</v>
       </c>
       <c r="AC145" s="47">
-        <f t="shared" si="36"/>
+        <f t="shared" si="58"/>
         <v>141</v>
       </c>
       <c r="AD145" s="47">
-        <f t="shared" si="36"/>
+        <f t="shared" si="58"/>
         <v>148</v>
       </c>
       <c r="AE145" s="47">
-        <f t="shared" si="36"/>
+        <f t="shared" si="58"/>
         <v>155</v>
       </c>
       <c r="AF145" s="47">
-        <f t="shared" si="36"/>
+        <f t="shared" si="58"/>
         <v>168</v>
       </c>
       <c r="AG145" s="47">
-        <f t="shared" si="36"/>
+        <f t="shared" si="58"/>
         <v>181</v>
       </c>
       <c r="AH145" s="47">
-        <f t="shared" si="36"/>
+        <f t="shared" si="58"/>
         <v>194</v>
       </c>
       <c r="AI145" s="47">
-        <f t="shared" si="36"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="AJ145" s="47">
-        <f t="shared" si="36"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="AK145" s="90">
-        <f t="shared" si="36"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
     </row>
@@ -29469,142 +29629,148 @@
         <v>103</v>
       </c>
       <c r="G146" s="45">
-        <f>G145-G141</f>
-        <v>-549</v>
-      </c>
-      <c r="H146" s="41" t="e">
-        <f>H145-H141</f>
-        <v>#N/A</v>
-      </c>
-      <c r="I146" s="41" t="e">
-        <f t="shared" ref="I146:AK146" si="37">I145-I141</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J146" s="41" t="e">
-        <f t="shared" si="37"/>
-        <v>#N/A</v>
-      </c>
-      <c r="K146" s="41" t="e">
-        <f t="shared" si="37"/>
-        <v>#N/A</v>
-      </c>
-      <c r="L146" s="41" t="e">
-        <f t="shared" si="37"/>
-        <v>#N/A</v>
-      </c>
-      <c r="M146" s="41" t="e">
-        <f t="shared" si="37"/>
-        <v>#N/A</v>
-      </c>
-      <c r="N146" s="41" t="e">
-        <f t="shared" si="37"/>
-        <v>#N/A</v>
-      </c>
-      <c r="O146" s="41" t="e">
-        <f t="shared" si="37"/>
-        <v>#N/A</v>
-      </c>
-      <c r="P146" s="41" t="e">
-        <f t="shared" si="37"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Q146" s="41" t="e">
-        <f t="shared" si="37"/>
-        <v>#N/A</v>
-      </c>
-      <c r="R146" s="41" t="e">
-        <f t="shared" si="37"/>
-        <v>#N/A</v>
-      </c>
-      <c r="S146" s="41" t="e">
-        <f t="shared" si="37"/>
-        <v>#N/A</v>
-      </c>
-      <c r="T146" s="41" t="e">
-        <f t="shared" si="37"/>
-        <v>#N/A</v>
-      </c>
-      <c r="U146" s="41" t="e">
-        <f t="shared" si="37"/>
-        <v>#N/A</v>
-      </c>
-      <c r="V146" s="41" t="e">
-        <f t="shared" si="37"/>
-        <v>#N/A</v>
-      </c>
-      <c r="W146" s="41" t="e">
-        <f t="shared" si="37"/>
-        <v>#N/A</v>
-      </c>
-      <c r="X146" s="41" t="e">
-        <f t="shared" si="37"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Y146" s="41" t="e">
-        <f t="shared" si="37"/>
-        <v>#N/A</v>
-      </c>
-      <c r="Z146" s="41" t="e">
-        <f t="shared" si="37"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AA146" s="41" t="e">
-        <f t="shared" si="37"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AB146" s="41" t="e">
-        <f t="shared" si="37"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AC146" s="41" t="e">
-        <f t="shared" si="37"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AD146" s="41" t="e">
-        <f t="shared" si="37"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AE146" s="41" t="e">
-        <f t="shared" si="37"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AF146" s="41" t="e">
-        <f t="shared" si="37"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AG146" s="41" t="e">
-        <f t="shared" si="37"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AH146" s="41" t="e">
-        <f t="shared" si="37"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AI146" s="41" t="e">
-        <f t="shared" si="37"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AJ146" s="41" t="e">
-        <f t="shared" si="37"/>
-        <v>#N/A</v>
-      </c>
-      <c r="AK146" s="42" t="e">
-        <f t="shared" si="37"/>
+        <f>G144-G145</f>
+        <v>451</v>
+      </c>
+      <c r="H146" s="45" t="e">
+        <f t="shared" ref="H146:AK146" si="59">H144-H145</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I146" s="45" t="e">
+        <f t="shared" si="59"/>
+        <v>#N/A</v>
+      </c>
+      <c r="J146" s="45" t="e">
+        <f t="shared" si="59"/>
+        <v>#N/A</v>
+      </c>
+      <c r="K146" s="45" t="e">
+        <f t="shared" si="59"/>
+        <v>#N/A</v>
+      </c>
+      <c r="L146" s="45" t="e">
+        <f t="shared" si="59"/>
+        <v>#N/A</v>
+      </c>
+      <c r="M146" s="45" t="e">
+        <f t="shared" si="59"/>
+        <v>#N/A</v>
+      </c>
+      <c r="N146" s="45" t="e">
+        <f t="shared" si="59"/>
+        <v>#N/A</v>
+      </c>
+      <c r="O146" s="45" t="e">
+        <f t="shared" si="59"/>
+        <v>#N/A</v>
+      </c>
+      <c r="P146" s="45" t="e">
+        <f t="shared" si="59"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Q146" s="45" t="e">
+        <f t="shared" si="59"/>
+        <v>#N/A</v>
+      </c>
+      <c r="R146" s="45" t="e">
+        <f t="shared" si="59"/>
+        <v>#N/A</v>
+      </c>
+      <c r="S146" s="45" t="e">
+        <f t="shared" si="59"/>
+        <v>#N/A</v>
+      </c>
+      <c r="T146" s="45" t="e">
+        <f t="shared" si="59"/>
+        <v>#N/A</v>
+      </c>
+      <c r="U146" s="45" t="e">
+        <f t="shared" si="59"/>
+        <v>#N/A</v>
+      </c>
+      <c r="V146" s="45" t="e">
+        <f t="shared" si="59"/>
+        <v>#N/A</v>
+      </c>
+      <c r="W146" s="45" t="e">
+        <f t="shared" si="59"/>
+        <v>#N/A</v>
+      </c>
+      <c r="X146" s="45" t="e">
+        <f t="shared" si="59"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Y146" s="45" t="e">
+        <f t="shared" si="59"/>
+        <v>#N/A</v>
+      </c>
+      <c r="Z146" s="45" t="e">
+        <f t="shared" si="59"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AA146" s="45" t="e">
+        <f t="shared" si="59"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AB146" s="45" t="e">
+        <f t="shared" si="59"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AC146" s="45" t="e">
+        <f t="shared" si="59"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AD146" s="45" t="e">
+        <f t="shared" si="59"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AE146" s="45" t="e">
+        <f t="shared" si="59"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AF146" s="45" t="e">
+        <f t="shared" si="59"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AG146" s="45" t="e">
+        <f t="shared" si="59"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AH146" s="45" t="e">
+        <f t="shared" si="59"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AI146" s="45" t="e">
+        <f t="shared" si="59"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AJ146" s="45" t="e">
+        <f t="shared" si="59"/>
+        <v>#N/A</v>
+      </c>
+      <c r="AK146" s="45" t="e">
+        <f t="shared" si="59"/>
         <v>#N/A</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="42">
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="A2:A15"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="B4:B8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B10:B14"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="C4:C8"/>
-    <mergeCell ref="C10:C14"/>
+    <mergeCell ref="A16:A59"/>
+    <mergeCell ref="B34:B36"/>
+    <mergeCell ref="C34:C36"/>
+    <mergeCell ref="D34:D36"/>
+    <mergeCell ref="C64:C74"/>
+    <mergeCell ref="D73:D74"/>
+    <mergeCell ref="D24:D29"/>
+    <mergeCell ref="D43:D46"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="C43:C48"/>
+    <mergeCell ref="B62:B63"/>
+    <mergeCell ref="C62:C63"/>
+    <mergeCell ref="D62:D63"/>
     <mergeCell ref="A82:A83"/>
     <mergeCell ref="C16:C17"/>
     <mergeCell ref="D16:D17"/>
@@ -29621,22 +29787,16 @@
     <mergeCell ref="B38:B48"/>
     <mergeCell ref="B16:B31"/>
     <mergeCell ref="A60:A81"/>
-    <mergeCell ref="A16:A59"/>
-    <mergeCell ref="B34:B36"/>
-    <mergeCell ref="C34:C36"/>
-    <mergeCell ref="D34:D36"/>
-    <mergeCell ref="C64:C74"/>
-    <mergeCell ref="D73:D74"/>
-    <mergeCell ref="D24:D29"/>
-    <mergeCell ref="D43:D46"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="C43:C48"/>
-    <mergeCell ref="B62:B63"/>
-    <mergeCell ref="C62:C63"/>
-    <mergeCell ref="D62:D63"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="A2:A15"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="B4:B8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B10:B14"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="C4:C8"/>
+    <mergeCell ref="C10:C14"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ライフプラン_猪飼.xlsx
+++ b/ライフプラン_猪飼.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC_USER\Documents\LocalLifeplanRepo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{783CA1FD-CB8E-4283-A107-621649B536BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE379F5E-949F-4EB9-8F46-DDAF21B132AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{934FA03D-99BD-49E0-BFEC-291BD79F4879}"/>
   </bookViews>
@@ -59,6 +59,32 @@
         </r>
       </text>
     </comment>
+    <comment ref="J6" authorId="0" shapeId="0" xr:uid="{E69F89B2-0434-41FB-A33B-3D28CD80AB17}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="MS P ゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>PC_USER:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="MS P ゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="H10" authorId="0" shapeId="0" xr:uid="{004E8166-C187-48BE-ACF1-58DC27A96611}">
       <text>
         <r>
@@ -70,7 +96,8 @@
             <family val="3"/>
             <charset val="128"/>
           </rPr>
-          <t>日本一周クルーズ</t>
+          <t>202606：奈良　8　
+日本一周クルーズ</t>
         </r>
       </text>
     </comment>
@@ -884,32 +911,6 @@
         </r>
       </text>
     </comment>
-    <comment ref="M110" authorId="0" shapeId="0" xr:uid="{810AE1A6-2695-4C15-9097-542FE06A2684}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="MS P ゴシック"/>
-            <family val="3"/>
-            <charset val="128"/>
-          </rPr>
-          <t>PC_USER:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="MS P ゴシック"/>
-            <family val="3"/>
-            <charset val="128"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-      </text>
-    </comment>
     <comment ref="G113" authorId="0" shapeId="0" xr:uid="{23DA8E04-2475-49BD-AD45-69212BFA74D0}">
       <text>
         <r>
@@ -1011,12 +1012,11 @@
             <family val="3"/>
             <charset val="128"/>
           </rPr>
-          <t xml:space="preserve">kaz
+          <t>kaz
  国民厚生年金　　　　+45
  パナ年金　　　  　　+12
  ﾌﾟﾙﾃﾞﾝｼｬﾙ保険金 　 + 9
- 明治安田生命　 　　 + 2
- </t>
+ 明治安田生命　 　　 + 2</t>
         </r>
       </text>
     </comment>
@@ -1036,6 +1036,26 @@
  全労済東１      + 4
  ﾌﾟﾙﾃﾞﾝｼｬﾙ保険金 + 9
 nao</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H116" authorId="0" shapeId="0" xr:uid="{178F64E5-DC06-436B-8FD7-0383E78406F2}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="MS P ゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t xml:space="preserve">kaz
+ パナ年金　　　  　　+ 6
+ ﾌﾟﾙﾃﾞﾝｼｬﾙ保険金 　 + 9
+ 全労済　　　　 　　 + 5
+ 株配当（東北電力）　+ 1
+</t>
         </r>
       </text>
     </comment>
@@ -1361,6 +1381,22 @@
           </rPr>
           <t>kazへ返済 -4 (新潟_網戸&amp;小嶋屋：1.1、医療費：1.4、ﾋﾞｭｰ：1。他)
 naoへ返済 -2.5（出雲；3，森永：0.3， 交通費返却：-0.7）</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H136" authorId="0" shapeId="0" xr:uid="{46C8C73A-BE64-4065-83AA-C5C36B0A63D0}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="MS P ゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>kazへ返済 -2.8 (医療費：1.2、ビューカード：0.3，瀬戸神社：0.2 外食：0.2，他：0.9)
+naoへ返済 2.3（森永：0.4，カイロ：0.7，医療費：0.3，ダンス：0.0，全神社：2.9，nao返却：6.6，他：0.2）</t>
         </r>
       </text>
     </comment>
@@ -6525,7 +6561,7 @@
                   <c:v>1076</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>#N/A</c:v>
+                  <c:v>1064</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>#N/A</c:v>
@@ -9942,7 +9978,7 @@
                   <c:v>691</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>#N/A</c:v>
+                  <c:v>322</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>#N/A</c:v>
@@ -13362,7 +13398,7 @@
                   <c:v>1767</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>#N/A</c:v>
+                  <c:v>1386</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>#N/A</c:v>
@@ -25262,9 +25298,9 @@
         <f t="shared" ref="G96:AK96" si="23">G116+G136</f>
         <v>1767</v>
       </c>
-      <c r="H96" s="57" t="e">
+      <c r="H96" s="57">
         <f t="shared" si="23"/>
-        <v>#N/A</v>
+        <v>1386</v>
       </c>
       <c r="I96" s="57" t="e">
         <f t="shared" si="23"/>
@@ -27079,8 +27115,8 @@
       <c r="G116" s="56">
         <v>1076</v>
       </c>
-      <c r="H116" s="57" t="e">
-        <v>#N/A</v>
+      <c r="H116" s="57">
+        <v>1064</v>
       </c>
       <c r="I116" s="57" t="e">
         <v>#N/A</v>
@@ -28619,8 +28655,8 @@
         <f>691</f>
         <v>691</v>
       </c>
-      <c r="H136" s="57" t="e">
-        <v>#N/A</v>
+      <c r="H136" s="57">
+        <v>322</v>
       </c>
       <c r="I136" s="57" t="e">
         <v>#N/A</v>

--- a/ライフプラン_猪飼.xlsx
+++ b/ライフプラン_猪飼.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC_USER\Documents\LocalLifeplanRepo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE379F5E-949F-4EB9-8F46-DDAF21B132AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABAA6CD7-45DC-448E-866B-C6CFA5CBDA06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{934FA03D-99BD-49E0-BFEC-291BD79F4879}"/>
   </bookViews>
@@ -911,6 +911,32 @@
         </r>
       </text>
     </comment>
+    <comment ref="N110" authorId="0" shapeId="0" xr:uid="{D651B64B-A804-4E0F-B522-BFD2BF745BFD}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="MS P ゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>PC_USER:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="MS P ゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="G113" authorId="0" shapeId="0" xr:uid="{23DA8E04-2475-49BD-AD45-69212BFA74D0}">
       <text>
         <r>
@@ -1075,6 +1101,35 @@
  パナ年金　　　  +12　
  ﾌﾟﾙﾃﾞﾝｼｬﾙ保険金 + 9
 nao</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H117" authorId="0" shapeId="0" xr:uid="{602A088E-FE0F-4413-ADF6-80CCD6C93EC9}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="MS P ゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>kaz
+ 国民厚生年金　　　　+46
+ パナ年金　　　  　　+12
+ ﾌﾟﾙﾃﾞﾝｼｬﾙ保険金 　 + 9</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="MS P ゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
         </r>
       </text>
     </comment>
@@ -1413,6 +1468,23 @@
           </rPr>
           <t>kazへ返済 -7 (墓参：1、飯山出雲&amp;鮎：1.2、実家修理：1.6，ﾋﾞｭｰ：1。衣笠浜寿司：1.2、他：1)
 naoへ返済 -2.5（飯山出雲；2，森永：0.2， 町内祭:0.3）</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H137" authorId="0" shapeId="0" xr:uid="{7537FAF8-1843-41AD-9AF8-31F355B90CBC}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="MS P ゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>kazへ返済 85396 -8.5 (医療費：1.0、ビューカード：0.3，ｺｰﾄﾞﾚｽｸﾘｰﾅｰ:5.0、タクシー：0.1、映画：0.1、外食：0.2，他：1.8)
+naoへ返済 34867 -3.5（森永：0.3，カイロ：0.7，医療費：0.0，ダンス：0.0，出雲大社：1.2，nao返却：-0.3，分踊り飯：0.6，他：1.0)
+ ＊ nao大腸検査 2.2，先月の奈良宿泊費の引落 2.1</t>
         </r>
       </text>
     </comment>
@@ -6804,7 +6876,7 @@
                   <c:v>1124</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>#N/A</c:v>
+                  <c:v>1120</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>#N/A</c:v>
@@ -10221,7 +10293,7 @@
                   <c:v>669</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>#N/A</c:v>
+                  <c:v>288</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>#N/A</c:v>
@@ -13641,7 +13713,7 @@
                   <c:v>1793</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>#N/A</c:v>
+                  <c:v>1408</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>#N/A</c:v>
@@ -25427,9 +25499,9 @@
         <f t="shared" ref="G97:AK97" si="24">G117+G137</f>
         <v>1793</v>
       </c>
-      <c r="H97" s="57" t="e">
+      <c r="H97" s="57">
         <f t="shared" si="24"/>
-        <v>#N/A</v>
+        <v>1408</v>
       </c>
       <c r="I97" s="57" t="e">
         <f t="shared" si="24"/>
@@ -27213,8 +27285,8 @@
       <c r="G117" s="56">
         <v>1124</v>
       </c>
-      <c r="H117" s="57" t="e">
-        <v>#N/A</v>
+      <c r="H117" s="57">
+        <v>1120</v>
       </c>
       <c r="I117" s="57" t="e">
         <v>#N/A</v>
@@ -28753,8 +28825,8 @@
       <c r="G137" s="56">
         <v>669</v>
       </c>
-      <c r="H137" s="57" t="e">
-        <v>#N/A</v>
+      <c r="H137" s="57">
+        <v>288</v>
       </c>
       <c r="I137" s="57" t="e">
         <v>#N/A</v>
